--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01187956-5FA0-43A1-951A-50CC400DDC9E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="984">
   <si>
     <t>NOM MATERIAU PARENTAL</t>
   </si>
@@ -3583,6 +3583,48 @@
   <si>
     <t>R44_Als_1121</t>
   </si>
+  <si>
+    <t>couleur</t>
+  </si>
+  <si>
+    <t>#CCFFFF</t>
+  </si>
+  <si>
+    <t>#99CCFF</t>
+  </si>
+  <si>
+    <t>#00CCFF</t>
+  </si>
+  <si>
+    <t>#FFCC99</t>
+  </si>
+  <si>
+    <t>#FF8080</t>
+  </si>
+  <si>
+    <t>#366092</t>
+  </si>
+  <si>
+    <t>#FFFF00</t>
+  </si>
+  <si>
+    <t>#FFCC00</t>
+  </si>
+  <si>
+    <t>#FF99CC</t>
+  </si>
+  <si>
+    <t>#993300</t>
+  </si>
+  <si>
+    <t>#663300</t>
+  </si>
+  <si>
+    <t>#808000</t>
+  </si>
+  <si>
+    <t>#339966</t>
+  </si>
 </sst>
 </file>
 
@@ -3591,7 +3633,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3865,8 +3907,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="46">
+  <fills count="56">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4137,6 +4185,66 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99CCFF"/>
+        <bgColor indexed="46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00CCFF"/>
+        <bgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8080"/>
+        <bgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC00"/>
+        <bgColor indexed="13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF993300"/>
+        <bgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808000"/>
+        <bgColor indexed="25"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF339966"/>
+        <bgColor indexed="38"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="21">
     <border>
@@ -4367,7 +4475,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="502">
+  <cellXfs count="530">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5533,6 +5641,96 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5563,103 +5761,97 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5671,14 +5863,15 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF009999"/>
-      <color rgb="FF006666"/>
+      <color rgb="FF339966"/>
+      <color rgb="FF663300"/>
       <color rgb="FF808000"/>
-      <color rgb="FFCCCC00"/>
+      <color rgb="FF993300"/>
       <color rgb="FFFF99CC"/>
-      <color rgb="FFFF66FF"/>
-      <color rgb="FFFF99FF"/>
-      <color rgb="FF66FFFF"/>
+      <color rgb="FFFFCC00"/>
+      <color rgb="FFFFFF00"/>
+      <color rgb="FFFF8080"/>
+      <color rgb="FFFFCC99"/>
       <color rgb="FF00CCFF"/>
     </mruColors>
   </colors>
@@ -5980,7 +6173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ281"/>
+  <dimension ref="A1:AR281"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.109375" customWidth="1"/>
@@ -6830,7 +7023,7 @@
     <col min="16159" max="16159" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="16" customFormat="1" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" s="16" customFormat="1" ht="67.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="456" t="s">
         <v>859</v>
       </c>
@@ -6960,15 +7153,18 @@
       <c r="AQ1" s="15" t="s">
         <v>29</v>
       </c>
+      <c r="AR1" s="16" t="s">
+        <v>970</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="457" t="s">
         <v>861</v>
       </c>
       <c r="B2" s="454" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="499">
+      <c r="C2" s="462">
         <v>11</v>
       </c>
       <c r="D2" s="296" t="s">
@@ -7089,11 +7285,14 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
+      <c r="AR2" s="499" t="s">
+        <v>971</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="457"/>
       <c r="B3" s="454"/>
-      <c r="C3" s="500"/>
+      <c r="C3" s="463"/>
       <c r="D3" s="296"/>
       <c r="E3" s="17"/>
       <c r="F3" s="224"/>
@@ -7178,11 +7377,12 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
+      <c r="AR3" s="499"/>
     </row>
-    <row r="4" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
       <c r="B4" s="454"/>
-      <c r="C4" s="501"/>
+      <c r="C4" s="464"/>
       <c r="D4" s="297"/>
       <c r="E4" s="209"/>
       <c r="F4" s="225"/>
@@ -7267,15 +7467,16 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
+      <c r="AR4" s="499"/>
     </row>
-    <row r="5" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="457" t="s">
         <v>863</v>
       </c>
       <c r="B5" s="454" t="s">
         <v>902</v>
       </c>
-      <c r="C5" s="499">
+      <c r="C5" s="462">
         <v>12</v>
       </c>
       <c r="D5" s="296" t="s">
@@ -7394,11 +7595,14 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
+      <c r="AR5" s="499" t="s">
+        <v>971</v>
+      </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="457"/>
       <c r="B6" s="454"/>
-      <c r="C6" s="500"/>
+      <c r="C6" s="463"/>
       <c r="D6" s="296"/>
       <c r="E6" s="34"/>
       <c r="F6" s="226"/>
@@ -7481,11 +7685,12 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
+      <c r="AR6" s="499"/>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
       <c r="B7" s="454"/>
-      <c r="C7" s="500"/>
+      <c r="C7" s="463"/>
       <c r="D7" s="296"/>
       <c r="E7" s="34"/>
       <c r="F7" s="226"/>
@@ -7568,11 +7773,12 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
+      <c r="AR7" s="499"/>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
       <c r="B8" s="454"/>
-      <c r="C8" s="500"/>
+      <c r="C8" s="463"/>
       <c r="D8" s="296"/>
       <c r="E8" s="53"/>
       <c r="F8" s="227"/>
@@ -7653,15 +7859,16 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
+      <c r="AR8" s="499"/>
     </row>
-    <row r="9" spans="1:43" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="457" t="s">
         <v>863</v>
       </c>
       <c r="B9" s="454" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="500"/>
+      <c r="C9" s="463"/>
       <c r="D9" s="296" t="s">
         <v>736</v>
       </c>
@@ -7776,11 +7983,14 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
+      <c r="AR9" s="499" t="s">
+        <v>971</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="457"/>
       <c r="B10" s="454"/>
-      <c r="C10" s="500"/>
+      <c r="C10" s="463"/>
       <c r="D10" s="296"/>
       <c r="E10" s="34"/>
       <c r="F10" s="226"/>
@@ -7861,11 +8071,12 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
+      <c r="AR10" s="499"/>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
       <c r="B11" s="454"/>
-      <c r="C11" s="500"/>
+      <c r="C11" s="463"/>
       <c r="D11" s="296"/>
       <c r="E11" s="34"/>
       <c r="F11" s="226"/>
@@ -7946,11 +8157,12 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
+      <c r="AR11" s="499"/>
     </row>
-    <row r="12" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
       <c r="B12" s="454"/>
-      <c r="C12" s="501"/>
+      <c r="C12" s="464"/>
       <c r="D12" s="297"/>
       <c r="E12" s="38"/>
       <c r="F12" s="228"/>
@@ -8029,15 +8241,16 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
+      <c r="AR12" s="499"/>
     </row>
-    <row r="13" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="457" t="s">
         <v>864</v>
       </c>
       <c r="B13" s="454" t="s">
         <v>904</v>
       </c>
-      <c r="C13" s="499">
+      <c r="C13" s="462">
         <v>13</v>
       </c>
       <c r="D13" s="296" t="s">
@@ -8154,11 +8367,14 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
+      <c r="AR13" s="499" t="s">
+        <v>971</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="457"/>
       <c r="B14" s="454"/>
-      <c r="C14" s="500"/>
+      <c r="C14" s="463"/>
       <c r="D14" s="296"/>
       <c r="E14" s="34"/>
       <c r="F14" s="226"/>
@@ -8239,11 +8455,12 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
+      <c r="AR14" s="499"/>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
       <c r="B15" s="454"/>
-      <c r="C15" s="500"/>
+      <c r="C15" s="463"/>
       <c r="D15" s="296"/>
       <c r="E15" s="34"/>
       <c r="F15" s="226"/>
@@ -8324,11 +8541,12 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
+      <c r="AR15" s="499"/>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
       <c r="B16" s="454"/>
-      <c r="C16" s="500"/>
+      <c r="C16" s="463"/>
       <c r="D16" s="296"/>
       <c r="E16" s="34"/>
       <c r="F16" s="226"/>
@@ -8409,11 +8627,12 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
+      <c r="AR16" s="499"/>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
       <c r="B17" s="454"/>
-      <c r="C17" s="500"/>
+      <c r="C17" s="463"/>
       <c r="D17" s="296"/>
       <c r="E17" s="53"/>
       <c r="F17" s="227"/>
@@ -8492,15 +8711,16 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
+      <c r="AR17" s="499"/>
     </row>
-    <row r="18" spans="1:43" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="457" t="s">
         <v>864</v>
       </c>
       <c r="B18" s="454" t="s">
         <v>905</v>
       </c>
-      <c r="C18" s="500"/>
+      <c r="C18" s="463"/>
       <c r="D18" s="296" t="s">
         <v>736</v>
       </c>
@@ -8613,11 +8833,14 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
+      <c r="AR18" s="499" t="s">
+        <v>971</v>
+      </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="457"/>
       <c r="B19" s="454"/>
-      <c r="C19" s="500"/>
+      <c r="C19" s="463"/>
       <c r="D19" s="296"/>
       <c r="E19" s="34"/>
       <c r="F19" s="226"/>
@@ -8698,11 +8921,12 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
+      <c r="AR19" s="499"/>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
       <c r="B20" s="454"/>
-      <c r="C20" s="500"/>
+      <c r="C20" s="463"/>
       <c r="D20" s="296"/>
       <c r="E20" s="34"/>
       <c r="F20" s="226"/>
@@ -8783,11 +9007,12 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
+      <c r="AR20" s="499"/>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
       <c r="B21" s="454"/>
-      <c r="C21" s="500"/>
+      <c r="C21" s="463"/>
       <c r="D21" s="296"/>
       <c r="E21" s="34"/>
       <c r="F21" s="226"/>
@@ -8868,11 +9093,12 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
+      <c r="AR21" s="499"/>
     </row>
-    <row r="22" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
       <c r="B22" s="454"/>
-      <c r="C22" s="501"/>
+      <c r="C22" s="464"/>
       <c r="D22" s="297"/>
       <c r="E22" s="38"/>
       <c r="F22" s="228"/>
@@ -8953,15 +9179,16 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
+      <c r="AR22" s="499"/>
     </row>
-    <row r="23" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="457" t="s">
         <v>865</v>
       </c>
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="487">
+      <c r="C23" s="500">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9082,11 +9309,14 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
+      <c r="AR23" s="499" t="s">
+        <v>972</v>
+      </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="488"/>
+      <c r="C24" s="501"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9171,11 +9401,12 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
+      <c r="AR24" s="499"/>
     </row>
-    <row r="25" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="489"/>
+      <c r="C25" s="502"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9260,15 +9491,16 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
+      <c r="AR25" s="499"/>
     </row>
-    <row r="26" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="457" t="s">
         <v>866</v>
       </c>
       <c r="B26" s="454" t="s">
         <v>907</v>
       </c>
-      <c r="C26" s="487">
+      <c r="C26" s="459">
         <v>22</v>
       </c>
       <c r="D26" s="298" t="s">
@@ -9385,11 +9617,14 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
+      <c r="AR26" s="499" t="s">
+        <v>972</v>
+      </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="457"/>
       <c r="B27" s="454"/>
-      <c r="C27" s="488"/>
+      <c r="C27" s="460"/>
       <c r="D27" s="298"/>
       <c r="E27" s="73"/>
       <c r="F27" s="230"/>
@@ -9470,11 +9705,12 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
+      <c r="AR27" s="499"/>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
       <c r="B28" s="454"/>
-      <c r="C28" s="488"/>
+      <c r="C28" s="460"/>
       <c r="D28" s="298"/>
       <c r="E28" s="73"/>
       <c r="F28" s="230"/>
@@ -9555,11 +9791,12 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
+      <c r="AR28" s="499"/>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
       <c r="B29" s="454"/>
-      <c r="C29" s="488"/>
+      <c r="C29" s="460"/>
       <c r="D29" s="298"/>
       <c r="E29" s="73"/>
       <c r="F29" s="230"/>
@@ -9642,11 +9879,12 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
+      <c r="AR29" s="499"/>
     </row>
-    <row r="30" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
       <c r="B30" s="454"/>
-      <c r="C30" s="489"/>
+      <c r="C30" s="461"/>
       <c r="D30" s="311"/>
       <c r="E30" s="74"/>
       <c r="F30" s="231"/>
@@ -9725,15 +9963,16 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
+      <c r="AR30" s="499"/>
     </row>
-    <row r="31" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="457" t="s">
         <v>867</v>
       </c>
       <c r="B31" s="454" t="s">
         <v>908</v>
       </c>
-      <c r="C31" s="487">
+      <c r="C31" s="459">
         <v>23</v>
       </c>
       <c r="D31" s="298" t="s">
@@ -9854,11 +10093,14 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
+      <c r="AR31" s="499" t="s">
+        <v>972</v>
+      </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="457"/>
       <c r="B32" s="454"/>
-      <c r="C32" s="488"/>
+      <c r="C32" s="460"/>
       <c r="D32" s="298"/>
       <c r="E32" s="73"/>
       <c r="F32" s="230"/>
@@ -9943,11 +10185,12 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
+      <c r="AR32" s="499"/>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
       <c r="B33" s="454"/>
-      <c r="C33" s="488"/>
+      <c r="C33" s="460"/>
       <c r="D33" s="298"/>
       <c r="E33" s="73"/>
       <c r="F33" s="230"/>
@@ -10032,11 +10275,12 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
+      <c r="AR33" s="499"/>
     </row>
-    <row r="34" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
       <c r="B34" s="454"/>
-      <c r="C34" s="489"/>
+      <c r="C34" s="461"/>
       <c r="D34" s="311"/>
       <c r="E34" s="74"/>
       <c r="F34" s="231"/>
@@ -10121,15 +10365,16 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
+      <c r="AR34" s="499"/>
     </row>
-    <row r="35" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="457" t="s">
         <v>868</v>
       </c>
       <c r="B35" s="454" t="s">
         <v>909</v>
       </c>
-      <c r="C35" s="487">
+      <c r="C35" s="459">
         <v>24</v>
       </c>
       <c r="D35" s="298" t="s">
@@ -10244,11 +10489,14 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
+      <c r="AR35" s="499" t="s">
+        <v>972</v>
+      </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="457"/>
       <c r="B36" s="454"/>
-      <c r="C36" s="488"/>
+      <c r="C36" s="460"/>
       <c r="D36" s="298"/>
       <c r="E36" s="73"/>
       <c r="F36" s="230"/>
@@ -10329,11 +10577,12 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
+      <c r="AR36" s="499"/>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
       <c r="B37" s="454"/>
-      <c r="C37" s="488"/>
+      <c r="C37" s="460"/>
       <c r="D37" s="298"/>
       <c r="E37" s="73"/>
       <c r="F37" s="230"/>
@@ -10414,11 +10663,12 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
+      <c r="AR37" s="499"/>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
       <c r="B38" s="454"/>
-      <c r="C38" s="488"/>
+      <c r="C38" s="460"/>
       <c r="D38" s="298"/>
       <c r="E38" s="77"/>
       <c r="F38" s="232"/>
@@ -10499,15 +10749,16 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
+      <c r="AR38" s="499"/>
     </row>
-    <row r="39" spans="1:43" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="457" t="s">
         <v>868</v>
       </c>
       <c r="B39" s="454" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="488"/>
+      <c r="C39" s="460"/>
       <c r="D39" s="298" t="s">
         <v>737</v>
       </c>
@@ -10622,11 +10873,14 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
+      <c r="AR39" s="499" t="s">
+        <v>972</v>
+      </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="457"/>
       <c r="B40" s="454"/>
-      <c r="C40" s="488"/>
+      <c r="C40" s="460"/>
       <c r="D40" s="298"/>
       <c r="E40" s="73"/>
       <c r="F40" s="230"/>
@@ -10707,11 +10961,12 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
+      <c r="AR40" s="499"/>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
       <c r="B41" s="454"/>
-      <c r="C41" s="488"/>
+      <c r="C41" s="460"/>
       <c r="D41" s="298"/>
       <c r="E41" s="73"/>
       <c r="F41" s="230"/>
@@ -10792,11 +11047,12 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
+      <c r="AR41" s="499"/>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
       <c r="B42" s="454"/>
-      <c r="C42" s="488"/>
+      <c r="C42" s="460"/>
       <c r="D42" s="298"/>
       <c r="E42" s="73"/>
       <c r="F42" s="230"/>
@@ -10877,11 +11133,12 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
+      <c r="AR42" s="499"/>
     </row>
-    <row r="43" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
       <c r="B43" s="454"/>
-      <c r="C43" s="489"/>
+      <c r="C43" s="461"/>
       <c r="D43" s="311"/>
       <c r="E43" s="74"/>
       <c r="F43" s="231"/>
@@ -10960,15 +11217,16 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
+      <c r="AR43" s="499"/>
     </row>
-    <row r="44" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="457" t="s">
         <v>869</v>
       </c>
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="490">
+      <c r="C44" s="503">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11087,11 +11345,14 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
+      <c r="AR44" s="499" t="s">
+        <v>973</v>
+      </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="491"/>
+      <c r="C45" s="504"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11176,11 +11437,12 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
+      <c r="AR45" s="499"/>
     </row>
-    <row r="46" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="492"/>
+      <c r="C46" s="505"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11265,15 +11527,16 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
+      <c r="AR46" s="499"/>
     </row>
-    <row r="47" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="457" t="s">
         <v>870</v>
       </c>
       <c r="B47" s="454" t="s">
         <v>912</v>
       </c>
-      <c r="C47" s="490">
+      <c r="C47" s="468">
         <v>32</v>
       </c>
       <c r="D47" s="299" t="s">
@@ -11392,11 +11655,14 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
+      <c r="AR47" s="499" t="s">
+        <v>973</v>
+      </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="457"/>
       <c r="B48" s="454"/>
-      <c r="C48" s="491"/>
+      <c r="C48" s="469"/>
       <c r="D48" s="299"/>
       <c r="E48" s="84"/>
       <c r="F48" s="235"/>
@@ -11479,11 +11745,12 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
+      <c r="AR48" s="499"/>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
       <c r="B49" s="454"/>
-      <c r="C49" s="491"/>
+      <c r="C49" s="469"/>
       <c r="D49" s="299"/>
       <c r="E49" s="84"/>
       <c r="F49" s="235"/>
@@ -11566,11 +11833,12 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
+      <c r="AR49" s="499"/>
     </row>
-    <row r="50" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="492"/>
+      <c r="C50" s="470"/>
       <c r="D50" s="312"/>
       <c r="E50" s="85"/>
       <c r="F50" s="236"/>
@@ -11653,15 +11921,16 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
+      <c r="AR50" s="499"/>
     </row>
-    <row r="51" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="457" t="s">
         <v>871</v>
       </c>
       <c r="B51" s="454" t="s">
         <v>913</v>
       </c>
-      <c r="C51" s="490">
+      <c r="C51" s="468">
         <v>33</v>
       </c>
       <c r="D51" s="299" t="s">
@@ -11782,11 +12051,14 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
+      <c r="AR51" s="499" t="s">
+        <v>973</v>
+      </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="457"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="491"/>
+      <c r="C52" s="469"/>
       <c r="D52" s="299"/>
       <c r="E52" s="84"/>
       <c r="F52" s="235"/>
@@ -11871,11 +12143,12 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
+      <c r="AR52" s="499"/>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
       <c r="B53" s="454"/>
-      <c r="C53" s="491"/>
+      <c r="C53" s="469"/>
       <c r="D53" s="299"/>
       <c r="E53" s="84"/>
       <c r="F53" s="235"/>
@@ -11956,11 +12229,12 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
+      <c r="AR53" s="499"/>
     </row>
-    <row r="54" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
       <c r="B54" s="454"/>
-      <c r="C54" s="492"/>
+      <c r="C54" s="470"/>
       <c r="D54" s="312"/>
       <c r="E54" s="85"/>
       <c r="F54" s="236"/>
@@ -12039,15 +12313,16 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
+      <c r="AR54" s="499"/>
     </row>
-    <row r="55" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="457" t="s">
         <v>872</v>
       </c>
       <c r="B55" s="454" t="s">
         <v>914</v>
       </c>
-      <c r="C55" s="490">
+      <c r="C55" s="468">
         <v>34</v>
       </c>
       <c r="D55" s="299" t="s">
@@ -12162,11 +12437,14 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
+      <c r="AR55" s="499" t="s">
+        <v>973</v>
+      </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="457"/>
       <c r="B56" s="454"/>
-      <c r="C56" s="491"/>
+      <c r="C56" s="469"/>
       <c r="D56" s="299"/>
       <c r="E56" s="84"/>
       <c r="F56" s="235"/>
@@ -12247,11 +12525,12 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
+      <c r="AR56" s="499"/>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
       <c r="B57" s="454"/>
-      <c r="C57" s="491"/>
+      <c r="C57" s="469"/>
       <c r="D57" s="299"/>
       <c r="E57" s="84"/>
       <c r="F57" s="235"/>
@@ -12332,11 +12611,12 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
+      <c r="AR57" s="499"/>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
       <c r="B58" s="454"/>
-      <c r="C58" s="491"/>
+      <c r="C58" s="469"/>
       <c r="D58" s="299"/>
       <c r="E58" s="84"/>
       <c r="F58" s="235"/>
@@ -12417,11 +12697,12 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
+      <c r="AR58" s="499"/>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
       <c r="B59" s="454"/>
-      <c r="C59" s="491"/>
+      <c r="C59" s="469"/>
       <c r="D59" s="299"/>
       <c r="E59" s="89"/>
       <c r="F59" s="237"/>
@@ -12502,15 +12783,16 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
+      <c r="AR59" s="499"/>
     </row>
-    <row r="60" spans="1:43" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="457" t="s">
         <v>872</v>
       </c>
       <c r="B60" s="454" t="s">
         <v>915</v>
       </c>
-      <c r="C60" s="491"/>
+      <c r="C60" s="469"/>
       <c r="D60" s="299" t="s">
         <v>738</v>
       </c>
@@ -12625,11 +12907,14 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
+      <c r="AR60" s="499" t="s">
+        <v>973</v>
+      </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="457"/>
       <c r="B61" s="454"/>
-      <c r="C61" s="491"/>
+      <c r="C61" s="469"/>
       <c r="D61" s="299"/>
       <c r="E61" s="84"/>
       <c r="F61" s="235"/>
@@ -12710,11 +12995,12 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
+      <c r="AR61" s="499"/>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
       <c r="B62" s="454"/>
-      <c r="C62" s="491"/>
+      <c r="C62" s="469"/>
       <c r="D62" s="299"/>
       <c r="E62" s="84"/>
       <c r="F62" s="235"/>
@@ -12795,11 +13081,12 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
+      <c r="AR62" s="499"/>
     </row>
-    <row r="63" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
       <c r="B63" s="454"/>
-      <c r="C63" s="492"/>
+      <c r="C63" s="470"/>
       <c r="D63" s="312"/>
       <c r="E63" s="85"/>
       <c r="F63" s="236"/>
@@ -12880,15 +13167,16 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
+      <c r="AR63" s="499"/>
     </row>
-    <row r="64" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="457" t="s">
         <v>873</v>
       </c>
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="493">
+      <c r="C64" s="506">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13007,11 +13295,14 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
+      <c r="AR64" s="499" t="s">
+        <v>974</v>
+      </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="494"/>
+      <c r="C65" s="507"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13096,11 +13387,12 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
+      <c r="AR65" s="499"/>
     </row>
-    <row r="66" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="495"/>
+      <c r="C66" s="508"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13185,15 +13477,16 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
+      <c r="AR66" s="499"/>
     </row>
-    <row r="67" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="457" t="s">
         <v>874</v>
       </c>
       <c r="B67" s="454" t="s">
         <v>917</v>
       </c>
-      <c r="C67" s="493">
+      <c r="C67" s="471">
         <v>42</v>
       </c>
       <c r="D67" s="300" t="s">
@@ -13312,11 +13605,14 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
+      <c r="AR67" s="499" t="s">
+        <v>974</v>
+      </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="457"/>
       <c r="B68" s="454"/>
-      <c r="C68" s="494"/>
+      <c r="C68" s="472"/>
       <c r="D68" s="300"/>
       <c r="E68" s="96"/>
       <c r="F68" s="238"/>
@@ -13399,11 +13695,12 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
+      <c r="AR68" s="499"/>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
       <c r="B69" s="454"/>
-      <c r="C69" s="494"/>
+      <c r="C69" s="472"/>
       <c r="D69" s="300"/>
       <c r="E69" s="100"/>
       <c r="F69" s="240"/>
@@ -13486,15 +13783,16 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
+      <c r="AR69" s="499"/>
     </row>
-    <row r="70" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A70" s="457" t="s">
         <v>874</v>
       </c>
       <c r="B70" s="454" t="s">
         <v>918</v>
       </c>
-      <c r="C70" s="494"/>
+      <c r="C70" s="472"/>
       <c r="D70" s="300" t="s">
         <v>739</v>
       </c>
@@ -13607,11 +13905,14 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
+      <c r="AR70" s="499" t="s">
+        <v>974</v>
+      </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="457"/>
       <c r="B71" s="454"/>
-      <c r="C71" s="494"/>
+      <c r="C71" s="472"/>
       <c r="D71" s="300"/>
       <c r="E71" s="96"/>
       <c r="F71" s="238"/>
@@ -13692,11 +13993,12 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
+      <c r="AR71" s="499"/>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
       <c r="B72" s="454"/>
-      <c r="C72" s="494"/>
+      <c r="C72" s="472"/>
       <c r="D72" s="300"/>
       <c r="E72" s="96"/>
       <c r="F72" s="238"/>
@@ -13777,11 +14079,12 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
+      <c r="AR72" s="499"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
       <c r="B73" s="454"/>
-      <c r="C73" s="494"/>
+      <c r="C73" s="472"/>
       <c r="D73" s="300"/>
       <c r="E73" s="96"/>
       <c r="F73" s="238"/>
@@ -13862,11 +14165,12 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
+      <c r="AR73" s="499"/>
     </row>
-    <row r="74" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
       <c r="B74" s="454"/>
-      <c r="C74" s="495"/>
+      <c r="C74" s="473"/>
       <c r="D74" s="313"/>
       <c r="E74" s="97"/>
       <c r="F74" s="239"/>
@@ -13947,15 +14251,16 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
+      <c r="AR74" s="499"/>
     </row>
-    <row r="75" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="457" t="s">
         <v>875</v>
       </c>
       <c r="B75" s="454" t="s">
         <v>919</v>
       </c>
-      <c r="C75" s="493">
+      <c r="C75" s="471">
         <v>43</v>
       </c>
       <c r="D75" s="300" t="s">
@@ -14072,11 +14377,14 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
+      <c r="AR75" s="499" t="s">
+        <v>974</v>
+      </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="457"/>
       <c r="B76" s="454"/>
-      <c r="C76" s="494"/>
+      <c r="C76" s="472"/>
       <c r="D76" s="300"/>
       <c r="E76" s="96"/>
       <c r="F76" s="238"/>
@@ -14157,11 +14465,12 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
+      <c r="AR76" s="499"/>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
       <c r="B77" s="454"/>
-      <c r="C77" s="494"/>
+      <c r="C77" s="472"/>
       <c r="D77" s="300"/>
       <c r="E77" s="96"/>
       <c r="F77" s="238"/>
@@ -14242,11 +14551,12 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
+      <c r="AR77" s="499"/>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
       <c r="B78" s="454"/>
-      <c r="C78" s="494"/>
+      <c r="C78" s="472"/>
       <c r="D78" s="300"/>
       <c r="E78" s="96"/>
       <c r="F78" s="238"/>
@@ -14327,11 +14637,12 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
+      <c r="AR78" s="499"/>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
       <c r="B79" s="454"/>
-      <c r="C79" s="494"/>
+      <c r="C79" s="472"/>
       <c r="D79" s="300"/>
       <c r="E79" s="100"/>
       <c r="F79" s="240"/>
@@ -14412,15 +14723,16 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
+      <c r="AR79" s="499"/>
     </row>
-    <row r="80" spans="1:43" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="457" t="s">
         <v>876</v>
       </c>
       <c r="B80" s="454" t="s">
         <v>920</v>
       </c>
-      <c r="C80" s="494"/>
+      <c r="C80" s="472"/>
       <c r="D80" s="300" t="s">
         <v>739</v>
       </c>
@@ -14531,11 +14843,14 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
+      <c r="AR80" s="499" t="s">
+        <v>974</v>
+      </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A81" s="457"/>
       <c r="B81" s="454"/>
-      <c r="C81" s="494"/>
+      <c r="C81" s="472"/>
       <c r="D81" s="300"/>
       <c r="E81" s="96"/>
       <c r="F81" s="238"/>
@@ -14616,11 +14931,12 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
+      <c r="AR81" s="499"/>
     </row>
-    <row r="82" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
       <c r="B82" s="454"/>
-      <c r="C82" s="495"/>
+      <c r="C82" s="473"/>
       <c r="D82" s="313"/>
       <c r="E82" s="97"/>
       <c r="F82" s="239"/>
@@ -14699,15 +15015,16 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
+      <c r="AR82" s="499"/>
     </row>
-    <row r="83" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="457" t="s">
         <v>877</v>
       </c>
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="496">
+      <c r="C83" s="509">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -14828,11 +15145,14 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
+      <c r="AR83" s="499" t="s">
+        <v>975</v>
+      </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="497"/>
+      <c r="C84" s="510"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -14917,11 +15237,12 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
+      <c r="AR84" s="499"/>
     </row>
-    <row r="85" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="498"/>
+      <c r="C85" s="511"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15004,15 +15325,16 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
+      <c r="AR85" s="499"/>
     </row>
-    <row r="86" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="457" t="s">
         <v>878</v>
       </c>
       <c r="B86" s="454" t="s">
         <v>922</v>
       </c>
-      <c r="C86" s="496">
+      <c r="C86" s="474">
         <v>52</v>
       </c>
       <c r="D86" s="301" t="s">
@@ -15131,11 +15453,14 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
+      <c r="AR86" s="499" t="s">
+        <v>975</v>
+      </c>
     </row>
-    <row r="87" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A87" s="457"/>
       <c r="B87" s="454"/>
-      <c r="C87" s="497"/>
+      <c r="C87" s="475"/>
       <c r="D87" s="301"/>
       <c r="E87" s="110"/>
       <c r="F87" s="241"/>
@@ -15220,11 +15545,12 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
+      <c r="AR87" s="499"/>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
       <c r="B88" s="454"/>
-      <c r="C88" s="497"/>
+      <c r="C88" s="475"/>
       <c r="D88" s="301"/>
       <c r="E88" s="110"/>
       <c r="F88" s="241"/>
@@ -15309,11 +15635,12 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
+      <c r="AR88" s="499"/>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
       <c r="B89" s="454"/>
-      <c r="C89" s="497"/>
+      <c r="C89" s="475"/>
       <c r="D89" s="301"/>
       <c r="E89" s="115"/>
       <c r="F89" s="243"/>
@@ -15398,15 +15725,16 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
+      <c r="AR89" s="499"/>
     </row>
-    <row r="90" spans="1:43" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="457" t="s">
         <v>878</v>
       </c>
       <c r="B90" s="454" t="s">
         <v>923</v>
       </c>
-      <c r="C90" s="497"/>
+      <c r="C90" s="475"/>
       <c r="D90" s="301" t="s">
         <v>740</v>
       </c>
@@ -15523,11 +15851,14 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
+      <c r="AR90" s="499" t="s">
+        <v>975</v>
+      </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A91" s="457"/>
       <c r="B91" s="454"/>
-      <c r="C91" s="497"/>
+      <c r="C91" s="475"/>
       <c r="D91" s="301"/>
       <c r="E91" s="110"/>
       <c r="F91" s="241"/>
@@ -15610,11 +15941,12 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
+      <c r="AR91" s="499"/>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
       <c r="B92" s="454"/>
-      <c r="C92" s="497"/>
+      <c r="C92" s="475"/>
       <c r="D92" s="301"/>
       <c r="E92" s="110"/>
       <c r="F92" s="241"/>
@@ -15697,11 +16029,12 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
+      <c r="AR92" s="499"/>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
       <c r="B93" s="454"/>
-      <c r="C93" s="497"/>
+      <c r="C93" s="475"/>
       <c r="D93" s="301"/>
       <c r="E93" s="115"/>
       <c r="F93" s="243"/>
@@ -15784,15 +16117,16 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
+      <c r="AR93" s="499"/>
     </row>
-    <row r="94" spans="1:43" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="457" t="s">
         <v>878</v>
       </c>
       <c r="B94" s="454" t="s">
         <v>924</v>
       </c>
-      <c r="C94" s="497"/>
+      <c r="C94" s="475"/>
       <c r="D94" s="301" t="s">
         <v>740</v>
       </c>
@@ -15909,11 +16243,14 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
+      <c r="AR94" s="499" t="s">
+        <v>975</v>
+      </c>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A95" s="457"/>
       <c r="B95" s="454"/>
-      <c r="C95" s="497"/>
+      <c r="C95" s="475"/>
       <c r="D95" s="301"/>
       <c r="E95" s="110"/>
       <c r="F95" s="241"/>
@@ -15996,11 +16333,12 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
+      <c r="AR95" s="499"/>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
       <c r="B96" s="454"/>
-      <c r="C96" s="497"/>
+      <c r="C96" s="475"/>
       <c r="D96" s="301"/>
       <c r="E96" s="110"/>
       <c r="F96" s="241"/>
@@ -16083,11 +16421,12 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
+      <c r="AR96" s="499"/>
     </row>
-    <row r="97" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
       <c r="B97" s="454"/>
-      <c r="C97" s="498"/>
+      <c r="C97" s="476"/>
       <c r="D97" s="314"/>
       <c r="E97" s="111"/>
       <c r="F97" s="242"/>
@@ -16170,15 +16509,16 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
+      <c r="AR97" s="499"/>
     </row>
-    <row r="98" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="457" t="s">
         <v>879</v>
       </c>
       <c r="B98" s="454" t="s">
         <v>925</v>
       </c>
-      <c r="C98" s="496">
+      <c r="C98" s="474">
         <v>53</v>
       </c>
       <c r="D98" s="301" t="s">
@@ -16295,11 +16635,14 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
+      <c r="AR98" s="499" t="s">
+        <v>975</v>
+      </c>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A99" s="457"/>
       <c r="B99" s="454"/>
-      <c r="C99" s="497"/>
+      <c r="C99" s="475"/>
       <c r="D99" s="301"/>
       <c r="E99" s="110"/>
       <c r="F99" s="241"/>
@@ -16382,11 +16725,12 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
+      <c r="AR99" s="499"/>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
       <c r="B100" s="454"/>
-      <c r="C100" s="497"/>
+      <c r="C100" s="475"/>
       <c r="D100" s="301"/>
       <c r="E100" s="110"/>
       <c r="F100" s="241"/>
@@ -16467,11 +16811,12 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
+      <c r="AR100" s="499"/>
     </row>
-    <row r="101" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
       <c r="B101" s="454"/>
-      <c r="C101" s="498"/>
+      <c r="C101" s="476"/>
       <c r="D101" s="301"/>
       <c r="E101" s="111"/>
       <c r="F101" s="242"/>
@@ -16554,15 +16899,16 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
+      <c r="AR101" s="499"/>
     </row>
-    <row r="102" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="457" t="s">
         <v>880</v>
       </c>
       <c r="B102" s="454" t="s">
         <v>926</v>
       </c>
-      <c r="C102" s="472">
+      <c r="C102" s="465">
         <v>61</v>
       </c>
       <c r="D102" s="323" t="s">
@@ -16675,11 +17021,14 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
+      <c r="AR102" s="499" t="s">
+        <v>976</v>
+      </c>
     </row>
-    <row r="103" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A103" s="457"/>
       <c r="B103" s="454"/>
-      <c r="C103" s="473"/>
+      <c r="C103" s="466"/>
       <c r="D103" s="323"/>
       <c r="E103" s="329"/>
       <c r="F103" s="330"/>
@@ -16760,11 +17109,12 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
+      <c r="AR103" s="499"/>
     </row>
-    <row r="104" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
       <c r="B104" s="454"/>
-      <c r="C104" s="473"/>
+      <c r="C104" s="466"/>
       <c r="D104" s="323"/>
       <c r="E104" s="329"/>
       <c r="F104" s="330"/>
@@ -16845,11 +17195,12 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
+      <c r="AR104" s="499"/>
     </row>
-    <row r="105" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
       <c r="B105" s="454"/>
-      <c r="C105" s="474"/>
+      <c r="C105" s="467"/>
       <c r="D105" s="331"/>
       <c r="E105" s="332"/>
       <c r="F105" s="333"/>
@@ -16930,15 +17281,16 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
+      <c r="AR105" s="499"/>
     </row>
-    <row r="106" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="457" t="s">
         <v>881</v>
       </c>
       <c r="B106" s="454" t="s">
         <v>927</v>
       </c>
-      <c r="C106" s="472">
+      <c r="C106" s="465">
         <v>62</v>
       </c>
       <c r="D106" s="323" t="s">
@@ -17055,11 +17407,14 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
+      <c r="AR106" s="499" t="s">
+        <v>976</v>
+      </c>
     </row>
-    <row r="107" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A107" s="457"/>
       <c r="B107" s="454"/>
-      <c r="C107" s="473"/>
+      <c r="C107" s="466"/>
       <c r="D107" s="323"/>
       <c r="E107" s="329"/>
       <c r="F107" s="330"/>
@@ -17140,11 +17495,12 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
+      <c r="AR107" s="499"/>
     </row>
-    <row r="108" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
       <c r="B108" s="454"/>
-      <c r="C108" s="473"/>
+      <c r="C108" s="466"/>
       <c r="D108" s="323"/>
       <c r="E108" s="329"/>
       <c r="F108" s="330"/>
@@ -17225,11 +17581,12 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
+      <c r="AR108" s="499"/>
     </row>
-    <row r="109" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
       <c r="B109" s="454"/>
-      <c r="C109" s="473"/>
+      <c r="C109" s="466"/>
       <c r="D109" s="323"/>
       <c r="E109" s="338"/>
       <c r="F109" s="339"/>
@@ -17310,15 +17667,16 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
+      <c r="AR109" s="499"/>
     </row>
-    <row r="110" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A110" s="457" t="s">
         <v>881</v>
       </c>
       <c r="B110" s="454" t="s">
         <v>928</v>
       </c>
-      <c r="C110" s="473"/>
+      <c r="C110" s="466"/>
       <c r="D110" s="323" t="s">
         <v>741</v>
       </c>
@@ -17433,11 +17791,14 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
+      <c r="AR110" s="499" t="s">
+        <v>976</v>
+      </c>
     </row>
-    <row r="111" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A111" s="457"/>
       <c r="B111" s="454"/>
-      <c r="C111" s="473"/>
+      <c r="C111" s="466"/>
       <c r="D111" s="323"/>
       <c r="E111" s="329"/>
       <c r="F111" s="330"/>
@@ -17518,11 +17879,12 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
+      <c r="AR111" s="499"/>
     </row>
-    <row r="112" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
       <c r="B112" s="454"/>
-      <c r="C112" s="473"/>
+      <c r="C112" s="466"/>
       <c r="D112" s="323"/>
       <c r="E112" s="329"/>
       <c r="F112" s="330"/>
@@ -17603,11 +17965,12 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
+      <c r="AR112" s="499"/>
     </row>
-    <row r="113" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
       <c r="B113" s="454"/>
-      <c r="C113" s="473"/>
+      <c r="C113" s="466"/>
       <c r="D113" s="323"/>
       <c r="E113" s="329"/>
       <c r="F113" s="330"/>
@@ -17688,11 +18051,12 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
+      <c r="AR113" s="499"/>
     </row>
-    <row r="114" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
       <c r="B114" s="454"/>
-      <c r="C114" s="474"/>
+      <c r="C114" s="467"/>
       <c r="D114" s="331"/>
       <c r="E114" s="332"/>
       <c r="F114" s="333"/>
@@ -17771,15 +18135,16 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
+      <c r="AR114" s="499"/>
     </row>
-    <row r="115" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="457" t="s">
         <v>882</v>
       </c>
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="475">
+      <c r="C115" s="512">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -17896,11 +18261,14 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
+      <c r="AR115" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="116" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="476"/>
+      <c r="C116" s="513"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -17981,11 +18349,12 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
+      <c r="AR116" s="499"/>
     </row>
-    <row r="117" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="476"/>
+      <c r="C117" s="513"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18066,11 +18435,12 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
+      <c r="AR117" s="499"/>
     </row>
-    <row r="118" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="476"/>
+      <c r="C118" s="513"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18151,15 +18521,16 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
+      <c r="AR118" s="499"/>
     </row>
-    <row r="119" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A119" s="457" t="s">
         <v>882</v>
       </c>
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="476"/>
+      <c r="C119" s="513"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18272,11 +18643,14 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
+      <c r="AR119" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="120" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="476"/>
+      <c r="C120" s="513"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18357,11 +18731,12 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
+      <c r="AR120" s="499"/>
     </row>
-    <row r="121" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="476"/>
+      <c r="C121" s="513"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -18442,11 +18817,12 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
+      <c r="AR121" s="499"/>
     </row>
-    <row r="122" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="477"/>
+      <c r="C122" s="514"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -18527,15 +18903,16 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
+      <c r="AR122" s="499"/>
     </row>
-    <row r="123" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="457" t="s">
         <v>883</v>
       </c>
       <c r="B123" s="454" t="s">
         <v>931</v>
       </c>
-      <c r="C123" s="475">
+      <c r="C123" s="480">
         <v>72</v>
       </c>
       <c r="D123" s="302" t="s">
@@ -18650,11 +19027,14 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
+      <c r="AR123" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="124" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A124" s="457"/>
       <c r="B124" s="454"/>
-      <c r="C124" s="476"/>
+      <c r="C124" s="481"/>
       <c r="D124" s="302"/>
       <c r="E124" s="125"/>
       <c r="F124" s="244"/>
@@ -18735,11 +19115,12 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
+      <c r="AR124" s="499"/>
     </row>
-    <row r="125" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
       <c r="B125" s="454"/>
-      <c r="C125" s="476"/>
+      <c r="C125" s="481"/>
       <c r="D125" s="302"/>
       <c r="E125" s="125"/>
       <c r="F125" s="244"/>
@@ -18820,11 +19201,12 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
+      <c r="AR125" s="499"/>
     </row>
-    <row r="126" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
       <c r="B126" s="454"/>
-      <c r="C126" s="476"/>
+      <c r="C126" s="481"/>
       <c r="D126" s="302"/>
       <c r="E126" s="125"/>
       <c r="F126" s="244"/>
@@ -18905,11 +19287,12 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
+      <c r="AR126" s="499"/>
     </row>
-    <row r="127" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
       <c r="B127" s="454"/>
-      <c r="C127" s="476"/>
+      <c r="C127" s="481"/>
       <c r="D127" s="302"/>
       <c r="E127" s="126"/>
       <c r="F127" s="245"/>
@@ -18990,15 +19373,16 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
+      <c r="AR127" s="499"/>
     </row>
-    <row r="128" spans="1:43" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:44" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="457" t="s">
         <v>883</v>
       </c>
       <c r="B128" s="454" t="s">
         <v>932</v>
       </c>
-      <c r="C128" s="476"/>
+      <c r="C128" s="481"/>
       <c r="D128" s="302" t="s">
         <v>742</v>
       </c>
@@ -19115,11 +19499,14 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
+      <c r="AR128" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="129" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A129" s="457"/>
       <c r="B129" s="454"/>
-      <c r="C129" s="476"/>
+      <c r="C129" s="481"/>
       <c r="D129" s="302"/>
       <c r="E129" s="125"/>
       <c r="F129" s="244"/>
@@ -19204,11 +19591,12 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
+      <c r="AR129" s="499"/>
     </row>
-    <row r="130" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
       <c r="B130" s="454"/>
-      <c r="C130" s="476"/>
+      <c r="C130" s="481"/>
       <c r="D130" s="302"/>
       <c r="E130" s="125"/>
       <c r="F130" s="244"/>
@@ -19293,11 +19681,12 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
+      <c r="AR130" s="499"/>
     </row>
-    <row r="131" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
       <c r="B131" s="454"/>
-      <c r="C131" s="477"/>
+      <c r="C131" s="482"/>
       <c r="D131" s="315"/>
       <c r="E131" s="129"/>
       <c r="F131" s="246"/>
@@ -19374,15 +19763,16 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
+      <c r="AR131" s="499"/>
     </row>
-    <row r="132" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="457" t="s">
         <v>884</v>
       </c>
       <c r="B132" s="454" t="s">
         <v>933</v>
       </c>
-      <c r="C132" s="475">
+      <c r="C132" s="480">
         <v>73</v>
       </c>
       <c r="D132" s="302" t="s">
@@ -19499,11 +19889,14 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
+      <c r="AR132" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="133" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A133" s="457"/>
       <c r="B133" s="454"/>
-      <c r="C133" s="476"/>
+      <c r="C133" s="481"/>
       <c r="D133" s="302"/>
       <c r="E133" s="125"/>
       <c r="F133" s="244"/>
@@ -19584,11 +19977,12 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
+      <c r="AR133" s="499"/>
     </row>
-    <row r="134" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
       <c r="B134" s="454"/>
-      <c r="C134" s="476"/>
+      <c r="C134" s="481"/>
       <c r="D134" s="302"/>
       <c r="E134" s="125"/>
       <c r="F134" s="244"/>
@@ -19669,11 +20063,12 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
+      <c r="AR134" s="499"/>
     </row>
-    <row r="135" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
       <c r="B135" s="454"/>
-      <c r="C135" s="476"/>
+      <c r="C135" s="481"/>
       <c r="D135" s="302"/>
       <c r="E135" s="126"/>
       <c r="F135" s="245"/>
@@ -19754,15 +20149,16 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
+      <c r="AR135" s="499"/>
     </row>
-    <row r="136" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A136" s="457" t="s">
         <v>884</v>
       </c>
       <c r="B136" s="454" t="s">
         <v>934</v>
       </c>
-      <c r="C136" s="476"/>
+      <c r="C136" s="481"/>
       <c r="D136" s="302" t="s">
         <v>742</v>
       </c>
@@ -19877,11 +20273,14 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
+      <c r="AR136" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="137" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A137" s="457"/>
       <c r="B137" s="454"/>
-      <c r="C137" s="476"/>
+      <c r="C137" s="481"/>
       <c r="D137" s="302"/>
       <c r="E137" s="125"/>
       <c r="F137" s="244"/>
@@ -19962,11 +20361,12 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
+      <c r="AR137" s="499"/>
     </row>
-    <row r="138" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
       <c r="B138" s="454"/>
-      <c r="C138" s="476"/>
+      <c r="C138" s="481"/>
       <c r="D138" s="302"/>
       <c r="E138" s="125"/>
       <c r="F138" s="244"/>
@@ -20047,11 +20447,12 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
+      <c r="AR138" s="499"/>
     </row>
-    <row r="139" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
       <c r="B139" s="454"/>
-      <c r="C139" s="476"/>
+      <c r="C139" s="481"/>
       <c r="D139" s="302"/>
       <c r="E139" s="125"/>
       <c r="F139" s="244"/>
@@ -20132,11 +20533,12 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
+      <c r="AR139" s="499"/>
     </row>
-    <row r="140" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
       <c r="B140" s="454"/>
-      <c r="C140" s="477"/>
+      <c r="C140" s="482"/>
       <c r="D140" s="315"/>
       <c r="E140" s="129"/>
       <c r="F140" s="246"/>
@@ -20215,15 +20617,16 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
+      <c r="AR140" s="499"/>
     </row>
-    <row r="141" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="457" t="s">
         <v>885</v>
       </c>
       <c r="B141" s="454" t="s">
         <v>935</v>
       </c>
-      <c r="C141" s="478">
+      <c r="C141" s="483">
         <v>74</v>
       </c>
       <c r="D141" s="302" t="s">
@@ -20338,11 +20741,14 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
+      <c r="AR141" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="142" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A142" s="457"/>
       <c r="B142" s="454"/>
-      <c r="C142" s="479"/>
+      <c r="C142" s="484"/>
       <c r="D142" s="303"/>
       <c r="E142" s="125"/>
       <c r="F142" s="244"/>
@@ -20423,11 +20829,12 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
+      <c r="AR142" s="499"/>
     </row>
-    <row r="143" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
       <c r="B143" s="454"/>
-      <c r="C143" s="479"/>
+      <c r="C143" s="484"/>
       <c r="D143" s="303"/>
       <c r="E143" s="125"/>
       <c r="F143" s="244"/>
@@ -20508,11 +20915,12 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
+      <c r="AR143" s="499"/>
     </row>
-    <row r="144" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
       <c r="B144" s="454"/>
-      <c r="C144" s="479"/>
+      <c r="C144" s="484"/>
       <c r="D144" s="303"/>
       <c r="E144" s="125"/>
       <c r="F144" s="244"/>
@@ -20593,11 +21001,12 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
+      <c r="AR144" s="499"/>
     </row>
-    <row r="145" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
       <c r="B145" s="454"/>
-      <c r="C145" s="479"/>
+      <c r="C145" s="484"/>
       <c r="D145" s="303"/>
       <c r="E145" s="126"/>
       <c r="F145" s="245"/>
@@ -20678,15 +21087,16 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
+      <c r="AR145" s="499"/>
     </row>
-    <row r="146" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A146" s="457" t="s">
         <v>885</v>
       </c>
       <c r="B146" s="454" t="s">
         <v>936</v>
       </c>
-      <c r="C146" s="479"/>
+      <c r="C146" s="484"/>
       <c r="D146" s="302" t="s">
         <v>742</v>
       </c>
@@ -20801,11 +21211,14 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
+      <c r="AR146" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="147" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A147" s="457"/>
       <c r="B147" s="454"/>
-      <c r="C147" s="479"/>
+      <c r="C147" s="484"/>
       <c r="D147" s="303"/>
       <c r="E147" s="125"/>
       <c r="F147" s="244"/>
@@ -20886,11 +21299,12 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
+      <c r="AR147" s="499"/>
     </row>
-    <row r="148" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
       <c r="B148" s="454"/>
-      <c r="C148" s="479"/>
+      <c r="C148" s="484"/>
       <c r="D148" s="303"/>
       <c r="E148" s="125"/>
       <c r="F148" s="244"/>
@@ -20971,11 +21385,12 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
+      <c r="AR148" s="499"/>
     </row>
-    <row r="149" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
       <c r="B149" s="454"/>
-      <c r="C149" s="480"/>
+      <c r="C149" s="485"/>
       <c r="D149" s="316"/>
       <c r="E149" s="129"/>
       <c r="F149" s="246"/>
@@ -21056,15 +21471,16 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
+      <c r="AR149" s="499"/>
     </row>
-    <row r="150" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="457" t="s">
         <v>886</v>
       </c>
       <c r="B150" s="454" t="s">
         <v>937</v>
       </c>
-      <c r="C150" s="475">
+      <c r="C150" s="480">
         <v>75</v>
       </c>
       <c r="D150" s="302" t="s">
@@ -21179,11 +21595,14 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
+      <c r="AR150" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="151" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A151" s="457"/>
       <c r="B151" s="454"/>
-      <c r="C151" s="476"/>
+      <c r="C151" s="481"/>
       <c r="D151" s="302"/>
       <c r="E151" s="125"/>
       <c r="F151" s="244"/>
@@ -21264,11 +21683,12 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
+      <c r="AR151" s="499"/>
     </row>
-    <row r="152" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
       <c r="B152" s="454"/>
-      <c r="C152" s="476"/>
+      <c r="C152" s="481"/>
       <c r="D152" s="302"/>
       <c r="E152" s="125"/>
       <c r="F152" s="244"/>
@@ -21349,11 +21769,12 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
+      <c r="AR152" s="499"/>
     </row>
-    <row r="153" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
       <c r="B153" s="454"/>
-      <c r="C153" s="476"/>
+      <c r="C153" s="481"/>
       <c r="D153" s="302"/>
       <c r="E153" s="126"/>
       <c r="F153" s="245"/>
@@ -21434,15 +21855,16 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
+      <c r="AR153" s="499"/>
     </row>
-    <row r="154" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A154" s="457" t="s">
         <v>886</v>
       </c>
       <c r="B154" s="454" t="s">
         <v>938</v>
       </c>
-      <c r="C154" s="476"/>
+      <c r="C154" s="481"/>
       <c r="D154" s="302" t="s">
         <v>742</v>
       </c>
@@ -21555,11 +21977,14 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
+      <c r="AR154" s="499" t="s">
+        <v>977</v>
+      </c>
     </row>
-    <row r="155" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A155" s="457"/>
       <c r="B155" s="454"/>
-      <c r="C155" s="476"/>
+      <c r="C155" s="481"/>
       <c r="D155" s="302"/>
       <c r="E155" s="125"/>
       <c r="F155" s="244"/>
@@ -21640,11 +22065,12 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
+      <c r="AR155" s="499"/>
     </row>
-    <row r="156" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
       <c r="B156" s="454"/>
-      <c r="C156" s="476"/>
+      <c r="C156" s="481"/>
       <c r="D156" s="302"/>
       <c r="E156" s="125"/>
       <c r="F156" s="244"/>
@@ -21725,11 +22151,12 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
+      <c r="AR156" s="499"/>
     </row>
-    <row r="157" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
       <c r="B157" s="454"/>
-      <c r="C157" s="476"/>
+      <c r="C157" s="481"/>
       <c r="D157" s="302"/>
       <c r="E157" s="125"/>
       <c r="F157" s="244"/>
@@ -21810,11 +22237,12 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
+      <c r="AR157" s="499"/>
     </row>
-    <row r="158" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
       <c r="B158" s="454"/>
-      <c r="C158" s="477"/>
+      <c r="C158" s="482"/>
       <c r="D158" s="315"/>
       <c r="E158" s="129"/>
       <c r="F158" s="246"/>
@@ -21893,15 +22321,16 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
+      <c r="AR158" s="499"/>
     </row>
-    <row r="159" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="457" t="s">
         <v>887</v>
       </c>
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="481">
+      <c r="C159" s="515">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22018,11 +22447,14 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
+      <c r="AR159" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="160" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="482"/>
+      <c r="C160" s="516"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22103,11 +22535,12 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
+      <c r="AR160" s="499"/>
     </row>
-    <row r="161" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="482"/>
+      <c r="C161" s="516"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22188,11 +22621,12 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
+      <c r="AR161" s="499"/>
     </row>
-    <row r="162" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="482"/>
+      <c r="C162" s="516"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22273,15 +22707,16 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
+      <c r="AR162" s="499"/>
     </row>
-    <row r="163" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A163" s="457" t="s">
         <v>887</v>
       </c>
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="482"/>
+      <c r="C163" s="516"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -22396,11 +22831,14 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
+      <c r="AR163" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="164" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="482"/>
+      <c r="C164" s="516"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -22481,11 +22919,12 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
+      <c r="AR164" s="499"/>
     </row>
-    <row r="165" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="482"/>
+      <c r="C165" s="516"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -22566,11 +23005,12 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
+      <c r="AR165" s="499"/>
     </row>
-    <row r="166" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="482"/>
+      <c r="C166" s="516"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -22651,15 +23091,16 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
+      <c r="AR166" s="499"/>
     </row>
-    <row r="167" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A167" s="457" t="s">
         <v>887</v>
       </c>
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="482"/>
+      <c r="C167" s="516"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -22774,11 +23215,14 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
+      <c r="AR167" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="168" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="482"/>
+      <c r="C168" s="516"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -22859,11 +23303,12 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
+      <c r="AR168" s="499"/>
     </row>
-    <row r="169" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="482"/>
+      <c r="C169" s="516"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -22944,11 +23389,12 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
+      <c r="AR169" s="499"/>
     </row>
-    <row r="170" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="483"/>
+      <c r="C170" s="517"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23029,15 +23475,16 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
+      <c r="AR170" s="499"/>
     </row>
-    <row r="171" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="457" t="s">
         <v>888</v>
       </c>
       <c r="B171" s="454" t="s">
         <v>942</v>
       </c>
-      <c r="C171" s="481">
+      <c r="C171" s="486">
         <v>82</v>
       </c>
       <c r="D171" s="304" t="s">
@@ -23154,11 +23601,14 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
+      <c r="AR171" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="172" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A172" s="457"/>
       <c r="B172" s="454"/>
-      <c r="C172" s="482"/>
+      <c r="C172" s="487"/>
       <c r="D172" s="304"/>
       <c r="E172" s="137"/>
       <c r="F172" s="247"/>
@@ -23239,11 +23689,12 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
+      <c r="AR172" s="499"/>
     </row>
-    <row r="173" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
       <c r="B173" s="454"/>
-      <c r="C173" s="482"/>
+      <c r="C173" s="487"/>
       <c r="D173" s="304"/>
       <c r="E173" s="137"/>
       <c r="F173" s="247"/>
@@ -23324,11 +23775,12 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
+      <c r="AR173" s="499"/>
     </row>
-    <row r="174" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
       <c r="B174" s="454"/>
-      <c r="C174" s="482"/>
+      <c r="C174" s="487"/>
       <c r="D174" s="304"/>
       <c r="E174" s="138"/>
       <c r="F174" s="248"/>
@@ -23411,15 +23863,16 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
+      <c r="AR174" s="499"/>
     </row>
-    <row r="175" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A175" s="457" t="s">
         <v>888</v>
       </c>
       <c r="B175" s="454" t="s">
         <v>943</v>
       </c>
-      <c r="C175" s="482"/>
+      <c r="C175" s="487"/>
       <c r="D175" s="304" t="s">
         <v>743</v>
       </c>
@@ -23534,11 +23987,14 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
+      <c r="AR175" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="176" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A176" s="457"/>
       <c r="B176" s="454"/>
-      <c r="C176" s="482"/>
+      <c r="C176" s="487"/>
       <c r="D176" s="304"/>
       <c r="E176" s="137"/>
       <c r="F176" s="247"/>
@@ -23625,11 +24081,12 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
+      <c r="AR176" s="499"/>
     </row>
-    <row r="177" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
       <c r="B177" s="454"/>
-      <c r="C177" s="482"/>
+      <c r="C177" s="487"/>
       <c r="D177" s="304"/>
       <c r="E177" s="137"/>
       <c r="F177" s="247"/>
@@ -23714,11 +24171,12 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
+      <c r="AR177" s="499"/>
     </row>
-    <row r="178" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
       <c r="B178" s="454"/>
-      <c r="C178" s="482"/>
+      <c r="C178" s="487"/>
       <c r="D178" s="304"/>
       <c r="E178" s="138"/>
       <c r="F178" s="248"/>
@@ -23801,15 +24259,16 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
+      <c r="AR178" s="499"/>
     </row>
-    <row r="179" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A179" s="457" t="s">
         <v>888</v>
       </c>
       <c r="B179" s="454" t="s">
         <v>944</v>
       </c>
-      <c r="C179" s="482"/>
+      <c r="C179" s="487"/>
       <c r="D179" s="304" t="s">
         <v>743</v>
       </c>
@@ -23924,11 +24383,14 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
+      <c r="AR179" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="180" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A180" s="457"/>
       <c r="B180" s="454"/>
-      <c r="C180" s="482"/>
+      <c r="C180" s="487"/>
       <c r="D180" s="304"/>
       <c r="E180" s="137"/>
       <c r="F180" s="247"/>
@@ -24009,11 +24471,12 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
+      <c r="AR180" s="499"/>
     </row>
-    <row r="181" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
       <c r="B181" s="454"/>
-      <c r="C181" s="482"/>
+      <c r="C181" s="487"/>
       <c r="D181" s="304"/>
       <c r="E181" s="137"/>
       <c r="F181" s="247"/>
@@ -24094,11 +24557,12 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
+      <c r="AR181" s="499"/>
     </row>
-    <row r="182" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
       <c r="B182" s="454"/>
-      <c r="C182" s="482"/>
+      <c r="C182" s="487"/>
       <c r="D182" s="304"/>
       <c r="E182" s="137"/>
       <c r="F182" s="247"/>
@@ -24179,11 +24643,12 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
+      <c r="AR182" s="499"/>
     </row>
-    <row r="183" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
       <c r="B183" s="454"/>
-      <c r="C183" s="483"/>
+      <c r="C183" s="488"/>
       <c r="D183" s="317"/>
       <c r="E183" s="141"/>
       <c r="F183" s="249"/>
@@ -24264,15 +24729,16 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
+      <c r="AR183" s="499"/>
     </row>
-    <row r="184" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="457" t="s">
         <v>889</v>
       </c>
       <c r="B184" s="454">
         <v>831</v>
       </c>
-      <c r="C184" s="481">
+      <c r="C184" s="486">
         <v>83</v>
       </c>
       <c r="D184" s="304" t="s">
@@ -24389,11 +24855,14 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
+      <c r="AR184" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="185" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A185" s="457"/>
       <c r="B185" s="454"/>
-      <c r="C185" s="482"/>
+      <c r="C185" s="487"/>
       <c r="D185" s="304"/>
       <c r="E185" s="137"/>
       <c r="F185" s="247"/>
@@ -24476,11 +24945,12 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
+      <c r="AR185" s="499"/>
     </row>
-    <row r="186" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
       <c r="B186" s="454"/>
-      <c r="C186" s="482"/>
+      <c r="C186" s="487"/>
       <c r="D186" s="304"/>
       <c r="E186" s="137"/>
       <c r="F186" s="247"/>
@@ -24561,11 +25031,12 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
+      <c r="AR186" s="499"/>
     </row>
-    <row r="187" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
       <c r="B187" s="454"/>
-      <c r="C187" s="482"/>
+      <c r="C187" s="487"/>
       <c r="D187" s="304"/>
       <c r="E187" s="138"/>
       <c r="F187" s="248"/>
@@ -24648,15 +25119,16 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
+      <c r="AR187" s="499"/>
     </row>
-    <row r="188" spans="1:43" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="457" t="s">
         <v>889</v>
       </c>
       <c r="B188" s="454" t="s">
         <v>945</v>
       </c>
-      <c r="C188" s="482"/>
+      <c r="C188" s="487"/>
       <c r="D188" s="304" t="s">
         <v>743</v>
       </c>
@@ -24769,11 +25241,14 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
+      <c r="AR188" s="499" t="s">
+        <v>978</v>
+      </c>
     </row>
-    <row r="189" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A189" s="457"/>
       <c r="B189" s="454"/>
-      <c r="C189" s="482"/>
+      <c r="C189" s="487"/>
       <c r="D189" s="304"/>
       <c r="E189" s="137"/>
       <c r="F189" s="247"/>
@@ -24854,11 +25329,12 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
+      <c r="AR189" s="499"/>
     </row>
-    <row r="190" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
       <c r="B190" s="454"/>
-      <c r="C190" s="482"/>
+      <c r="C190" s="487"/>
       <c r="D190" s="304"/>
       <c r="E190" s="137"/>
       <c r="F190" s="247"/>
@@ -24939,11 +25415,12 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
+      <c r="AR190" s="499"/>
     </row>
-    <row r="191" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
       <c r="B191" s="454"/>
-      <c r="C191" s="483"/>
+      <c r="C191" s="488"/>
       <c r="D191" s="317"/>
       <c r="E191" s="141"/>
       <c r="F191" s="249"/>
@@ -25022,15 +25499,16 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
+      <c r="AR191" s="499"/>
     </row>
-    <row r="192" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="457" t="s">
         <v>890</v>
       </c>
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="484">
+      <c r="C192" s="518">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25145,11 +25623,14 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
+      <c r="AR192" s="499" t="s">
+        <v>979</v>
+      </c>
     </row>
-    <row r="193" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="485"/>
+      <c r="C193" s="519"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -25230,11 +25711,12 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
+      <c r="AR193" s="499"/>
     </row>
-    <row r="194" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="485"/>
+      <c r="C194" s="519"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -25315,11 +25797,12 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
+      <c r="AR194" s="499"/>
     </row>
-    <row r="195" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="485"/>
+      <c r="C195" s="519"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -25400,15 +25883,16 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
+      <c r="AR195" s="499"/>
     </row>
-    <row r="196" spans="1:43" ht="63.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:44" ht="63.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="457" t="s">
         <v>890</v>
       </c>
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="485"/>
+      <c r="C196" s="519"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -25521,11 +26005,14 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
+      <c r="AR196" s="499" t="s">
+        <v>979</v>
+      </c>
     </row>
-    <row r="197" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="485"/>
+      <c r="C197" s="519"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -25606,11 +26093,12 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
+      <c r="AR197" s="499"/>
     </row>
-    <row r="198" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="485"/>
+      <c r="C198" s="519"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -25691,11 +26179,12 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
+      <c r="AR198" s="499"/>
     </row>
-    <row r="199" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="486"/>
+      <c r="C199" s="520"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -25776,15 +26265,16 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
+      <c r="AR199" s="499"/>
     </row>
-    <row r="200" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="457" t="s">
         <v>891</v>
       </c>
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="469">
+      <c r="C200" s="521">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -25903,11 +26393,14 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
+      <c r="AR200" s="499" t="s">
+        <v>980</v>
+      </c>
     </row>
-    <row r="201" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="470"/>
+      <c r="C201" s="522"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -25992,11 +26485,12 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
+      <c r="AR201" s="499"/>
     </row>
-    <row r="202" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="470"/>
+      <c r="C202" s="522"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26079,15 +26573,16 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
+      <c r="AR202" s="499"/>
     </row>
-    <row r="203" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A203" s="457" t="s">
         <v>891</v>
       </c>
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="470"/>
+      <c r="C203" s="522"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -26206,11 +26701,14 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
+      <c r="AR203" s="499" t="s">
+        <v>980</v>
+      </c>
     </row>
-    <row r="204" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="470"/>
+      <c r="C204" s="522"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -26295,11 +26793,12 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
+      <c r="AR204" s="499"/>
     </row>
-    <row r="205" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="470"/>
+      <c r="C205" s="522"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -26382,15 +26881,16 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
+      <c r="AR205" s="499"/>
     </row>
-    <row r="206" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A206" s="457" t="s">
         <v>891</v>
       </c>
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="470"/>
+      <c r="C206" s="522"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -26509,11 +27009,14 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
+      <c r="AR206" s="499" t="s">
+        <v>980</v>
+      </c>
     </row>
-    <row r="207" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="470"/>
+      <c r="C207" s="522"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -26594,11 +27097,12 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
+      <c r="AR207" s="499"/>
     </row>
-    <row r="208" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="471"/>
+      <c r="C208" s="523"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -26683,15 +27187,16 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
+      <c r="AR208" s="499"/>
     </row>
-    <row r="209" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="457" t="s">
         <v>892</v>
       </c>
       <c r="B209" s="454" t="s">
         <v>951</v>
       </c>
-      <c r="C209" s="469">
+      <c r="C209" s="477">
         <v>101</v>
       </c>
       <c r="D209" s="306" t="s">
@@ -26812,11 +27317,14 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
+      <c r="AR209" s="499" t="s">
+        <v>980</v>
+      </c>
     </row>
-    <row r="210" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A210" s="457"/>
       <c r="B210" s="454"/>
-      <c r="C210" s="470"/>
+      <c r="C210" s="478"/>
       <c r="D210" s="306"/>
       <c r="E210" s="163"/>
       <c r="F210" s="253"/>
@@ -26901,11 +27409,12 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
+      <c r="AR210" s="499"/>
     </row>
-    <row r="211" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
       <c r="B211" s="454"/>
-      <c r="C211" s="470"/>
+      <c r="C211" s="478"/>
       <c r="D211" s="306"/>
       <c r="E211" s="163"/>
       <c r="F211" s="253"/>
@@ -26990,11 +27499,12 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
+      <c r="AR211" s="499"/>
     </row>
-    <row r="212" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
       <c r="B212" s="454"/>
-      <c r="C212" s="470"/>
+      <c r="C212" s="478"/>
       <c r="D212" s="306"/>
       <c r="E212" s="164"/>
       <c r="F212" s="254"/>
@@ -27077,15 +27587,16 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
+      <c r="AR212" s="499"/>
     </row>
-    <row r="213" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A213" s="457" t="s">
         <v>892</v>
       </c>
       <c r="B213" s="454" t="s">
         <v>952</v>
       </c>
-      <c r="C213" s="470"/>
+      <c r="C213" s="478"/>
       <c r="D213" s="306" t="s">
         <v>745</v>
       </c>
@@ -27204,11 +27715,14 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
+      <c r="AR213" s="499" t="s">
+        <v>980</v>
+      </c>
     </row>
-    <row r="214" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A214" s="457"/>
       <c r="B214" s="454"/>
-      <c r="C214" s="470"/>
+      <c r="C214" s="478"/>
       <c r="D214" s="306"/>
       <c r="E214" s="163"/>
       <c r="F214" s="253"/>
@@ -27293,11 +27807,12 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
+      <c r="AR214" s="499"/>
     </row>
-    <row r="215" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
       <c r="B215" s="454"/>
-      <c r="C215" s="471"/>
+      <c r="C215" s="479"/>
       <c r="D215" s="319"/>
       <c r="E215" s="166"/>
       <c r="F215" s="255"/>
@@ -27382,15 +27897,16 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
+      <c r="AR215" s="499"/>
     </row>
-    <row r="216" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="457" t="s">
         <v>893</v>
       </c>
       <c r="B216" s="454" t="s">
         <v>953</v>
       </c>
-      <c r="C216" s="459">
+      <c r="C216" s="489">
         <v>102</v>
       </c>
       <c r="D216" s="307" t="s">
@@ -27511,11 +28027,14 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
+      <c r="AR216" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="217" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A217" s="457"/>
       <c r="B217" s="454"/>
-      <c r="C217" s="460"/>
+      <c r="C217" s="490"/>
       <c r="D217" s="307"/>
       <c r="E217" s="174"/>
       <c r="F217" s="256"/>
@@ -27600,11 +28119,12 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
+      <c r="AR217" s="499"/>
     </row>
-    <row r="218" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
       <c r="B218" s="454"/>
-      <c r="C218" s="460"/>
+      <c r="C218" s="490"/>
       <c r="D218" s="307"/>
       <c r="E218" s="174"/>
       <c r="F218" s="256"/>
@@ -27689,11 +28209,12 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
+      <c r="AR218" s="499"/>
     </row>
-    <row r="219" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
       <c r="B219" s="454"/>
-      <c r="C219" s="461"/>
+      <c r="C219" s="491"/>
       <c r="D219" s="320"/>
       <c r="E219" s="175"/>
       <c r="F219" s="257"/>
@@ -27778,15 +28299,16 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
+      <c r="AR219" s="499"/>
     </row>
-    <row r="220" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="457" t="s">
         <v>894</v>
       </c>
       <c r="B220" s="454" t="s">
         <v>954</v>
       </c>
-      <c r="C220" s="459">
+      <c r="C220" s="489">
         <v>103</v>
       </c>
       <c r="D220" s="307" t="s">
@@ -27903,11 +28425,14 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
+      <c r="AR220" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="221" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A221" s="457"/>
       <c r="B221" s="454"/>
-      <c r="C221" s="460"/>
+      <c r="C221" s="490"/>
       <c r="D221" s="307"/>
       <c r="E221" s="174"/>
       <c r="F221" s="256"/>
@@ -27990,11 +28515,12 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
+      <c r="AR221" s="499"/>
     </row>
-    <row r="222" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
       <c r="B222" s="454"/>
-      <c r="C222" s="460"/>
+      <c r="C222" s="490"/>
       <c r="D222" s="307"/>
       <c r="E222" s="178"/>
       <c r="F222" s="258"/>
@@ -28077,15 +28603,16 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
+      <c r="AR222" s="499"/>
     </row>
-    <row r="223" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A223" s="457" t="s">
         <v>894</v>
       </c>
       <c r="B223" s="454" t="s">
         <v>955</v>
       </c>
-      <c r="C223" s="460"/>
+      <c r="C223" s="490"/>
       <c r="D223" s="307" t="s">
         <v>745</v>
       </c>
@@ -28204,11 +28731,14 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
+      <c r="AR223" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="224" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A224" s="457"/>
       <c r="B224" s="454"/>
-      <c r="C224" s="460"/>
+      <c r="C224" s="490"/>
       <c r="D224" s="307"/>
       <c r="E224" s="174"/>
       <c r="F224" s="256"/>
@@ -28293,11 +28823,12 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
+      <c r="AR224" s="499"/>
     </row>
-    <row r="225" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
       <c r="B225" s="454"/>
-      <c r="C225" s="460"/>
+      <c r="C225" s="490"/>
       <c r="D225" s="307"/>
       <c r="E225" s="174"/>
       <c r="F225" s="256"/>
@@ -28382,11 +28913,12 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
+      <c r="AR225" s="499"/>
     </row>
-    <row r="226" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
       <c r="B226" s="454"/>
-      <c r="C226" s="461"/>
+      <c r="C226" s="491"/>
       <c r="D226" s="320"/>
       <c r="E226" s="175"/>
       <c r="F226" s="257"/>
@@ -28465,15 +28997,16 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
+      <c r="AR226" s="499"/>
     </row>
-    <row r="227" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="457" t="s">
         <v>895</v>
       </c>
       <c r="B227" s="454" t="s">
         <v>956</v>
       </c>
-      <c r="C227" s="459">
+      <c r="C227" s="489">
         <v>104</v>
       </c>
       <c r="D227" s="307" t="s">
@@ -28590,11 +29123,14 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
+      <c r="AR227" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="228" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A228" s="457"/>
       <c r="B228" s="454"/>
-      <c r="C228" s="460"/>
+      <c r="C228" s="490"/>
       <c r="D228" s="307"/>
       <c r="E228" s="174"/>
       <c r="F228" s="256"/>
@@ -28675,11 +29211,12 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
+      <c r="AR228" s="499"/>
     </row>
-    <row r="229" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
       <c r="B229" s="454"/>
-      <c r="C229" s="460"/>
+      <c r="C229" s="490"/>
       <c r="D229" s="307"/>
       <c r="E229" s="174"/>
       <c r="F229" s="256"/>
@@ -28760,11 +29297,12 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
+      <c r="AR229" s="499"/>
     </row>
-    <row r="230" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
       <c r="B230" s="454"/>
-      <c r="C230" s="460"/>
+      <c r="C230" s="490"/>
       <c r="D230" s="307"/>
       <c r="E230" s="178"/>
       <c r="F230" s="258"/>
@@ -28845,15 +29383,16 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
+      <c r="AR230" s="499"/>
     </row>
-    <row r="231" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A231" s="457" t="s">
         <v>895</v>
       </c>
       <c r="B231" s="454" t="s">
         <v>957</v>
       </c>
-      <c r="C231" s="460"/>
+      <c r="C231" s="490"/>
       <c r="D231" s="307" t="s">
         <v>745</v>
       </c>
@@ -28968,11 +29507,14 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
+      <c r="AR231" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="232" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A232" s="457"/>
       <c r="B232" s="454"/>
-      <c r="C232" s="460"/>
+      <c r="C232" s="490"/>
       <c r="D232" s="307"/>
       <c r="E232" s="174"/>
       <c r="F232" s="256"/>
@@ -29053,11 +29595,12 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
+      <c r="AR232" s="499"/>
     </row>
-    <row r="233" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
       <c r="B233" s="454"/>
-      <c r="C233" s="460"/>
+      <c r="C233" s="490"/>
       <c r="D233" s="307"/>
       <c r="E233" s="174"/>
       <c r="F233" s="256"/>
@@ -29138,11 +29681,12 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
+      <c r="AR233" s="499"/>
     </row>
-    <row r="234" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
       <c r="B234" s="454"/>
-      <c r="C234" s="461"/>
+      <c r="C234" s="491"/>
       <c r="D234" s="320"/>
       <c r="E234" s="175"/>
       <c r="F234" s="257"/>
@@ -29219,15 +29763,16 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
+      <c r="AR234" s="499"/>
     </row>
-    <row r="235" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="457" t="s">
         <v>896</v>
       </c>
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="465">
+      <c r="C235" s="524">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -29344,11 +29889,14 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
+      <c r="AR235" s="499" t="s">
+        <v>982</v>
+      </c>
     </row>
-    <row r="236" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="466"/>
+      <c r="C236" s="525"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -29429,11 +29977,12 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
+      <c r="AR236" s="499"/>
     </row>
-    <row r="237" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="466"/>
+      <c r="C237" s="525"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -29514,11 +30063,12 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
+      <c r="AR237" s="499"/>
     </row>
-    <row r="238" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="467"/>
+      <c r="C238" s="526"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -29597,15 +30147,16 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
+      <c r="AR238" s="499"/>
     </row>
-    <row r="239" spans="1:43" ht="56.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:44" ht="56.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="457" t="s">
         <v>897</v>
       </c>
       <c r="B239" s="454" t="s">
         <v>959</v>
       </c>
-      <c r="C239" s="465">
+      <c r="C239" s="495">
         <v>106</v>
       </c>
       <c r="D239" s="308" t="s">
@@ -29722,11 +30273,14 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
+      <c r="AR239" s="499" t="s">
+        <v>982</v>
+      </c>
     </row>
-    <row r="240" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A240" s="457"/>
       <c r="B240" s="454"/>
-      <c r="C240" s="466"/>
+      <c r="C240" s="496"/>
       <c r="D240" s="308"/>
       <c r="E240" s="185"/>
       <c r="F240" s="259"/>
@@ -29807,11 +30361,12 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
+      <c r="AR240" s="499"/>
     </row>
-    <row r="241" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
       <c r="B241" s="454"/>
-      <c r="C241" s="466"/>
+      <c r="C241" s="496"/>
       <c r="D241" s="308"/>
       <c r="E241" s="185"/>
       <c r="F241" s="259"/>
@@ -29892,11 +30447,12 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
+      <c r="AR241" s="499"/>
     </row>
-    <row r="242" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
       <c r="B242" s="454"/>
-      <c r="C242" s="466"/>
+      <c r="C242" s="496"/>
       <c r="D242" s="308"/>
       <c r="E242" s="189"/>
       <c r="F242" s="261"/>
@@ -29975,15 +30531,16 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
+      <c r="AR242" s="499"/>
     </row>
-    <row r="243" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A243" s="457" t="s">
         <v>897</v>
       </c>
       <c r="B243" s="454" t="s">
         <v>960</v>
       </c>
-      <c r="C243" s="466"/>
+      <c r="C243" s="496"/>
       <c r="D243" s="308" t="s">
         <v>745</v>
       </c>
@@ -30098,11 +30655,14 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
+      <c r="AR243" s="499" t="s">
+        <v>982</v>
+      </c>
     </row>
-    <row r="244" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A244" s="457"/>
       <c r="B244" s="454"/>
-      <c r="C244" s="466"/>
+      <c r="C244" s="496"/>
       <c r="D244" s="308"/>
       <c r="E244" s="185"/>
       <c r="F244" s="259"/>
@@ -30183,11 +30743,12 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
+      <c r="AR244" s="499"/>
     </row>
-    <row r="245" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
       <c r="B245" s="454"/>
-      <c r="C245" s="466"/>
+      <c r="C245" s="496"/>
       <c r="D245" s="308"/>
       <c r="E245" s="185"/>
       <c r="F245" s="259"/>
@@ -30268,11 +30829,12 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
+      <c r="AR245" s="499"/>
     </row>
-    <row r="246" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
       <c r="B246" s="454"/>
-      <c r="C246" s="466"/>
+      <c r="C246" s="496"/>
       <c r="D246" s="308"/>
       <c r="E246" s="185"/>
       <c r="F246" s="259"/>
@@ -30353,11 +30915,12 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
+      <c r="AR246" s="499"/>
     </row>
-    <row r="247" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
       <c r="B247" s="454"/>
-      <c r="C247" s="466"/>
+      <c r="C247" s="496"/>
       <c r="D247" s="308"/>
       <c r="E247" s="181"/>
       <c r="F247" s="181"/>
@@ -30444,15 +31007,18 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
+      <c r="AR247" s="499" t="s">
+        <v>982</v>
+      </c>
     </row>
-    <row r="248" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A248" s="457" t="s">
         <v>897</v>
       </c>
       <c r="B248" s="454" t="s">
         <v>961</v>
       </c>
-      <c r="C248" s="468"/>
+      <c r="C248" s="498"/>
       <c r="D248" s="308" t="s">
         <v>745</v>
       </c>
@@ -30561,11 +31127,12 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
+      <c r="AR248" s="499"/>
     </row>
-    <row r="249" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
       <c r="B249" s="454"/>
-      <c r="C249" s="466"/>
+      <c r="C249" s="496"/>
       <c r="D249" s="308"/>
       <c r="E249" s="185"/>
       <c r="F249" s="259"/>
@@ -30648,11 +31215,12 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
+      <c r="AR249" s="499"/>
     </row>
-    <row r="250" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
       <c r="B250" s="454"/>
-      <c r="C250" s="466"/>
+      <c r="C250" s="496"/>
       <c r="D250" s="308"/>
       <c r="E250" s="185"/>
       <c r="F250" s="259"/>
@@ -30735,11 +31303,12 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
+      <c r="AR250" s="499"/>
     </row>
-    <row r="251" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
       <c r="B251" s="454"/>
-      <c r="C251" s="466"/>
+      <c r="C251" s="496"/>
       <c r="D251" s="308"/>
       <c r="E251" s="189"/>
       <c r="F251" s="261"/>
@@ -30822,15 +31391,16 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
+      <c r="AR251" s="499"/>
     </row>
-    <row r="252" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A252" s="457" t="s">
         <v>897</v>
       </c>
       <c r="B252" s="454" t="s">
         <v>962</v>
       </c>
-      <c r="C252" s="466"/>
+      <c r="C252" s="496"/>
       <c r="D252" s="308" t="s">
         <v>745</v>
       </c>
@@ -30945,11 +31515,14 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
+      <c r="AR252" s="499" t="s">
+        <v>982</v>
+      </c>
     </row>
-    <row r="253" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A253" s="457"/>
       <c r="B253" s="454"/>
-      <c r="C253" s="466"/>
+      <c r="C253" s="496"/>
       <c r="D253" s="308"/>
       <c r="E253" s="185"/>
       <c r="F253" s="259"/>
@@ -31030,11 +31603,12 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
+      <c r="AR253" s="499"/>
     </row>
-    <row r="254" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
       <c r="B254" s="454"/>
-      <c r="C254" s="466"/>
+      <c r="C254" s="496"/>
       <c r="D254" s="308"/>
       <c r="E254" s="185"/>
       <c r="F254" s="259"/>
@@ -31115,11 +31689,12 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
+      <c r="AR254" s="499"/>
     </row>
-    <row r="255" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
       <c r="B255" s="454"/>
-      <c r="C255" s="466"/>
+      <c r="C255" s="496"/>
       <c r="D255" s="308"/>
       <c r="E255" s="185"/>
       <c r="F255" s="259"/>
@@ -31200,11 +31775,12 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
+      <c r="AR255" s="499"/>
     </row>
-    <row r="256" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
       <c r="B256" s="454"/>
-      <c r="C256" s="467"/>
+      <c r="C256" s="497"/>
       <c r="D256" s="321"/>
       <c r="E256" s="186"/>
       <c r="F256" s="260"/>
@@ -31285,15 +31861,16 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
+      <c r="AR256" s="499"/>
     </row>
-    <row r="257" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="457" t="s">
         <v>898</v>
       </c>
       <c r="B257" s="454" t="s">
         <v>963</v>
       </c>
-      <c r="C257" s="459">
+      <c r="C257" s="489">
         <v>107</v>
       </c>
       <c r="D257" s="307" t="s">
@@ -31410,11 +31987,14 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
+      <c r="AR257" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="258" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A258" s="457"/>
       <c r="B258" s="454"/>
-      <c r="C258" s="460"/>
+      <c r="C258" s="490"/>
       <c r="D258" s="307"/>
       <c r="E258" s="174"/>
       <c r="F258" s="256"/>
@@ -31497,11 +32077,12 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
+      <c r="AR258" s="499"/>
     </row>
-    <row r="259" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
       <c r="B259" s="454"/>
-      <c r="C259" s="460"/>
+      <c r="C259" s="490"/>
       <c r="D259" s="307"/>
       <c r="E259" s="174"/>
       <c r="F259" s="256"/>
@@ -31584,11 +32165,12 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
+      <c r="AR259" s="499"/>
     </row>
-    <row r="260" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
       <c r="B260" s="454"/>
-      <c r="C260" s="460"/>
+      <c r="C260" s="490"/>
       <c r="D260" s="307"/>
       <c r="E260" s="178"/>
       <c r="F260" s="258"/>
@@ -31669,15 +32251,16 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
+      <c r="AR260" s="499"/>
     </row>
-    <row r="261" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="457" t="s">
         <v>898</v>
       </c>
       <c r="B261" s="454" t="s">
         <v>964</v>
       </c>
-      <c r="C261" s="460"/>
+      <c r="C261" s="490"/>
       <c r="D261" s="307" t="s">
         <v>745</v>
       </c>
@@ -31792,11 +32375,14 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
+      <c r="AR261" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="262" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A262" s="457"/>
       <c r="B262" s="454"/>
-      <c r="C262" s="460"/>
+      <c r="C262" s="490"/>
       <c r="D262" s="307"/>
       <c r="E262" s="174"/>
       <c r="F262" s="256"/>
@@ -31875,11 +32461,12 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
+      <c r="AR262" s="499"/>
     </row>
-    <row r="263" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
       <c r="B263" s="454"/>
-      <c r="C263" s="461"/>
+      <c r="C263" s="491"/>
       <c r="D263" s="320"/>
       <c r="E263" s="175"/>
       <c r="F263" s="257"/>
@@ -31958,15 +32545,16 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
+      <c r="AR263" s="499"/>
     </row>
-    <row r="264" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="457" t="s">
         <v>899</v>
       </c>
       <c r="B264" s="454" t="s">
         <v>965</v>
       </c>
-      <c r="C264" s="459">
+      <c r="C264" s="489">
         <v>108</v>
       </c>
       <c r="D264" s="307" t="s">
@@ -32085,11 +32673,14 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
+      <c r="AR264" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="265" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A265" s="457"/>
       <c r="B265" s="454"/>
-      <c r="C265" s="460"/>
+      <c r="C265" s="490"/>
       <c r="D265" s="307"/>
       <c r="E265" s="174"/>
       <c r="F265" s="256"/>
@@ -32172,11 +32763,12 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
+      <c r="AR265" s="499"/>
     </row>
-    <row r="266" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
       <c r="B266" s="454"/>
-      <c r="C266" s="460"/>
+      <c r="C266" s="490"/>
       <c r="D266" s="307"/>
       <c r="E266" s="174"/>
       <c r="F266" s="256"/>
@@ -32259,11 +32851,12 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
+      <c r="AR266" s="499"/>
     </row>
-    <row r="267" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
       <c r="B267" s="454"/>
-      <c r="C267" s="461"/>
+      <c r="C267" s="491"/>
       <c r="D267" s="320"/>
       <c r="E267" s="175"/>
       <c r="F267" s="257"/>
@@ -32346,15 +32939,16 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
+      <c r="AR267" s="499"/>
     </row>
-    <row r="268" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="457" t="s">
         <v>900</v>
       </c>
       <c r="B268" s="454" t="s">
         <v>966</v>
       </c>
-      <c r="C268" s="459">
+      <c r="C268" s="489">
         <v>109</v>
       </c>
       <c r="D268" s="307" t="s">
@@ -32475,11 +33069,14 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
+      <c r="AR268" s="499" t="s">
+        <v>981</v>
+      </c>
     </row>
-    <row r="269" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A269" s="457"/>
       <c r="B269" s="454"/>
-      <c r="C269" s="460"/>
+      <c r="C269" s="490"/>
       <c r="D269" s="307"/>
       <c r="E269" s="174"/>
       <c r="F269" s="256"/>
@@ -32564,11 +33161,12 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
+      <c r="AR269" s="499"/>
     </row>
-    <row r="270" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
       <c r="B270" s="454"/>
-      <c r="C270" s="461"/>
+      <c r="C270" s="491"/>
       <c r="D270" s="320"/>
       <c r="E270" s="175"/>
       <c r="F270" s="257"/>
@@ -32653,15 +33251,16 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
+      <c r="AR270" s="499"/>
     </row>
-    <row r="271" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="457" t="s">
         <v>862</v>
       </c>
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="462">
+      <c r="C271" s="527">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -32782,11 +33381,14 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
+      <c r="AR271" s="499" t="s">
+        <v>983</v>
+      </c>
     </row>
-    <row r="272" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="463"/>
+      <c r="C272" s="528"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -32869,11 +33471,12 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
+      <c r="AR272" s="499"/>
     </row>
-    <row r="273" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="463"/>
+      <c r="C273" s="528"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -32956,15 +33559,16 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
+      <c r="AR273" s="499"/>
     </row>
-    <row r="274" spans="1:43" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:44" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="457" t="s">
         <v>862</v>
       </c>
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="463"/>
+      <c r="C274" s="528"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -33075,11 +33679,14 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
+      <c r="AR274" s="499" t="s">
+        <v>983</v>
+      </c>
     </row>
-    <row r="275" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="463"/>
+      <c r="C275" s="528"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -33168,11 +33775,12 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
+      <c r="AR275" s="499"/>
     </row>
-    <row r="276" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="463"/>
+      <c r="C276" s="528"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -33255,11 +33863,12 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
+      <c r="AR276" s="499"/>
     </row>
-    <row r="277" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="464"/>
+      <c r="C277" s="529"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -33342,15 +33951,16 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
+      <c r="AR277" s="499"/>
     </row>
-    <row r="278" spans="1:43" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="457" t="s">
         <v>901</v>
       </c>
       <c r="B278" s="454" t="s">
         <v>969</v>
       </c>
-      <c r="C278" s="462">
+      <c r="C278" s="492">
         <v>112</v>
       </c>
       <c r="D278" s="309" t="s">
@@ -33467,11 +34077,14 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
+      <c r="AR278" s="499" t="s">
+        <v>983</v>
+      </c>
     </row>
-    <row r="279" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A279" s="457"/>
       <c r="B279" s="454"/>
-      <c r="C279" s="463"/>
+      <c r="C279" s="493"/>
       <c r="D279" s="309"/>
       <c r="E279" s="197"/>
       <c r="F279" s="262"/>
@@ -33552,11 +34165,12 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
+      <c r="AR279" s="499"/>
     </row>
-    <row r="280" spans="1:43" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
       <c r="B280" s="454"/>
-      <c r="C280" s="463"/>
+      <c r="C280" s="493"/>
       <c r="D280" s="309"/>
       <c r="E280" s="197"/>
       <c r="F280" s="262"/>
@@ -33637,11 +34251,12 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
+      <c r="AR280" s="499"/>
     </row>
-    <row r="281" spans="1:43" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
       <c r="B281" s="455"/>
-      <c r="C281" s="464"/>
+      <c r="C281" s="494"/>
       <c r="D281" s="322"/>
       <c r="E281" s="201"/>
       <c r="F281" s="264"/>
@@ -33722,15 +34337,102 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
+      <c r="AR281" s="499"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="C13:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C30"/>
+  <mergeCells count="110">
+    <mergeCell ref="AR264:AR267"/>
+    <mergeCell ref="AR268:AR270"/>
+    <mergeCell ref="AR271:AR273"/>
+    <mergeCell ref="AR274:AR277"/>
+    <mergeCell ref="AR278:AR281"/>
+    <mergeCell ref="AR243:AR246"/>
+    <mergeCell ref="AR247:AR251"/>
+    <mergeCell ref="AR252:AR256"/>
+    <mergeCell ref="AR257:AR260"/>
+    <mergeCell ref="AR261:AR263"/>
+    <mergeCell ref="AR223:AR226"/>
+    <mergeCell ref="AR227:AR230"/>
+    <mergeCell ref="AR231:AR234"/>
+    <mergeCell ref="AR235:AR238"/>
+    <mergeCell ref="AR239:AR242"/>
+    <mergeCell ref="AR206:AR208"/>
+    <mergeCell ref="AR209:AR212"/>
+    <mergeCell ref="AR213:AR215"/>
+    <mergeCell ref="AR216:AR219"/>
+    <mergeCell ref="AR220:AR222"/>
+    <mergeCell ref="AR188:AR191"/>
+    <mergeCell ref="AR192:AR195"/>
+    <mergeCell ref="AR196:AR199"/>
+    <mergeCell ref="AR200:AR202"/>
+    <mergeCell ref="AR203:AR205"/>
+    <mergeCell ref="AR167:AR170"/>
+    <mergeCell ref="AR171:AR174"/>
+    <mergeCell ref="AR175:AR178"/>
+    <mergeCell ref="AR179:AR183"/>
+    <mergeCell ref="AR184:AR187"/>
+    <mergeCell ref="AR146:AR149"/>
+    <mergeCell ref="AR150:AR153"/>
+    <mergeCell ref="AR154:AR158"/>
+    <mergeCell ref="AR159:AR162"/>
+    <mergeCell ref="AR163:AR166"/>
+    <mergeCell ref="AR123:AR127"/>
+    <mergeCell ref="AR128:AR131"/>
+    <mergeCell ref="AR132:AR135"/>
+    <mergeCell ref="AR136:AR140"/>
+    <mergeCell ref="AR141:AR145"/>
+    <mergeCell ref="AR102:AR105"/>
+    <mergeCell ref="AR106:AR109"/>
+    <mergeCell ref="AR110:AR114"/>
+    <mergeCell ref="AR115:AR118"/>
+    <mergeCell ref="AR119:AR122"/>
+    <mergeCell ref="AR83:AR85"/>
+    <mergeCell ref="AR86:AR89"/>
+    <mergeCell ref="AR90:AR93"/>
+    <mergeCell ref="AR94:AR97"/>
+    <mergeCell ref="AR98:AR101"/>
+    <mergeCell ref="AR64:AR66"/>
+    <mergeCell ref="AR67:AR69"/>
+    <mergeCell ref="AR70:AR74"/>
+    <mergeCell ref="AR75:AR79"/>
+    <mergeCell ref="AR80:AR82"/>
+    <mergeCell ref="AR44:AR46"/>
+    <mergeCell ref="AR47:AR50"/>
+    <mergeCell ref="AR51:AR54"/>
+    <mergeCell ref="AR55:AR59"/>
+    <mergeCell ref="AR60:AR63"/>
+    <mergeCell ref="AR23:AR25"/>
+    <mergeCell ref="AR26:AR30"/>
+    <mergeCell ref="AR31:AR34"/>
+    <mergeCell ref="AR35:AR38"/>
+    <mergeCell ref="AR39:AR43"/>
+    <mergeCell ref="AR2:AR4"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AR9:AR12"/>
+    <mergeCell ref="AR13:AR17"/>
+    <mergeCell ref="AR18:AR22"/>
+    <mergeCell ref="C264:C267"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="C271:C277"/>
+    <mergeCell ref="C278:C281"/>
+    <mergeCell ref="C216:C219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="C235:C238"/>
+    <mergeCell ref="C239:C256"/>
+    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C209:C215"/>
+    <mergeCell ref="C106:C114"/>
+    <mergeCell ref="C115:C122"/>
+    <mergeCell ref="C123:C131"/>
+    <mergeCell ref="C132:C140"/>
+    <mergeCell ref="C141:C149"/>
+    <mergeCell ref="C150:C158"/>
+    <mergeCell ref="C159:C170"/>
+    <mergeCell ref="C171:C183"/>
+    <mergeCell ref="C184:C191"/>
+    <mergeCell ref="C192:C199"/>
+    <mergeCell ref="C200:C208"/>
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="C35:C43"/>
     <mergeCell ref="C44:C46"/>
@@ -33743,29 +34445,14 @@
     <mergeCell ref="C83:C85"/>
     <mergeCell ref="C86:C97"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C209:C215"/>
-    <mergeCell ref="C106:C114"/>
-    <mergeCell ref="C115:C122"/>
-    <mergeCell ref="C123:C131"/>
-    <mergeCell ref="C132:C140"/>
-    <mergeCell ref="C141:C149"/>
-    <mergeCell ref="C150:C158"/>
-    <mergeCell ref="C159:C170"/>
-    <mergeCell ref="C171:C183"/>
-    <mergeCell ref="C184:C191"/>
-    <mergeCell ref="C192:C199"/>
-    <mergeCell ref="C200:C208"/>
-    <mergeCell ref="C264:C267"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="C271:C277"/>
-    <mergeCell ref="C278:C281"/>
-    <mergeCell ref="C216:C219"/>
-    <mergeCell ref="C220:C226"/>
-    <mergeCell ref="C227:C234"/>
-    <mergeCell ref="C235:C238"/>
-    <mergeCell ref="C239:C256"/>
-    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="C13:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C30"/>
   </mergeCells>
+  <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01187956-5FA0-43A1-951A-50CC400DDC9E}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98CFB26-F101-454F-8A17-8FDA2B528115}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="985">
   <si>
     <t>NOM MATERIAU PARENTAL</t>
   </si>
@@ -3624,6 +3624,9 @@
   </si>
   <si>
     <t>#339966</t>
+  </si>
+  <si>
+    <t>#339967</t>
   </si>
 </sst>
 </file>
@@ -5761,9 +5764,6 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5854,6 +5854,7 @@
     <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7285,7 +7286,7 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
-      <c r="AR2" s="499" t="s">
+      <c r="AR2" s="529" t="s">
         <v>971</v>
       </c>
     </row>
@@ -7377,7 +7378,9 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
-      <c r="AR3" s="499"/>
+      <c r="AR3" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
@@ -7467,7 +7470,9 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
-      <c r="AR4" s="499"/>
+      <c r="AR4" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="5" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="457" t="s">
@@ -7595,7 +7600,7 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
-      <c r="AR5" s="499" t="s">
+      <c r="AR5" s="529" t="s">
         <v>971</v>
       </c>
     </row>
@@ -7685,7 +7690,9 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
-      <c r="AR6" s="499"/>
+      <c r="AR6" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
@@ -7773,7 +7780,9 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
-      <c r="AR7" s="499"/>
+      <c r="AR7" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
@@ -7859,7 +7868,9 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
-      <c r="AR8" s="499"/>
+      <c r="AR8" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="9" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="457" t="s">
@@ -7983,7 +7994,7 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
-      <c r="AR9" s="499" t="s">
+      <c r="AR9" s="529" t="s">
         <v>971</v>
       </c>
     </row>
@@ -8071,7 +8082,9 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
-      <c r="AR10" s="499"/>
+      <c r="AR10" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
@@ -8157,7 +8170,9 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
-      <c r="AR11" s="499"/>
+      <c r="AR11" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
@@ -8241,7 +8256,9 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
-      <c r="AR12" s="499"/>
+      <c r="AR12" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="13" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="457" t="s">
@@ -8367,7 +8384,7 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
-      <c r="AR13" s="499" t="s">
+      <c r="AR13" s="529" t="s">
         <v>971</v>
       </c>
     </row>
@@ -8455,7 +8472,9 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
-      <c r="AR14" s="499"/>
+      <c r="AR14" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
@@ -8541,7 +8560,9 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
-      <c r="AR15" s="499"/>
+      <c r="AR15" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
@@ -8627,7 +8648,9 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
-      <c r="AR16" s="499"/>
+      <c r="AR16" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
@@ -8711,7 +8734,9 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
-      <c r="AR17" s="499"/>
+      <c r="AR17" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="18" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="457" t="s">
@@ -8833,7 +8858,7 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
-      <c r="AR18" s="499" t="s">
+      <c r="AR18" s="529" t="s">
         <v>971</v>
       </c>
     </row>
@@ -8921,7 +8946,9 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
-      <c r="AR19" s="499"/>
+      <c r="AR19" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
@@ -9007,7 +9034,9 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
-      <c r="AR20" s="499"/>
+      <c r="AR20" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
@@ -9093,7 +9122,9 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
-      <c r="AR21" s="499"/>
+      <c r="AR21" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
@@ -9179,7 +9210,9 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" s="499"/>
+      <c r="AR22" s="529" t="s">
+        <v>971</v>
+      </c>
     </row>
     <row r="23" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="457" t="s">
@@ -9188,7 +9221,7 @@
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="500">
+      <c r="C23" s="499">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9309,14 +9342,14 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
-      <c r="AR23" s="499" t="s">
+      <c r="AR23" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="501"/>
+      <c r="C24" s="500"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9401,12 +9434,14 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
-      <c r="AR24" s="499"/>
+      <c r="AR24" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="502"/>
+      <c r="C25" s="501"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9491,7 +9526,9 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
-      <c r="AR25" s="499"/>
+      <c r="AR25" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="457" t="s">
@@ -9617,7 +9654,7 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
-      <c r="AR26" s="499" t="s">
+      <c r="AR26" s="529" t="s">
         <v>972</v>
       </c>
     </row>
@@ -9705,7 +9742,9 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
-      <c r="AR27" s="499"/>
+      <c r="AR27" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
@@ -9791,7 +9830,9 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
-      <c r="AR28" s="499"/>
+      <c r="AR28" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
@@ -9879,7 +9920,9 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
-      <c r="AR29" s="499"/>
+      <c r="AR29" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
@@ -9963,7 +10006,9 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" s="499"/>
+      <c r="AR30" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="31" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="457" t="s">
@@ -10093,7 +10138,7 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
-      <c r="AR31" s="499" t="s">
+      <c r="AR31" s="529" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10185,7 +10230,9 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
-      <c r="AR32" s="499"/>
+      <c r="AR32" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
@@ -10275,7 +10322,9 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
-      <c r="AR33" s="499"/>
+      <c r="AR33" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
@@ -10365,7 +10414,9 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
-      <c r="AR34" s="499"/>
+      <c r="AR34" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="35" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="457" t="s">
@@ -10489,7 +10540,7 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
-      <c r="AR35" s="499" t="s">
+      <c r="AR35" s="529" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10577,7 +10628,9 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
-      <c r="AR36" s="499"/>
+      <c r="AR36" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
@@ -10663,7 +10716,9 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
-      <c r="AR37" s="499"/>
+      <c r="AR37" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
@@ -10749,7 +10804,9 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
-      <c r="AR38" s="499"/>
+      <c r="AR38" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="39" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="457" t="s">
@@ -10873,7 +10930,7 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
-      <c r="AR39" s="499" t="s">
+      <c r="AR39" s="529" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10961,7 +11018,9 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
-      <c r="AR40" s="499"/>
+      <c r="AR40" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
@@ -11047,7 +11106,9 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
-      <c r="AR41" s="499"/>
+      <c r="AR41" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
@@ -11133,7 +11194,9 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
-      <c r="AR42" s="499"/>
+      <c r="AR42" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
@@ -11217,7 +11280,9 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
-      <c r="AR43" s="499"/>
+      <c r="AR43" s="529" t="s">
+        <v>972</v>
+      </c>
     </row>
     <row r="44" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="457" t="s">
@@ -11226,7 +11291,7 @@
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="503">
+      <c r="C44" s="502">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11345,14 +11410,14 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
-      <c r="AR44" s="499" t="s">
+      <c r="AR44" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="504"/>
+      <c r="C45" s="503"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11437,12 +11502,14 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
-      <c r="AR45" s="499"/>
+      <c r="AR45" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="505"/>
+      <c r="C46" s="504"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11527,7 +11594,9 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
-      <c r="AR46" s="499"/>
+      <c r="AR46" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="47" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="457" t="s">
@@ -11655,7 +11724,7 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
-      <c r="AR47" s="499" t="s">
+      <c r="AR47" s="529" t="s">
         <v>973</v>
       </c>
     </row>
@@ -11745,7 +11814,9 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
-      <c r="AR48" s="499"/>
+      <c r="AR48" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
@@ -11833,7 +11904,9 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
-      <c r="AR49" s="499"/>
+      <c r="AR49" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
@@ -11921,7 +11994,9 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
-      <c r="AR50" s="499"/>
+      <c r="AR50" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="51" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="457" t="s">
@@ -12051,7 +12126,7 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
-      <c r="AR51" s="499" t="s">
+      <c r="AR51" s="529" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12143,7 +12218,9 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
-      <c r="AR52" s="499"/>
+      <c r="AR52" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
@@ -12229,7 +12306,9 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
-      <c r="AR53" s="499"/>
+      <c r="AR53" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
@@ -12313,7 +12392,9 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
-      <c r="AR54" s="499"/>
+      <c r="AR54" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="55" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="457" t="s">
@@ -12437,7 +12518,7 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
-      <c r="AR55" s="499" t="s">
+      <c r="AR55" s="529" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12525,7 +12606,9 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
-      <c r="AR56" s="499"/>
+      <c r="AR56" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
@@ -12611,7 +12694,9 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
-      <c r="AR57" s="499"/>
+      <c r="AR57" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
@@ -12697,7 +12782,9 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
-      <c r="AR58" s="499"/>
+      <c r="AR58" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
@@ -12783,7 +12870,9 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
-      <c r="AR59" s="499"/>
+      <c r="AR59" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="60" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="457" t="s">
@@ -12907,7 +12996,7 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
-      <c r="AR60" s="499" t="s">
+      <c r="AR60" s="529" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12995,7 +13084,9 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
-      <c r="AR61" s="499"/>
+      <c r="AR61" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
@@ -13081,7 +13172,9 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
-      <c r="AR62" s="499"/>
+      <c r="AR62" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
@@ -13167,7 +13260,9 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
-      <c r="AR63" s="499"/>
+      <c r="AR63" s="529" t="s">
+        <v>973</v>
+      </c>
     </row>
     <row r="64" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="457" t="s">
@@ -13176,7 +13271,7 @@
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="506">
+      <c r="C64" s="505">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13295,14 +13390,14 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
-      <c r="AR64" s="499" t="s">
+      <c r="AR64" s="529" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="507"/>
+      <c r="C65" s="506"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13387,12 +13482,14 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
-      <c r="AR65" s="499"/>
+      <c r="AR65" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="508"/>
+      <c r="C66" s="507"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13477,7 +13574,9 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
-      <c r="AR66" s="499"/>
+      <c r="AR66" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="67" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="457" t="s">
@@ -13605,7 +13704,7 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
-      <c r="AR67" s="499" t="s">
+      <c r="AR67" s="529" t="s">
         <v>974</v>
       </c>
     </row>
@@ -13695,7 +13794,9 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
-      <c r="AR68" s="499"/>
+      <c r="AR68" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
@@ -13783,7 +13884,9 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
-      <c r="AR69" s="499"/>
+      <c r="AR69" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="70" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A70" s="457" t="s">
@@ -13905,7 +14008,7 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
-      <c r="AR70" s="499" t="s">
+      <c r="AR70" s="529" t="s">
         <v>974</v>
       </c>
     </row>
@@ -13993,7 +14096,9 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
-      <c r="AR71" s="499"/>
+      <c r="AR71" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
@@ -14079,7 +14184,9 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
-      <c r="AR72" s="499"/>
+      <c r="AR72" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
@@ -14165,7 +14272,9 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
-      <c r="AR73" s="499"/>
+      <c r="AR73" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
@@ -14251,7 +14360,9 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
-      <c r="AR74" s="499"/>
+      <c r="AR74" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="75" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="457" t="s">
@@ -14377,7 +14488,7 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
-      <c r="AR75" s="499" t="s">
+      <c r="AR75" s="529" t="s">
         <v>974</v>
       </c>
     </row>
@@ -14465,7 +14576,9 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
-      <c r="AR76" s="499"/>
+      <c r="AR76" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
@@ -14551,7 +14664,9 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
-      <c r="AR77" s="499"/>
+      <c r="AR77" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
@@ -14637,7 +14752,9 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
-      <c r="AR78" s="499"/>
+      <c r="AR78" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
@@ -14723,7 +14840,9 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
-      <c r="AR79" s="499"/>
+      <c r="AR79" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="80" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="457" t="s">
@@ -14843,7 +14962,7 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
-      <c r="AR80" s="499" t="s">
+      <c r="AR80" s="529" t="s">
         <v>974</v>
       </c>
     </row>
@@ -14931,7 +15050,9 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
-      <c r="AR81" s="499"/>
+      <c r="AR81" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
@@ -15015,7 +15136,9 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
-      <c r="AR82" s="499"/>
+      <c r="AR82" s="529" t="s">
+        <v>974</v>
+      </c>
     </row>
     <row r="83" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="457" t="s">
@@ -15024,7 +15147,7 @@
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="509">
+      <c r="C83" s="508">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -15145,14 +15268,14 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
-      <c r="AR83" s="499" t="s">
+      <c r="AR83" s="529" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="510"/>
+      <c r="C84" s="509"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -15237,12 +15360,14 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
-      <c r="AR84" s="499"/>
+      <c r="AR84" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="511"/>
+      <c r="C85" s="510"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15325,7 +15450,9 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
-      <c r="AR85" s="499"/>
+      <c r="AR85" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="86" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="457" t="s">
@@ -15453,7 +15580,7 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
-      <c r="AR86" s="499" t="s">
+      <c r="AR86" s="529" t="s">
         <v>975</v>
       </c>
     </row>
@@ -15545,7 +15672,9 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
-      <c r="AR87" s="499"/>
+      <c r="AR87" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
@@ -15635,7 +15764,9 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
-      <c r="AR88" s="499"/>
+      <c r="AR88" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
@@ -15725,7 +15856,9 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
-      <c r="AR89" s="499"/>
+      <c r="AR89" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="90" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="457" t="s">
@@ -15851,7 +15984,7 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
-      <c r="AR90" s="499" t="s">
+      <c r="AR90" s="529" t="s">
         <v>975</v>
       </c>
     </row>
@@ -15941,7 +16074,9 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
-      <c r="AR91" s="499"/>
+      <c r="AR91" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
@@ -16029,7 +16164,9 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
-      <c r="AR92" s="499"/>
+      <c r="AR92" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
@@ -16117,7 +16254,9 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
-      <c r="AR93" s="499"/>
+      <c r="AR93" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="94" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="457" t="s">
@@ -16243,7 +16382,7 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR94" s="499" t="s">
+      <c r="AR94" s="529" t="s">
         <v>975</v>
       </c>
     </row>
@@ -16333,7 +16472,9 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
-      <c r="AR95" s="499"/>
+      <c r="AR95" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
@@ -16421,7 +16562,9 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
-      <c r="AR96" s="499"/>
+      <c r="AR96" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
@@ -16509,7 +16652,9 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
-      <c r="AR97" s="499"/>
+      <c r="AR97" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="98" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="457" t="s">
@@ -16635,7 +16780,7 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
-      <c r="AR98" s="499" t="s">
+      <c r="AR98" s="529" t="s">
         <v>975</v>
       </c>
     </row>
@@ -16725,7 +16870,9 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
-      <c r="AR99" s="499"/>
+      <c r="AR99" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
@@ -16811,7 +16958,9 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
-      <c r="AR100" s="499"/>
+      <c r="AR100" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
@@ -16899,7 +17048,9 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
-      <c r="AR101" s="499"/>
+      <c r="AR101" s="529" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="102" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="457" t="s">
@@ -17021,7 +17172,7 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
-      <c r="AR102" s="499" t="s">
+      <c r="AR102" s="529" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17109,7 +17260,9 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
-      <c r="AR103" s="499"/>
+      <c r="AR103" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
@@ -17195,7 +17348,9 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
-      <c r="AR104" s="499"/>
+      <c r="AR104" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
@@ -17281,7 +17436,9 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
-      <c r="AR105" s="499"/>
+      <c r="AR105" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="106" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="457" t="s">
@@ -17407,7 +17564,7 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
-      <c r="AR106" s="499" t="s">
+      <c r="AR106" s="529" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17495,7 +17652,9 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
-      <c r="AR107" s="499"/>
+      <c r="AR107" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
@@ -17581,7 +17740,9 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
-      <c r="AR108" s="499"/>
+      <c r="AR108" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
@@ -17667,7 +17828,9 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
-      <c r="AR109" s="499"/>
+      <c r="AR109" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="110" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A110" s="457" t="s">
@@ -17791,7 +17954,7 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
-      <c r="AR110" s="499" t="s">
+      <c r="AR110" s="529" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17879,7 +18042,9 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
-      <c r="AR111" s="499"/>
+      <c r="AR111" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
@@ -17965,7 +18130,9 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
-      <c r="AR112" s="499"/>
+      <c r="AR112" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
@@ -18051,7 +18218,9 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
-      <c r="AR113" s="499"/>
+      <c r="AR113" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
@@ -18135,7 +18304,9 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
-      <c r="AR114" s="499"/>
+      <c r="AR114" s="529" t="s">
+        <v>976</v>
+      </c>
     </row>
     <row r="115" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="457" t="s">
@@ -18144,7 +18315,7 @@
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="512">
+      <c r="C115" s="511">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -18261,14 +18432,14 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR115" s="499" t="s">
+      <c r="AR115" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="513"/>
+      <c r="C116" s="512"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -18349,12 +18520,14 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
-      <c r="AR116" s="499"/>
+      <c r="AR116" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="513"/>
+      <c r="C117" s="512"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18435,12 +18608,14 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
-      <c r="AR117" s="499"/>
+      <c r="AR117" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="513"/>
+      <c r="C118" s="512"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18521,7 +18696,9 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
-      <c r="AR118" s="499"/>
+      <c r="AR118" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="119" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A119" s="457" t="s">
@@ -18530,7 +18707,7 @@
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="513"/>
+      <c r="C119" s="512"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18643,14 +18820,14 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
-      <c r="AR119" s="499" t="s">
+      <c r="AR119" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="513"/>
+      <c r="C120" s="512"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18731,12 +18908,14 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
-      <c r="AR120" s="499"/>
+      <c r="AR120" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="513"/>
+      <c r="C121" s="512"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -18817,12 +18996,14 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
-      <c r="AR121" s="499"/>
+      <c r="AR121" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="514"/>
+      <c r="C122" s="513"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -18903,7 +19084,9 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
-      <c r="AR122" s="499"/>
+      <c r="AR122" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="123" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="457" t="s">
@@ -19027,7 +19210,7 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
-      <c r="AR123" s="499" t="s">
+      <c r="AR123" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19115,7 +19298,9 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
-      <c r="AR124" s="499"/>
+      <c r="AR124" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
@@ -19201,7 +19386,9 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
-      <c r="AR125" s="499"/>
+      <c r="AR125" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
@@ -19287,7 +19474,9 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
-      <c r="AR126" s="499"/>
+      <c r="AR126" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
@@ -19373,7 +19562,9 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
-      <c r="AR127" s="499"/>
+      <c r="AR127" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="128" spans="1:44" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="457" t="s">
@@ -19499,7 +19690,7 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
-      <c r="AR128" s="499" t="s">
+      <c r="AR128" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19591,7 +19782,9 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
-      <c r="AR129" s="499"/>
+      <c r="AR129" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
@@ -19681,7 +19874,9 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
-      <c r="AR130" s="499"/>
+      <c r="AR130" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
@@ -19763,7 +19958,9 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
-      <c r="AR131" s="499"/>
+      <c r="AR131" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="132" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="457" t="s">
@@ -19889,7 +20086,7 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR132" s="499" t="s">
+      <c r="AR132" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19977,7 +20174,9 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
-      <c r="AR133" s="499"/>
+      <c r="AR133" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
@@ -20063,7 +20262,9 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
-      <c r="AR134" s="499"/>
+      <c r="AR134" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
@@ -20149,7 +20350,9 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
-      <c r="AR135" s="499"/>
+      <c r="AR135" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="136" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A136" s="457" t="s">
@@ -20273,7 +20476,7 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
-      <c r="AR136" s="499" t="s">
+      <c r="AR136" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -20361,7 +20564,9 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
-      <c r="AR137" s="499"/>
+      <c r="AR137" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
@@ -20447,7 +20652,9 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
-      <c r="AR138" s="499"/>
+      <c r="AR138" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
@@ -20533,7 +20740,9 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
-      <c r="AR139" s="499"/>
+      <c r="AR139" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
@@ -20617,7 +20826,9 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
-      <c r="AR140" s="499"/>
+      <c r="AR140" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="141" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="457" t="s">
@@ -20741,7 +20952,7 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
-      <c r="AR141" s="499" t="s">
+      <c r="AR141" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -20829,7 +21040,9 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
-      <c r="AR142" s="499"/>
+      <c r="AR142" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
@@ -20915,7 +21128,9 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
-      <c r="AR143" s="499"/>
+      <c r="AR143" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
@@ -21001,7 +21216,9 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
-      <c r="AR144" s="499"/>
+      <c r="AR144" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
@@ -21087,7 +21304,9 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
-      <c r="AR145" s="499"/>
+      <c r="AR145" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="146" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A146" s="457" t="s">
@@ -21211,7 +21430,7 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
-      <c r="AR146" s="499" t="s">
+      <c r="AR146" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -21299,7 +21518,9 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
-      <c r="AR147" s="499"/>
+      <c r="AR147" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
@@ -21385,7 +21606,9 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
-      <c r="AR148" s="499"/>
+      <c r="AR148" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
@@ -21471,7 +21694,9 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
-      <c r="AR149" s="499"/>
+      <c r="AR149" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="150" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="457" t="s">
@@ -21595,7 +21820,7 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
-      <c r="AR150" s="499" t="s">
+      <c r="AR150" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -21683,7 +21908,9 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
-      <c r="AR151" s="499"/>
+      <c r="AR151" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
@@ -21769,7 +21996,9 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
-      <c r="AR152" s="499"/>
+      <c r="AR152" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
@@ -21855,7 +22084,9 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
-      <c r="AR153" s="499"/>
+      <c r="AR153" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="154" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A154" s="457" t="s">
@@ -21977,7 +22208,7 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
-      <c r="AR154" s="499" t="s">
+      <c r="AR154" s="529" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22065,7 +22296,9 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
-      <c r="AR155" s="499"/>
+      <c r="AR155" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
@@ -22151,7 +22384,9 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
-      <c r="AR156" s="499"/>
+      <c r="AR156" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
@@ -22237,7 +22472,9 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
-      <c r="AR157" s="499"/>
+      <c r="AR157" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
@@ -22321,7 +22558,9 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
-      <c r="AR158" s="499"/>
+      <c r="AR158" s="529" t="s">
+        <v>977</v>
+      </c>
     </row>
     <row r="159" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="457" t="s">
@@ -22330,7 +22569,7 @@
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="515">
+      <c r="C159" s="514">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22447,14 +22686,14 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
-      <c r="AR159" s="499" t="s">
+      <c r="AR159" s="529" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="516"/>
+      <c r="C160" s="515"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22535,12 +22774,14 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
-      <c r="AR160" s="499"/>
+      <c r="AR160" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="516"/>
+      <c r="C161" s="515"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22621,12 +22862,14 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
-      <c r="AR161" s="499"/>
+      <c r="AR161" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="516"/>
+      <c r="C162" s="515"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22707,7 +22950,9 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
-      <c r="AR162" s="499"/>
+      <c r="AR162" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="163" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A163" s="457" t="s">
@@ -22716,7 +22961,7 @@
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="516"/>
+      <c r="C163" s="515"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -22831,14 +23076,14 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
-      <c r="AR163" s="499" t="s">
+      <c r="AR163" s="529" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="516"/>
+      <c r="C164" s="515"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -22919,12 +23164,14 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
-      <c r="AR164" s="499"/>
+      <c r="AR164" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="516"/>
+      <c r="C165" s="515"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -23005,12 +23252,14 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
-      <c r="AR165" s="499"/>
+      <c r="AR165" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="516"/>
+      <c r="C166" s="515"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -23091,7 +23340,9 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
-      <c r="AR166" s="499"/>
+      <c r="AR166" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="167" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A167" s="457" t="s">
@@ -23100,7 +23351,7 @@
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="516"/>
+      <c r="C167" s="515"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -23215,14 +23466,14 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
-      <c r="AR167" s="499" t="s">
+      <c r="AR167" s="529" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="516"/>
+      <c r="C168" s="515"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -23303,12 +23554,14 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
-      <c r="AR168" s="499"/>
+      <c r="AR168" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="516"/>
+      <c r="C169" s="515"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -23389,12 +23642,14 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
-      <c r="AR169" s="499"/>
+      <c r="AR169" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="517"/>
+      <c r="C170" s="516"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23475,7 +23730,9 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
-      <c r="AR170" s="499"/>
+      <c r="AR170" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="171" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="457" t="s">
@@ -23601,7 +23858,7 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR171" s="499" t="s">
+      <c r="AR171" s="529" t="s">
         <v>978</v>
       </c>
     </row>
@@ -23689,7 +23946,9 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
-      <c r="AR172" s="499"/>
+      <c r="AR172" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
@@ -23775,7 +24034,9 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
-      <c r="AR173" s="499"/>
+      <c r="AR173" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
@@ -23863,7 +24124,9 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
-      <c r="AR174" s="499"/>
+      <c r="AR174" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="175" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A175" s="457" t="s">
@@ -23987,7 +24250,7 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
-      <c r="AR175" s="499" t="s">
+      <c r="AR175" s="529" t="s">
         <v>978</v>
       </c>
     </row>
@@ -24081,7 +24344,9 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
-      <c r="AR176" s="499"/>
+      <c r="AR176" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
@@ -24171,7 +24436,9 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
-      <c r="AR177" s="499"/>
+      <c r="AR177" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
@@ -24259,7 +24526,9 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
-      <c r="AR178" s="499"/>
+      <c r="AR178" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="179" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A179" s="457" t="s">
@@ -24383,7 +24652,7 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR179" s="499" t="s">
+      <c r="AR179" s="529" t="s">
         <v>978</v>
       </c>
     </row>
@@ -24471,7 +24740,9 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
-      <c r="AR180" s="499"/>
+      <c r="AR180" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
@@ -24557,7 +24828,9 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
-      <c r="AR181" s="499"/>
+      <c r="AR181" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
@@ -24643,7 +24916,9 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
-      <c r="AR182" s="499"/>
+      <c r="AR182" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
@@ -24729,7 +25004,9 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
-      <c r="AR183" s="499"/>
+      <c r="AR183" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="184" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="457" t="s">
@@ -24855,7 +25132,7 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
-      <c r="AR184" s="499" t="s">
+      <c r="AR184" s="529" t="s">
         <v>978</v>
       </c>
     </row>
@@ -24945,7 +25222,9 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
-      <c r="AR185" s="499"/>
+      <c r="AR185" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
@@ -25031,7 +25310,9 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
-      <c r="AR186" s="499"/>
+      <c r="AR186" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
@@ -25119,7 +25400,9 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
-      <c r="AR187" s="499"/>
+      <c r="AR187" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="188" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="457" t="s">
@@ -25241,7 +25524,7 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
-      <c r="AR188" s="499" t="s">
+      <c r="AR188" s="529" t="s">
         <v>978</v>
       </c>
     </row>
@@ -25329,7 +25612,9 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
-      <c r="AR189" s="499"/>
+      <c r="AR189" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
@@ -25415,7 +25700,9 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
-      <c r="AR190" s="499"/>
+      <c r="AR190" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
@@ -25499,7 +25786,9 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
-      <c r="AR191" s="499"/>
+      <c r="AR191" s="529" t="s">
+        <v>978</v>
+      </c>
     </row>
     <row r="192" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="457" t="s">
@@ -25508,7 +25797,7 @@
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="518">
+      <c r="C192" s="517">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25623,14 +25912,14 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
-      <c r="AR192" s="499" t="s">
+      <c r="AR192" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="519"/>
+      <c r="C193" s="518"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -25711,12 +26000,14 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
-      <c r="AR193" s="499"/>
+      <c r="AR193" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="519"/>
+      <c r="C194" s="518"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -25797,12 +26088,14 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
-      <c r="AR194" s="499"/>
+      <c r="AR194" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="519"/>
+      <c r="C195" s="518"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -25883,7 +26176,9 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
-      <c r="AR195" s="499"/>
+      <c r="AR195" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="196" spans="1:44" ht="63.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="457" t="s">
@@ -25892,7 +26187,7 @@
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="519"/>
+      <c r="C196" s="518"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -26005,14 +26300,14 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
-      <c r="AR196" s="499" t="s">
+      <c r="AR196" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="519"/>
+      <c r="C197" s="518"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -26093,12 +26388,14 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
-      <c r="AR197" s="499"/>
+      <c r="AR197" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="519"/>
+      <c r="C198" s="518"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -26179,12 +26476,14 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
-      <c r="AR198" s="499"/>
+      <c r="AR198" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="520"/>
+      <c r="C199" s="519"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -26265,7 +26564,9 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
-      <c r="AR199" s="499"/>
+      <c r="AR199" s="529" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="200" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="457" t="s">
@@ -26274,7 +26575,7 @@
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="521">
+      <c r="C200" s="520">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -26393,14 +26694,14 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
-      <c r="AR200" s="499" t="s">
+      <c r="AR200" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="522"/>
+      <c r="C201" s="521"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -26485,12 +26786,14 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
-      <c r="AR201" s="499"/>
+      <c r="AR201" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="522"/>
+      <c r="C202" s="521"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26573,7 +26876,9 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
-      <c r="AR202" s="499"/>
+      <c r="AR202" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="203" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A203" s="457" t="s">
@@ -26582,7 +26887,7 @@
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="522"/>
+      <c r="C203" s="521"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -26701,14 +27006,14 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
-      <c r="AR203" s="499" t="s">
+      <c r="AR203" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="522"/>
+      <c r="C204" s="521"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -26793,12 +27098,14 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
-      <c r="AR204" s="499"/>
+      <c r="AR204" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="522"/>
+      <c r="C205" s="521"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -26881,7 +27188,9 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
-      <c r="AR205" s="499"/>
+      <c r="AR205" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="206" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A206" s="457" t="s">
@@ -26890,7 +27199,7 @@
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="522"/>
+      <c r="C206" s="521"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -27009,14 +27318,14 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
-      <c r="AR206" s="499" t="s">
+      <c r="AR206" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="522"/>
+      <c r="C207" s="521"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -27097,12 +27406,14 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
-      <c r="AR207" s="499"/>
+      <c r="AR207" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="523"/>
+      <c r="C208" s="522"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -27187,7 +27498,9 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
-      <c r="AR208" s="499"/>
+      <c r="AR208" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="209" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="457" t="s">
@@ -27317,7 +27630,7 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
-      <c r="AR209" s="499" t="s">
+      <c r="AR209" s="529" t="s">
         <v>980</v>
       </c>
     </row>
@@ -27409,7 +27722,9 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
-      <c r="AR210" s="499"/>
+      <c r="AR210" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
@@ -27499,7 +27814,9 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
-      <c r="AR211" s="499"/>
+      <c r="AR211" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
@@ -27587,7 +27904,9 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
-      <c r="AR212" s="499"/>
+      <c r="AR212" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="213" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A213" s="457" t="s">
@@ -27715,7 +28034,7 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
-      <c r="AR213" s="499" t="s">
+      <c r="AR213" s="529" t="s">
         <v>980</v>
       </c>
     </row>
@@ -27807,7 +28126,9 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
-      <c r="AR214" s="499"/>
+      <c r="AR214" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
@@ -27897,7 +28218,9 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
-      <c r="AR215" s="499"/>
+      <c r="AR215" s="529" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="216" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="457" t="s">
@@ -28027,7 +28350,7 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
-      <c r="AR216" s="499" t="s">
+      <c r="AR216" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -28119,7 +28442,9 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
-      <c r="AR217" s="499"/>
+      <c r="AR217" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
@@ -28209,7 +28534,9 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
-      <c r="AR218" s="499"/>
+      <c r="AR218" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
@@ -28299,7 +28626,9 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
-      <c r="AR219" s="499"/>
+      <c r="AR219" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="220" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="457" t="s">
@@ -28425,7 +28754,7 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
-      <c r="AR220" s="499" t="s">
+      <c r="AR220" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -28515,7 +28844,9 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
-      <c r="AR221" s="499"/>
+      <c r="AR221" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
@@ -28603,7 +28934,9 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
-      <c r="AR222" s="499"/>
+      <c r="AR222" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="223" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A223" s="457" t="s">
@@ -28731,7 +29064,7 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
-      <c r="AR223" s="499" t="s">
+      <c r="AR223" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -28823,7 +29156,9 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
-      <c r="AR224" s="499"/>
+      <c r="AR224" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
@@ -28913,7 +29248,9 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
-      <c r="AR225" s="499"/>
+      <c r="AR225" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
@@ -28997,7 +29334,9 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
-      <c r="AR226" s="499"/>
+      <c r="AR226" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="227" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="457" t="s">
@@ -29123,7 +29462,7 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
-      <c r="AR227" s="499" t="s">
+      <c r="AR227" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -29211,7 +29550,9 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
-      <c r="AR228" s="499"/>
+      <c r="AR228" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
@@ -29297,7 +29638,9 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
-      <c r="AR229" s="499"/>
+      <c r="AR229" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
@@ -29383,7 +29726,9 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
-      <c r="AR230" s="499"/>
+      <c r="AR230" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="231" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A231" s="457" t="s">
@@ -29507,7 +29852,7 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
-      <c r="AR231" s="499" t="s">
+      <c r="AR231" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -29595,7 +29940,9 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
-      <c r="AR232" s="499"/>
+      <c r="AR232" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
@@ -29681,7 +30028,9 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
-      <c r="AR233" s="499"/>
+      <c r="AR233" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
@@ -29763,7 +30112,9 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
-      <c r="AR234" s="499"/>
+      <c r="AR234" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="235" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="457" t="s">
@@ -29772,7 +30123,7 @@
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="524">
+      <c r="C235" s="523">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -29889,14 +30240,14 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
-      <c r="AR235" s="499" t="s">
+      <c r="AR235" s="529" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="525"/>
+      <c r="C236" s="524"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -29977,12 +30328,14 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
-      <c r="AR236" s="499"/>
+      <c r="AR236" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="525"/>
+      <c r="C237" s="524"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -30063,12 +30416,14 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
-      <c r="AR237" s="499"/>
+      <c r="AR237" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="526"/>
+      <c r="C238" s="525"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -30147,7 +30502,9 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
-      <c r="AR238" s="499"/>
+      <c r="AR238" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="239" spans="1:44" ht="56.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="457" t="s">
@@ -30273,7 +30630,7 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
-      <c r="AR239" s="499" t="s">
+      <c r="AR239" s="529" t="s">
         <v>982</v>
       </c>
     </row>
@@ -30361,7 +30718,9 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
-      <c r="AR240" s="499"/>
+      <c r="AR240" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
@@ -30447,7 +30806,9 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
-      <c r="AR241" s="499"/>
+      <c r="AR241" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
@@ -30531,7 +30892,9 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
-      <c r="AR242" s="499"/>
+      <c r="AR242" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="243" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A243" s="457" t="s">
@@ -30655,7 +31018,7 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
-      <c r="AR243" s="499" t="s">
+      <c r="AR243" s="529" t="s">
         <v>982</v>
       </c>
     </row>
@@ -30743,7 +31106,9 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
-      <c r="AR244" s="499"/>
+      <c r="AR244" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
@@ -30829,7 +31194,9 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
-      <c r="AR245" s="499"/>
+      <c r="AR245" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
@@ -30915,7 +31282,9 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
-      <c r="AR246" s="499"/>
+      <c r="AR246" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
@@ -31007,7 +31376,7 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
-      <c r="AR247" s="499" t="s">
+      <c r="AR247" s="529" t="s">
         <v>982</v>
       </c>
     </row>
@@ -31127,7 +31496,9 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
-      <c r="AR248" s="499"/>
+      <c r="AR248" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
@@ -31215,7 +31586,9 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
-      <c r="AR249" s="499"/>
+      <c r="AR249" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
@@ -31303,7 +31676,9 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
-      <c r="AR250" s="499"/>
+      <c r="AR250" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
@@ -31391,7 +31766,9 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
-      <c r="AR251" s="499"/>
+      <c r="AR251" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="252" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A252" s="457" t="s">
@@ -31515,7 +31892,7 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
-      <c r="AR252" s="499" t="s">
+      <c r="AR252" s="529" t="s">
         <v>982</v>
       </c>
     </row>
@@ -31603,7 +31980,9 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
-      <c r="AR253" s="499"/>
+      <c r="AR253" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
@@ -31689,7 +32068,9 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
-      <c r="AR254" s="499"/>
+      <c r="AR254" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
@@ -31775,7 +32156,9 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
-      <c r="AR255" s="499"/>
+      <c r="AR255" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
@@ -31861,7 +32244,9 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
-      <c r="AR256" s="499"/>
+      <c r="AR256" s="529" t="s">
+        <v>982</v>
+      </c>
     </row>
     <row r="257" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="457" t="s">
@@ -31987,7 +32372,7 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
-      <c r="AR257" s="499" t="s">
+      <c r="AR257" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32077,7 +32462,9 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
-      <c r="AR258" s="499"/>
+      <c r="AR258" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
@@ -32165,7 +32552,9 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
-      <c r="AR259" s="499"/>
+      <c r="AR259" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
@@ -32251,7 +32640,9 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
-      <c r="AR260" s="499"/>
+      <c r="AR260" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="261" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="457" t="s">
@@ -32375,7 +32766,7 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
-      <c r="AR261" s="499" t="s">
+      <c r="AR261" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32461,7 +32852,9 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
-      <c r="AR262" s="499"/>
+      <c r="AR262" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
@@ -32545,7 +32938,9 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
-      <c r="AR263" s="499"/>
+      <c r="AR263" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="264" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="457" t="s">
@@ -32673,7 +33068,7 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
-      <c r="AR264" s="499" t="s">
+      <c r="AR264" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32763,7 +33158,9 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
-      <c r="AR265" s="499"/>
+      <c r="AR265" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
@@ -32851,7 +33248,9 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
-      <c r="AR266" s="499"/>
+      <c r="AR266" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
@@ -32939,7 +33338,9 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
-      <c r="AR267" s="499"/>
+      <c r="AR267" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="268" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="457" t="s">
@@ -33069,7 +33470,7 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
-      <c r="AR268" s="499" t="s">
+      <c r="AR268" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -33161,7 +33562,9 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
-      <c r="AR269" s="499"/>
+      <c r="AR269" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
@@ -33251,7 +33654,9 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
-      <c r="AR270" s="499"/>
+      <c r="AR270" s="529" t="s">
+        <v>981</v>
+      </c>
     </row>
     <row r="271" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="457" t="s">
@@ -33260,7 +33665,7 @@
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="527">
+      <c r="C271" s="526">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -33381,14 +33786,14 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
-      <c r="AR271" s="499" t="s">
+      <c r="AR271" s="529" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="528"/>
+      <c r="C272" s="527"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -33471,12 +33876,14 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
-      <c r="AR272" s="499"/>
+      <c r="AR272" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="528"/>
+      <c r="C273" s="527"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -33559,7 +33966,9 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
-      <c r="AR273" s="499"/>
+      <c r="AR273" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="274" spans="1:44" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="457" t="s">
@@ -33568,7 +33977,7 @@
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="528"/>
+      <c r="C274" s="527"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -33679,14 +34088,14 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
-      <c r="AR274" s="499" t="s">
+      <c r="AR274" s="529" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="528"/>
+      <c r="C275" s="527"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -33775,12 +34184,14 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
-      <c r="AR275" s="499"/>
+      <c r="AR275" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="528"/>
+      <c r="C276" s="527"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -33863,12 +34274,14 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
-      <c r="AR276" s="499"/>
+      <c r="AR276" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="529"/>
+      <c r="C277" s="528"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -33951,7 +34364,9 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
-      <c r="AR277" s="499"/>
+      <c r="AR277" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="278" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="457" t="s">
@@ -34077,7 +34492,7 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
-      <c r="AR278" s="499" t="s">
+      <c r="AR278" s="529" t="s">
         <v>983</v>
       </c>
     </row>
@@ -34165,7 +34580,9 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
-      <c r="AR279" s="499"/>
+      <c r="AR279" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
@@ -34251,7 +34668,9 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
-      <c r="AR280" s="499"/>
+      <c r="AR280" s="529" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
@@ -34337,80 +34756,12 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
-      <c r="AR281" s="499"/>
+      <c r="AR281" s="529" t="s">
+        <v>984</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="AR264:AR267"/>
-    <mergeCell ref="AR268:AR270"/>
-    <mergeCell ref="AR271:AR273"/>
-    <mergeCell ref="AR274:AR277"/>
-    <mergeCell ref="AR278:AR281"/>
-    <mergeCell ref="AR243:AR246"/>
-    <mergeCell ref="AR247:AR251"/>
-    <mergeCell ref="AR252:AR256"/>
-    <mergeCell ref="AR257:AR260"/>
-    <mergeCell ref="AR261:AR263"/>
-    <mergeCell ref="AR223:AR226"/>
-    <mergeCell ref="AR227:AR230"/>
-    <mergeCell ref="AR231:AR234"/>
-    <mergeCell ref="AR235:AR238"/>
-    <mergeCell ref="AR239:AR242"/>
-    <mergeCell ref="AR206:AR208"/>
-    <mergeCell ref="AR209:AR212"/>
-    <mergeCell ref="AR213:AR215"/>
-    <mergeCell ref="AR216:AR219"/>
-    <mergeCell ref="AR220:AR222"/>
-    <mergeCell ref="AR188:AR191"/>
-    <mergeCell ref="AR192:AR195"/>
-    <mergeCell ref="AR196:AR199"/>
-    <mergeCell ref="AR200:AR202"/>
-    <mergeCell ref="AR203:AR205"/>
-    <mergeCell ref="AR167:AR170"/>
-    <mergeCell ref="AR171:AR174"/>
-    <mergeCell ref="AR175:AR178"/>
-    <mergeCell ref="AR179:AR183"/>
-    <mergeCell ref="AR184:AR187"/>
-    <mergeCell ref="AR146:AR149"/>
-    <mergeCell ref="AR150:AR153"/>
-    <mergeCell ref="AR154:AR158"/>
-    <mergeCell ref="AR159:AR162"/>
-    <mergeCell ref="AR163:AR166"/>
-    <mergeCell ref="AR123:AR127"/>
-    <mergeCell ref="AR128:AR131"/>
-    <mergeCell ref="AR132:AR135"/>
-    <mergeCell ref="AR136:AR140"/>
-    <mergeCell ref="AR141:AR145"/>
-    <mergeCell ref="AR102:AR105"/>
-    <mergeCell ref="AR106:AR109"/>
-    <mergeCell ref="AR110:AR114"/>
-    <mergeCell ref="AR115:AR118"/>
-    <mergeCell ref="AR119:AR122"/>
-    <mergeCell ref="AR83:AR85"/>
-    <mergeCell ref="AR86:AR89"/>
-    <mergeCell ref="AR90:AR93"/>
-    <mergeCell ref="AR94:AR97"/>
-    <mergeCell ref="AR98:AR101"/>
-    <mergeCell ref="AR64:AR66"/>
-    <mergeCell ref="AR67:AR69"/>
-    <mergeCell ref="AR70:AR74"/>
-    <mergeCell ref="AR75:AR79"/>
-    <mergeCell ref="AR80:AR82"/>
-    <mergeCell ref="AR44:AR46"/>
-    <mergeCell ref="AR47:AR50"/>
-    <mergeCell ref="AR51:AR54"/>
-    <mergeCell ref="AR55:AR59"/>
-    <mergeCell ref="AR60:AR63"/>
-    <mergeCell ref="AR23:AR25"/>
-    <mergeCell ref="AR26:AR30"/>
-    <mergeCell ref="AR31:AR34"/>
-    <mergeCell ref="AR35:AR38"/>
-    <mergeCell ref="AR39:AR43"/>
-    <mergeCell ref="AR2:AR4"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AR9:AR12"/>
-    <mergeCell ref="AR13:AR17"/>
-    <mergeCell ref="AR18:AR22"/>
+  <mergeCells count="40">
     <mergeCell ref="C264:C267"/>
     <mergeCell ref="C268:C270"/>
     <mergeCell ref="C271:C277"/>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E98CFB26-F101-454F-8A17-8FDA2B528115}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A2121F7-BC8D-42C4-B451-7E9F568B7D03}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4478,7 +4478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="530">
+  <cellXfs count="529">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5644,6 +5644,135 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5653,6 +5782,60 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5662,108 +5845,6 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5773,88 +5854,6 @@
     <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5885,6 +5884,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7165,7 +7168,7 @@
       <c r="B2" s="454" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="462">
+      <c r="C2" s="523">
         <v>11</v>
       </c>
       <c r="D2" s="296" t="s">
@@ -7286,14 +7289,14 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
-      <c r="AR2" s="529" t="s">
+      <c r="AR2" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="457"/>
       <c r="B3" s="454"/>
-      <c r="C3" s="463"/>
+      <c r="C3" s="524"/>
       <c r="D3" s="296"/>
       <c r="E3" s="17"/>
       <c r="F3" s="224"/>
@@ -7378,14 +7381,14 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
-      <c r="AR3" s="529" t="s">
+      <c r="AR3" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
       <c r="B4" s="454"/>
-      <c r="C4" s="464"/>
+      <c r="C4" s="525"/>
       <c r="D4" s="297"/>
       <c r="E4" s="209"/>
       <c r="F4" s="225"/>
@@ -7470,7 +7473,7 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
-      <c r="AR4" s="529" t="s">
+      <c r="AR4" t="s">
         <v>971</v>
       </c>
     </row>
@@ -7481,7 +7484,7 @@
       <c r="B5" s="454" t="s">
         <v>902</v>
       </c>
-      <c r="C5" s="462">
+      <c r="C5" s="523">
         <v>12</v>
       </c>
       <c r="D5" s="296" t="s">
@@ -7600,14 +7603,14 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
-      <c r="AR5" s="529" t="s">
+      <c r="AR5" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="457"/>
       <c r="B6" s="454"/>
-      <c r="C6" s="463"/>
+      <c r="C6" s="524"/>
       <c r="D6" s="296"/>
       <c r="E6" s="34"/>
       <c r="F6" s="226"/>
@@ -7690,14 +7693,14 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
-      <c r="AR6" s="529" t="s">
+      <c r="AR6" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
       <c r="B7" s="454"/>
-      <c r="C7" s="463"/>
+      <c r="C7" s="524"/>
       <c r="D7" s="296"/>
       <c r="E7" s="34"/>
       <c r="F7" s="226"/>
@@ -7780,14 +7783,14 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
-      <c r="AR7" s="529" t="s">
+      <c r="AR7" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
       <c r="B8" s="454"/>
-      <c r="C8" s="463"/>
+      <c r="C8" s="524"/>
       <c r="D8" s="296"/>
       <c r="E8" s="53"/>
       <c r="F8" s="227"/>
@@ -7868,7 +7871,7 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
-      <c r="AR8" s="529" t="s">
+      <c r="AR8" t="s">
         <v>971</v>
       </c>
     </row>
@@ -7879,7 +7882,7 @@
       <c r="B9" s="454" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="463"/>
+      <c r="C9" s="524"/>
       <c r="D9" s="296" t="s">
         <v>736</v>
       </c>
@@ -7994,14 +7997,14 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
-      <c r="AR9" s="529" t="s">
+      <c r="AR9" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="457"/>
       <c r="B10" s="454"/>
-      <c r="C10" s="463"/>
+      <c r="C10" s="524"/>
       <c r="D10" s="296"/>
       <c r="E10" s="34"/>
       <c r="F10" s="226"/>
@@ -8082,14 +8085,14 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
-      <c r="AR10" s="529" t="s">
+      <c r="AR10" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
       <c r="B11" s="454"/>
-      <c r="C11" s="463"/>
+      <c r="C11" s="524"/>
       <c r="D11" s="296"/>
       <c r="E11" s="34"/>
       <c r="F11" s="226"/>
@@ -8170,14 +8173,14 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
-      <c r="AR11" s="529" t="s">
+      <c r="AR11" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
       <c r="B12" s="454"/>
-      <c r="C12" s="464"/>
+      <c r="C12" s="525"/>
       <c r="D12" s="297"/>
       <c r="E12" s="38"/>
       <c r="F12" s="228"/>
@@ -8256,7 +8259,7 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
-      <c r="AR12" s="529" t="s">
+      <c r="AR12" t="s">
         <v>971</v>
       </c>
     </row>
@@ -8267,7 +8270,7 @@
       <c r="B13" s="454" t="s">
         <v>904</v>
       </c>
-      <c r="C13" s="462">
+      <c r="C13" s="523">
         <v>13</v>
       </c>
       <c r="D13" s="296" t="s">
@@ -8384,14 +8387,14 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
-      <c r="AR13" s="529" t="s">
+      <c r="AR13" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="457"/>
       <c r="B14" s="454"/>
-      <c r="C14" s="463"/>
+      <c r="C14" s="524"/>
       <c r="D14" s="296"/>
       <c r="E14" s="34"/>
       <c r="F14" s="226"/>
@@ -8472,14 +8475,14 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
-      <c r="AR14" s="529" t="s">
+      <c r="AR14" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
       <c r="B15" s="454"/>
-      <c r="C15" s="463"/>
+      <c r="C15" s="524"/>
       <c r="D15" s="296"/>
       <c r="E15" s="34"/>
       <c r="F15" s="226"/>
@@ -8560,14 +8563,14 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
-      <c r="AR15" s="529" t="s">
+      <c r="AR15" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
       <c r="B16" s="454"/>
-      <c r="C16" s="463"/>
+      <c r="C16" s="524"/>
       <c r="D16" s="296"/>
       <c r="E16" s="34"/>
       <c r="F16" s="226"/>
@@ -8648,14 +8651,14 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
-      <c r="AR16" s="529" t="s">
+      <c r="AR16" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
       <c r="B17" s="454"/>
-      <c r="C17" s="463"/>
+      <c r="C17" s="524"/>
       <c r="D17" s="296"/>
       <c r="E17" s="53"/>
       <c r="F17" s="227"/>
@@ -8734,7 +8737,7 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
-      <c r="AR17" s="529" t="s">
+      <c r="AR17" t="s">
         <v>971</v>
       </c>
     </row>
@@ -8745,7 +8748,7 @@
       <c r="B18" s="454" t="s">
         <v>905</v>
       </c>
-      <c r="C18" s="463"/>
+      <c r="C18" s="524"/>
       <c r="D18" s="296" t="s">
         <v>736</v>
       </c>
@@ -8858,14 +8861,14 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
-      <c r="AR18" s="529" t="s">
+      <c r="AR18" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="457"/>
       <c r="B19" s="454"/>
-      <c r="C19" s="463"/>
+      <c r="C19" s="524"/>
       <c r="D19" s="296"/>
       <c r="E19" s="34"/>
       <c r="F19" s="226"/>
@@ -8946,14 +8949,14 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
-      <c r="AR19" s="529" t="s">
+      <c r="AR19" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
       <c r="B20" s="454"/>
-      <c r="C20" s="463"/>
+      <c r="C20" s="524"/>
       <c r="D20" s="296"/>
       <c r="E20" s="34"/>
       <c r="F20" s="226"/>
@@ -9034,14 +9037,14 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
-      <c r="AR20" s="529" t="s">
+      <c r="AR20" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
       <c r="B21" s="454"/>
-      <c r="C21" s="463"/>
+      <c r="C21" s="524"/>
       <c r="D21" s="296"/>
       <c r="E21" s="34"/>
       <c r="F21" s="226"/>
@@ -9122,14 +9125,14 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
-      <c r="AR21" s="529" t="s">
+      <c r="AR21" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
       <c r="B22" s="454"/>
-      <c r="C22" s="464"/>
+      <c r="C22" s="525"/>
       <c r="D22" s="297"/>
       <c r="E22" s="38"/>
       <c r="F22" s="228"/>
@@ -9210,7 +9213,7 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" s="529" t="s">
+      <c r="AR22" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9221,7 +9224,7 @@
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="499">
+      <c r="C23" s="526">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9342,14 +9345,14 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
-      <c r="AR23" s="529" t="s">
+      <c r="AR23" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="500"/>
+      <c r="C24" s="527"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9434,14 +9437,14 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
-      <c r="AR24" s="529" t="s">
+      <c r="AR24" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="501"/>
+      <c r="C25" s="528"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9526,7 +9529,7 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
-      <c r="AR25" s="529" t="s">
+      <c r="AR25" t="s">
         <v>972</v>
       </c>
     </row>
@@ -9537,7 +9540,7 @@
       <c r="B26" s="454" t="s">
         <v>907</v>
       </c>
-      <c r="C26" s="459">
+      <c r="C26" s="502">
         <v>22</v>
       </c>
       <c r="D26" s="298" t="s">
@@ -9654,14 +9657,14 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
-      <c r="AR26" s="529" t="s">
+      <c r="AR26" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="457"/>
       <c r="B27" s="454"/>
-      <c r="C27" s="460"/>
+      <c r="C27" s="503"/>
       <c r="D27" s="298"/>
       <c r="E27" s="73"/>
       <c r="F27" s="230"/>
@@ -9742,14 +9745,14 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
-      <c r="AR27" s="529" t="s">
+      <c r="AR27" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
       <c r="B28" s="454"/>
-      <c r="C28" s="460"/>
+      <c r="C28" s="503"/>
       <c r="D28" s="298"/>
       <c r="E28" s="73"/>
       <c r="F28" s="230"/>
@@ -9830,14 +9833,14 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
-      <c r="AR28" s="529" t="s">
+      <c r="AR28" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
       <c r="B29" s="454"/>
-      <c r="C29" s="460"/>
+      <c r="C29" s="503"/>
       <c r="D29" s="298"/>
       <c r="E29" s="73"/>
       <c r="F29" s="230"/>
@@ -9920,14 +9923,14 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
-      <c r="AR29" s="529" t="s">
+      <c r="AR29" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
       <c r="B30" s="454"/>
-      <c r="C30" s="461"/>
+      <c r="C30" s="504"/>
       <c r="D30" s="311"/>
       <c r="E30" s="74"/>
       <c r="F30" s="231"/>
@@ -10006,7 +10009,7 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" s="529" t="s">
+      <c r="AR30" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10017,7 +10020,7 @@
       <c r="B31" s="454" t="s">
         <v>908</v>
       </c>
-      <c r="C31" s="459">
+      <c r="C31" s="502">
         <v>23</v>
       </c>
       <c r="D31" s="298" t="s">
@@ -10138,14 +10141,14 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
-      <c r="AR31" s="529" t="s">
+      <c r="AR31" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="457"/>
       <c r="B32" s="454"/>
-      <c r="C32" s="460"/>
+      <c r="C32" s="503"/>
       <c r="D32" s="298"/>
       <c r="E32" s="73"/>
       <c r="F32" s="230"/>
@@ -10230,14 +10233,14 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
-      <c r="AR32" s="529" t="s">
+      <c r="AR32" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
       <c r="B33" s="454"/>
-      <c r="C33" s="460"/>
+      <c r="C33" s="503"/>
       <c r="D33" s="298"/>
       <c r="E33" s="73"/>
       <c r="F33" s="230"/>
@@ -10322,14 +10325,14 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
-      <c r="AR33" s="529" t="s">
+      <c r="AR33" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
       <c r="B34" s="454"/>
-      <c r="C34" s="461"/>
+      <c r="C34" s="504"/>
       <c r="D34" s="311"/>
       <c r="E34" s="74"/>
       <c r="F34" s="231"/>
@@ -10414,7 +10417,7 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
-      <c r="AR34" s="529" t="s">
+      <c r="AR34" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10425,7 +10428,7 @@
       <c r="B35" s="454" t="s">
         <v>909</v>
       </c>
-      <c r="C35" s="459">
+      <c r="C35" s="502">
         <v>24</v>
       </c>
       <c r="D35" s="298" t="s">
@@ -10540,14 +10543,14 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
-      <c r="AR35" s="529" t="s">
+      <c r="AR35" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="457"/>
       <c r="B36" s="454"/>
-      <c r="C36" s="460"/>
+      <c r="C36" s="503"/>
       <c r="D36" s="298"/>
       <c r="E36" s="73"/>
       <c r="F36" s="230"/>
@@ -10628,14 +10631,14 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
-      <c r="AR36" s="529" t="s">
+      <c r="AR36" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
       <c r="B37" s="454"/>
-      <c r="C37" s="460"/>
+      <c r="C37" s="503"/>
       <c r="D37" s="298"/>
       <c r="E37" s="73"/>
       <c r="F37" s="230"/>
@@ -10716,14 +10719,14 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
-      <c r="AR37" s="529" t="s">
+      <c r="AR37" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
       <c r="B38" s="454"/>
-      <c r="C38" s="460"/>
+      <c r="C38" s="503"/>
       <c r="D38" s="298"/>
       <c r="E38" s="77"/>
       <c r="F38" s="232"/>
@@ -10804,7 +10807,7 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
-      <c r="AR38" s="529" t="s">
+      <c r="AR38" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10815,7 +10818,7 @@
       <c r="B39" s="454" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="460"/>
+      <c r="C39" s="503"/>
       <c r="D39" s="298" t="s">
         <v>737</v>
       </c>
@@ -10930,14 +10933,14 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
-      <c r="AR39" s="529" t="s">
+      <c r="AR39" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="457"/>
       <c r="B40" s="454"/>
-      <c r="C40" s="460"/>
+      <c r="C40" s="503"/>
       <c r="D40" s="298"/>
       <c r="E40" s="73"/>
       <c r="F40" s="230"/>
@@ -11018,14 +11021,14 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
-      <c r="AR40" s="529" t="s">
+      <c r="AR40" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
       <c r="B41" s="454"/>
-      <c r="C41" s="460"/>
+      <c r="C41" s="503"/>
       <c r="D41" s="298"/>
       <c r="E41" s="73"/>
       <c r="F41" s="230"/>
@@ -11106,14 +11109,14 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
-      <c r="AR41" s="529" t="s">
+      <c r="AR41" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
       <c r="B42" s="454"/>
-      <c r="C42" s="460"/>
+      <c r="C42" s="503"/>
       <c r="D42" s="298"/>
       <c r="E42" s="73"/>
       <c r="F42" s="230"/>
@@ -11194,14 +11197,14 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
-      <c r="AR42" s="529" t="s">
+      <c r="AR42" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
       <c r="B43" s="454"/>
-      <c r="C43" s="461"/>
+      <c r="C43" s="504"/>
       <c r="D43" s="311"/>
       <c r="E43" s="74"/>
       <c r="F43" s="231"/>
@@ -11280,7 +11283,7 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
-      <c r="AR43" s="529" t="s">
+      <c r="AR43" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11291,7 +11294,7 @@
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="502">
+      <c r="C44" s="505">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11410,14 +11413,14 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
-      <c r="AR44" s="529" t="s">
+      <c r="AR44" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="503"/>
+      <c r="C45" s="506"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11502,14 +11505,14 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
-      <c r="AR45" s="529" t="s">
+      <c r="AR45" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="504"/>
+      <c r="C46" s="507"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11594,7 +11597,7 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
-      <c r="AR46" s="529" t="s">
+      <c r="AR46" t="s">
         <v>973</v>
       </c>
     </row>
@@ -11605,7 +11608,7 @@
       <c r="B47" s="454" t="s">
         <v>912</v>
       </c>
-      <c r="C47" s="468">
+      <c r="C47" s="508">
         <v>32</v>
       </c>
       <c r="D47" s="299" t="s">
@@ -11724,14 +11727,14 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
-      <c r="AR47" s="529" t="s">
+      <c r="AR47" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="457"/>
       <c r="B48" s="454"/>
-      <c r="C48" s="469"/>
+      <c r="C48" s="509"/>
       <c r="D48" s="299"/>
       <c r="E48" s="84"/>
       <c r="F48" s="235"/>
@@ -11814,14 +11817,14 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
-      <c r="AR48" s="529" t="s">
+      <c r="AR48" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
       <c r="B49" s="454"/>
-      <c r="C49" s="469"/>
+      <c r="C49" s="509"/>
       <c r="D49" s="299"/>
       <c r="E49" s="84"/>
       <c r="F49" s="235"/>
@@ -11904,14 +11907,14 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
-      <c r="AR49" s="529" t="s">
+      <c r="AR49" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="470"/>
+      <c r="C50" s="510"/>
       <c r="D50" s="312"/>
       <c r="E50" s="85"/>
       <c r="F50" s="236"/>
@@ -11994,7 +11997,7 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
-      <c r="AR50" s="529" t="s">
+      <c r="AR50" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12005,7 +12008,7 @@
       <c r="B51" s="454" t="s">
         <v>913</v>
       </c>
-      <c r="C51" s="468">
+      <c r="C51" s="508">
         <v>33</v>
       </c>
       <c r="D51" s="299" t="s">
@@ -12126,14 +12129,14 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
-      <c r="AR51" s="529" t="s">
+      <c r="AR51" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="457"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="469"/>
+      <c r="C52" s="509"/>
       <c r="D52" s="299"/>
       <c r="E52" s="84"/>
       <c r="F52" s="235"/>
@@ -12218,14 +12221,14 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
-      <c r="AR52" s="529" t="s">
+      <c r="AR52" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
       <c r="B53" s="454"/>
-      <c r="C53" s="469"/>
+      <c r="C53" s="509"/>
       <c r="D53" s="299"/>
       <c r="E53" s="84"/>
       <c r="F53" s="235"/>
@@ -12306,14 +12309,14 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
-      <c r="AR53" s="529" t="s">
+      <c r="AR53" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
       <c r="B54" s="454"/>
-      <c r="C54" s="470"/>
+      <c r="C54" s="510"/>
       <c r="D54" s="312"/>
       <c r="E54" s="85"/>
       <c r="F54" s="236"/>
@@ -12392,7 +12395,7 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
-      <c r="AR54" s="529" t="s">
+      <c r="AR54" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12403,7 +12406,7 @@
       <c r="B55" s="454" t="s">
         <v>914</v>
       </c>
-      <c r="C55" s="468">
+      <c r="C55" s="508">
         <v>34</v>
       </c>
       <c r="D55" s="299" t="s">
@@ -12518,14 +12521,14 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
-      <c r="AR55" s="529" t="s">
+      <c r="AR55" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="457"/>
       <c r="B56" s="454"/>
-      <c r="C56" s="469"/>
+      <c r="C56" s="509"/>
       <c r="D56" s="299"/>
       <c r="E56" s="84"/>
       <c r="F56" s="235"/>
@@ -12606,14 +12609,14 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
-      <c r="AR56" s="529" t="s">
+      <c r="AR56" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
       <c r="B57" s="454"/>
-      <c r="C57" s="469"/>
+      <c r="C57" s="509"/>
       <c r="D57" s="299"/>
       <c r="E57" s="84"/>
       <c r="F57" s="235"/>
@@ -12694,14 +12697,14 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
-      <c r="AR57" s="529" t="s">
+      <c r="AR57" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
       <c r="B58" s="454"/>
-      <c r="C58" s="469"/>
+      <c r="C58" s="509"/>
       <c r="D58" s="299"/>
       <c r="E58" s="84"/>
       <c r="F58" s="235"/>
@@ -12782,14 +12785,14 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
-      <c r="AR58" s="529" t="s">
+      <c r="AR58" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
       <c r="B59" s="454"/>
-      <c r="C59" s="469"/>
+      <c r="C59" s="509"/>
       <c r="D59" s="299"/>
       <c r="E59" s="89"/>
       <c r="F59" s="237"/>
@@ -12870,7 +12873,7 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
-      <c r="AR59" s="529" t="s">
+      <c r="AR59" t="s">
         <v>973</v>
       </c>
     </row>
@@ -12881,7 +12884,7 @@
       <c r="B60" s="454" t="s">
         <v>915</v>
       </c>
-      <c r="C60" s="469"/>
+      <c r="C60" s="509"/>
       <c r="D60" s="299" t="s">
         <v>738</v>
       </c>
@@ -12996,14 +12999,14 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
-      <c r="AR60" s="529" t="s">
+      <c r="AR60" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="457"/>
       <c r="B61" s="454"/>
-      <c r="C61" s="469"/>
+      <c r="C61" s="509"/>
       <c r="D61" s="299"/>
       <c r="E61" s="84"/>
       <c r="F61" s="235"/>
@@ -13084,14 +13087,14 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
-      <c r="AR61" s="529" t="s">
+      <c r="AR61" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
       <c r="B62" s="454"/>
-      <c r="C62" s="469"/>
+      <c r="C62" s="509"/>
       <c r="D62" s="299"/>
       <c r="E62" s="84"/>
       <c r="F62" s="235"/>
@@ -13172,14 +13175,14 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
-      <c r="AR62" s="529" t="s">
+      <c r="AR62" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
       <c r="B63" s="454"/>
-      <c r="C63" s="470"/>
+      <c r="C63" s="510"/>
       <c r="D63" s="312"/>
       <c r="E63" s="85"/>
       <c r="F63" s="236"/>
@@ -13260,7 +13263,7 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
-      <c r="AR63" s="529" t="s">
+      <c r="AR63" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13271,7 +13274,7 @@
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="505">
+      <c r="C64" s="511">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13390,14 +13393,14 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
-      <c r="AR64" s="529" t="s">
+      <c r="AR64" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="506"/>
+      <c r="C65" s="512"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13482,14 +13485,14 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
-      <c r="AR65" s="529" t="s">
+      <c r="AR65" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="507"/>
+      <c r="C66" s="513"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13574,7 +13577,7 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
-      <c r="AR66" s="529" t="s">
+      <c r="AR66" t="s">
         <v>974</v>
       </c>
     </row>
@@ -13585,7 +13588,7 @@
       <c r="B67" s="454" t="s">
         <v>917</v>
       </c>
-      <c r="C67" s="471">
+      <c r="C67" s="514">
         <v>42</v>
       </c>
       <c r="D67" s="300" t="s">
@@ -13704,14 +13707,14 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
-      <c r="AR67" s="529" t="s">
+      <c r="AR67" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="457"/>
       <c r="B68" s="454"/>
-      <c r="C68" s="472"/>
+      <c r="C68" s="515"/>
       <c r="D68" s="300"/>
       <c r="E68" s="96"/>
       <c r="F68" s="238"/>
@@ -13794,14 +13797,14 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
-      <c r="AR68" s="529" t="s">
+      <c r="AR68" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
       <c r="B69" s="454"/>
-      <c r="C69" s="472"/>
+      <c r="C69" s="515"/>
       <c r="D69" s="300"/>
       <c r="E69" s="100"/>
       <c r="F69" s="240"/>
@@ -13884,7 +13887,7 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
-      <c r="AR69" s="529" t="s">
+      <c r="AR69" t="s">
         <v>974</v>
       </c>
     </row>
@@ -13895,7 +13898,7 @@
       <c r="B70" s="454" t="s">
         <v>918</v>
       </c>
-      <c r="C70" s="472"/>
+      <c r="C70" s="515"/>
       <c r="D70" s="300" t="s">
         <v>739</v>
       </c>
@@ -14008,14 +14011,14 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
-      <c r="AR70" s="529" t="s">
+      <c r="AR70" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="457"/>
       <c r="B71" s="454"/>
-      <c r="C71" s="472"/>
+      <c r="C71" s="515"/>
       <c r="D71" s="300"/>
       <c r="E71" s="96"/>
       <c r="F71" s="238"/>
@@ -14096,14 +14099,14 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
-      <c r="AR71" s="529" t="s">
+      <c r="AR71" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
       <c r="B72" s="454"/>
-      <c r="C72" s="472"/>
+      <c r="C72" s="515"/>
       <c r="D72" s="300"/>
       <c r="E72" s="96"/>
       <c r="F72" s="238"/>
@@ -14184,14 +14187,14 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
-      <c r="AR72" s="529" t="s">
+      <c r="AR72" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
       <c r="B73" s="454"/>
-      <c r="C73" s="472"/>
+      <c r="C73" s="515"/>
       <c r="D73" s="300"/>
       <c r="E73" s="96"/>
       <c r="F73" s="238"/>
@@ -14272,14 +14275,14 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
-      <c r="AR73" s="529" t="s">
+      <c r="AR73" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
       <c r="B74" s="454"/>
-      <c r="C74" s="473"/>
+      <c r="C74" s="516"/>
       <c r="D74" s="313"/>
       <c r="E74" s="97"/>
       <c r="F74" s="239"/>
@@ -14360,7 +14363,7 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
-      <c r="AR74" s="529" t="s">
+      <c r="AR74" t="s">
         <v>974</v>
       </c>
     </row>
@@ -14371,7 +14374,7 @@
       <c r="B75" s="454" t="s">
         <v>919</v>
       </c>
-      <c r="C75" s="471">
+      <c r="C75" s="514">
         <v>43</v>
       </c>
       <c r="D75" s="300" t="s">
@@ -14488,14 +14491,14 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
-      <c r="AR75" s="529" t="s">
+      <c r="AR75" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="457"/>
       <c r="B76" s="454"/>
-      <c r="C76" s="472"/>
+      <c r="C76" s="515"/>
       <c r="D76" s="300"/>
       <c r="E76" s="96"/>
       <c r="F76" s="238"/>
@@ -14576,14 +14579,14 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
-      <c r="AR76" s="529" t="s">
+      <c r="AR76" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
       <c r="B77" s="454"/>
-      <c r="C77" s="472"/>
+      <c r="C77" s="515"/>
       <c r="D77" s="300"/>
       <c r="E77" s="96"/>
       <c r="F77" s="238"/>
@@ -14664,14 +14667,14 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
-      <c r="AR77" s="529" t="s">
+      <c r="AR77" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
       <c r="B78" s="454"/>
-      <c r="C78" s="472"/>
+      <c r="C78" s="515"/>
       <c r="D78" s="300"/>
       <c r="E78" s="96"/>
       <c r="F78" s="238"/>
@@ -14752,14 +14755,14 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
-      <c r="AR78" s="529" t="s">
+      <c r="AR78" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
       <c r="B79" s="454"/>
-      <c r="C79" s="472"/>
+      <c r="C79" s="515"/>
       <c r="D79" s="300"/>
       <c r="E79" s="100"/>
       <c r="F79" s="240"/>
@@ -14840,7 +14843,7 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
-      <c r="AR79" s="529" t="s">
+      <c r="AR79" t="s">
         <v>974</v>
       </c>
     </row>
@@ -14851,7 +14854,7 @@
       <c r="B80" s="454" t="s">
         <v>920</v>
       </c>
-      <c r="C80" s="472"/>
+      <c r="C80" s="515"/>
       <c r="D80" s="300" t="s">
         <v>739</v>
       </c>
@@ -14962,14 +14965,14 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
-      <c r="AR80" s="529" t="s">
+      <c r="AR80" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="81" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A81" s="457"/>
       <c r="B81" s="454"/>
-      <c r="C81" s="472"/>
+      <c r="C81" s="515"/>
       <c r="D81" s="300"/>
       <c r="E81" s="96"/>
       <c r="F81" s="238"/>
@@ -15050,14 +15053,14 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
-      <c r="AR81" s="529" t="s">
+      <c r="AR81" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
       <c r="B82" s="454"/>
-      <c r="C82" s="473"/>
+      <c r="C82" s="516"/>
       <c r="D82" s="313"/>
       <c r="E82" s="97"/>
       <c r="F82" s="239"/>
@@ -15136,7 +15139,7 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
-      <c r="AR82" s="529" t="s">
+      <c r="AR82" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15147,7 +15150,7 @@
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="508">
+      <c r="C83" s="517">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -15268,14 +15271,14 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
-      <c r="AR83" s="529" t="s">
+      <c r="AR83" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="509"/>
+      <c r="C84" s="518"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -15360,14 +15363,14 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
-      <c r="AR84" s="529" t="s">
+      <c r="AR84" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="510"/>
+      <c r="C85" s="519"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15450,7 +15453,7 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
-      <c r="AR85" s="529" t="s">
+      <c r="AR85" t="s">
         <v>975</v>
       </c>
     </row>
@@ -15461,7 +15464,7 @@
       <c r="B86" s="454" t="s">
         <v>922</v>
       </c>
-      <c r="C86" s="474">
+      <c r="C86" s="520">
         <v>52</v>
       </c>
       <c r="D86" s="301" t="s">
@@ -15580,14 +15583,14 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
-      <c r="AR86" s="529" t="s">
+      <c r="AR86" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="87" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A87" s="457"/>
       <c r="B87" s="454"/>
-      <c r="C87" s="475"/>
+      <c r="C87" s="521"/>
       <c r="D87" s="301"/>
       <c r="E87" s="110"/>
       <c r="F87" s="241"/>
@@ -15672,14 +15675,14 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
-      <c r="AR87" s="529" t="s">
+      <c r="AR87" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
       <c r="B88" s="454"/>
-      <c r="C88" s="475"/>
+      <c r="C88" s="521"/>
       <c r="D88" s="301"/>
       <c r="E88" s="110"/>
       <c r="F88" s="241"/>
@@ -15764,14 +15767,14 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
-      <c r="AR88" s="529" t="s">
+      <c r="AR88" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
       <c r="B89" s="454"/>
-      <c r="C89" s="475"/>
+      <c r="C89" s="521"/>
       <c r="D89" s="301"/>
       <c r="E89" s="115"/>
       <c r="F89" s="243"/>
@@ -15856,7 +15859,7 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
-      <c r="AR89" s="529" t="s">
+      <c r="AR89" t="s">
         <v>975</v>
       </c>
     </row>
@@ -15867,7 +15870,7 @@
       <c r="B90" s="454" t="s">
         <v>923</v>
       </c>
-      <c r="C90" s="475"/>
+      <c r="C90" s="521"/>
       <c r="D90" s="301" t="s">
         <v>740</v>
       </c>
@@ -15984,14 +15987,14 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
-      <c r="AR90" s="529" t="s">
+      <c r="AR90" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="91" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A91" s="457"/>
       <c r="B91" s="454"/>
-      <c r="C91" s="475"/>
+      <c r="C91" s="521"/>
       <c r="D91" s="301"/>
       <c r="E91" s="110"/>
       <c r="F91" s="241"/>
@@ -16074,14 +16077,14 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
-      <c r="AR91" s="529" t="s">
+      <c r="AR91" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
       <c r="B92" s="454"/>
-      <c r="C92" s="475"/>
+      <c r="C92" s="521"/>
       <c r="D92" s="301"/>
       <c r="E92" s="110"/>
       <c r="F92" s="241"/>
@@ -16164,14 +16167,14 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
-      <c r="AR92" s="529" t="s">
+      <c r="AR92" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
       <c r="B93" s="454"/>
-      <c r="C93" s="475"/>
+      <c r="C93" s="521"/>
       <c r="D93" s="301"/>
       <c r="E93" s="115"/>
       <c r="F93" s="243"/>
@@ -16254,7 +16257,7 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
-      <c r="AR93" s="529" t="s">
+      <c r="AR93" t="s">
         <v>975</v>
       </c>
     </row>
@@ -16265,7 +16268,7 @@
       <c r="B94" s="454" t="s">
         <v>924</v>
       </c>
-      <c r="C94" s="475"/>
+      <c r="C94" s="521"/>
       <c r="D94" s="301" t="s">
         <v>740</v>
       </c>
@@ -16382,14 +16385,14 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR94" s="529" t="s">
+      <c r="AR94" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="95" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A95" s="457"/>
       <c r="B95" s="454"/>
-      <c r="C95" s="475"/>
+      <c r="C95" s="521"/>
       <c r="D95" s="301"/>
       <c r="E95" s="110"/>
       <c r="F95" s="241"/>
@@ -16472,14 +16475,14 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
-      <c r="AR95" s="529" t="s">
+      <c r="AR95" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
       <c r="B96" s="454"/>
-      <c r="C96" s="475"/>
+      <c r="C96" s="521"/>
       <c r="D96" s="301"/>
       <c r="E96" s="110"/>
       <c r="F96" s="241"/>
@@ -16562,14 +16565,14 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
-      <c r="AR96" s="529" t="s">
+      <c r="AR96" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
       <c r="B97" s="454"/>
-      <c r="C97" s="476"/>
+      <c r="C97" s="522"/>
       <c r="D97" s="314"/>
       <c r="E97" s="111"/>
       <c r="F97" s="242"/>
@@ -16652,7 +16655,7 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
-      <c r="AR97" s="529" t="s">
+      <c r="AR97" t="s">
         <v>975</v>
       </c>
     </row>
@@ -16663,7 +16666,7 @@
       <c r="B98" s="454" t="s">
         <v>925</v>
       </c>
-      <c r="C98" s="474">
+      <c r="C98" s="520">
         <v>53</v>
       </c>
       <c r="D98" s="301" t="s">
@@ -16780,14 +16783,14 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
-      <c r="AR98" s="529" t="s">
+      <c r="AR98" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="99" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A99" s="457"/>
       <c r="B99" s="454"/>
-      <c r="C99" s="475"/>
+      <c r="C99" s="521"/>
       <c r="D99" s="301"/>
       <c r="E99" s="110"/>
       <c r="F99" s="241"/>
@@ -16870,14 +16873,14 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
-      <c r="AR99" s="529" t="s">
+      <c r="AR99" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
       <c r="B100" s="454"/>
-      <c r="C100" s="475"/>
+      <c r="C100" s="521"/>
       <c r="D100" s="301"/>
       <c r="E100" s="110"/>
       <c r="F100" s="241"/>
@@ -16958,14 +16961,14 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
-      <c r="AR100" s="529" t="s">
+      <c r="AR100" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
       <c r="B101" s="454"/>
-      <c r="C101" s="476"/>
+      <c r="C101" s="522"/>
       <c r="D101" s="301"/>
       <c r="E101" s="111"/>
       <c r="F101" s="242"/>
@@ -17048,7 +17051,7 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
-      <c r="AR101" s="529" t="s">
+      <c r="AR101" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17059,7 +17062,7 @@
       <c r="B102" s="454" t="s">
         <v>926</v>
       </c>
-      <c r="C102" s="465">
+      <c r="C102" s="478">
         <v>61</v>
       </c>
       <c r="D102" s="323" t="s">
@@ -17172,14 +17175,14 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
-      <c r="AR102" s="529" t="s">
+      <c r="AR102" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="103" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A103" s="457"/>
       <c r="B103" s="454"/>
-      <c r="C103" s="466"/>
+      <c r="C103" s="479"/>
       <c r="D103" s="323"/>
       <c r="E103" s="329"/>
       <c r="F103" s="330"/>
@@ -17260,14 +17263,14 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
-      <c r="AR103" s="529" t="s">
+      <c r="AR103" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
       <c r="B104" s="454"/>
-      <c r="C104" s="466"/>
+      <c r="C104" s="479"/>
       <c r="D104" s="323"/>
       <c r="E104" s="329"/>
       <c r="F104" s="330"/>
@@ -17348,14 +17351,14 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
-      <c r="AR104" s="529" t="s">
+      <c r="AR104" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
       <c r="B105" s="454"/>
-      <c r="C105" s="467"/>
+      <c r="C105" s="480"/>
       <c r="D105" s="331"/>
       <c r="E105" s="332"/>
       <c r="F105" s="333"/>
@@ -17436,7 +17439,7 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
-      <c r="AR105" s="529" t="s">
+      <c r="AR105" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17447,7 +17450,7 @@
       <c r="B106" s="454" t="s">
         <v>927</v>
       </c>
-      <c r="C106" s="465">
+      <c r="C106" s="478">
         <v>62</v>
       </c>
       <c r="D106" s="323" t="s">
@@ -17564,14 +17567,14 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
-      <c r="AR106" s="529" t="s">
+      <c r="AR106" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="107" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A107" s="457"/>
       <c r="B107" s="454"/>
-      <c r="C107" s="466"/>
+      <c r="C107" s="479"/>
       <c r="D107" s="323"/>
       <c r="E107" s="329"/>
       <c r="F107" s="330"/>
@@ -17652,14 +17655,14 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
-      <c r="AR107" s="529" t="s">
+      <c r="AR107" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
       <c r="B108" s="454"/>
-      <c r="C108" s="466"/>
+      <c r="C108" s="479"/>
       <c r="D108" s="323"/>
       <c r="E108" s="329"/>
       <c r="F108" s="330"/>
@@ -17740,14 +17743,14 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
-      <c r="AR108" s="529" t="s">
+      <c r="AR108" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
       <c r="B109" s="454"/>
-      <c r="C109" s="466"/>
+      <c r="C109" s="479"/>
       <c r="D109" s="323"/>
       <c r="E109" s="338"/>
       <c r="F109" s="339"/>
@@ -17828,7 +17831,7 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
-      <c r="AR109" s="529" t="s">
+      <c r="AR109" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17839,7 +17842,7 @@
       <c r="B110" s="454" t="s">
         <v>928</v>
       </c>
-      <c r="C110" s="466"/>
+      <c r="C110" s="479"/>
       <c r="D110" s="323" t="s">
         <v>741</v>
       </c>
@@ -17954,14 +17957,14 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
-      <c r="AR110" s="529" t="s">
+      <c r="AR110" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="111" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A111" s="457"/>
       <c r="B111" s="454"/>
-      <c r="C111" s="466"/>
+      <c r="C111" s="479"/>
       <c r="D111" s="323"/>
       <c r="E111" s="329"/>
       <c r="F111" s="330"/>
@@ -18042,14 +18045,14 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
-      <c r="AR111" s="529" t="s">
+      <c r="AR111" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
       <c r="B112" s="454"/>
-      <c r="C112" s="466"/>
+      <c r="C112" s="479"/>
       <c r="D112" s="323"/>
       <c r="E112" s="329"/>
       <c r="F112" s="330"/>
@@ -18130,14 +18133,14 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
-      <c r="AR112" s="529" t="s">
+      <c r="AR112" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
       <c r="B113" s="454"/>
-      <c r="C113" s="466"/>
+      <c r="C113" s="479"/>
       <c r="D113" s="323"/>
       <c r="E113" s="329"/>
       <c r="F113" s="330"/>
@@ -18218,14 +18221,14 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
-      <c r="AR113" s="529" t="s">
+      <c r="AR113" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
       <c r="B114" s="454"/>
-      <c r="C114" s="467"/>
+      <c r="C114" s="480"/>
       <c r="D114" s="331"/>
       <c r="E114" s="332"/>
       <c r="F114" s="333"/>
@@ -18304,7 +18307,7 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
-      <c r="AR114" s="529" t="s">
+      <c r="AR114" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18315,7 +18318,7 @@
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="511">
+      <c r="C115" s="481">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -18432,14 +18435,14 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR115" s="529" t="s">
+      <c r="AR115" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="512"/>
+      <c r="C116" s="482"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -18520,14 +18523,14 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
-      <c r="AR116" s="529" t="s">
+      <c r="AR116" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="512"/>
+      <c r="C117" s="482"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18608,14 +18611,14 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
-      <c r="AR117" s="529" t="s">
+      <c r="AR117" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="512"/>
+      <c r="C118" s="482"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18696,7 +18699,7 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
-      <c r="AR118" s="529" t="s">
+      <c r="AR118" t="s">
         <v>977</v>
       </c>
     </row>
@@ -18707,7 +18710,7 @@
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="512"/>
+      <c r="C119" s="482"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18820,14 +18823,14 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
-      <c r="AR119" s="529" t="s">
+      <c r="AR119" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="512"/>
+      <c r="C120" s="482"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18908,14 +18911,14 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
-      <c r="AR120" s="529" t="s">
+      <c r="AR120" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="512"/>
+      <c r="C121" s="482"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -18996,14 +18999,14 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
-      <c r="AR121" s="529" t="s">
+      <c r="AR121" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="513"/>
+      <c r="C122" s="483"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -19084,7 +19087,7 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
-      <c r="AR122" s="529" t="s">
+      <c r="AR122" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19095,7 +19098,7 @@
       <c r="B123" s="454" t="s">
         <v>931</v>
       </c>
-      <c r="C123" s="480">
+      <c r="C123" s="484">
         <v>72</v>
       </c>
       <c r="D123" s="302" t="s">
@@ -19210,14 +19213,14 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
-      <c r="AR123" s="529" t="s">
+      <c r="AR123" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="124" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A124" s="457"/>
       <c r="B124" s="454"/>
-      <c r="C124" s="481"/>
+      <c r="C124" s="485"/>
       <c r="D124" s="302"/>
       <c r="E124" s="125"/>
       <c r="F124" s="244"/>
@@ -19298,14 +19301,14 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
-      <c r="AR124" s="529" t="s">
+      <c r="AR124" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
       <c r="B125" s="454"/>
-      <c r="C125" s="481"/>
+      <c r="C125" s="485"/>
       <c r="D125" s="302"/>
       <c r="E125" s="125"/>
       <c r="F125" s="244"/>
@@ -19386,14 +19389,14 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
-      <c r="AR125" s="529" t="s">
+      <c r="AR125" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
       <c r="B126" s="454"/>
-      <c r="C126" s="481"/>
+      <c r="C126" s="485"/>
       <c r="D126" s="302"/>
       <c r="E126" s="125"/>
       <c r="F126" s="244"/>
@@ -19474,14 +19477,14 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
-      <c r="AR126" s="529" t="s">
+      <c r="AR126" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
       <c r="B127" s="454"/>
-      <c r="C127" s="481"/>
+      <c r="C127" s="485"/>
       <c r="D127" s="302"/>
       <c r="E127" s="126"/>
       <c r="F127" s="245"/>
@@ -19562,7 +19565,7 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
-      <c r="AR127" s="529" t="s">
+      <c r="AR127" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19573,7 +19576,7 @@
       <c r="B128" s="454" t="s">
         <v>932</v>
       </c>
-      <c r="C128" s="481"/>
+      <c r="C128" s="485"/>
       <c r="D128" s="302" t="s">
         <v>742</v>
       </c>
@@ -19690,14 +19693,14 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
-      <c r="AR128" s="529" t="s">
+      <c r="AR128" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="129" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A129" s="457"/>
       <c r="B129" s="454"/>
-      <c r="C129" s="481"/>
+      <c r="C129" s="485"/>
       <c r="D129" s="302"/>
       <c r="E129" s="125"/>
       <c r="F129" s="244"/>
@@ -19782,14 +19785,14 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
-      <c r="AR129" s="529" t="s">
+      <c r="AR129" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
       <c r="B130" s="454"/>
-      <c r="C130" s="481"/>
+      <c r="C130" s="485"/>
       <c r="D130" s="302"/>
       <c r="E130" s="125"/>
       <c r="F130" s="244"/>
@@ -19874,14 +19877,14 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
-      <c r="AR130" s="529" t="s">
+      <c r="AR130" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
       <c r="B131" s="454"/>
-      <c r="C131" s="482"/>
+      <c r="C131" s="486"/>
       <c r="D131" s="315"/>
       <c r="E131" s="129"/>
       <c r="F131" s="246"/>
@@ -19958,7 +19961,7 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
-      <c r="AR131" s="529" t="s">
+      <c r="AR131" t="s">
         <v>977</v>
       </c>
     </row>
@@ -19969,7 +19972,7 @@
       <c r="B132" s="454" t="s">
         <v>933</v>
       </c>
-      <c r="C132" s="480">
+      <c r="C132" s="484">
         <v>73</v>
       </c>
       <c r="D132" s="302" t="s">
@@ -20086,14 +20089,14 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR132" s="529" t="s">
+      <c r="AR132" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="133" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A133" s="457"/>
       <c r="B133" s="454"/>
-      <c r="C133" s="481"/>
+      <c r="C133" s="485"/>
       <c r="D133" s="302"/>
       <c r="E133" s="125"/>
       <c r="F133" s="244"/>
@@ -20174,14 +20177,14 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
-      <c r="AR133" s="529" t="s">
+      <c r="AR133" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
       <c r="B134" s="454"/>
-      <c r="C134" s="481"/>
+      <c r="C134" s="485"/>
       <c r="D134" s="302"/>
       <c r="E134" s="125"/>
       <c r="F134" s="244"/>
@@ -20262,14 +20265,14 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
-      <c r="AR134" s="529" t="s">
+      <c r="AR134" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
       <c r="B135" s="454"/>
-      <c r="C135" s="481"/>
+      <c r="C135" s="485"/>
       <c r="D135" s="302"/>
       <c r="E135" s="126"/>
       <c r="F135" s="245"/>
@@ -20350,7 +20353,7 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
-      <c r="AR135" s="529" t="s">
+      <c r="AR135" t="s">
         <v>977</v>
       </c>
     </row>
@@ -20361,7 +20364,7 @@
       <c r="B136" s="454" t="s">
         <v>934</v>
       </c>
-      <c r="C136" s="481"/>
+      <c r="C136" s="485"/>
       <c r="D136" s="302" t="s">
         <v>742</v>
       </c>
@@ -20476,14 +20479,14 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
-      <c r="AR136" s="529" t="s">
+      <c r="AR136" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="137" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A137" s="457"/>
       <c r="B137" s="454"/>
-      <c r="C137" s="481"/>
+      <c r="C137" s="485"/>
       <c r="D137" s="302"/>
       <c r="E137" s="125"/>
       <c r="F137" s="244"/>
@@ -20564,14 +20567,14 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
-      <c r="AR137" s="529" t="s">
+      <c r="AR137" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
       <c r="B138" s="454"/>
-      <c r="C138" s="481"/>
+      <c r="C138" s="485"/>
       <c r="D138" s="302"/>
       <c r="E138" s="125"/>
       <c r="F138" s="244"/>
@@ -20652,14 +20655,14 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
-      <c r="AR138" s="529" t="s">
+      <c r="AR138" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
       <c r="B139" s="454"/>
-      <c r="C139" s="481"/>
+      <c r="C139" s="485"/>
       <c r="D139" s="302"/>
       <c r="E139" s="125"/>
       <c r="F139" s="244"/>
@@ -20740,14 +20743,14 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
-      <c r="AR139" s="529" t="s">
+      <c r="AR139" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
       <c r="B140" s="454"/>
-      <c r="C140" s="482"/>
+      <c r="C140" s="486"/>
       <c r="D140" s="315"/>
       <c r="E140" s="129"/>
       <c r="F140" s="246"/>
@@ -20826,7 +20829,7 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
-      <c r="AR140" s="529" t="s">
+      <c r="AR140" t="s">
         <v>977</v>
       </c>
     </row>
@@ -20837,7 +20840,7 @@
       <c r="B141" s="454" t="s">
         <v>935</v>
       </c>
-      <c r="C141" s="483">
+      <c r="C141" s="487">
         <v>74</v>
       </c>
       <c r="D141" s="302" t="s">
@@ -20952,14 +20955,14 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
-      <c r="AR141" s="529" t="s">
+      <c r="AR141" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="142" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A142" s="457"/>
       <c r="B142" s="454"/>
-      <c r="C142" s="484"/>
+      <c r="C142" s="488"/>
       <c r="D142" s="303"/>
       <c r="E142" s="125"/>
       <c r="F142" s="244"/>
@@ -21040,14 +21043,14 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
-      <c r="AR142" s="529" t="s">
+      <c r="AR142" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
       <c r="B143" s="454"/>
-      <c r="C143" s="484"/>
+      <c r="C143" s="488"/>
       <c r="D143" s="303"/>
       <c r="E143" s="125"/>
       <c r="F143" s="244"/>
@@ -21128,14 +21131,14 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
-      <c r="AR143" s="529" t="s">
+      <c r="AR143" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
       <c r="B144" s="454"/>
-      <c r="C144" s="484"/>
+      <c r="C144" s="488"/>
       <c r="D144" s="303"/>
       <c r="E144" s="125"/>
       <c r="F144" s="244"/>
@@ -21216,14 +21219,14 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
-      <c r="AR144" s="529" t="s">
+      <c r="AR144" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
       <c r="B145" s="454"/>
-      <c r="C145" s="484"/>
+      <c r="C145" s="488"/>
       <c r="D145" s="303"/>
       <c r="E145" s="126"/>
       <c r="F145" s="245"/>
@@ -21304,7 +21307,7 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
-      <c r="AR145" s="529" t="s">
+      <c r="AR145" t="s">
         <v>977</v>
       </c>
     </row>
@@ -21315,7 +21318,7 @@
       <c r="B146" s="454" t="s">
         <v>936</v>
       </c>
-      <c r="C146" s="484"/>
+      <c r="C146" s="488"/>
       <c r="D146" s="302" t="s">
         <v>742</v>
       </c>
@@ -21430,14 +21433,14 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
-      <c r="AR146" s="529" t="s">
+      <c r="AR146" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="147" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A147" s="457"/>
       <c r="B147" s="454"/>
-      <c r="C147" s="484"/>
+      <c r="C147" s="488"/>
       <c r="D147" s="303"/>
       <c r="E147" s="125"/>
       <c r="F147" s="244"/>
@@ -21518,14 +21521,14 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
-      <c r="AR147" s="529" t="s">
+      <c r="AR147" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
       <c r="B148" s="454"/>
-      <c r="C148" s="484"/>
+      <c r="C148" s="488"/>
       <c r="D148" s="303"/>
       <c r="E148" s="125"/>
       <c r="F148" s="244"/>
@@ -21606,14 +21609,14 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
-      <c r="AR148" s="529" t="s">
+      <c r="AR148" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
       <c r="B149" s="454"/>
-      <c r="C149" s="485"/>
+      <c r="C149" s="489"/>
       <c r="D149" s="316"/>
       <c r="E149" s="129"/>
       <c r="F149" s="246"/>
@@ -21694,7 +21697,7 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
-      <c r="AR149" s="529" t="s">
+      <c r="AR149" t="s">
         <v>977</v>
       </c>
     </row>
@@ -21705,7 +21708,7 @@
       <c r="B150" s="454" t="s">
         <v>937</v>
       </c>
-      <c r="C150" s="480">
+      <c r="C150" s="484">
         <v>75</v>
       </c>
       <c r="D150" s="302" t="s">
@@ -21820,14 +21823,14 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
-      <c r="AR150" s="529" t="s">
+      <c r="AR150" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="151" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A151" s="457"/>
       <c r="B151" s="454"/>
-      <c r="C151" s="481"/>
+      <c r="C151" s="485"/>
       <c r="D151" s="302"/>
       <c r="E151" s="125"/>
       <c r="F151" s="244"/>
@@ -21908,14 +21911,14 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
-      <c r="AR151" s="529" t="s">
+      <c r="AR151" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
       <c r="B152" s="454"/>
-      <c r="C152" s="481"/>
+      <c r="C152" s="485"/>
       <c r="D152" s="302"/>
       <c r="E152" s="125"/>
       <c r="F152" s="244"/>
@@ -21996,14 +21999,14 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
-      <c r="AR152" s="529" t="s">
+      <c r="AR152" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
       <c r="B153" s="454"/>
-      <c r="C153" s="481"/>
+      <c r="C153" s="485"/>
       <c r="D153" s="302"/>
       <c r="E153" s="126"/>
       <c r="F153" s="245"/>
@@ -22084,7 +22087,7 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
-      <c r="AR153" s="529" t="s">
+      <c r="AR153" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22095,7 +22098,7 @@
       <c r="B154" s="454" t="s">
         <v>938</v>
       </c>
-      <c r="C154" s="481"/>
+      <c r="C154" s="485"/>
       <c r="D154" s="302" t="s">
         <v>742</v>
       </c>
@@ -22208,14 +22211,14 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
-      <c r="AR154" s="529" t="s">
+      <c r="AR154" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="155" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A155" s="457"/>
       <c r="B155" s="454"/>
-      <c r="C155" s="481"/>
+      <c r="C155" s="485"/>
       <c r="D155" s="302"/>
       <c r="E155" s="125"/>
       <c r="F155" s="244"/>
@@ -22296,14 +22299,14 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
-      <c r="AR155" s="529" t="s">
+      <c r="AR155" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
       <c r="B156" s="454"/>
-      <c r="C156" s="481"/>
+      <c r="C156" s="485"/>
       <c r="D156" s="302"/>
       <c r="E156" s="125"/>
       <c r="F156" s="244"/>
@@ -22384,14 +22387,14 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
-      <c r="AR156" s="529" t="s">
+      <c r="AR156" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
       <c r="B157" s="454"/>
-      <c r="C157" s="481"/>
+      <c r="C157" s="485"/>
       <c r="D157" s="302"/>
       <c r="E157" s="125"/>
       <c r="F157" s="244"/>
@@ -22472,14 +22475,14 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
-      <c r="AR157" s="529" t="s">
+      <c r="AR157" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
       <c r="B158" s="454"/>
-      <c r="C158" s="482"/>
+      <c r="C158" s="486"/>
       <c r="D158" s="315"/>
       <c r="E158" s="129"/>
       <c r="F158" s="246"/>
@@ -22558,7 +22561,7 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
-      <c r="AR158" s="529" t="s">
+      <c r="AR158" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22569,7 +22572,7 @@
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="514">
+      <c r="C159" s="490">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22686,14 +22689,14 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
-      <c r="AR159" s="529" t="s">
+      <c r="AR159" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="515"/>
+      <c r="C160" s="491"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22774,14 +22777,14 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
-      <c r="AR160" s="529" t="s">
+      <c r="AR160" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="515"/>
+      <c r="C161" s="491"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22862,14 +22865,14 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
-      <c r="AR161" s="529" t="s">
+      <c r="AR161" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="515"/>
+      <c r="C162" s="491"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22950,7 +22953,7 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
-      <c r="AR162" s="529" t="s">
+      <c r="AR162" t="s">
         <v>978</v>
       </c>
     </row>
@@ -22961,7 +22964,7 @@
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="515"/>
+      <c r="C163" s="491"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -23076,14 +23079,14 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
-      <c r="AR163" s="529" t="s">
+      <c r="AR163" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="515"/>
+      <c r="C164" s="491"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -23164,14 +23167,14 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
-      <c r="AR164" s="529" t="s">
+      <c r="AR164" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="515"/>
+      <c r="C165" s="491"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -23252,14 +23255,14 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
-      <c r="AR165" s="529" t="s">
+      <c r="AR165" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="515"/>
+      <c r="C166" s="491"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -23340,7 +23343,7 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
-      <c r="AR166" s="529" t="s">
+      <c r="AR166" t="s">
         <v>978</v>
       </c>
     </row>
@@ -23351,7 +23354,7 @@
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="515"/>
+      <c r="C167" s="491"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -23466,14 +23469,14 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
-      <c r="AR167" s="529" t="s">
+      <c r="AR167" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="515"/>
+      <c r="C168" s="491"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -23554,14 +23557,14 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
-      <c r="AR168" s="529" t="s">
+      <c r="AR168" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="515"/>
+      <c r="C169" s="491"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -23642,14 +23645,14 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
-      <c r="AR169" s="529" t="s">
+      <c r="AR169" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="516"/>
+      <c r="C170" s="492"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23730,7 +23733,7 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
-      <c r="AR170" s="529" t="s">
+      <c r="AR170" t="s">
         <v>978</v>
       </c>
     </row>
@@ -23741,7 +23744,7 @@
       <c r="B171" s="454" t="s">
         <v>942</v>
       </c>
-      <c r="C171" s="486">
+      <c r="C171" s="493">
         <v>82</v>
       </c>
       <c r="D171" s="304" t="s">
@@ -23858,14 +23861,14 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR171" s="529" t="s">
+      <c r="AR171" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="172" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A172" s="457"/>
       <c r="B172" s="454"/>
-      <c r="C172" s="487"/>
+      <c r="C172" s="494"/>
       <c r="D172" s="304"/>
       <c r="E172" s="137"/>
       <c r="F172" s="247"/>
@@ -23946,14 +23949,14 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
-      <c r="AR172" s="529" t="s">
+      <c r="AR172" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
       <c r="B173" s="454"/>
-      <c r="C173" s="487"/>
+      <c r="C173" s="494"/>
       <c r="D173" s="304"/>
       <c r="E173" s="137"/>
       <c r="F173" s="247"/>
@@ -24034,14 +24037,14 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
-      <c r="AR173" s="529" t="s">
+      <c r="AR173" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
       <c r="B174" s="454"/>
-      <c r="C174" s="487"/>
+      <c r="C174" s="494"/>
       <c r="D174" s="304"/>
       <c r="E174" s="138"/>
       <c r="F174" s="248"/>
@@ -24124,7 +24127,7 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
-      <c r="AR174" s="529" t="s">
+      <c r="AR174" t="s">
         <v>978</v>
       </c>
     </row>
@@ -24135,7 +24138,7 @@
       <c r="B175" s="454" t="s">
         <v>943</v>
       </c>
-      <c r="C175" s="487"/>
+      <c r="C175" s="494"/>
       <c r="D175" s="304" t="s">
         <v>743</v>
       </c>
@@ -24250,14 +24253,14 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
-      <c r="AR175" s="529" t="s">
+      <c r="AR175" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="176" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A176" s="457"/>
       <c r="B176" s="454"/>
-      <c r="C176" s="487"/>
+      <c r="C176" s="494"/>
       <c r="D176" s="304"/>
       <c r="E176" s="137"/>
       <c r="F176" s="247"/>
@@ -24344,14 +24347,14 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
-      <c r="AR176" s="529" t="s">
+      <c r="AR176" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
       <c r="B177" s="454"/>
-      <c r="C177" s="487"/>
+      <c r="C177" s="494"/>
       <c r="D177" s="304"/>
       <c r="E177" s="137"/>
       <c r="F177" s="247"/>
@@ -24436,14 +24439,14 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
-      <c r="AR177" s="529" t="s">
+      <c r="AR177" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
       <c r="B178" s="454"/>
-      <c r="C178" s="487"/>
+      <c r="C178" s="494"/>
       <c r="D178" s="304"/>
       <c r="E178" s="138"/>
       <c r="F178" s="248"/>
@@ -24526,7 +24529,7 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
-      <c r="AR178" s="529" t="s">
+      <c r="AR178" t="s">
         <v>978</v>
       </c>
     </row>
@@ -24537,7 +24540,7 @@
       <c r="B179" s="454" t="s">
         <v>944</v>
       </c>
-      <c r="C179" s="487"/>
+      <c r="C179" s="494"/>
       <c r="D179" s="304" t="s">
         <v>743</v>
       </c>
@@ -24652,14 +24655,14 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR179" s="529" t="s">
+      <c r="AR179" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="180" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A180" s="457"/>
       <c r="B180" s="454"/>
-      <c r="C180" s="487"/>
+      <c r="C180" s="494"/>
       <c r="D180" s="304"/>
       <c r="E180" s="137"/>
       <c r="F180" s="247"/>
@@ -24740,14 +24743,14 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
-      <c r="AR180" s="529" t="s">
+      <c r="AR180" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
       <c r="B181" s="454"/>
-      <c r="C181" s="487"/>
+      <c r="C181" s="494"/>
       <c r="D181" s="304"/>
       <c r="E181" s="137"/>
       <c r="F181" s="247"/>
@@ -24828,14 +24831,14 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
-      <c r="AR181" s="529" t="s">
+      <c r="AR181" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
       <c r="B182" s="454"/>
-      <c r="C182" s="487"/>
+      <c r="C182" s="494"/>
       <c r="D182" s="304"/>
       <c r="E182" s="137"/>
       <c r="F182" s="247"/>
@@ -24916,14 +24919,14 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
-      <c r="AR182" s="529" t="s">
+      <c r="AR182" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
       <c r="B183" s="454"/>
-      <c r="C183" s="488"/>
+      <c r="C183" s="495"/>
       <c r="D183" s="317"/>
       <c r="E183" s="141"/>
       <c r="F183" s="249"/>
@@ -25004,7 +25007,7 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
-      <c r="AR183" s="529" t="s">
+      <c r="AR183" t="s">
         <v>978</v>
       </c>
     </row>
@@ -25015,7 +25018,7 @@
       <c r="B184" s="454">
         <v>831</v>
       </c>
-      <c r="C184" s="486">
+      <c r="C184" s="493">
         <v>83</v>
       </c>
       <c r="D184" s="304" t="s">
@@ -25132,14 +25135,14 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
-      <c r="AR184" s="529" t="s">
+      <c r="AR184" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="185" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A185" s="457"/>
       <c r="B185" s="454"/>
-      <c r="C185" s="487"/>
+      <c r="C185" s="494"/>
       <c r="D185" s="304"/>
       <c r="E185" s="137"/>
       <c r="F185" s="247"/>
@@ -25222,14 +25225,14 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
-      <c r="AR185" s="529" t="s">
+      <c r="AR185" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
       <c r="B186" s="454"/>
-      <c r="C186" s="487"/>
+      <c r="C186" s="494"/>
       <c r="D186" s="304"/>
       <c r="E186" s="137"/>
       <c r="F186" s="247"/>
@@ -25310,14 +25313,14 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
-      <c r="AR186" s="529" t="s">
+      <c r="AR186" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
       <c r="B187" s="454"/>
-      <c r="C187" s="487"/>
+      <c r="C187" s="494"/>
       <c r="D187" s="304"/>
       <c r="E187" s="138"/>
       <c r="F187" s="248"/>
@@ -25400,7 +25403,7 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
-      <c r="AR187" s="529" t="s">
+      <c r="AR187" t="s">
         <v>978</v>
       </c>
     </row>
@@ -25411,7 +25414,7 @@
       <c r="B188" s="454" t="s">
         <v>945</v>
       </c>
-      <c r="C188" s="487"/>
+      <c r="C188" s="494"/>
       <c r="D188" s="304" t="s">
         <v>743</v>
       </c>
@@ -25524,14 +25527,14 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
-      <c r="AR188" s="529" t="s">
+      <c r="AR188" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="189" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A189" s="457"/>
       <c r="B189" s="454"/>
-      <c r="C189" s="487"/>
+      <c r="C189" s="494"/>
       <c r="D189" s="304"/>
       <c r="E189" s="137"/>
       <c r="F189" s="247"/>
@@ -25612,14 +25615,14 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
-      <c r="AR189" s="529" t="s">
+      <c r="AR189" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
       <c r="B190" s="454"/>
-      <c r="C190" s="487"/>
+      <c r="C190" s="494"/>
       <c r="D190" s="304"/>
       <c r="E190" s="137"/>
       <c r="F190" s="247"/>
@@ -25700,14 +25703,14 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
-      <c r="AR190" s="529" t="s">
+      <c r="AR190" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
       <c r="B191" s="454"/>
-      <c r="C191" s="488"/>
+      <c r="C191" s="495"/>
       <c r="D191" s="317"/>
       <c r="E191" s="141"/>
       <c r="F191" s="249"/>
@@ -25786,7 +25789,7 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
-      <c r="AR191" s="529" t="s">
+      <c r="AR191" t="s">
         <v>978</v>
       </c>
     </row>
@@ -25797,7 +25800,7 @@
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="517">
+      <c r="C192" s="496">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25912,14 +25915,14 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
-      <c r="AR192" s="529" t="s">
+      <c r="AR192" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="518"/>
+      <c r="C193" s="497"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -26000,14 +26003,14 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
-      <c r="AR193" s="529" t="s">
+      <c r="AR193" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="518"/>
+      <c r="C194" s="497"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -26088,14 +26091,14 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
-      <c r="AR194" s="529" t="s">
+      <c r="AR194" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="518"/>
+      <c r="C195" s="497"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -26176,7 +26179,7 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
-      <c r="AR195" s="529" t="s">
+      <c r="AR195" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26187,7 +26190,7 @@
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="518"/>
+      <c r="C196" s="497"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -26300,14 +26303,14 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
-      <c r="AR196" s="529" t="s">
+      <c r="AR196" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="518"/>
+      <c r="C197" s="497"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -26388,14 +26391,14 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
-      <c r="AR197" s="529" t="s">
+      <c r="AR197" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="518"/>
+      <c r="C198" s="497"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -26476,14 +26479,14 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
-      <c r="AR198" s="529" t="s">
+      <c r="AR198" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="519"/>
+      <c r="C199" s="498"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -26564,7 +26567,7 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
-      <c r="AR199" s="529" t="s">
+      <c r="AR199" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26575,7 +26578,7 @@
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="520">
+      <c r="C200" s="499">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -26694,14 +26697,14 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
-      <c r="AR200" s="529" t="s">
+      <c r="AR200" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="521"/>
+      <c r="C201" s="500"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -26786,14 +26789,14 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
-      <c r="AR201" s="529" t="s">
+      <c r="AR201" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="521"/>
+      <c r="C202" s="500"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26876,7 +26879,7 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
-      <c r="AR202" s="529" t="s">
+      <c r="AR202" t="s">
         <v>980</v>
       </c>
     </row>
@@ -26887,7 +26890,7 @@
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="521"/>
+      <c r="C203" s="500"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -27006,14 +27009,14 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
-      <c r="AR203" s="529" t="s">
+      <c r="AR203" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="521"/>
+      <c r="C204" s="500"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -27098,14 +27101,14 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
-      <c r="AR204" s="529" t="s">
+      <c r="AR204" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="521"/>
+      <c r="C205" s="500"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -27188,7 +27191,7 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
-      <c r="AR205" s="529" t="s">
+      <c r="AR205" t="s">
         <v>980</v>
       </c>
     </row>
@@ -27199,7 +27202,7 @@
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="521"/>
+      <c r="C206" s="500"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -27318,14 +27321,14 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
-      <c r="AR206" s="529" t="s">
+      <c r="AR206" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="521"/>
+      <c r="C207" s="500"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -27406,14 +27409,14 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
-      <c r="AR207" s="529" t="s">
+      <c r="AR207" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="522"/>
+      <c r="C208" s="501"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -27498,7 +27501,7 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
-      <c r="AR208" s="529" t="s">
+      <c r="AR208" t="s">
         <v>980</v>
       </c>
     </row>
@@ -27509,7 +27512,7 @@
       <c r="B209" s="454" t="s">
         <v>951</v>
       </c>
-      <c r="C209" s="477">
+      <c r="C209" s="475">
         <v>101</v>
       </c>
       <c r="D209" s="306" t="s">
@@ -27630,14 +27633,14 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
-      <c r="AR209" s="529" t="s">
+      <c r="AR209" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="210" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A210" s="457"/>
       <c r="B210" s="454"/>
-      <c r="C210" s="478"/>
+      <c r="C210" s="476"/>
       <c r="D210" s="306"/>
       <c r="E210" s="163"/>
       <c r="F210" s="253"/>
@@ -27722,14 +27725,14 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
-      <c r="AR210" s="529" t="s">
+      <c r="AR210" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
       <c r="B211" s="454"/>
-      <c r="C211" s="478"/>
+      <c r="C211" s="476"/>
       <c r="D211" s="306"/>
       <c r="E211" s="163"/>
       <c r="F211" s="253"/>
@@ -27814,14 +27817,14 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
-      <c r="AR211" s="529" t="s">
+      <c r="AR211" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
       <c r="B212" s="454"/>
-      <c r="C212" s="478"/>
+      <c r="C212" s="476"/>
       <c r="D212" s="306"/>
       <c r="E212" s="164"/>
       <c r="F212" s="254"/>
@@ -27904,7 +27907,7 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
-      <c r="AR212" s="529" t="s">
+      <c r="AR212" t="s">
         <v>980</v>
       </c>
     </row>
@@ -27915,7 +27918,7 @@
       <c r="B213" s="454" t="s">
         <v>952</v>
       </c>
-      <c r="C213" s="478"/>
+      <c r="C213" s="476"/>
       <c r="D213" s="306" t="s">
         <v>745</v>
       </c>
@@ -28034,14 +28037,14 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
-      <c r="AR213" s="529" t="s">
+      <c r="AR213" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="214" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A214" s="457"/>
       <c r="B214" s="454"/>
-      <c r="C214" s="478"/>
+      <c r="C214" s="476"/>
       <c r="D214" s="306"/>
       <c r="E214" s="163"/>
       <c r="F214" s="253"/>
@@ -28126,14 +28129,14 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
-      <c r="AR214" s="529" t="s">
+      <c r="AR214" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
       <c r="B215" s="454"/>
-      <c r="C215" s="479"/>
+      <c r="C215" s="477"/>
       <c r="D215" s="319"/>
       <c r="E215" s="166"/>
       <c r="F215" s="255"/>
@@ -28218,7 +28221,7 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
-      <c r="AR215" s="529" t="s">
+      <c r="AR215" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28229,7 +28232,7 @@
       <c r="B216" s="454" t="s">
         <v>953</v>
       </c>
-      <c r="C216" s="489">
+      <c r="C216" s="459">
         <v>102</v>
       </c>
       <c r="D216" s="307" t="s">
@@ -28350,14 +28353,14 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
-      <c r="AR216" s="529" t="s">
+      <c r="AR216" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="217" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A217" s="457"/>
       <c r="B217" s="454"/>
-      <c r="C217" s="490"/>
+      <c r="C217" s="460"/>
       <c r="D217" s="307"/>
       <c r="E217" s="174"/>
       <c r="F217" s="256"/>
@@ -28442,14 +28445,14 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
-      <c r="AR217" s="529" t="s">
+      <c r="AR217" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
       <c r="B218" s="454"/>
-      <c r="C218" s="490"/>
+      <c r="C218" s="460"/>
       <c r="D218" s="307"/>
       <c r="E218" s="174"/>
       <c r="F218" s="256"/>
@@ -28534,14 +28537,14 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
-      <c r="AR218" s="529" t="s">
+      <c r="AR218" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
       <c r="B219" s="454"/>
-      <c r="C219" s="491"/>
+      <c r="C219" s="461"/>
       <c r="D219" s="320"/>
       <c r="E219" s="175"/>
       <c r="F219" s="257"/>
@@ -28626,7 +28629,7 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
-      <c r="AR219" s="529" t="s">
+      <c r="AR219" t="s">
         <v>981</v>
       </c>
     </row>
@@ -28637,7 +28640,7 @@
       <c r="B220" s="454" t="s">
         <v>954</v>
       </c>
-      <c r="C220" s="489">
+      <c r="C220" s="459">
         <v>103</v>
       </c>
       <c r="D220" s="307" t="s">
@@ -28754,14 +28757,14 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
-      <c r="AR220" s="529" t="s">
+      <c r="AR220" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="221" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A221" s="457"/>
       <c r="B221" s="454"/>
-      <c r="C221" s="490"/>
+      <c r="C221" s="460"/>
       <c r="D221" s="307"/>
       <c r="E221" s="174"/>
       <c r="F221" s="256"/>
@@ -28844,14 +28847,14 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
-      <c r="AR221" s="529" t="s">
+      <c r="AR221" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
       <c r="B222" s="454"/>
-      <c r="C222" s="490"/>
+      <c r="C222" s="460"/>
       <c r="D222" s="307"/>
       <c r="E222" s="178"/>
       <c r="F222" s="258"/>
@@ -28934,7 +28937,7 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
-      <c r="AR222" s="529" t="s">
+      <c r="AR222" t="s">
         <v>981</v>
       </c>
     </row>
@@ -28945,7 +28948,7 @@
       <c r="B223" s="454" t="s">
         <v>955</v>
       </c>
-      <c r="C223" s="490"/>
+      <c r="C223" s="460"/>
       <c r="D223" s="307" t="s">
         <v>745</v>
       </c>
@@ -29064,14 +29067,14 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
-      <c r="AR223" s="529" t="s">
+      <c r="AR223" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="224" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A224" s="457"/>
       <c r="B224" s="454"/>
-      <c r="C224" s="490"/>
+      <c r="C224" s="460"/>
       <c r="D224" s="307"/>
       <c r="E224" s="174"/>
       <c r="F224" s="256"/>
@@ -29156,14 +29159,14 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
-      <c r="AR224" s="529" t="s">
+      <c r="AR224" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
       <c r="B225" s="454"/>
-      <c r="C225" s="490"/>
+      <c r="C225" s="460"/>
       <c r="D225" s="307"/>
       <c r="E225" s="174"/>
       <c r="F225" s="256"/>
@@ -29248,14 +29251,14 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
-      <c r="AR225" s="529" t="s">
+      <c r="AR225" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
       <c r="B226" s="454"/>
-      <c r="C226" s="491"/>
+      <c r="C226" s="461"/>
       <c r="D226" s="320"/>
       <c r="E226" s="175"/>
       <c r="F226" s="257"/>
@@ -29334,7 +29337,7 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
-      <c r="AR226" s="529" t="s">
+      <c r="AR226" t="s">
         <v>981</v>
       </c>
     </row>
@@ -29345,7 +29348,7 @@
       <c r="B227" s="454" t="s">
         <v>956</v>
       </c>
-      <c r="C227" s="489">
+      <c r="C227" s="459">
         <v>104</v>
       </c>
       <c r="D227" s="307" t="s">
@@ -29462,14 +29465,14 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
-      <c r="AR227" s="529" t="s">
+      <c r="AR227" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="228" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A228" s="457"/>
       <c r="B228" s="454"/>
-      <c r="C228" s="490"/>
+      <c r="C228" s="460"/>
       <c r="D228" s="307"/>
       <c r="E228" s="174"/>
       <c r="F228" s="256"/>
@@ -29550,14 +29553,14 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
-      <c r="AR228" s="529" t="s">
+      <c r="AR228" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
       <c r="B229" s="454"/>
-      <c r="C229" s="490"/>
+      <c r="C229" s="460"/>
       <c r="D229" s="307"/>
       <c r="E229" s="174"/>
       <c r="F229" s="256"/>
@@ -29638,14 +29641,14 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
-      <c r="AR229" s="529" t="s">
+      <c r="AR229" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
       <c r="B230" s="454"/>
-      <c r="C230" s="490"/>
+      <c r="C230" s="460"/>
       <c r="D230" s="307"/>
       <c r="E230" s="178"/>
       <c r="F230" s="258"/>
@@ -29726,7 +29729,7 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
-      <c r="AR230" s="529" t="s">
+      <c r="AR230" t="s">
         <v>981</v>
       </c>
     </row>
@@ -29737,7 +29740,7 @@
       <c r="B231" s="454" t="s">
         <v>957</v>
       </c>
-      <c r="C231" s="490"/>
+      <c r="C231" s="460"/>
       <c r="D231" s="307" t="s">
         <v>745</v>
       </c>
@@ -29852,14 +29855,14 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
-      <c r="AR231" s="529" t="s">
+      <c r="AR231" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="232" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A232" s="457"/>
       <c r="B232" s="454"/>
-      <c r="C232" s="490"/>
+      <c r="C232" s="460"/>
       <c r="D232" s="307"/>
       <c r="E232" s="174"/>
       <c r="F232" s="256"/>
@@ -29940,14 +29943,14 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
-      <c r="AR232" s="529" t="s">
+      <c r="AR232" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
       <c r="B233" s="454"/>
-      <c r="C233" s="490"/>
+      <c r="C233" s="460"/>
       <c r="D233" s="307"/>
       <c r="E233" s="174"/>
       <c r="F233" s="256"/>
@@ -30028,14 +30031,14 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
-      <c r="AR233" s="529" t="s">
+      <c r="AR233" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
       <c r="B234" s="454"/>
-      <c r="C234" s="491"/>
+      <c r="C234" s="461"/>
       <c r="D234" s="320"/>
       <c r="E234" s="175"/>
       <c r="F234" s="257"/>
@@ -30112,7 +30115,7 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
-      <c r="AR234" s="529" t="s">
+      <c r="AR234" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30123,7 +30126,7 @@
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="523">
+      <c r="C235" s="468">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -30240,14 +30243,14 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
-      <c r="AR235" s="529" t="s">
+      <c r="AR235" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="524"/>
+      <c r="C236" s="469"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -30328,14 +30331,14 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
-      <c r="AR236" s="529" t="s">
+      <c r="AR236" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="524"/>
+      <c r="C237" s="469"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -30416,14 +30419,14 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
-      <c r="AR237" s="529" t="s">
+      <c r="AR237" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="525"/>
+      <c r="C238" s="470"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -30502,7 +30505,7 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
-      <c r="AR238" s="529" t="s">
+      <c r="AR238" t="s">
         <v>982</v>
       </c>
     </row>
@@ -30513,7 +30516,7 @@
       <c r="B239" s="454" t="s">
         <v>959</v>
       </c>
-      <c r="C239" s="495">
+      <c r="C239" s="471">
         <v>106</v>
       </c>
       <c r="D239" s="308" t="s">
@@ -30630,14 +30633,14 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
-      <c r="AR239" s="529" t="s">
+      <c r="AR239" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="240" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A240" s="457"/>
       <c r="B240" s="454"/>
-      <c r="C240" s="496"/>
+      <c r="C240" s="472"/>
       <c r="D240" s="308"/>
       <c r="E240" s="185"/>
       <c r="F240" s="259"/>
@@ -30718,14 +30721,14 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
-      <c r="AR240" s="529" t="s">
+      <c r="AR240" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
       <c r="B241" s="454"/>
-      <c r="C241" s="496"/>
+      <c r="C241" s="472"/>
       <c r="D241" s="308"/>
       <c r="E241" s="185"/>
       <c r="F241" s="259"/>
@@ -30806,14 +30809,14 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
-      <c r="AR241" s="529" t="s">
+      <c r="AR241" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
       <c r="B242" s="454"/>
-      <c r="C242" s="496"/>
+      <c r="C242" s="472"/>
       <c r="D242" s="308"/>
       <c r="E242" s="189"/>
       <c r="F242" s="261"/>
@@ -30892,7 +30895,7 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
-      <c r="AR242" s="529" t="s">
+      <c r="AR242" t="s">
         <v>982</v>
       </c>
     </row>
@@ -30903,7 +30906,7 @@
       <c r="B243" s="454" t="s">
         <v>960</v>
       </c>
-      <c r="C243" s="496"/>
+      <c r="C243" s="472"/>
       <c r="D243" s="308" t="s">
         <v>745</v>
       </c>
@@ -31018,14 +31021,14 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
-      <c r="AR243" s="529" t="s">
+      <c r="AR243" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="244" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A244" s="457"/>
       <c r="B244" s="454"/>
-      <c r="C244" s="496"/>
+      <c r="C244" s="472"/>
       <c r="D244" s="308"/>
       <c r="E244" s="185"/>
       <c r="F244" s="259"/>
@@ -31106,14 +31109,14 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
-      <c r="AR244" s="529" t="s">
+      <c r="AR244" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
       <c r="B245" s="454"/>
-      <c r="C245" s="496"/>
+      <c r="C245" s="472"/>
       <c r="D245" s="308"/>
       <c r="E245" s="185"/>
       <c r="F245" s="259"/>
@@ -31194,14 +31197,14 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
-      <c r="AR245" s="529" t="s">
+      <c r="AR245" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
       <c r="B246" s="454"/>
-      <c r="C246" s="496"/>
+      <c r="C246" s="472"/>
       <c r="D246" s="308"/>
       <c r="E246" s="185"/>
       <c r="F246" s="259"/>
@@ -31282,14 +31285,14 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
-      <c r="AR246" s="529" t="s">
+      <c r="AR246" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
       <c r="B247" s="454"/>
-      <c r="C247" s="496"/>
+      <c r="C247" s="472"/>
       <c r="D247" s="308"/>
       <c r="E247" s="181"/>
       <c r="F247" s="181"/>
@@ -31376,7 +31379,7 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
-      <c r="AR247" s="529" t="s">
+      <c r="AR247" t="s">
         <v>982</v>
       </c>
     </row>
@@ -31387,7 +31390,7 @@
       <c r="B248" s="454" t="s">
         <v>961</v>
       </c>
-      <c r="C248" s="498"/>
+      <c r="C248" s="473"/>
       <c r="D248" s="308" t="s">
         <v>745</v>
       </c>
@@ -31496,14 +31499,14 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
-      <c r="AR248" s="529" t="s">
+      <c r="AR248" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
       <c r="B249" s="454"/>
-      <c r="C249" s="496"/>
+      <c r="C249" s="472"/>
       <c r="D249" s="308"/>
       <c r="E249" s="185"/>
       <c r="F249" s="259"/>
@@ -31586,14 +31589,14 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
-      <c r="AR249" s="529" t="s">
+      <c r="AR249" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
       <c r="B250" s="454"/>
-      <c r="C250" s="496"/>
+      <c r="C250" s="472"/>
       <c r="D250" s="308"/>
       <c r="E250" s="185"/>
       <c r="F250" s="259"/>
@@ -31676,14 +31679,14 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
-      <c r="AR250" s="529" t="s">
+      <c r="AR250" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
       <c r="B251" s="454"/>
-      <c r="C251" s="496"/>
+      <c r="C251" s="472"/>
       <c r="D251" s="308"/>
       <c r="E251" s="189"/>
       <c r="F251" s="261"/>
@@ -31766,7 +31769,7 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
-      <c r="AR251" s="529" t="s">
+      <c r="AR251" t="s">
         <v>982</v>
       </c>
     </row>
@@ -31777,7 +31780,7 @@
       <c r="B252" s="454" t="s">
         <v>962</v>
       </c>
-      <c r="C252" s="496"/>
+      <c r="C252" s="472"/>
       <c r="D252" s="308" t="s">
         <v>745</v>
       </c>
@@ -31892,14 +31895,14 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
-      <c r="AR252" s="529" t="s">
+      <c r="AR252" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="253" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A253" s="457"/>
       <c r="B253" s="454"/>
-      <c r="C253" s="496"/>
+      <c r="C253" s="472"/>
       <c r="D253" s="308"/>
       <c r="E253" s="185"/>
       <c r="F253" s="259"/>
@@ -31980,14 +31983,14 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
-      <c r="AR253" s="529" t="s">
+      <c r="AR253" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
       <c r="B254" s="454"/>
-      <c r="C254" s="496"/>
+      <c r="C254" s="472"/>
       <c r="D254" s="308"/>
       <c r="E254" s="185"/>
       <c r="F254" s="259"/>
@@ -32068,14 +32071,14 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
-      <c r="AR254" s="529" t="s">
+      <c r="AR254" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
       <c r="B255" s="454"/>
-      <c r="C255" s="496"/>
+      <c r="C255" s="472"/>
       <c r="D255" s="308"/>
       <c r="E255" s="185"/>
       <c r="F255" s="259"/>
@@ -32156,14 +32159,14 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
-      <c r="AR255" s="529" t="s">
+      <c r="AR255" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
       <c r="B256" s="454"/>
-      <c r="C256" s="497"/>
+      <c r="C256" s="474"/>
       <c r="D256" s="321"/>
       <c r="E256" s="186"/>
       <c r="F256" s="260"/>
@@ -32244,7 +32247,7 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
-      <c r="AR256" s="529" t="s">
+      <c r="AR256" t="s">
         <v>982</v>
       </c>
     </row>
@@ -32255,7 +32258,7 @@
       <c r="B257" s="454" t="s">
         <v>963</v>
       </c>
-      <c r="C257" s="489">
+      <c r="C257" s="459">
         <v>107</v>
       </c>
       <c r="D257" s="307" t="s">
@@ -32372,14 +32375,14 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
-      <c r="AR257" s="529" t="s">
+      <c r="AR257" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="258" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A258" s="457"/>
       <c r="B258" s="454"/>
-      <c r="C258" s="490"/>
+      <c r="C258" s="460"/>
       <c r="D258" s="307"/>
       <c r="E258" s="174"/>
       <c r="F258" s="256"/>
@@ -32462,14 +32465,14 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
-      <c r="AR258" s="529" t="s">
+      <c r="AR258" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
       <c r="B259" s="454"/>
-      <c r="C259" s="490"/>
+      <c r="C259" s="460"/>
       <c r="D259" s="307"/>
       <c r="E259" s="174"/>
       <c r="F259" s="256"/>
@@ -32552,14 +32555,14 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
-      <c r="AR259" s="529" t="s">
+      <c r="AR259" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
       <c r="B260" s="454"/>
-      <c r="C260" s="490"/>
+      <c r="C260" s="460"/>
       <c r="D260" s="307"/>
       <c r="E260" s="178"/>
       <c r="F260" s="258"/>
@@ -32640,7 +32643,7 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
-      <c r="AR260" s="529" t="s">
+      <c r="AR260" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32651,7 +32654,7 @@
       <c r="B261" s="454" t="s">
         <v>964</v>
       </c>
-      <c r="C261" s="490"/>
+      <c r="C261" s="460"/>
       <c r="D261" s="307" t="s">
         <v>745</v>
       </c>
@@ -32766,14 +32769,14 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
-      <c r="AR261" s="529" t="s">
+      <c r="AR261" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="262" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A262" s="457"/>
       <c r="B262" s="454"/>
-      <c r="C262" s="490"/>
+      <c r="C262" s="460"/>
       <c r="D262" s="307"/>
       <c r="E262" s="174"/>
       <c r="F262" s="256"/>
@@ -32852,14 +32855,14 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
-      <c r="AR262" s="529" t="s">
+      <c r="AR262" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
       <c r="B263" s="454"/>
-      <c r="C263" s="491"/>
+      <c r="C263" s="461"/>
       <c r="D263" s="320"/>
       <c r="E263" s="175"/>
       <c r="F263" s="257"/>
@@ -32938,7 +32941,7 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
-      <c r="AR263" s="529" t="s">
+      <c r="AR263" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32949,7 +32952,7 @@
       <c r="B264" s="454" t="s">
         <v>965</v>
       </c>
-      <c r="C264" s="489">
+      <c r="C264" s="459">
         <v>108</v>
       </c>
       <c r="D264" s="307" t="s">
@@ -33068,14 +33071,14 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
-      <c r="AR264" s="529" t="s">
+      <c r="AR264" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="265" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A265" s="457"/>
       <c r="B265" s="454"/>
-      <c r="C265" s="490"/>
+      <c r="C265" s="460"/>
       <c r="D265" s="307"/>
       <c r="E265" s="174"/>
       <c r="F265" s="256"/>
@@ -33158,14 +33161,14 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
-      <c r="AR265" s="529" t="s">
+      <c r="AR265" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
       <c r="B266" s="454"/>
-      <c r="C266" s="490"/>
+      <c r="C266" s="460"/>
       <c r="D266" s="307"/>
       <c r="E266" s="174"/>
       <c r="F266" s="256"/>
@@ -33248,14 +33251,14 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
-      <c r="AR266" s="529" t="s">
+      <c r="AR266" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
       <c r="B267" s="454"/>
-      <c r="C267" s="491"/>
+      <c r="C267" s="461"/>
       <c r="D267" s="320"/>
       <c r="E267" s="175"/>
       <c r="F267" s="257"/>
@@ -33338,7 +33341,7 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
-      <c r="AR267" s="529" t="s">
+      <c r="AR267" t="s">
         <v>981</v>
       </c>
     </row>
@@ -33349,7 +33352,7 @@
       <c r="B268" s="454" t="s">
         <v>966</v>
       </c>
-      <c r="C268" s="489">
+      <c r="C268" s="459">
         <v>109</v>
       </c>
       <c r="D268" s="307" t="s">
@@ -33470,14 +33473,14 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
-      <c r="AR268" s="529" t="s">
+      <c r="AR268" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="269" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A269" s="457"/>
       <c r="B269" s="454"/>
-      <c r="C269" s="490"/>
+      <c r="C269" s="460"/>
       <c r="D269" s="307"/>
       <c r="E269" s="174"/>
       <c r="F269" s="256"/>
@@ -33562,14 +33565,14 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
-      <c r="AR269" s="529" t="s">
+      <c r="AR269" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
       <c r="B270" s="454"/>
-      <c r="C270" s="491"/>
+      <c r="C270" s="461"/>
       <c r="D270" s="320"/>
       <c r="E270" s="175"/>
       <c r="F270" s="257"/>
@@ -33654,7 +33657,7 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
-      <c r="AR270" s="529" t="s">
+      <c r="AR270" t="s">
         <v>981</v>
       </c>
     </row>
@@ -33665,7 +33668,7 @@
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="526">
+      <c r="C271" s="462">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -33786,14 +33789,14 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
-      <c r="AR271" s="529" t="s">
+      <c r="AR271" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="527"/>
+      <c r="C272" s="463"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -33876,14 +33879,14 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
-      <c r="AR272" s="529" t="s">
+      <c r="AR272" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="527"/>
+      <c r="C273" s="463"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -33966,7 +33969,7 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
-      <c r="AR273" s="529" t="s">
+      <c r="AR273" t="s">
         <v>983</v>
       </c>
     </row>
@@ -33977,7 +33980,7 @@
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="527"/>
+      <c r="C274" s="463"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -34088,14 +34091,14 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
-      <c r="AR274" s="529" t="s">
+      <c r="AR274" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="527"/>
+      <c r="C275" s="463"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -34184,14 +34187,14 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
-      <c r="AR275" s="529" t="s">
+      <c r="AR275" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="527"/>
+      <c r="C276" s="463"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -34274,14 +34277,14 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
-      <c r="AR276" s="529" t="s">
+      <c r="AR276" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="528"/>
+      <c r="C277" s="464"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -34364,7 +34367,7 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
-      <c r="AR277" s="529" t="s">
+      <c r="AR277" t="s">
         <v>983</v>
       </c>
     </row>
@@ -34375,7 +34378,7 @@
       <c r="B278" s="454" t="s">
         <v>969</v>
       </c>
-      <c r="C278" s="492">
+      <c r="C278" s="465">
         <v>112</v>
       </c>
       <c r="D278" s="309" t="s">
@@ -34492,14 +34495,14 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
-      <c r="AR278" s="529" t="s">
+      <c r="AR278" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="279" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A279" s="457"/>
       <c r="B279" s="454"/>
-      <c r="C279" s="493"/>
+      <c r="C279" s="466"/>
       <c r="D279" s="309"/>
       <c r="E279" s="197"/>
       <c r="F279" s="262"/>
@@ -34580,14 +34583,14 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
-      <c r="AR279" s="529" t="s">
+      <c r="AR279" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
       <c r="B280" s="454"/>
-      <c r="C280" s="493"/>
+      <c r="C280" s="466"/>
       <c r="D280" s="309"/>
       <c r="E280" s="197"/>
       <c r="F280" s="262"/>
@@ -34668,14 +34671,14 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
-      <c r="AR280" s="529" t="s">
+      <c r="AR280" t="s">
         <v>983</v>
       </c>
     </row>
     <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
       <c r="B281" s="455"/>
-      <c r="C281" s="494"/>
+      <c r="C281" s="467"/>
       <c r="D281" s="322"/>
       <c r="E281" s="201"/>
       <c r="F281" s="264"/>
@@ -34756,22 +34759,30 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
-      <c r="AR281" s="529" t="s">
+      <c r="AR281" t="s">
         <v>984</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C264:C267"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="C271:C277"/>
-    <mergeCell ref="C278:C281"/>
-    <mergeCell ref="C216:C219"/>
-    <mergeCell ref="C220:C226"/>
-    <mergeCell ref="C227:C234"/>
-    <mergeCell ref="C235:C238"/>
-    <mergeCell ref="C239:C256"/>
-    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="C13:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="C35:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="C55:C63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="C67:C74"/>
+    <mergeCell ref="C75:C82"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="C86:C97"/>
+    <mergeCell ref="C98:C101"/>
     <mergeCell ref="C209:C215"/>
     <mergeCell ref="C106:C114"/>
     <mergeCell ref="C115:C122"/>
@@ -34784,24 +34795,16 @@
     <mergeCell ref="C184:C191"/>
     <mergeCell ref="C192:C199"/>
     <mergeCell ref="C200:C208"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="C35:C43"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="C55:C63"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="C67:C74"/>
-    <mergeCell ref="C75:C82"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="C86:C97"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="C13:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C264:C267"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="C271:C277"/>
+    <mergeCell ref="C278:C281"/>
+    <mergeCell ref="C216:C219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="C235:C238"/>
+    <mergeCell ref="C239:C256"/>
+    <mergeCell ref="C257:C263"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A2121F7-BC8D-42C4-B451-7E9F568B7D03}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D816325-2C0C-477E-B9AF-62E6D98157EB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3584,9 +3584,6 @@
     <t>R44_Als_1121</t>
   </si>
   <si>
-    <t>couleur</t>
-  </si>
-  <si>
     <t>#CCFFFF</t>
   </si>
   <si>
@@ -3627,6 +3624,9 @@
   </si>
   <si>
     <t>#339967</t>
+  </si>
+  <si>
+    <t>couleur_fond</t>
   </si>
 </sst>
 </file>
@@ -5644,6 +5644,168 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5690,168 +5852,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7158,7 +7158,7 @@
         <v>29</v>
       </c>
       <c r="AR1" s="16" t="s">
-        <v>970</v>
+        <v>984</v>
       </c>
     </row>
     <row r="2" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7168,7 +7168,7 @@
       <c r="B2" s="454" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="523">
+      <c r="C2" s="462">
         <v>11</v>
       </c>
       <c r="D2" s="296" t="s">
@@ -7290,13 +7290,13 @@
         <v>57</v>
       </c>
       <c r="AR2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="457"/>
       <c r="B3" s="454"/>
-      <c r="C3" s="524"/>
+      <c r="C3" s="463"/>
       <c r="D3" s="296"/>
       <c r="E3" s="17"/>
       <c r="F3" s="224"/>
@@ -7382,13 +7382,13 @@
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
       <c r="AR3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
       <c r="B4" s="454"/>
-      <c r="C4" s="525"/>
+      <c r="C4" s="464"/>
       <c r="D4" s="297"/>
       <c r="E4" s="209"/>
       <c r="F4" s="225"/>
@@ -7474,7 +7474,7 @@
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
       <c r="AR4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="5" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7484,7 +7484,7 @@
       <c r="B5" s="454" t="s">
         <v>902</v>
       </c>
-      <c r="C5" s="523">
+      <c r="C5" s="462">
         <v>12</v>
       </c>
       <c r="D5" s="296" t="s">
@@ -7604,13 +7604,13 @@
         <v>147</v>
       </c>
       <c r="AR5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="457"/>
       <c r="B6" s="454"/>
-      <c r="C6" s="524"/>
+      <c r="C6" s="463"/>
       <c r="D6" s="296"/>
       <c r="E6" s="34"/>
       <c r="F6" s="226"/>
@@ -7694,13 +7694,13 @@
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
       <c r="AR6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
       <c r="B7" s="454"/>
-      <c r="C7" s="524"/>
+      <c r="C7" s="463"/>
       <c r="D7" s="296"/>
       <c r="E7" s="34"/>
       <c r="F7" s="226"/>
@@ -7784,13 +7784,13 @@
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
       <c r="AR7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
       <c r="B8" s="454"/>
-      <c r="C8" s="524"/>
+      <c r="C8" s="463"/>
       <c r="D8" s="296"/>
       <c r="E8" s="53"/>
       <c r="F8" s="227"/>
@@ -7872,7 +7872,7 @@
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
       <c r="AR8" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
@@ -7882,7 +7882,7 @@
       <c r="B9" s="454" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="524"/>
+      <c r="C9" s="463"/>
       <c r="D9" s="296" t="s">
         <v>736</v>
       </c>
@@ -7998,13 +7998,13 @@
         <v>179</v>
       </c>
       <c r="AR9" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="457"/>
       <c r="B10" s="454"/>
-      <c r="C10" s="524"/>
+      <c r="C10" s="463"/>
       <c r="D10" s="296"/>
       <c r="E10" s="34"/>
       <c r="F10" s="226"/>
@@ -8086,13 +8086,13 @@
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
       <c r="AR10" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
       <c r="B11" s="454"/>
-      <c r="C11" s="524"/>
+      <c r="C11" s="463"/>
       <c r="D11" s="296"/>
       <c r="E11" s="34"/>
       <c r="F11" s="226"/>
@@ -8174,13 +8174,13 @@
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
       <c r="AR11" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
       <c r="B12" s="454"/>
-      <c r="C12" s="525"/>
+      <c r="C12" s="464"/>
       <c r="D12" s="297"/>
       <c r="E12" s="38"/>
       <c r="F12" s="228"/>
@@ -8260,7 +8260,7 @@
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
       <c r="AR12" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8270,7 +8270,7 @@
       <c r="B13" s="454" t="s">
         <v>904</v>
       </c>
-      <c r="C13" s="523">
+      <c r="C13" s="462">
         <v>13</v>
       </c>
       <c r="D13" s="296" t="s">
@@ -8388,13 +8388,13 @@
         <v>175</v>
       </c>
       <c r="AR13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="457"/>
       <c r="B14" s="454"/>
-      <c r="C14" s="524"/>
+      <c r="C14" s="463"/>
       <c r="D14" s="296"/>
       <c r="E14" s="34"/>
       <c r="F14" s="226"/>
@@ -8476,13 +8476,13 @@
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
       <c r="AR14" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
       <c r="B15" s="454"/>
-      <c r="C15" s="524"/>
+      <c r="C15" s="463"/>
       <c r="D15" s="296"/>
       <c r="E15" s="34"/>
       <c r="F15" s="226"/>
@@ -8564,13 +8564,13 @@
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
       <c r="AR15" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
       <c r="B16" s="454"/>
-      <c r="C16" s="524"/>
+      <c r="C16" s="463"/>
       <c r="D16" s="296"/>
       <c r="E16" s="34"/>
       <c r="F16" s="226"/>
@@ -8652,13 +8652,13 @@
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
       <c r="AR16" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
       <c r="B17" s="454"/>
-      <c r="C17" s="524"/>
+      <c r="C17" s="463"/>
       <c r="D17" s="296"/>
       <c r="E17" s="53"/>
       <c r="F17" s="227"/>
@@ -8738,7 +8738,7 @@
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
       <c r="AR17" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
@@ -8748,7 +8748,7 @@
       <c r="B18" s="454" t="s">
         <v>905</v>
       </c>
-      <c r="C18" s="524"/>
+      <c r="C18" s="463"/>
       <c r="D18" s="296" t="s">
         <v>736</v>
       </c>
@@ -8862,13 +8862,13 @@
         <v>84</v>
       </c>
       <c r="AR18" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="457"/>
       <c r="B19" s="454"/>
-      <c r="C19" s="524"/>
+      <c r="C19" s="463"/>
       <c r="D19" s="296"/>
       <c r="E19" s="34"/>
       <c r="F19" s="226"/>
@@ -8950,13 +8950,13 @@
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
       <c r="AR19" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
       <c r="B20" s="454"/>
-      <c r="C20" s="524"/>
+      <c r="C20" s="463"/>
       <c r="D20" s="296"/>
       <c r="E20" s="34"/>
       <c r="F20" s="226"/>
@@ -9038,13 +9038,13 @@
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
       <c r="AR20" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
       <c r="B21" s="454"/>
-      <c r="C21" s="524"/>
+      <c r="C21" s="463"/>
       <c r="D21" s="296"/>
       <c r="E21" s="34"/>
       <c r="F21" s="226"/>
@@ -9126,13 +9126,13 @@
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
       <c r="AR21" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
       <c r="B22" s="454"/>
-      <c r="C22" s="525"/>
+      <c r="C22" s="464"/>
       <c r="D22" s="297"/>
       <c r="E22" s="38"/>
       <c r="F22" s="228"/>
@@ -9214,7 +9214,7 @@
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
       <c r="AR22" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="23" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -9224,7 +9224,7 @@
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="526">
+      <c r="C23" s="465">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9346,13 +9346,13 @@
         <v>70</v>
       </c>
       <c r="AR23" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="527"/>
+      <c r="C24" s="466"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9438,13 +9438,13 @@
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
       <c r="AR24" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="528"/>
+      <c r="C25" s="467"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9530,7 +9530,7 @@
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
       <c r="AR25" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="26" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -9540,7 +9540,7 @@
       <c r="B26" s="454" t="s">
         <v>907</v>
       </c>
-      <c r="C26" s="502">
+      <c r="C26" s="459">
         <v>22</v>
       </c>
       <c r="D26" s="298" t="s">
@@ -9658,13 +9658,13 @@
         <v>148</v>
       </c>
       <c r="AR26" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="457"/>
       <c r="B27" s="454"/>
-      <c r="C27" s="503"/>
+      <c r="C27" s="460"/>
       <c r="D27" s="298"/>
       <c r="E27" s="73"/>
       <c r="F27" s="230"/>
@@ -9746,13 +9746,13 @@
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
       <c r="AR27" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
       <c r="B28" s="454"/>
-      <c r="C28" s="503"/>
+      <c r="C28" s="460"/>
       <c r="D28" s="298"/>
       <c r="E28" s="73"/>
       <c r="F28" s="230"/>
@@ -9834,13 +9834,13 @@
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
       <c r="AR28" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
       <c r="B29" s="454"/>
-      <c r="C29" s="503"/>
+      <c r="C29" s="460"/>
       <c r="D29" s="298"/>
       <c r="E29" s="73"/>
       <c r="F29" s="230"/>
@@ -9924,13 +9924,13 @@
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
       <c r="AR29" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
       <c r="B30" s="454"/>
-      <c r="C30" s="504"/>
+      <c r="C30" s="461"/>
       <c r="D30" s="311"/>
       <c r="E30" s="74"/>
       <c r="F30" s="231"/>
@@ -10010,7 +10010,7 @@
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
       <c r="AR30" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="31" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -10020,7 +10020,7 @@
       <c r="B31" s="454" t="s">
         <v>908</v>
       </c>
-      <c r="C31" s="502">
+      <c r="C31" s="459">
         <v>23</v>
       </c>
       <c r="D31" s="298" t="s">
@@ -10142,13 +10142,13 @@
         <v>116</v>
       </c>
       <c r="AR31" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="457"/>
       <c r="B32" s="454"/>
-      <c r="C32" s="503"/>
+      <c r="C32" s="460"/>
       <c r="D32" s="298"/>
       <c r="E32" s="73"/>
       <c r="F32" s="230"/>
@@ -10234,13 +10234,13 @@
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
       <c r="AR32" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
       <c r="B33" s="454"/>
-      <c r="C33" s="503"/>
+      <c r="C33" s="460"/>
       <c r="D33" s="298"/>
       <c r="E33" s="73"/>
       <c r="F33" s="230"/>
@@ -10326,13 +10326,13 @@
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
       <c r="AR33" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
       <c r="B34" s="454"/>
-      <c r="C34" s="504"/>
+      <c r="C34" s="461"/>
       <c r="D34" s="311"/>
       <c r="E34" s="74"/>
       <c r="F34" s="231"/>
@@ -10418,7 +10418,7 @@
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
       <c r="AR34" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="35" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -10428,7 +10428,7 @@
       <c r="B35" s="454" t="s">
         <v>909</v>
       </c>
-      <c r="C35" s="502">
+      <c r="C35" s="459">
         <v>24</v>
       </c>
       <c r="D35" s="298" t="s">
@@ -10544,13 +10544,13 @@
         <v>72</v>
       </c>
       <c r="AR35" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="457"/>
       <c r="B36" s="454"/>
-      <c r="C36" s="503"/>
+      <c r="C36" s="460"/>
       <c r="D36" s="298"/>
       <c r="E36" s="73"/>
       <c r="F36" s="230"/>
@@ -10632,13 +10632,13 @@
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
       <c r="AR36" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
       <c r="B37" s="454"/>
-      <c r="C37" s="503"/>
+      <c r="C37" s="460"/>
       <c r="D37" s="298"/>
       <c r="E37" s="73"/>
       <c r="F37" s="230"/>
@@ -10720,13 +10720,13 @@
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
       <c r="AR37" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
       <c r="B38" s="454"/>
-      <c r="C38" s="503"/>
+      <c r="C38" s="460"/>
       <c r="D38" s="298"/>
       <c r="E38" s="77"/>
       <c r="F38" s="232"/>
@@ -10808,7 +10808,7 @@
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
       <c r="AR38" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
@@ -10818,7 +10818,7 @@
       <c r="B39" s="454" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="503"/>
+      <c r="C39" s="460"/>
       <c r="D39" s="298" t="s">
         <v>737</v>
       </c>
@@ -10934,13 +10934,13 @@
         <v>105</v>
       </c>
       <c r="AR39" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="457"/>
       <c r="B40" s="454"/>
-      <c r="C40" s="503"/>
+      <c r="C40" s="460"/>
       <c r="D40" s="298"/>
       <c r="E40" s="73"/>
       <c r="F40" s="230"/>
@@ -11022,13 +11022,13 @@
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
       <c r="AR40" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
       <c r="B41" s="454"/>
-      <c r="C41" s="503"/>
+      <c r="C41" s="460"/>
       <c r="D41" s="298"/>
       <c r="E41" s="73"/>
       <c r="F41" s="230"/>
@@ -11110,13 +11110,13 @@
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
       <c r="AR41" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
       <c r="B42" s="454"/>
-      <c r="C42" s="503"/>
+      <c r="C42" s="460"/>
       <c r="D42" s="298"/>
       <c r="E42" s="73"/>
       <c r="F42" s="230"/>
@@ -11198,13 +11198,13 @@
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
       <c r="AR42" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
       <c r="B43" s="454"/>
-      <c r="C43" s="504"/>
+      <c r="C43" s="461"/>
       <c r="D43" s="311"/>
       <c r="E43" s="74"/>
       <c r="F43" s="231"/>
@@ -11284,7 +11284,7 @@
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
       <c r="AR43" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="44" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -11294,7 +11294,7 @@
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="505">
+      <c r="C44" s="471">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11414,13 +11414,13 @@
         <v>77</v>
       </c>
       <c r="AR44" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="506"/>
+      <c r="C45" s="472"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11506,13 +11506,13 @@
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
       <c r="AR45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="507"/>
+      <c r="C46" s="473"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11598,7 +11598,7 @@
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
       <c r="AR46" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="47" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -11608,7 +11608,7 @@
       <c r="B47" s="454" t="s">
         <v>912</v>
       </c>
-      <c r="C47" s="508">
+      <c r="C47" s="474">
         <v>32</v>
       </c>
       <c r="D47" s="299" t="s">
@@ -11728,13 +11728,13 @@
         <v>219</v>
       </c>
       <c r="AR47" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="457"/>
       <c r="B48" s="454"/>
-      <c r="C48" s="509"/>
+      <c r="C48" s="475"/>
       <c r="D48" s="299"/>
       <c r="E48" s="84"/>
       <c r="F48" s="235"/>
@@ -11818,13 +11818,13 @@
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
       <c r="AR48" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
       <c r="B49" s="454"/>
-      <c r="C49" s="509"/>
+      <c r="C49" s="475"/>
       <c r="D49" s="299"/>
       <c r="E49" s="84"/>
       <c r="F49" s="235"/>
@@ -11908,13 +11908,13 @@
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
       <c r="AR49" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="510"/>
+      <c r="C50" s="476"/>
       <c r="D50" s="312"/>
       <c r="E50" s="85"/>
       <c r="F50" s="236"/>
@@ -11998,7 +11998,7 @@
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
       <c r="AR50" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="51" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -12008,7 +12008,7 @@
       <c r="B51" s="454" t="s">
         <v>913</v>
       </c>
-      <c r="C51" s="508">
+      <c r="C51" s="474">
         <v>33</v>
       </c>
       <c r="D51" s="299" t="s">
@@ -12130,13 +12130,13 @@
         <v>163</v>
       </c>
       <c r="AR51" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="457"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="509"/>
+      <c r="C52" s="475"/>
       <c r="D52" s="299"/>
       <c r="E52" s="84"/>
       <c r="F52" s="235"/>
@@ -12222,13 +12222,13 @@
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
       <c r="AR52" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
       <c r="B53" s="454"/>
-      <c r="C53" s="509"/>
+      <c r="C53" s="475"/>
       <c r="D53" s="299"/>
       <c r="E53" s="84"/>
       <c r="F53" s="235"/>
@@ -12310,13 +12310,13 @@
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
       <c r="AR53" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
       <c r="B54" s="454"/>
-      <c r="C54" s="510"/>
+      <c r="C54" s="476"/>
       <c r="D54" s="312"/>
       <c r="E54" s="85"/>
       <c r="F54" s="236"/>
@@ -12396,7 +12396,7 @@
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
       <c r="AR54" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="55" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -12406,7 +12406,7 @@
       <c r="B55" s="454" t="s">
         <v>914</v>
       </c>
-      <c r="C55" s="508">
+      <c r="C55" s="474">
         <v>34</v>
       </c>
       <c r="D55" s="299" t="s">
@@ -12522,13 +12522,13 @@
         <v>150</v>
       </c>
       <c r="AR55" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="457"/>
       <c r="B56" s="454"/>
-      <c r="C56" s="509"/>
+      <c r="C56" s="475"/>
       <c r="D56" s="299"/>
       <c r="E56" s="84"/>
       <c r="F56" s="235"/>
@@ -12610,13 +12610,13 @@
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
       <c r="AR56" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
       <c r="B57" s="454"/>
-      <c r="C57" s="509"/>
+      <c r="C57" s="475"/>
       <c r="D57" s="299"/>
       <c r="E57" s="84"/>
       <c r="F57" s="235"/>
@@ -12698,13 +12698,13 @@
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
       <c r="AR57" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
       <c r="B58" s="454"/>
-      <c r="C58" s="509"/>
+      <c r="C58" s="475"/>
       <c r="D58" s="299"/>
       <c r="E58" s="84"/>
       <c r="F58" s="235"/>
@@ -12786,13 +12786,13 @@
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
       <c r="AR58" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
       <c r="B59" s="454"/>
-      <c r="C59" s="509"/>
+      <c r="C59" s="475"/>
       <c r="D59" s="299"/>
       <c r="E59" s="89"/>
       <c r="F59" s="237"/>
@@ -12874,7 +12874,7 @@
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
       <c r="AR59" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="60" spans="1:44" ht="28.8" x14ac:dyDescent="0.3">
@@ -12884,7 +12884,7 @@
       <c r="B60" s="454" t="s">
         <v>915</v>
       </c>
-      <c r="C60" s="509"/>
+      <c r="C60" s="475"/>
       <c r="D60" s="299" t="s">
         <v>738</v>
       </c>
@@ -13000,13 +13000,13 @@
         <v>137</v>
       </c>
       <c r="AR60" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="457"/>
       <c r="B61" s="454"/>
-      <c r="C61" s="509"/>
+      <c r="C61" s="475"/>
       <c r="D61" s="299"/>
       <c r="E61" s="84"/>
       <c r="F61" s="235"/>
@@ -13088,13 +13088,13 @@
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
       <c r="AR61" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
       <c r="B62" s="454"/>
-      <c r="C62" s="509"/>
+      <c r="C62" s="475"/>
       <c r="D62" s="299"/>
       <c r="E62" s="84"/>
       <c r="F62" s="235"/>
@@ -13176,13 +13176,13 @@
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
       <c r="AR62" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
       <c r="B63" s="454"/>
-      <c r="C63" s="510"/>
+      <c r="C63" s="476"/>
       <c r="D63" s="312"/>
       <c r="E63" s="85"/>
       <c r="F63" s="236"/>
@@ -13264,7 +13264,7 @@
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
       <c r="AR63" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="64" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -13274,7 +13274,7 @@
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="511">
+      <c r="C64" s="477">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13394,13 +13394,13 @@
         <v>63</v>
       </c>
       <c r="AR64" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="512"/>
+      <c r="C65" s="478"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13486,13 +13486,13 @@
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
       <c r="AR65" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="513"/>
+      <c r="C66" s="479"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13578,7 +13578,7 @@
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
       <c r="AR66" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="67" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -13588,7 +13588,7 @@
       <c r="B67" s="454" t="s">
         <v>917</v>
       </c>
-      <c r="C67" s="514">
+      <c r="C67" s="480">
         <v>42</v>
       </c>
       <c r="D67" s="300" t="s">
@@ -13708,13 +13708,13 @@
         <v>55</v>
       </c>
       <c r="AR67" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="457"/>
       <c r="B68" s="454"/>
-      <c r="C68" s="515"/>
+      <c r="C68" s="481"/>
       <c r="D68" s="300"/>
       <c r="E68" s="96"/>
       <c r="F68" s="238"/>
@@ -13798,13 +13798,13 @@
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
       <c r="AR68" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
       <c r="B69" s="454"/>
-      <c r="C69" s="515"/>
+      <c r="C69" s="481"/>
       <c r="D69" s="300"/>
       <c r="E69" s="100"/>
       <c r="F69" s="240"/>
@@ -13888,7 +13888,7 @@
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
       <c r="AR69" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="70" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
@@ -13898,7 +13898,7 @@
       <c r="B70" s="454" t="s">
         <v>918</v>
       </c>
-      <c r="C70" s="515"/>
+      <c r="C70" s="481"/>
       <c r="D70" s="300" t="s">
         <v>739</v>
       </c>
@@ -14012,13 +14012,13 @@
         <v>137</v>
       </c>
       <c r="AR70" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="457"/>
       <c r="B71" s="454"/>
-      <c r="C71" s="515"/>
+      <c r="C71" s="481"/>
       <c r="D71" s="300"/>
       <c r="E71" s="96"/>
       <c r="F71" s="238"/>
@@ -14100,13 +14100,13 @@
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
       <c r="AR71" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
       <c r="B72" s="454"/>
-      <c r="C72" s="515"/>
+      <c r="C72" s="481"/>
       <c r="D72" s="300"/>
       <c r="E72" s="96"/>
       <c r="F72" s="238"/>
@@ -14188,13 +14188,13 @@
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
       <c r="AR72" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
       <c r="B73" s="454"/>
-      <c r="C73" s="515"/>
+      <c r="C73" s="481"/>
       <c r="D73" s="300"/>
       <c r="E73" s="96"/>
       <c r="F73" s="238"/>
@@ -14276,13 +14276,13 @@
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
       <c r="AR73" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
       <c r="B74" s="454"/>
-      <c r="C74" s="516"/>
+      <c r="C74" s="482"/>
       <c r="D74" s="313"/>
       <c r="E74" s="97"/>
       <c r="F74" s="239"/>
@@ -14364,7 +14364,7 @@
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
       <c r="AR74" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="75" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -14374,7 +14374,7 @@
       <c r="B75" s="454" t="s">
         <v>919</v>
       </c>
-      <c r="C75" s="514">
+      <c r="C75" s="480">
         <v>43</v>
       </c>
       <c r="D75" s="300" t="s">
@@ -14492,13 +14492,13 @@
         <v>114</v>
       </c>
       <c r="AR75" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="457"/>
       <c r="B76" s="454"/>
-      <c r="C76" s="515"/>
+      <c r="C76" s="481"/>
       <c r="D76" s="300"/>
       <c r="E76" s="96"/>
       <c r="F76" s="238"/>
@@ -14580,13 +14580,13 @@
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
       <c r="AR76" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
       <c r="B77" s="454"/>
-      <c r="C77" s="515"/>
+      <c r="C77" s="481"/>
       <c r="D77" s="300"/>
       <c r="E77" s="96"/>
       <c r="F77" s="238"/>
@@ -14668,13 +14668,13 @@
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
       <c r="AR77" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
       <c r="B78" s="454"/>
-      <c r="C78" s="515"/>
+      <c r="C78" s="481"/>
       <c r="D78" s="300"/>
       <c r="E78" s="96"/>
       <c r="F78" s="238"/>
@@ -14756,13 +14756,13 @@
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
       <c r="AR78" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
       <c r="B79" s="454"/>
-      <c r="C79" s="515"/>
+      <c r="C79" s="481"/>
       <c r="D79" s="300"/>
       <c r="E79" s="100"/>
       <c r="F79" s="240"/>
@@ -14844,7 +14844,7 @@
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
       <c r="AR79" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="80" spans="1:44" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -14854,7 +14854,7 @@
       <c r="B80" s="454" t="s">
         <v>920</v>
       </c>
-      <c r="C80" s="515"/>
+      <c r="C80" s="481"/>
       <c r="D80" s="300" t="s">
         <v>739</v>
       </c>
@@ -14966,13 +14966,13 @@
         <v>41</v>
       </c>
       <c r="AR80" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="81" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A81" s="457"/>
       <c r="B81" s="454"/>
-      <c r="C81" s="515"/>
+      <c r="C81" s="481"/>
       <c r="D81" s="300"/>
       <c r="E81" s="96"/>
       <c r="F81" s="238"/>
@@ -15054,13 +15054,13 @@
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
       <c r="AR81" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
       <c r="B82" s="454"/>
-      <c r="C82" s="516"/>
+      <c r="C82" s="482"/>
       <c r="D82" s="313"/>
       <c r="E82" s="97"/>
       <c r="F82" s="239"/>
@@ -15140,7 +15140,7 @@
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
       <c r="AR82" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="83" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -15150,7 +15150,7 @@
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="517">
+      <c r="C83" s="483">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -15272,13 +15272,13 @@
         <v>64</v>
       </c>
       <c r="AR83" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="518"/>
+      <c r="C84" s="484"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -15364,13 +15364,13 @@
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
       <c r="AR84" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="519"/>
+      <c r="C85" s="485"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15454,7 +15454,7 @@
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
       <c r="AR85" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="86" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -15464,7 +15464,7 @@
       <c r="B86" s="454" t="s">
         <v>922</v>
       </c>
-      <c r="C86" s="520">
+      <c r="C86" s="486">
         <v>52</v>
       </c>
       <c r="D86" s="301" t="s">
@@ -15584,13 +15584,13 @@
         <v>157</v>
       </c>
       <c r="AR86" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="87" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A87" s="457"/>
       <c r="B87" s="454"/>
-      <c r="C87" s="521"/>
+      <c r="C87" s="487"/>
       <c r="D87" s="301"/>
       <c r="E87" s="110"/>
       <c r="F87" s="241"/>
@@ -15676,13 +15676,13 @@
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
       <c r="AR87" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
       <c r="B88" s="454"/>
-      <c r="C88" s="521"/>
+      <c r="C88" s="487"/>
       <c r="D88" s="301"/>
       <c r="E88" s="110"/>
       <c r="F88" s="241"/>
@@ -15768,13 +15768,13 @@
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
       <c r="AR88" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
       <c r="B89" s="454"/>
-      <c r="C89" s="521"/>
+      <c r="C89" s="487"/>
       <c r="D89" s="301"/>
       <c r="E89" s="115"/>
       <c r="F89" s="243"/>
@@ -15860,7 +15860,7 @@
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
       <c r="AR89" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="90" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -15870,7 +15870,7 @@
       <c r="B90" s="454" t="s">
         <v>923</v>
       </c>
-      <c r="C90" s="521"/>
+      <c r="C90" s="487"/>
       <c r="D90" s="301" t="s">
         <v>740</v>
       </c>
@@ -15988,13 +15988,13 @@
         <v>230</v>
       </c>
       <c r="AR90" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="91" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A91" s="457"/>
       <c r="B91" s="454"/>
-      <c r="C91" s="521"/>
+      <c r="C91" s="487"/>
       <c r="D91" s="301"/>
       <c r="E91" s="110"/>
       <c r="F91" s="241"/>
@@ -16078,13 +16078,13 @@
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
       <c r="AR91" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
       <c r="B92" s="454"/>
-      <c r="C92" s="521"/>
+      <c r="C92" s="487"/>
       <c r="D92" s="301"/>
       <c r="E92" s="110"/>
       <c r="F92" s="241"/>
@@ -16168,13 +16168,13 @@
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
       <c r="AR92" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
       <c r="B93" s="454"/>
-      <c r="C93" s="521"/>
+      <c r="C93" s="487"/>
       <c r="D93" s="301"/>
       <c r="E93" s="115"/>
       <c r="F93" s="243"/>
@@ -16258,7 +16258,7 @@
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
       <c r="AR93" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="94" spans="1:44" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -16268,7 +16268,7 @@
       <c r="B94" s="454" t="s">
         <v>924</v>
       </c>
-      <c r="C94" s="521"/>
+      <c r="C94" s="487"/>
       <c r="D94" s="301" t="s">
         <v>740</v>
       </c>
@@ -16386,13 +16386,13 @@
         <v>280</v>
       </c>
       <c r="AR94" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="95" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A95" s="457"/>
       <c r="B95" s="454"/>
-      <c r="C95" s="521"/>
+      <c r="C95" s="487"/>
       <c r="D95" s="301"/>
       <c r="E95" s="110"/>
       <c r="F95" s="241"/>
@@ -16476,13 +16476,13 @@
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
       <c r="AR95" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
       <c r="B96" s="454"/>
-      <c r="C96" s="521"/>
+      <c r="C96" s="487"/>
       <c r="D96" s="301"/>
       <c r="E96" s="110"/>
       <c r="F96" s="241"/>
@@ -16566,13 +16566,13 @@
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
       <c r="AR96" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
       <c r="B97" s="454"/>
-      <c r="C97" s="522"/>
+      <c r="C97" s="488"/>
       <c r="D97" s="314"/>
       <c r="E97" s="111"/>
       <c r="F97" s="242"/>
@@ -16656,7 +16656,7 @@
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
       <c r="AR97" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="98" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -16666,7 +16666,7 @@
       <c r="B98" s="454" t="s">
         <v>925</v>
       </c>
-      <c r="C98" s="520">
+      <c r="C98" s="486">
         <v>53</v>
       </c>
       <c r="D98" s="301" t="s">
@@ -16784,13 +16784,13 @@
         <v>151</v>
       </c>
       <c r="AR98" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="99" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A99" s="457"/>
       <c r="B99" s="454"/>
-      <c r="C99" s="521"/>
+      <c r="C99" s="487"/>
       <c r="D99" s="301"/>
       <c r="E99" s="110"/>
       <c r="F99" s="241"/>
@@ -16874,13 +16874,13 @@
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
       <c r="AR99" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
       <c r="B100" s="454"/>
-      <c r="C100" s="521"/>
+      <c r="C100" s="487"/>
       <c r="D100" s="301"/>
       <c r="E100" s="110"/>
       <c r="F100" s="241"/>
@@ -16962,13 +16962,13 @@
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
       <c r="AR100" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
       <c r="B101" s="454"/>
-      <c r="C101" s="522"/>
+      <c r="C101" s="488"/>
       <c r="D101" s="301"/>
       <c r="E101" s="111"/>
       <c r="F101" s="242"/>
@@ -17052,7 +17052,7 @@
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
       <c r="AR101" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="102" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -17062,7 +17062,7 @@
       <c r="B102" s="454" t="s">
         <v>926</v>
       </c>
-      <c r="C102" s="478">
+      <c r="C102" s="468">
         <v>61</v>
       </c>
       <c r="D102" s="323" t="s">
@@ -17176,13 +17176,13 @@
         <v>154</v>
       </c>
       <c r="AR102" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="103" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A103" s="457"/>
       <c r="B103" s="454"/>
-      <c r="C103" s="479"/>
+      <c r="C103" s="469"/>
       <c r="D103" s="323"/>
       <c r="E103" s="329"/>
       <c r="F103" s="330"/>
@@ -17264,13 +17264,13 @@
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
       <c r="AR103" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
       <c r="B104" s="454"/>
-      <c r="C104" s="479"/>
+      <c r="C104" s="469"/>
       <c r="D104" s="323"/>
       <c r="E104" s="329"/>
       <c r="F104" s="330"/>
@@ -17352,13 +17352,13 @@
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
       <c r="AR104" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
       <c r="B105" s="454"/>
-      <c r="C105" s="480"/>
+      <c r="C105" s="470"/>
       <c r="D105" s="331"/>
       <c r="E105" s="332"/>
       <c r="F105" s="333"/>
@@ -17440,7 +17440,7 @@
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
       <c r="AR105" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="106" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -17450,7 +17450,7 @@
       <c r="B106" s="454" t="s">
         <v>927</v>
       </c>
-      <c r="C106" s="478">
+      <c r="C106" s="468">
         <v>62</v>
       </c>
       <c r="D106" s="323" t="s">
@@ -17568,13 +17568,13 @@
         <v>128</v>
       </c>
       <c r="AR106" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="107" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A107" s="457"/>
       <c r="B107" s="454"/>
-      <c r="C107" s="479"/>
+      <c r="C107" s="469"/>
       <c r="D107" s="323"/>
       <c r="E107" s="329"/>
       <c r="F107" s="330"/>
@@ -17656,13 +17656,13 @@
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
       <c r="AR107" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
       <c r="B108" s="454"/>
-      <c r="C108" s="479"/>
+      <c r="C108" s="469"/>
       <c r="D108" s="323"/>
       <c r="E108" s="329"/>
       <c r="F108" s="330"/>
@@ -17744,13 +17744,13 @@
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
       <c r="AR108" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
       <c r="B109" s="454"/>
-      <c r="C109" s="479"/>
+      <c r="C109" s="469"/>
       <c r="D109" s="323"/>
       <c r="E109" s="338"/>
       <c r="F109" s="339"/>
@@ -17832,7 +17832,7 @@
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
       <c r="AR109" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="110" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
@@ -17842,7 +17842,7 @@
       <c r="B110" s="454" t="s">
         <v>928</v>
       </c>
-      <c r="C110" s="479"/>
+      <c r="C110" s="469"/>
       <c r="D110" s="323" t="s">
         <v>741</v>
       </c>
@@ -17958,13 +17958,13 @@
         <v>214</v>
       </c>
       <c r="AR110" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="111" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A111" s="457"/>
       <c r="B111" s="454"/>
-      <c r="C111" s="479"/>
+      <c r="C111" s="469"/>
       <c r="D111" s="323"/>
       <c r="E111" s="329"/>
       <c r="F111" s="330"/>
@@ -18046,13 +18046,13 @@
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
       <c r="AR111" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
       <c r="B112" s="454"/>
-      <c r="C112" s="479"/>
+      <c r="C112" s="469"/>
       <c r="D112" s="323"/>
       <c r="E112" s="329"/>
       <c r="F112" s="330"/>
@@ -18134,13 +18134,13 @@
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
       <c r="AR112" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
       <c r="B113" s="454"/>
-      <c r="C113" s="479"/>
+      <c r="C113" s="469"/>
       <c r="D113" s="323"/>
       <c r="E113" s="329"/>
       <c r="F113" s="330"/>
@@ -18222,13 +18222,13 @@
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
       <c r="AR113" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
       <c r="B114" s="454"/>
-      <c r="C114" s="480"/>
+      <c r="C114" s="470"/>
       <c r="D114" s="331"/>
       <c r="E114" s="332"/>
       <c r="F114" s="333"/>
@@ -18308,7 +18308,7 @@
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
       <c r="AR114" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="115" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -18318,7 +18318,7 @@
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="481">
+      <c r="C115" s="492">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -18436,13 +18436,13 @@
         <v>280</v>
       </c>
       <c r="AR115" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="482"/>
+      <c r="C116" s="493"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -18524,13 +18524,13 @@
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
       <c r="AR116" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="482"/>
+      <c r="C117" s="493"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18612,13 +18612,13 @@
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
       <c r="AR117" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="482"/>
+      <c r="C118" s="493"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18700,7 +18700,7 @@
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
       <c r="AR118" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="119" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -18710,7 +18710,7 @@
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="482"/>
+      <c r="C119" s="493"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18824,13 +18824,13 @@
         <v>244</v>
       </c>
       <c r="AR119" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="482"/>
+      <c r="C120" s="493"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18912,13 +18912,13 @@
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
       <c r="AR120" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="482"/>
+      <c r="C121" s="493"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -19000,13 +19000,13 @@
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
       <c r="AR121" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="483"/>
+      <c r="C122" s="494"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -19088,7 +19088,7 @@
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
       <c r="AR122" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="123" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -19098,7 +19098,7 @@
       <c r="B123" s="454" t="s">
         <v>931</v>
       </c>
-      <c r="C123" s="484">
+      <c r="C123" s="495">
         <v>72</v>
       </c>
       <c r="D123" s="302" t="s">
@@ -19214,13 +19214,13 @@
         <v>244</v>
       </c>
       <c r="AR123" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="124" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A124" s="457"/>
       <c r="B124" s="454"/>
-      <c r="C124" s="485"/>
+      <c r="C124" s="496"/>
       <c r="D124" s="302"/>
       <c r="E124" s="125"/>
       <c r="F124" s="244"/>
@@ -19302,13 +19302,13 @@
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
       <c r="AR124" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
       <c r="B125" s="454"/>
-      <c r="C125" s="485"/>
+      <c r="C125" s="496"/>
       <c r="D125" s="302"/>
       <c r="E125" s="125"/>
       <c r="F125" s="244"/>
@@ -19390,13 +19390,13 @@
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
       <c r="AR125" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
       <c r="B126" s="454"/>
-      <c r="C126" s="485"/>
+      <c r="C126" s="496"/>
       <c r="D126" s="302"/>
       <c r="E126" s="125"/>
       <c r="F126" s="244"/>
@@ -19478,13 +19478,13 @@
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
       <c r="AR126" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
       <c r="B127" s="454"/>
-      <c r="C127" s="485"/>
+      <c r="C127" s="496"/>
       <c r="D127" s="302"/>
       <c r="E127" s="126"/>
       <c r="F127" s="245"/>
@@ -19566,7 +19566,7 @@
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
       <c r="AR127" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="128" spans="1:44" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -19576,7 +19576,7 @@
       <c r="B128" s="454" t="s">
         <v>932</v>
       </c>
-      <c r="C128" s="485"/>
+      <c r="C128" s="496"/>
       <c r="D128" s="302" t="s">
         <v>742</v>
       </c>
@@ -19694,13 +19694,13 @@
         <v>122</v>
       </c>
       <c r="AR128" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="129" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A129" s="457"/>
       <c r="B129" s="454"/>
-      <c r="C129" s="485"/>
+      <c r="C129" s="496"/>
       <c r="D129" s="302"/>
       <c r="E129" s="125"/>
       <c r="F129" s="244"/>
@@ -19786,13 +19786,13 @@
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
       <c r="AR129" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
       <c r="B130" s="454"/>
-      <c r="C130" s="485"/>
+      <c r="C130" s="496"/>
       <c r="D130" s="302"/>
       <c r="E130" s="125"/>
       <c r="F130" s="244"/>
@@ -19878,13 +19878,13 @@
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
       <c r="AR130" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
       <c r="B131" s="454"/>
-      <c r="C131" s="486"/>
+      <c r="C131" s="497"/>
       <c r="D131" s="315"/>
       <c r="E131" s="129"/>
       <c r="F131" s="246"/>
@@ -19962,7 +19962,7 @@
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
       <c r="AR131" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="132" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -19972,7 +19972,7 @@
       <c r="B132" s="454" t="s">
         <v>933</v>
       </c>
-      <c r="C132" s="484">
+      <c r="C132" s="495">
         <v>73</v>
       </c>
       <c r="D132" s="302" t="s">
@@ -20090,13 +20090,13 @@
         <v>280</v>
       </c>
       <c r="AR132" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="133" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A133" s="457"/>
       <c r="B133" s="454"/>
-      <c r="C133" s="485"/>
+      <c r="C133" s="496"/>
       <c r="D133" s="302"/>
       <c r="E133" s="125"/>
       <c r="F133" s="244"/>
@@ -20178,13 +20178,13 @@
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
       <c r="AR133" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
       <c r="B134" s="454"/>
-      <c r="C134" s="485"/>
+      <c r="C134" s="496"/>
       <c r="D134" s="302"/>
       <c r="E134" s="125"/>
       <c r="F134" s="244"/>
@@ -20266,13 +20266,13 @@
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
       <c r="AR134" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
       <c r="B135" s="454"/>
-      <c r="C135" s="485"/>
+      <c r="C135" s="496"/>
       <c r="D135" s="302"/>
       <c r="E135" s="126"/>
       <c r="F135" s="245"/>
@@ -20354,7 +20354,7 @@
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
       <c r="AR135" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="136" spans="1:44" x14ac:dyDescent="0.3">
@@ -20364,7 +20364,7 @@
       <c r="B136" s="454" t="s">
         <v>934</v>
       </c>
-      <c r="C136" s="485"/>
+      <c r="C136" s="496"/>
       <c r="D136" s="302" t="s">
         <v>742</v>
       </c>
@@ -20480,13 +20480,13 @@
         <v>272</v>
       </c>
       <c r="AR136" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="137" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A137" s="457"/>
       <c r="B137" s="454"/>
-      <c r="C137" s="485"/>
+      <c r="C137" s="496"/>
       <c r="D137" s="302"/>
       <c r="E137" s="125"/>
       <c r="F137" s="244"/>
@@ -20568,13 +20568,13 @@
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
       <c r="AR137" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
       <c r="B138" s="454"/>
-      <c r="C138" s="485"/>
+      <c r="C138" s="496"/>
       <c r="D138" s="302"/>
       <c r="E138" s="125"/>
       <c r="F138" s="244"/>
@@ -20656,13 +20656,13 @@
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
       <c r="AR138" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
       <c r="B139" s="454"/>
-      <c r="C139" s="485"/>
+      <c r="C139" s="496"/>
       <c r="D139" s="302"/>
       <c r="E139" s="125"/>
       <c r="F139" s="244"/>
@@ -20744,13 +20744,13 @@
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
       <c r="AR139" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
       <c r="B140" s="454"/>
-      <c r="C140" s="486"/>
+      <c r="C140" s="497"/>
       <c r="D140" s="315"/>
       <c r="E140" s="129"/>
       <c r="F140" s="246"/>
@@ -20830,7 +20830,7 @@
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
       <c r="AR140" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="141" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -20840,7 +20840,7 @@
       <c r="B141" s="454" t="s">
         <v>935</v>
       </c>
-      <c r="C141" s="487">
+      <c r="C141" s="498">
         <v>74</v>
       </c>
       <c r="D141" s="302" t="s">
@@ -20956,13 +20956,13 @@
         <v>193</v>
       </c>
       <c r="AR141" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="142" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A142" s="457"/>
       <c r="B142" s="454"/>
-      <c r="C142" s="488"/>
+      <c r="C142" s="499"/>
       <c r="D142" s="303"/>
       <c r="E142" s="125"/>
       <c r="F142" s="244"/>
@@ -21044,13 +21044,13 @@
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
       <c r="AR142" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
       <c r="B143" s="454"/>
-      <c r="C143" s="488"/>
+      <c r="C143" s="499"/>
       <c r="D143" s="303"/>
       <c r="E143" s="125"/>
       <c r="F143" s="244"/>
@@ -21132,13 +21132,13 @@
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
       <c r="AR143" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
       <c r="B144" s="454"/>
-      <c r="C144" s="488"/>
+      <c r="C144" s="499"/>
       <c r="D144" s="303"/>
       <c r="E144" s="125"/>
       <c r="F144" s="244"/>
@@ -21220,13 +21220,13 @@
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
       <c r="AR144" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
       <c r="B145" s="454"/>
-      <c r="C145" s="488"/>
+      <c r="C145" s="499"/>
       <c r="D145" s="303"/>
       <c r="E145" s="126"/>
       <c r="F145" s="245"/>
@@ -21308,7 +21308,7 @@
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
       <c r="AR145" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="146" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -21318,7 +21318,7 @@
       <c r="B146" s="454" t="s">
         <v>936</v>
       </c>
-      <c r="C146" s="488"/>
+      <c r="C146" s="499"/>
       <c r="D146" s="302" t="s">
         <v>742</v>
       </c>
@@ -21434,13 +21434,13 @@
         <v>215</v>
       </c>
       <c r="AR146" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="147" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A147" s="457"/>
       <c r="B147" s="454"/>
-      <c r="C147" s="488"/>
+      <c r="C147" s="499"/>
       <c r="D147" s="303"/>
       <c r="E147" s="125"/>
       <c r="F147" s="244"/>
@@ -21522,13 +21522,13 @@
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
       <c r="AR147" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
       <c r="B148" s="454"/>
-      <c r="C148" s="488"/>
+      <c r="C148" s="499"/>
       <c r="D148" s="303"/>
       <c r="E148" s="125"/>
       <c r="F148" s="244"/>
@@ -21610,13 +21610,13 @@
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
       <c r="AR148" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
       <c r="B149" s="454"/>
-      <c r="C149" s="489"/>
+      <c r="C149" s="500"/>
       <c r="D149" s="316"/>
       <c r="E149" s="129"/>
       <c r="F149" s="246"/>
@@ -21698,7 +21698,7 @@
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
       <c r="AR149" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="150" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -21708,7 +21708,7 @@
       <c r="B150" s="454" t="s">
         <v>937</v>
       </c>
-      <c r="C150" s="484">
+      <c r="C150" s="495">
         <v>75</v>
       </c>
       <c r="D150" s="302" t="s">
@@ -21824,13 +21824,13 @@
         <v>273</v>
       </c>
       <c r="AR150" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="151" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A151" s="457"/>
       <c r="B151" s="454"/>
-      <c r="C151" s="485"/>
+      <c r="C151" s="496"/>
       <c r="D151" s="302"/>
       <c r="E151" s="125"/>
       <c r="F151" s="244"/>
@@ -21912,13 +21912,13 @@
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
       <c r="AR151" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
       <c r="B152" s="454"/>
-      <c r="C152" s="485"/>
+      <c r="C152" s="496"/>
       <c r="D152" s="302"/>
       <c r="E152" s="125"/>
       <c r="F152" s="244"/>
@@ -22000,13 +22000,13 @@
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
       <c r="AR152" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
       <c r="B153" s="454"/>
-      <c r="C153" s="485"/>
+      <c r="C153" s="496"/>
       <c r="D153" s="302"/>
       <c r="E153" s="126"/>
       <c r="F153" s="245"/>
@@ -22088,7 +22088,7 @@
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
       <c r="AR153" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="154" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -22098,7 +22098,7 @@
       <c r="B154" s="454" t="s">
         <v>938</v>
       </c>
-      <c r="C154" s="485"/>
+      <c r="C154" s="496"/>
       <c r="D154" s="302" t="s">
         <v>742</v>
       </c>
@@ -22212,13 +22212,13 @@
         <v>162</v>
       </c>
       <c r="AR154" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="155" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A155" s="457"/>
       <c r="B155" s="454"/>
-      <c r="C155" s="485"/>
+      <c r="C155" s="496"/>
       <c r="D155" s="302"/>
       <c r="E155" s="125"/>
       <c r="F155" s="244"/>
@@ -22300,13 +22300,13 @@
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
       <c r="AR155" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
       <c r="B156" s="454"/>
-      <c r="C156" s="485"/>
+      <c r="C156" s="496"/>
       <c r="D156" s="302"/>
       <c r="E156" s="125"/>
       <c r="F156" s="244"/>
@@ -22388,13 +22388,13 @@
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
       <c r="AR156" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
       <c r="B157" s="454"/>
-      <c r="C157" s="485"/>
+      <c r="C157" s="496"/>
       <c r="D157" s="302"/>
       <c r="E157" s="125"/>
       <c r="F157" s="244"/>
@@ -22476,13 +22476,13 @@
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
       <c r="AR157" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
       <c r="B158" s="454"/>
-      <c r="C158" s="486"/>
+      <c r="C158" s="497"/>
       <c r="D158" s="315"/>
       <c r="E158" s="129"/>
       <c r="F158" s="246"/>
@@ -22562,7 +22562,7 @@
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
       <c r="AR158" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="159" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -22572,7 +22572,7 @@
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="490">
+      <c r="C159" s="501">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22690,13 +22690,13 @@
         <v>199</v>
       </c>
       <c r="AR159" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="491"/>
+      <c r="C160" s="502"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22778,13 +22778,13 @@
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
       <c r="AR160" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="491"/>
+      <c r="C161" s="502"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22866,13 +22866,13 @@
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
       <c r="AR161" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="491"/>
+      <c r="C162" s="502"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22954,7 +22954,7 @@
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
       <c r="AR162" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="163" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -22964,7 +22964,7 @@
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="491"/>
+      <c r="C163" s="502"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -23080,13 +23080,13 @@
         <v>201</v>
       </c>
       <c r="AR163" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="491"/>
+      <c r="C164" s="502"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -23168,13 +23168,13 @@
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
       <c r="AR164" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="491"/>
+      <c r="C165" s="502"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -23256,13 +23256,13 @@
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
       <c r="AR165" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="491"/>
+      <c r="C166" s="502"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -23344,7 +23344,7 @@
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
       <c r="AR166" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="167" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -23354,7 +23354,7 @@
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="491"/>
+      <c r="C167" s="502"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -23470,13 +23470,13 @@
         <v>198</v>
       </c>
       <c r="AR167" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="491"/>
+      <c r="C168" s="502"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -23558,13 +23558,13 @@
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
       <c r="AR168" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="491"/>
+      <c r="C169" s="502"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -23646,13 +23646,13 @@
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
       <c r="AR169" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="492"/>
+      <c r="C170" s="503"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23734,7 +23734,7 @@
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
       <c r="AR170" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="171" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -23744,7 +23744,7 @@
       <c r="B171" s="454" t="s">
         <v>942</v>
       </c>
-      <c r="C171" s="493">
+      <c r="C171" s="504">
         <v>82</v>
       </c>
       <c r="D171" s="304" t="s">
@@ -23862,13 +23862,13 @@
         <v>280</v>
       </c>
       <c r="AR171" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="172" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A172" s="457"/>
       <c r="B172" s="454"/>
-      <c r="C172" s="494"/>
+      <c r="C172" s="505"/>
       <c r="D172" s="304"/>
       <c r="E172" s="137"/>
       <c r="F172" s="247"/>
@@ -23950,13 +23950,13 @@
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
       <c r="AR172" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
       <c r="B173" s="454"/>
-      <c r="C173" s="494"/>
+      <c r="C173" s="505"/>
       <c r="D173" s="304"/>
       <c r="E173" s="137"/>
       <c r="F173" s="247"/>
@@ -24038,13 +24038,13 @@
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
       <c r="AR173" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
       <c r="B174" s="454"/>
-      <c r="C174" s="494"/>
+      <c r="C174" s="505"/>
       <c r="D174" s="304"/>
       <c r="E174" s="138"/>
       <c r="F174" s="248"/>
@@ -24128,7 +24128,7 @@
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
       <c r="AR174" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="175" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -24138,7 +24138,7 @@
       <c r="B175" s="454" t="s">
         <v>943</v>
       </c>
-      <c r="C175" s="494"/>
+      <c r="C175" s="505"/>
       <c r="D175" s="304" t="s">
         <v>743</v>
       </c>
@@ -24254,13 +24254,13 @@
         <v>256</v>
       </c>
       <c r="AR175" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="176" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A176" s="457"/>
       <c r="B176" s="454"/>
-      <c r="C176" s="494"/>
+      <c r="C176" s="505"/>
       <c r="D176" s="304"/>
       <c r="E176" s="137"/>
       <c r="F176" s="247"/>
@@ -24348,13 +24348,13 @@
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
       <c r="AR176" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
       <c r="B177" s="454"/>
-      <c r="C177" s="494"/>
+      <c r="C177" s="505"/>
       <c r="D177" s="304"/>
       <c r="E177" s="137"/>
       <c r="F177" s="247"/>
@@ -24440,13 +24440,13 @@
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
       <c r="AR177" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
       <c r="B178" s="454"/>
-      <c r="C178" s="494"/>
+      <c r="C178" s="505"/>
       <c r="D178" s="304"/>
       <c r="E178" s="138"/>
       <c r="F178" s="248"/>
@@ -24530,7 +24530,7 @@
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
       <c r="AR178" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="179" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -24540,7 +24540,7 @@
       <c r="B179" s="454" t="s">
         <v>944</v>
       </c>
-      <c r="C179" s="494"/>
+      <c r="C179" s="505"/>
       <c r="D179" s="304" t="s">
         <v>743</v>
       </c>
@@ -24656,13 +24656,13 @@
         <v>280</v>
       </c>
       <c r="AR179" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="180" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A180" s="457"/>
       <c r="B180" s="454"/>
-      <c r="C180" s="494"/>
+      <c r="C180" s="505"/>
       <c r="D180" s="304"/>
       <c r="E180" s="137"/>
       <c r="F180" s="247"/>
@@ -24744,13 +24744,13 @@
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
       <c r="AR180" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
       <c r="B181" s="454"/>
-      <c r="C181" s="494"/>
+      <c r="C181" s="505"/>
       <c r="D181" s="304"/>
       <c r="E181" s="137"/>
       <c r="F181" s="247"/>
@@ -24832,13 +24832,13 @@
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
       <c r="AR181" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
       <c r="B182" s="454"/>
-      <c r="C182" s="494"/>
+      <c r="C182" s="505"/>
       <c r="D182" s="304"/>
       <c r="E182" s="137"/>
       <c r="F182" s="247"/>
@@ -24920,13 +24920,13 @@
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
       <c r="AR182" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
       <c r="B183" s="454"/>
-      <c r="C183" s="495"/>
+      <c r="C183" s="506"/>
       <c r="D183" s="317"/>
       <c r="E183" s="141"/>
       <c r="F183" s="249"/>
@@ -25008,7 +25008,7 @@
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
       <c r="AR183" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="184" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -25018,7 +25018,7 @@
       <c r="B184" s="454">
         <v>831</v>
       </c>
-      <c r="C184" s="493">
+      <c r="C184" s="504">
         <v>83</v>
       </c>
       <c r="D184" s="304" t="s">
@@ -25136,13 +25136,13 @@
         <v>224</v>
       </c>
       <c r="AR184" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="185" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A185" s="457"/>
       <c r="B185" s="454"/>
-      <c r="C185" s="494"/>
+      <c r="C185" s="505"/>
       <c r="D185" s="304"/>
       <c r="E185" s="137"/>
       <c r="F185" s="247"/>
@@ -25226,13 +25226,13 @@
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
       <c r="AR185" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
       <c r="B186" s="454"/>
-      <c r="C186" s="494"/>
+      <c r="C186" s="505"/>
       <c r="D186" s="304"/>
       <c r="E186" s="137"/>
       <c r="F186" s="247"/>
@@ -25314,13 +25314,13 @@
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
       <c r="AR186" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
       <c r="B187" s="454"/>
-      <c r="C187" s="494"/>
+      <c r="C187" s="505"/>
       <c r="D187" s="304"/>
       <c r="E187" s="138"/>
       <c r="F187" s="248"/>
@@ -25404,7 +25404,7 @@
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
       <c r="AR187" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="188" spans="1:44" ht="39" customHeight="1" x14ac:dyDescent="0.3">
@@ -25414,7 +25414,7 @@
       <c r="B188" s="454" t="s">
         <v>945</v>
       </c>
-      <c r="C188" s="494"/>
+      <c r="C188" s="505"/>
       <c r="D188" s="304" t="s">
         <v>743</v>
       </c>
@@ -25528,13 +25528,13 @@
         <v>237</v>
       </c>
       <c r="AR188" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="189" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A189" s="457"/>
       <c r="B189" s="454"/>
-      <c r="C189" s="494"/>
+      <c r="C189" s="505"/>
       <c r="D189" s="304"/>
       <c r="E189" s="137"/>
       <c r="F189" s="247"/>
@@ -25616,13 +25616,13 @@
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
       <c r="AR189" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
       <c r="B190" s="454"/>
-      <c r="C190" s="494"/>
+      <c r="C190" s="505"/>
       <c r="D190" s="304"/>
       <c r="E190" s="137"/>
       <c r="F190" s="247"/>
@@ -25704,13 +25704,13 @@
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
       <c r="AR190" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
       <c r="B191" s="454"/>
-      <c r="C191" s="495"/>
+      <c r="C191" s="506"/>
       <c r="D191" s="317"/>
       <c r="E191" s="141"/>
       <c r="F191" s="249"/>
@@ -25790,7 +25790,7 @@
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
       <c r="AR191" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="192" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -25800,7 +25800,7 @@
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="496">
+      <c r="C192" s="507">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25916,13 +25916,13 @@
         <v>117</v>
       </c>
       <c r="AR192" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="497"/>
+      <c r="C193" s="508"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -26004,13 +26004,13 @@
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
       <c r="AR193" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="497"/>
+      <c r="C194" s="508"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -26092,13 +26092,13 @@
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
       <c r="AR194" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="497"/>
+      <c r="C195" s="508"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -26180,7 +26180,7 @@
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
       <c r="AR195" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="196" spans="1:44" ht="63.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -26190,7 +26190,7 @@
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="497"/>
+      <c r="C196" s="508"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -26304,13 +26304,13 @@
         <v>131</v>
       </c>
       <c r="AR196" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="497"/>
+      <c r="C197" s="508"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -26392,13 +26392,13 @@
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
       <c r="AR197" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="497"/>
+      <c r="C198" s="508"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -26480,13 +26480,13 @@
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
       <c r="AR198" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="498"/>
+      <c r="C199" s="509"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -26568,7 +26568,7 @@
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
       <c r="AR199" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="200" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -26578,7 +26578,7 @@
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="499">
+      <c r="C200" s="510">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -26698,13 +26698,13 @@
         <v>66</v>
       </c>
       <c r="AR200" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="500"/>
+      <c r="C201" s="511"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -26790,13 +26790,13 @@
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
       <c r="AR201" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="500"/>
+      <c r="C202" s="511"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26880,7 +26880,7 @@
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
       <c r="AR202" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="203" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
@@ -26890,7 +26890,7 @@
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="500"/>
+      <c r="C203" s="511"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -27010,13 +27010,13 @@
         <v>47</v>
       </c>
       <c r="AR203" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="500"/>
+      <c r="C204" s="511"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -27102,13 +27102,13 @@
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
       <c r="AR204" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="500"/>
+      <c r="C205" s="511"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -27192,7 +27192,7 @@
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
       <c r="AR205" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="206" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
@@ -27202,7 +27202,7 @@
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="500"/>
+      <c r="C206" s="511"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -27322,13 +27322,13 @@
         <v>42</v>
       </c>
       <c r="AR206" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="500"/>
+      <c r="C207" s="511"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -27410,13 +27410,13 @@
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
       <c r="AR207" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="501"/>
+      <c r="C208" s="512"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -27502,7 +27502,7 @@
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
       <c r="AR208" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="209" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -27512,7 +27512,7 @@
       <c r="B209" s="454" t="s">
         <v>951</v>
       </c>
-      <c r="C209" s="475">
+      <c r="C209" s="489">
         <v>101</v>
       </c>
       <c r="D209" s="306" t="s">
@@ -27634,13 +27634,13 @@
         <v>151</v>
       </c>
       <c r="AR209" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="210" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A210" s="457"/>
       <c r="B210" s="454"/>
-      <c r="C210" s="476"/>
+      <c r="C210" s="490"/>
       <c r="D210" s="306"/>
       <c r="E210" s="163"/>
       <c r="F210" s="253"/>
@@ -27726,13 +27726,13 @@
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
       <c r="AR210" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
       <c r="B211" s="454"/>
-      <c r="C211" s="476"/>
+      <c r="C211" s="490"/>
       <c r="D211" s="306"/>
       <c r="E211" s="163"/>
       <c r="F211" s="253"/>
@@ -27818,13 +27818,13 @@
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
       <c r="AR211" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
       <c r="B212" s="454"/>
-      <c r="C212" s="476"/>
+      <c r="C212" s="490"/>
       <c r="D212" s="306"/>
       <c r="E212" s="164"/>
       <c r="F212" s="254"/>
@@ -27908,7 +27908,7 @@
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
       <c r="AR212" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="213" spans="1:44" ht="41.4" x14ac:dyDescent="0.3">
@@ -27918,7 +27918,7 @@
       <c r="B213" s="454" t="s">
         <v>952</v>
       </c>
-      <c r="C213" s="476"/>
+      <c r="C213" s="490"/>
       <c r="D213" s="306" t="s">
         <v>745</v>
       </c>
@@ -28038,13 +28038,13 @@
         <v>130</v>
       </c>
       <c r="AR213" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="214" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A214" s="457"/>
       <c r="B214" s="454"/>
-      <c r="C214" s="476"/>
+      <c r="C214" s="490"/>
       <c r="D214" s="306"/>
       <c r="E214" s="163"/>
       <c r="F214" s="253"/>
@@ -28130,13 +28130,13 @@
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
       <c r="AR214" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
       <c r="B215" s="454"/>
-      <c r="C215" s="477"/>
+      <c r="C215" s="491"/>
       <c r="D215" s="319"/>
       <c r="E215" s="166"/>
       <c r="F215" s="255"/>
@@ -28222,7 +28222,7 @@
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
       <c r="AR215" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="216" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -28232,7 +28232,7 @@
       <c r="B216" s="454" t="s">
         <v>953</v>
       </c>
-      <c r="C216" s="459">
+      <c r="C216" s="513">
         <v>102</v>
       </c>
       <c r="D216" s="307" t="s">
@@ -28354,13 +28354,13 @@
         <v>81</v>
       </c>
       <c r="AR216" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="217" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A217" s="457"/>
       <c r="B217" s="454"/>
-      <c r="C217" s="460"/>
+      <c r="C217" s="514"/>
       <c r="D217" s="307"/>
       <c r="E217" s="174"/>
       <c r="F217" s="256"/>
@@ -28446,13 +28446,13 @@
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
       <c r="AR217" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
       <c r="B218" s="454"/>
-      <c r="C218" s="460"/>
+      <c r="C218" s="514"/>
       <c r="D218" s="307"/>
       <c r="E218" s="174"/>
       <c r="F218" s="256"/>
@@ -28538,13 +28538,13 @@
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
       <c r="AR218" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
       <c r="B219" s="454"/>
-      <c r="C219" s="461"/>
+      <c r="C219" s="515"/>
       <c r="D219" s="320"/>
       <c r="E219" s="175"/>
       <c r="F219" s="257"/>
@@ -28630,7 +28630,7 @@
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
       <c r="AR219" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="220" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -28640,7 +28640,7 @@
       <c r="B220" s="454" t="s">
         <v>954</v>
       </c>
-      <c r="C220" s="459">
+      <c r="C220" s="513">
         <v>103</v>
       </c>
       <c r="D220" s="307" t="s">
@@ -28758,13 +28758,13 @@
         <v>119</v>
       </c>
       <c r="AR220" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="221" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A221" s="457"/>
       <c r="B221" s="454"/>
-      <c r="C221" s="460"/>
+      <c r="C221" s="514"/>
       <c r="D221" s="307"/>
       <c r="E221" s="174"/>
       <c r="F221" s="256"/>
@@ -28848,13 +28848,13 @@
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
       <c r="AR221" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
       <c r="B222" s="454"/>
-      <c r="C222" s="460"/>
+      <c r="C222" s="514"/>
       <c r="D222" s="307"/>
       <c r="E222" s="178"/>
       <c r="F222" s="258"/>
@@ -28938,7 +28938,7 @@
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
       <c r="AR222" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="223" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -28948,7 +28948,7 @@
       <c r="B223" s="454" t="s">
         <v>955</v>
       </c>
-      <c r="C223" s="460"/>
+      <c r="C223" s="514"/>
       <c r="D223" s="307" t="s">
         <v>745</v>
       </c>
@@ -29068,13 +29068,13 @@
         <v>151</v>
       </c>
       <c r="AR223" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="224" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A224" s="457"/>
       <c r="B224" s="454"/>
-      <c r="C224" s="460"/>
+      <c r="C224" s="514"/>
       <c r="D224" s="307"/>
       <c r="E224" s="174"/>
       <c r="F224" s="256"/>
@@ -29160,13 +29160,13 @@
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
       <c r="AR224" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
       <c r="B225" s="454"/>
-      <c r="C225" s="460"/>
+      <c r="C225" s="514"/>
       <c r="D225" s="307"/>
       <c r="E225" s="174"/>
       <c r="F225" s="256"/>
@@ -29252,13 +29252,13 @@
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
       <c r="AR225" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
       <c r="B226" s="454"/>
-      <c r="C226" s="461"/>
+      <c r="C226" s="515"/>
       <c r="D226" s="320"/>
       <c r="E226" s="175"/>
       <c r="F226" s="257"/>
@@ -29338,7 +29338,7 @@
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
       <c r="AR226" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="227" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -29348,7 +29348,7 @@
       <c r="B227" s="454" t="s">
         <v>956</v>
       </c>
-      <c r="C227" s="459">
+      <c r="C227" s="513">
         <v>104</v>
       </c>
       <c r="D227" s="307" t="s">
@@ -29466,13 +29466,13 @@
         <v>139</v>
       </c>
       <c r="AR227" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="228" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A228" s="457"/>
       <c r="B228" s="454"/>
-      <c r="C228" s="460"/>
+      <c r="C228" s="514"/>
       <c r="D228" s="307"/>
       <c r="E228" s="174"/>
       <c r="F228" s="256"/>
@@ -29554,13 +29554,13 @@
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
       <c r="AR228" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
       <c r="B229" s="454"/>
-      <c r="C229" s="460"/>
+      <c r="C229" s="514"/>
       <c r="D229" s="307"/>
       <c r="E229" s="174"/>
       <c r="F229" s="256"/>
@@ -29642,13 +29642,13 @@
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
       <c r="AR229" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
       <c r="B230" s="454"/>
-      <c r="C230" s="460"/>
+      <c r="C230" s="514"/>
       <c r="D230" s="307"/>
       <c r="E230" s="178"/>
       <c r="F230" s="258"/>
@@ -29730,7 +29730,7 @@
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
       <c r="AR230" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="231" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -29740,7 +29740,7 @@
       <c r="B231" s="454" t="s">
         <v>957</v>
       </c>
-      <c r="C231" s="460"/>
+      <c r="C231" s="514"/>
       <c r="D231" s="307" t="s">
         <v>745</v>
       </c>
@@ -29856,13 +29856,13 @@
         <v>134</v>
       </c>
       <c r="AR231" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="232" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A232" s="457"/>
       <c r="B232" s="454"/>
-      <c r="C232" s="460"/>
+      <c r="C232" s="514"/>
       <c r="D232" s="307"/>
       <c r="E232" s="174"/>
       <c r="F232" s="256"/>
@@ -29944,13 +29944,13 @@
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
       <c r="AR232" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
       <c r="B233" s="454"/>
-      <c r="C233" s="460"/>
+      <c r="C233" s="514"/>
       <c r="D233" s="307"/>
       <c r="E233" s="174"/>
       <c r="F233" s="256"/>
@@ -30032,13 +30032,13 @@
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
       <c r="AR233" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
       <c r="B234" s="454"/>
-      <c r="C234" s="461"/>
+      <c r="C234" s="515"/>
       <c r="D234" s="320"/>
       <c r="E234" s="175"/>
       <c r="F234" s="257"/>
@@ -30116,7 +30116,7 @@
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
       <c r="AR234" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="235" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -30126,7 +30126,7 @@
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="468">
+      <c r="C235" s="522">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -30244,13 +30244,13 @@
         <v>146</v>
       </c>
       <c r="AR235" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="469"/>
+      <c r="C236" s="523"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -30332,13 +30332,13 @@
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
       <c r="AR236" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="469"/>
+      <c r="C237" s="523"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -30420,13 +30420,13 @@
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
       <c r="AR237" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="470"/>
+      <c r="C238" s="524"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -30506,7 +30506,7 @@
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
       <c r="AR238" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="239" spans="1:44" ht="56.7" customHeight="1" x14ac:dyDescent="0.3">
@@ -30516,7 +30516,7 @@
       <c r="B239" s="454" t="s">
         <v>959</v>
       </c>
-      <c r="C239" s="471">
+      <c r="C239" s="525">
         <v>106</v>
       </c>
       <c r="D239" s="308" t="s">
@@ -30634,13 +30634,13 @@
         <v>193</v>
       </c>
       <c r="AR239" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="240" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A240" s="457"/>
       <c r="B240" s="454"/>
-      <c r="C240" s="472"/>
+      <c r="C240" s="526"/>
       <c r="D240" s="308"/>
       <c r="E240" s="185"/>
       <c r="F240" s="259"/>
@@ -30722,13 +30722,13 @@
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
       <c r="AR240" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
       <c r="B241" s="454"/>
-      <c r="C241" s="472"/>
+      <c r="C241" s="526"/>
       <c r="D241" s="308"/>
       <c r="E241" s="185"/>
       <c r="F241" s="259"/>
@@ -30810,13 +30810,13 @@
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
       <c r="AR241" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
       <c r="B242" s="454"/>
-      <c r="C242" s="472"/>
+      <c r="C242" s="526"/>
       <c r="D242" s="308"/>
       <c r="E242" s="189"/>
       <c r="F242" s="261"/>
@@ -30896,7 +30896,7 @@
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
       <c r="AR242" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="243" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -30906,7 +30906,7 @@
       <c r="B243" s="454" t="s">
         <v>960</v>
       </c>
-      <c r="C243" s="472"/>
+      <c r="C243" s="526"/>
       <c r="D243" s="308" t="s">
         <v>745</v>
       </c>
@@ -31022,13 +31022,13 @@
         <v>74</v>
       </c>
       <c r="AR243" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="244" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A244" s="457"/>
       <c r="B244" s="454"/>
-      <c r="C244" s="472"/>
+      <c r="C244" s="526"/>
       <c r="D244" s="308"/>
       <c r="E244" s="185"/>
       <c r="F244" s="259"/>
@@ -31110,13 +31110,13 @@
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
       <c r="AR244" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
       <c r="B245" s="454"/>
-      <c r="C245" s="472"/>
+      <c r="C245" s="526"/>
       <c r="D245" s="308"/>
       <c r="E245" s="185"/>
       <c r="F245" s="259"/>
@@ -31198,13 +31198,13 @@
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
       <c r="AR245" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
       <c r="B246" s="454"/>
-      <c r="C246" s="472"/>
+      <c r="C246" s="526"/>
       <c r="D246" s="308"/>
       <c r="E246" s="185"/>
       <c r="F246" s="259"/>
@@ -31286,13 +31286,13 @@
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
       <c r="AR246" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
       <c r="B247" s="454"/>
-      <c r="C247" s="472"/>
+      <c r="C247" s="526"/>
       <c r="D247" s="308"/>
       <c r="E247" s="181"/>
       <c r="F247" s="181"/>
@@ -31380,7 +31380,7 @@
         <v>191</v>
       </c>
       <c r="AR247" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="248" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -31390,7 +31390,7 @@
       <c r="B248" s="454" t="s">
         <v>961</v>
       </c>
-      <c r="C248" s="473"/>
+      <c r="C248" s="527"/>
       <c r="D248" s="308" t="s">
         <v>745</v>
       </c>
@@ -31500,13 +31500,13 @@
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
       <c r="AR248" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
       <c r="B249" s="454"/>
-      <c r="C249" s="472"/>
+      <c r="C249" s="526"/>
       <c r="D249" s="308"/>
       <c r="E249" s="185"/>
       <c r="F249" s="259"/>
@@ -31590,13 +31590,13 @@
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
       <c r="AR249" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
       <c r="B250" s="454"/>
-      <c r="C250" s="472"/>
+      <c r="C250" s="526"/>
       <c r="D250" s="308"/>
       <c r="E250" s="185"/>
       <c r="F250" s="259"/>
@@ -31680,13 +31680,13 @@
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
       <c r="AR250" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
       <c r="B251" s="454"/>
-      <c r="C251" s="472"/>
+      <c r="C251" s="526"/>
       <c r="D251" s="308"/>
       <c r="E251" s="189"/>
       <c r="F251" s="261"/>
@@ -31770,7 +31770,7 @@
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
       <c r="AR251" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="252" spans="1:44" ht="27.6" x14ac:dyDescent="0.3">
@@ -31780,7 +31780,7 @@
       <c r="B252" s="454" t="s">
         <v>962</v>
       </c>
-      <c r="C252" s="472"/>
+      <c r="C252" s="526"/>
       <c r="D252" s="308" t="s">
         <v>745</v>
       </c>
@@ -31896,13 +31896,13 @@
         <v>160</v>
       </c>
       <c r="AR252" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="253" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A253" s="457"/>
       <c r="B253" s="454"/>
-      <c r="C253" s="472"/>
+      <c r="C253" s="526"/>
       <c r="D253" s="308"/>
       <c r="E253" s="185"/>
       <c r="F253" s="259"/>
@@ -31984,13 +31984,13 @@
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
       <c r="AR253" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
       <c r="B254" s="454"/>
-      <c r="C254" s="472"/>
+      <c r="C254" s="526"/>
       <c r="D254" s="308"/>
       <c r="E254" s="185"/>
       <c r="F254" s="259"/>
@@ -32072,13 +32072,13 @@
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
       <c r="AR254" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
       <c r="B255" s="454"/>
-      <c r="C255" s="472"/>
+      <c r="C255" s="526"/>
       <c r="D255" s="308"/>
       <c r="E255" s="185"/>
       <c r="F255" s="259"/>
@@ -32160,13 +32160,13 @@
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
       <c r="AR255" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
       <c r="B256" s="454"/>
-      <c r="C256" s="474"/>
+      <c r="C256" s="528"/>
       <c r="D256" s="321"/>
       <c r="E256" s="186"/>
       <c r="F256" s="260"/>
@@ -32248,7 +32248,7 @@
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
       <c r="AR256" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="257" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -32258,7 +32258,7 @@
       <c r="B257" s="454" t="s">
         <v>963</v>
       </c>
-      <c r="C257" s="459">
+      <c r="C257" s="513">
         <v>107</v>
       </c>
       <c r="D257" s="307" t="s">
@@ -32376,13 +32376,13 @@
         <v>210</v>
       </c>
       <c r="AR257" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="258" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A258" s="457"/>
       <c r="B258" s="454"/>
-      <c r="C258" s="460"/>
+      <c r="C258" s="514"/>
       <c r="D258" s="307"/>
       <c r="E258" s="174"/>
       <c r="F258" s="256"/>
@@ -32466,13 +32466,13 @@
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
       <c r="AR258" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
       <c r="B259" s="454"/>
-      <c r="C259" s="460"/>
+      <c r="C259" s="514"/>
       <c r="D259" s="307"/>
       <c r="E259" s="174"/>
       <c r="F259" s="256"/>
@@ -32556,13 +32556,13 @@
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
       <c r="AR259" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
       <c r="B260" s="454"/>
-      <c r="C260" s="460"/>
+      <c r="C260" s="514"/>
       <c r="D260" s="307"/>
       <c r="E260" s="178"/>
       <c r="F260" s="258"/>
@@ -32644,7 +32644,7 @@
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
       <c r="AR260" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="261" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -32654,7 +32654,7 @@
       <c r="B261" s="454" t="s">
         <v>964</v>
       </c>
-      <c r="C261" s="460"/>
+      <c r="C261" s="514"/>
       <c r="D261" s="307" t="s">
         <v>745</v>
       </c>
@@ -32770,13 +32770,13 @@
         <v>101</v>
       </c>
       <c r="AR261" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="262" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A262" s="457"/>
       <c r="B262" s="454"/>
-      <c r="C262" s="460"/>
+      <c r="C262" s="514"/>
       <c r="D262" s="307"/>
       <c r="E262" s="174"/>
       <c r="F262" s="256"/>
@@ -32856,13 +32856,13 @@
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
       <c r="AR262" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
       <c r="B263" s="454"/>
-      <c r="C263" s="461"/>
+      <c r="C263" s="515"/>
       <c r="D263" s="320"/>
       <c r="E263" s="175"/>
       <c r="F263" s="257"/>
@@ -32942,7 +32942,7 @@
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
       <c r="AR263" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="264" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -32952,7 +32952,7 @@
       <c r="B264" s="454" t="s">
         <v>965</v>
       </c>
-      <c r="C264" s="459">
+      <c r="C264" s="513">
         <v>108</v>
       </c>
       <c r="D264" s="307" t="s">
@@ -33072,13 +33072,13 @@
         <v>231</v>
       </c>
       <c r="AR264" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="265" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A265" s="457"/>
       <c r="B265" s="454"/>
-      <c r="C265" s="460"/>
+      <c r="C265" s="514"/>
       <c r="D265" s="307"/>
       <c r="E265" s="174"/>
       <c r="F265" s="256"/>
@@ -33162,13 +33162,13 @@
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
       <c r="AR265" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
       <c r="B266" s="454"/>
-      <c r="C266" s="460"/>
+      <c r="C266" s="514"/>
       <c r="D266" s="307"/>
       <c r="E266" s="174"/>
       <c r="F266" s="256"/>
@@ -33252,13 +33252,13 @@
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
       <c r="AR266" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
       <c r="B267" s="454"/>
-      <c r="C267" s="461"/>
+      <c r="C267" s="515"/>
       <c r="D267" s="320"/>
       <c r="E267" s="175"/>
       <c r="F267" s="257"/>
@@ -33342,7 +33342,7 @@
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
       <c r="AR267" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="268" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -33352,7 +33352,7 @@
       <c r="B268" s="454" t="s">
         <v>966</v>
       </c>
-      <c r="C268" s="459">
+      <c r="C268" s="513">
         <v>109</v>
       </c>
       <c r="D268" s="307" t="s">
@@ -33474,13 +33474,13 @@
         <v>76</v>
       </c>
       <c r="AR268" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="269" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A269" s="457"/>
       <c r="B269" s="454"/>
-      <c r="C269" s="460"/>
+      <c r="C269" s="514"/>
       <c r="D269" s="307"/>
       <c r="E269" s="174"/>
       <c r="F269" s="256"/>
@@ -33566,13 +33566,13 @@
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
       <c r="AR269" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
       <c r="B270" s="454"/>
-      <c r="C270" s="461"/>
+      <c r="C270" s="515"/>
       <c r="D270" s="320"/>
       <c r="E270" s="175"/>
       <c r="F270" s="257"/>
@@ -33658,7 +33658,7 @@
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
       <c r="AR270" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="271" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -33668,7 +33668,7 @@
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="462">
+      <c r="C271" s="516">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -33790,13 +33790,13 @@
         <v>46</v>
       </c>
       <c r="AR271" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="463"/>
+      <c r="C272" s="517"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -33880,13 +33880,13 @@
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
       <c r="AR272" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="463"/>
+      <c r="C273" s="517"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -33970,7 +33970,7 @@
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
       <c r="AR273" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="274" spans="1:44" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -33980,7 +33980,7 @@
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="463"/>
+      <c r="C274" s="517"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -34092,13 +34092,13 @@
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
       <c r="AR274" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="463"/>
+      <c r="C275" s="517"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -34188,13 +34188,13 @@
         <v>126</v>
       </c>
       <c r="AR275" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="463"/>
+      <c r="C276" s="517"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -34278,13 +34278,13 @@
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
       <c r="AR276" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="464"/>
+      <c r="C277" s="518"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -34368,7 +34368,7 @@
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
       <c r="AR277" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="278" spans="1:44" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -34378,7 +34378,7 @@
       <c r="B278" s="454" t="s">
         <v>969</v>
       </c>
-      <c r="C278" s="465">
+      <c r="C278" s="519">
         <v>112</v>
       </c>
       <c r="D278" s="309" t="s">
@@ -34496,13 +34496,13 @@
         <v>72</v>
       </c>
       <c r="AR278" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="279" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A279" s="457"/>
       <c r="B279" s="454"/>
-      <c r="C279" s="466"/>
+      <c r="C279" s="520"/>
       <c r="D279" s="309"/>
       <c r="E279" s="197"/>
       <c r="F279" s="262"/>
@@ -34584,13 +34584,13 @@
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
       <c r="AR279" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
       <c r="B280" s="454"/>
-      <c r="C280" s="466"/>
+      <c r="C280" s="520"/>
       <c r="D280" s="309"/>
       <c r="E280" s="197"/>
       <c r="F280" s="262"/>
@@ -34672,13 +34672,13 @@
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
       <c r="AR280" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
       <c r="B281" s="455"/>
-      <c r="C281" s="467"/>
+      <c r="C281" s="521"/>
       <c r="D281" s="322"/>
       <c r="E281" s="201"/>
       <c r="F281" s="264"/>
@@ -34760,17 +34760,33 @@
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
       <c r="AR281" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="C13:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C264:C267"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="C271:C277"/>
+    <mergeCell ref="C278:C281"/>
+    <mergeCell ref="C216:C219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="C235:C238"/>
+    <mergeCell ref="C239:C256"/>
+    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C209:C215"/>
+    <mergeCell ref="C106:C114"/>
+    <mergeCell ref="C115:C122"/>
+    <mergeCell ref="C123:C131"/>
+    <mergeCell ref="C132:C140"/>
+    <mergeCell ref="C141:C149"/>
+    <mergeCell ref="C150:C158"/>
+    <mergeCell ref="C159:C170"/>
+    <mergeCell ref="C171:C183"/>
+    <mergeCell ref="C184:C191"/>
+    <mergeCell ref="C192:C199"/>
+    <mergeCell ref="C200:C208"/>
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="C35:C43"/>
     <mergeCell ref="C44:C46"/>
@@ -34783,28 +34799,12 @@
     <mergeCell ref="C83:C85"/>
     <mergeCell ref="C86:C97"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C209:C215"/>
-    <mergeCell ref="C106:C114"/>
-    <mergeCell ref="C115:C122"/>
-    <mergeCell ref="C123:C131"/>
-    <mergeCell ref="C132:C140"/>
-    <mergeCell ref="C141:C149"/>
-    <mergeCell ref="C150:C158"/>
-    <mergeCell ref="C159:C170"/>
-    <mergeCell ref="C171:C183"/>
-    <mergeCell ref="C184:C191"/>
-    <mergeCell ref="C192:C199"/>
-    <mergeCell ref="C200:C208"/>
-    <mergeCell ref="C264:C267"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="C271:C277"/>
-    <mergeCell ref="C278:C281"/>
-    <mergeCell ref="C216:C219"/>
-    <mergeCell ref="C220:C226"/>
-    <mergeCell ref="C227:C234"/>
-    <mergeCell ref="C235:C238"/>
-    <mergeCell ref="C239:C256"/>
-    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="C13:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C30"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D816325-2C0C-477E-B9AF-62E6D98157EB}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB765728-974F-4088-8FF4-3DCF0F7179D8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6205,7 +6205,7 @@
     <col min="31" max="31" width="13.21875" customWidth="1"/>
     <col min="32" max="32" width="11.5546875" style="206"/>
     <col min="34" max="35" width="11.5546875" style="206"/>
-    <col min="41" max="43" width="11.5546875" style="206"/>
+    <col min="41" max="44" width="11.5546875" style="206"/>
     <col min="262" max="262" width="19.21875" customWidth="1"/>
     <col min="263" max="263" width="51.109375" customWidth="1"/>
     <col min="264" max="264" width="25.5546875" customWidth="1"/>
@@ -7157,7 +7157,7 @@
       <c r="AQ1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AR1" s="16" t="s">
+      <c r="AR1" s="15" t="s">
         <v>984</v>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" s="33" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
-      <c r="AR3" t="s">
+      <c r="AR3" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
-      <c r="AR4" t="s">
+      <c r="AR4" s="51" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AR5" s="33" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
-      <c r="AR6" t="s">
+      <c r="AR6" s="52" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7783,7 +7783,7 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
-      <c r="AR7" t="s">
+      <c r="AR7" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
-      <c r="AR8" t="s">
+      <c r="AR8" s="66" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
-      <c r="AR9" t="s">
+      <c r="AR9" s="33" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
-      <c r="AR10" t="s">
+      <c r="AR10" s="52" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
-      <c r="AR11" t="s">
+      <c r="AR11" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
-      <c r="AR12" t="s">
+      <c r="AR12" s="51" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
-      <c r="AR13" t="s">
+      <c r="AR13" s="33" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
-      <c r="AR14" t="s">
+      <c r="AR14" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
-      <c r="AR15" t="s">
+      <c r="AR15" s="52" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
-      <c r="AR16" t="s">
+      <c r="AR16" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
-      <c r="AR17" t="s">
+      <c r="AR17" s="66" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8861,7 +8861,7 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
-      <c r="AR18" t="s">
+      <c r="AR18" s="33" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
-      <c r="AR19" t="s">
+      <c r="AR19" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
-      <c r="AR20" t="s">
+      <c r="AR20" s="52" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9125,7 +9125,7 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
-      <c r="AR21" t="s">
+      <c r="AR21" s="37" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" t="s">
+      <c r="AR22" s="51" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9345,7 +9345,7 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
-      <c r="AR23" t="s">
+      <c r="AR23" s="33" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
-      <c r="AR24" t="s">
+      <c r="AR24" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
-      <c r="AR25" t="s">
+      <c r="AR25" s="51" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
-      <c r="AR26" t="s">
+      <c r="AR26" s="33" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
-      <c r="AR27" t="s">
+      <c r="AR27" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9833,7 +9833,7 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
-      <c r="AR28" t="s">
+      <c r="AR28" s="52" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
-      <c r="AR29" t="s">
+      <c r="AR29" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" t="s">
+      <c r="AR30" s="51" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
-      <c r="AR31" t="s">
+      <c r="AR31" s="33" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10233,7 +10233,7 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
-      <c r="AR32" t="s">
+      <c r="AR32" s="52" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10325,7 +10325,7 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
-      <c r="AR33" t="s">
+      <c r="AR33" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10417,7 +10417,7 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
-      <c r="AR34" t="s">
+      <c r="AR34" s="51" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
-      <c r="AR35" t="s">
+      <c r="AR35" s="33" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
-      <c r="AR36" t="s">
+      <c r="AR36" s="52" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
-      <c r="AR37" t="s">
+      <c r="AR37" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10807,7 +10807,7 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
-      <c r="AR38" t="s">
+      <c r="AR38" s="66" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
-      <c r="AR39" t="s">
+      <c r="AR39" s="33" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
-      <c r="AR40" t="s">
+      <c r="AR40" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11109,7 +11109,7 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
-      <c r="AR41" t="s">
+      <c r="AR41" s="52" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11197,7 +11197,7 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
-      <c r="AR42" t="s">
+      <c r="AR42" s="37" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
-      <c r="AR43" t="s">
+      <c r="AR43" s="51" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
-      <c r="AR44" t="s">
+      <c r="AR44" s="33" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11505,7 +11505,7 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
-      <c r="AR45" t="s">
+      <c r="AR45" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
-      <c r="AR46" t="s">
+      <c r="AR46" s="51" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
-      <c r="AR47" t="s">
+      <c r="AR47" s="33" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11817,7 +11817,7 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
-      <c r="AR48" t="s">
+      <c r="AR48" s="52" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11907,7 +11907,7 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
-      <c r="AR49" t="s">
+      <c r="AR49" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
-      <c r="AR50" t="s">
+      <c r="AR50" s="51" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
-      <c r="AR51" t="s">
+      <c r="AR51" s="33" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
-      <c r="AR52" t="s">
+      <c r="AR52" s="52" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
-      <c r="AR53" t="s">
+      <c r="AR53" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
-      <c r="AR54" t="s">
+      <c r="AR54" s="51" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
-      <c r="AR55" t="s">
+      <c r="AR55" s="33" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12609,7 +12609,7 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
-      <c r="AR56" t="s">
+      <c r="AR56" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12697,7 +12697,7 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
-      <c r="AR57" t="s">
+      <c r="AR57" s="52" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
-      <c r="AR58" t="s">
+      <c r="AR58" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
-      <c r="AR59" t="s">
+      <c r="AR59" s="66" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
-      <c r="AR60" t="s">
+      <c r="AR60" s="33" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
-      <c r="AR61" t="s">
+      <c r="AR61" s="52" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
-      <c r="AR62" t="s">
+      <c r="AR62" s="37" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
-      <c r="AR63" t="s">
+      <c r="AR63" s="51" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13393,7 +13393,7 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
-      <c r="AR64" t="s">
+      <c r="AR64" s="33" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
-      <c r="AR65" t="s">
+      <c r="AR65" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13577,7 +13577,7 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
-      <c r="AR66" t="s">
+      <c r="AR66" s="51" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
-      <c r="AR67" t="s">
+      <c r="AR67" s="33" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13797,7 +13797,7 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
-      <c r="AR68" t="s">
+      <c r="AR68" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13887,7 +13887,7 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
-      <c r="AR69" t="s">
+      <c r="AR69" s="66" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14011,7 +14011,7 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
-      <c r="AR70" t="s">
+      <c r="AR70" s="33" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14099,7 +14099,7 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
-      <c r="AR71" t="s">
+      <c r="AR71" s="52" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
-      <c r="AR72" t="s">
+      <c r="AR72" s="103" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14275,7 +14275,7 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
-      <c r="AR73" t="s">
+      <c r="AR73" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
-      <c r="AR74" t="s">
+      <c r="AR74" s="51" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14491,7 +14491,7 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
-      <c r="AR75" t="s">
+      <c r="AR75" s="33" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14579,7 +14579,7 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
-      <c r="AR76" t="s">
+      <c r="AR76" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14667,7 +14667,7 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
-      <c r="AR77" t="s">
+      <c r="AR77" s="52" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14755,7 +14755,7 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
-      <c r="AR78" t="s">
+      <c r="AR78" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
-      <c r="AR79" t="s">
+      <c r="AR79" s="66" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14965,7 +14965,7 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
-      <c r="AR80" t="s">
+      <c r="AR80" s="33" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15053,7 +15053,7 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
-      <c r="AR81" t="s">
+      <c r="AR81" s="37" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
-      <c r="AR82" t="s">
+      <c r="AR82" s="51" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15271,7 +15271,7 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
-      <c r="AR83" t="s">
+      <c r="AR83" s="33" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15363,7 +15363,7 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
-      <c r="AR84" t="s">
+      <c r="AR84" s="37" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15453,7 +15453,7 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
-      <c r="AR85" t="s">
+      <c r="AR85" s="51" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15583,7 +15583,7 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
-      <c r="AR86" t="s">
+      <c r="AR86" s="33" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
-      <c r="AR87" t="s">
+      <c r="AR87" s="52" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15767,7 +15767,7 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
-      <c r="AR88" t="s">
+      <c r="AR88" s="37" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15859,7 +15859,7 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
-      <c r="AR89" t="s">
+      <c r="AR89" s="66" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15987,7 +15987,7 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
-      <c r="AR90" t="s">
+      <c r="AR90" s="33" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
-      <c r="AR91" t="s">
+      <c r="AR91" s="52" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
-      <c r="AR92" t="s">
+      <c r="AR92" s="37" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16257,7 +16257,7 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
-      <c r="AR93" t="s">
+      <c r="AR93" s="66" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16385,7 +16385,7 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR94" t="s">
+      <c r="AR94" s="118" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
-      <c r="AR95" t="s">
+      <c r="AR95" s="52" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
-      <c r="AR96" t="s">
+      <c r="AR96" s="37" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16655,7 +16655,7 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
-      <c r="AR97" t="s">
+      <c r="AR97" s="51" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
-      <c r="AR98" t="s">
+      <c r="AR98" s="33" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
-      <c r="AR99" t="s">
+      <c r="AR99" s="52" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16961,7 +16961,7 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
-      <c r="AR100" t="s">
+      <c r="AR100" s="37" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17051,7 +17051,7 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
-      <c r="AR101" t="s">
+      <c r="AR101" s="51" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17175,7 +17175,7 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
-      <c r="AR102" t="s">
+      <c r="AR102" s="33" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17263,7 +17263,7 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
-      <c r="AR103" t="s">
+      <c r="AR103" s="52" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17351,7 +17351,7 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
-      <c r="AR104" t="s">
+      <c r="AR104" s="37" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
-      <c r="AR105" t="s">
+      <c r="AR105" s="51" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17567,7 +17567,7 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
-      <c r="AR106" t="s">
+      <c r="AR106" s="33" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
-      <c r="AR107" t="s">
+      <c r="AR107" s="52" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17743,7 +17743,7 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
-      <c r="AR108" t="s">
+      <c r="AR108" s="37" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17831,7 +17831,7 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
-      <c r="AR109" t="s">
+      <c r="AR109" s="66" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17957,7 +17957,7 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
-      <c r="AR110" t="s">
+      <c r="AR110" s="33" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
-      <c r="AR111" t="s">
+      <c r="AR111" s="37" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18133,7 +18133,7 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
-      <c r="AR112" t="s">
+      <c r="AR112" s="52" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
-      <c r="AR113" t="s">
+      <c r="AR113" s="37" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18307,7 +18307,7 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
-      <c r="AR114" t="s">
+      <c r="AR114" s="51" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR115" t="s">
+      <c r="AR115" s="118" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18523,7 +18523,7 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
-      <c r="AR116" t="s">
+      <c r="AR116" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18611,7 +18611,7 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
-      <c r="AR117" t="s">
+      <c r="AR117" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18699,7 +18699,7 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
-      <c r="AR118" t="s">
+      <c r="AR118" s="66" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18823,7 +18823,7 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
-      <c r="AR119" t="s">
+      <c r="AR119" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
-      <c r="AR120" t="s">
+      <c r="AR120" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
-      <c r="AR121" t="s">
+      <c r="AR121" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19087,7 +19087,7 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
-      <c r="AR122" t="s">
+      <c r="AR122" s="51" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19213,7 +19213,7 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
-      <c r="AR123" t="s">
+      <c r="AR123" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19301,7 +19301,7 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
-      <c r="AR124" t="s">
+      <c r="AR124" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
-      <c r="AR125" t="s">
+      <c r="AR125" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19477,7 +19477,7 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
-      <c r="AR126" t="s">
+      <c r="AR126" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19565,7 +19565,7 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
-      <c r="AR127" t="s">
+      <c r="AR127" s="66" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
-      <c r="AR128" t="s">
+      <c r="AR128" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
-      <c r="AR129" t="s">
+      <c r="AR129" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
-      <c r="AR130" t="s">
+      <c r="AR130" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19961,7 +19961,7 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
-      <c r="AR131" t="s">
+      <c r="AR131" s="51" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20089,7 +20089,7 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR132" t="s">
+      <c r="AR132" s="118" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20177,7 +20177,7 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
-      <c r="AR133" t="s">
+      <c r="AR133" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20265,7 +20265,7 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
-      <c r="AR134" t="s">
+      <c r="AR134" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20353,7 +20353,7 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
-      <c r="AR135" t="s">
+      <c r="AR135" s="66" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20479,7 +20479,7 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
-      <c r="AR136" t="s">
+      <c r="AR136" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
-      <c r="AR137" t="s">
+      <c r="AR137" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20655,7 +20655,7 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
-      <c r="AR138" t="s">
+      <c r="AR138" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20743,7 +20743,7 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
-      <c r="AR139" t="s">
+      <c r="AR139" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20829,7 +20829,7 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
-      <c r="AR140" t="s">
+      <c r="AR140" s="51" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20955,7 +20955,7 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
-      <c r="AR141" t="s">
+      <c r="AR141" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21043,7 +21043,7 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
-      <c r="AR142" t="s">
+      <c r="AR142" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
-      <c r="AR143" t="s">
+      <c r="AR143" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21219,7 +21219,7 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
-      <c r="AR144" t="s">
+      <c r="AR144" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
-      <c r="AR145" t="s">
+      <c r="AR145" s="66" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21433,7 +21433,7 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
-      <c r="AR146" t="s">
+      <c r="AR146" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21521,7 +21521,7 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
-      <c r="AR147" t="s">
+      <c r="AR147" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21609,7 +21609,7 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
-      <c r="AR148" t="s">
+      <c r="AR148" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21697,7 +21697,7 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
-      <c r="AR149" t="s">
+      <c r="AR149" s="51" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21823,7 +21823,7 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
-      <c r="AR150" t="s">
+      <c r="AR150" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21911,7 +21911,7 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
-      <c r="AR151" t="s">
+      <c r="AR151" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21999,7 +21999,7 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
-      <c r="AR152" t="s">
+      <c r="AR152" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
-      <c r="AR153" t="s">
+      <c r="AR153" s="66" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
-      <c r="AR154" t="s">
+      <c r="AR154" s="33" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22299,7 +22299,7 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
-      <c r="AR155" t="s">
+      <c r="AR155" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22387,7 +22387,7 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
-      <c r="AR156" t="s">
+      <c r="AR156" s="52" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22475,7 +22475,7 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
-      <c r="AR157" t="s">
+      <c r="AR157" s="37" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22561,7 +22561,7 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
-      <c r="AR158" t="s">
+      <c r="AR158" s="51" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22689,7 +22689,7 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
-      <c r="AR159" t="s">
+      <c r="AR159" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
-      <c r="AR160" t="s">
+      <c r="AR160" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22865,7 +22865,7 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
-      <c r="AR161" t="s">
+      <c r="AR161" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22953,7 +22953,7 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
-      <c r="AR162" t="s">
+      <c r="AR162" s="66" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23079,7 +23079,7 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
-      <c r="AR163" t="s">
+      <c r="AR163" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23167,7 +23167,7 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
-      <c r="AR164" t="s">
+      <c r="AR164" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23255,7 +23255,7 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
-      <c r="AR165" t="s">
+      <c r="AR165" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23343,7 +23343,7 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
-      <c r="AR166" t="s">
+      <c r="AR166" s="66" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
-      <c r="AR167" t="s">
+      <c r="AR167" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
-      <c r="AR168" t="s">
+      <c r="AR168" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23645,7 +23645,7 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
-      <c r="AR169" t="s">
+      <c r="AR169" s="103" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23733,7 +23733,7 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
-      <c r="AR170" t="s">
+      <c r="AR170" s="51" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23861,7 +23861,7 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR171" t="s">
+      <c r="AR171" s="118" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
-      <c r="AR172" t="s">
+      <c r="AR172" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24037,7 +24037,7 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
-      <c r="AR173" t="s">
+      <c r="AR173" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24127,7 +24127,7 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
-      <c r="AR174" t="s">
+      <c r="AR174" s="66" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24253,7 +24253,7 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
-      <c r="AR175" t="s">
+      <c r="AR175" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
-      <c r="AR176" t="s">
+      <c r="AR176" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24439,7 +24439,7 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
-      <c r="AR177" t="s">
+      <c r="AR177" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24529,7 +24529,7 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
-      <c r="AR178" t="s">
+      <c r="AR178" s="66" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR179" t="s">
+      <c r="AR179" s="118" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24743,7 +24743,7 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
-      <c r="AR180" t="s">
+      <c r="AR180" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
-      <c r="AR181" t="s">
+      <c r="AR181" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24919,7 +24919,7 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
-      <c r="AR182" t="s">
+      <c r="AR182" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25007,7 +25007,7 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
-      <c r="AR183" t="s">
+      <c r="AR183" s="51" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
-      <c r="AR184" t="s">
+      <c r="AR184" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25225,7 +25225,7 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
-      <c r="AR185" t="s">
+      <c r="AR185" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
-      <c r="AR186" t="s">
+      <c r="AR186" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25403,7 +25403,7 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
-      <c r="AR187" t="s">
+      <c r="AR187" s="119" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
-      <c r="AR188" t="s">
+      <c r="AR188" s="33" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25615,7 +25615,7 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
-      <c r="AR189" t="s">
+      <c r="AR189" s="52" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25703,7 +25703,7 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
-      <c r="AR190" t="s">
+      <c r="AR190" s="37" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25789,7 +25789,7 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
-      <c r="AR191" t="s">
+      <c r="AR191" s="51" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25915,7 +25915,7 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
-      <c r="AR192" t="s">
+      <c r="AR192" s="33" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26003,7 +26003,7 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
-      <c r="AR193" t="s">
+      <c r="AR193" s="52" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26091,7 +26091,7 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
-      <c r="AR194" t="s">
+      <c r="AR194" s="37" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26179,7 +26179,7 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
-      <c r="AR195" t="s">
+      <c r="AR195" s="66" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26303,7 +26303,7 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
-      <c r="AR196" t="s">
+      <c r="AR196" s="33" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
-      <c r="AR197" t="s">
+      <c r="AR197" s="52" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26479,7 +26479,7 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
-      <c r="AR198" t="s">
+      <c r="AR198" s="37" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26567,7 +26567,7 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
-      <c r="AR199" t="s">
+      <c r="AR199" s="51" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26697,7 +26697,7 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
-      <c r="AR200" t="s">
+      <c r="AR200" s="33" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26789,7 +26789,7 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
-      <c r="AR201" t="s">
+      <c r="AR201" s="37" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26879,7 +26879,7 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
-      <c r="AR202" t="s">
+      <c r="AR202" s="119" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27009,7 +27009,7 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
-      <c r="AR203" t="s">
+      <c r="AR203" s="33" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27101,7 +27101,7 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
-      <c r="AR204" t="s">
+      <c r="AR204" s="37" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27191,7 +27191,7 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
-      <c r="AR205" t="s">
+      <c r="AR205" s="66" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27321,7 +27321,7 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
-      <c r="AR206" t="s">
+      <c r="AR206" s="33" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27409,7 +27409,7 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
-      <c r="AR207" t="s">
+      <c r="AR207" s="37" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27501,7 +27501,7 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
-      <c r="AR208" t="s">
+      <c r="AR208" s="51" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27633,7 +27633,7 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
-      <c r="AR209" t="s">
+      <c r="AR209" s="33" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27725,7 +27725,7 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
-      <c r="AR210" t="s">
+      <c r="AR210" s="52" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27817,7 +27817,7 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
-      <c r="AR211" t="s">
+      <c r="AR211" s="37" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27907,7 +27907,7 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
-      <c r="AR212" t="s">
+      <c r="AR212" s="66" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28037,7 +28037,7 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
-      <c r="AR213" t="s">
+      <c r="AR213" s="33" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28129,7 +28129,7 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
-      <c r="AR214" t="s">
+      <c r="AR214" s="37" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28221,7 +28221,7 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
-      <c r="AR215" t="s">
+      <c r="AR215" s="51" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
-      <c r="AR216" t="s">
+      <c r="AR216" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28445,7 +28445,7 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
-      <c r="AR217" t="s">
+      <c r="AR217" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28537,7 +28537,7 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
-      <c r="AR218" t="s">
+      <c r="AR218" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28629,7 +28629,7 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
-      <c r="AR219" t="s">
+      <c r="AR219" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28757,7 +28757,7 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
-      <c r="AR220" t="s">
+      <c r="AR220" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28847,7 +28847,7 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
-      <c r="AR221" t="s">
+      <c r="AR221" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28937,7 +28937,7 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
-      <c r="AR222" t="s">
+      <c r="AR222" s="66" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29067,7 +29067,7 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
-      <c r="AR223" t="s">
+      <c r="AR223" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29159,7 +29159,7 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
-      <c r="AR224" t="s">
+      <c r="AR224" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29251,7 +29251,7 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
-      <c r="AR225" t="s">
+      <c r="AR225" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
-      <c r="AR226" t="s">
+      <c r="AR226" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29465,7 +29465,7 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
-      <c r="AR227" t="s">
+      <c r="AR227" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
-      <c r="AR228" t="s">
+      <c r="AR228" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29641,7 +29641,7 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
-      <c r="AR229" t="s">
+      <c r="AR229" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29729,7 +29729,7 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
-      <c r="AR230" t="s">
+      <c r="AR230" s="66" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29855,7 +29855,7 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
-      <c r="AR231" t="s">
+      <c r="AR231" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29943,7 +29943,7 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
-      <c r="AR232" t="s">
+      <c r="AR232" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30031,7 +30031,7 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
-      <c r="AR233" t="s">
+      <c r="AR233" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30115,7 +30115,7 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
-      <c r="AR234" t="s">
+      <c r="AR234" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30243,7 +30243,7 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
-      <c r="AR235" t="s">
+      <c r="AR235" s="33" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30331,7 +30331,7 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
-      <c r="AR236" t="s">
+      <c r="AR236" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
-      <c r="AR237" t="s">
+      <c r="AR237" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30505,7 +30505,7 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
-      <c r="AR238" t="s">
+      <c r="AR238" s="51" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30633,7 +30633,7 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
-      <c r="AR239" t="s">
+      <c r="AR239" s="33" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30721,7 +30721,7 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
-      <c r="AR240" t="s">
+      <c r="AR240" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30809,7 +30809,7 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
-      <c r="AR241" t="s">
+      <c r="AR241" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30895,7 +30895,7 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
-      <c r="AR242" t="s">
+      <c r="AR242" s="66" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31021,7 +31021,7 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
-      <c r="AR243" t="s">
+      <c r="AR243" s="33" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31109,7 +31109,7 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
-      <c r="AR244" t="s">
+      <c r="AR244" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31197,7 +31197,7 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
-      <c r="AR245" t="s">
+      <c r="AR245" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31285,7 +31285,7 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
-      <c r="AR246" t="s">
+      <c r="AR246" s="66" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31379,7 +31379,7 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
-      <c r="AR247" t="s">
+      <c r="AR247" s="33" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31499,7 +31499,7 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
-      <c r="AR248" t="s">
+      <c r="AR248" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31589,7 +31589,7 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
-      <c r="AR249" t="s">
+      <c r="AR249" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31679,7 +31679,7 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
-      <c r="AR250" t="s">
+      <c r="AR250" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31769,7 +31769,7 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
-      <c r="AR251" t="s">
+      <c r="AR251" s="66" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31895,7 +31895,7 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
-      <c r="AR252" t="s">
+      <c r="AR252" s="33" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31983,7 +31983,7 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
-      <c r="AR253" t="s">
+      <c r="AR253" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32071,7 +32071,7 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
-      <c r="AR254" t="s">
+      <c r="AR254" s="52" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32159,7 +32159,7 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
-      <c r="AR255" t="s">
+      <c r="AR255" s="37" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32247,7 +32247,7 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
-      <c r="AR256" t="s">
+      <c r="AR256" s="51" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32375,7 +32375,7 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
-      <c r="AR257" t="s">
+      <c r="AR257" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32465,7 +32465,7 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
-      <c r="AR258" t="s">
+      <c r="AR258" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32555,7 +32555,7 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
-      <c r="AR259" t="s">
+      <c r="AR259" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32643,7 +32643,7 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
-      <c r="AR260" t="s">
+      <c r="AR260" s="66" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32769,7 +32769,7 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
-      <c r="AR261" t="s">
+      <c r="AR261" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32855,7 +32855,7 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
-      <c r="AR262" t="s">
+      <c r="AR262" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32941,7 +32941,7 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
-      <c r="AR263" t="s">
+      <c r="AR263" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
-      <c r="AR264" t="s">
+      <c r="AR264" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33161,7 +33161,7 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
-      <c r="AR265" t="s">
+      <c r="AR265" s="52" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33251,7 +33251,7 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
-      <c r="AR266" t="s">
+      <c r="AR266" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33341,7 +33341,7 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
-      <c r="AR267" t="s">
+      <c r="AR267" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33473,7 +33473,7 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
-      <c r="AR268" t="s">
+      <c r="AR268" s="33" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33565,7 +33565,7 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
-      <c r="AR269" t="s">
+      <c r="AR269" s="37" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33657,7 +33657,7 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
-      <c r="AR270" t="s">
+      <c r="AR270" s="51" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33789,7 +33789,7 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
-      <c r="AR271" t="s">
+      <c r="AR271" s="33" t="s">
         <v>982</v>
       </c>
     </row>
@@ -33879,7 +33879,7 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
-      <c r="AR272" t="s">
+      <c r="AR272" s="37" t="s">
         <v>982</v>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
-      <c r="AR273" t="s">
+      <c r="AR273" s="66" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34091,7 +34091,7 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
-      <c r="AR274" t="s">
+      <c r="AR274" s="37" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34187,7 +34187,7 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
-      <c r="AR275" t="s">
+      <c r="AR275" s="33" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
-      <c r="AR276" t="s">
+      <c r="AR276" s="37" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34367,7 +34367,7 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
-      <c r="AR277" t="s">
+      <c r="AR277" s="51" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34495,7 +34495,7 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
-      <c r="AR278" t="s">
+      <c r="AR278" s="33" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34583,7 +34583,7 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
-      <c r="AR279" t="s">
+      <c r="AR279" s="52" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34671,7 +34671,7 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
-      <c r="AR280" t="s">
+      <c r="AR280" s="204" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34759,7 +34759,7 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
-      <c r="AR281" t="s">
+      <c r="AR281" s="205" t="s">
         <v>983</v>
       </c>
     </row>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB765728-974F-4088-8FF4-3DCF0F7179D8}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47056976-65D7-465A-A358-2EE1CB91D610}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5644,6 +5644,135 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="54" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5653,6 +5782,60 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5669,189 +5852,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="54" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6205,7 +6205,8 @@
     <col min="31" max="31" width="13.21875" customWidth="1"/>
     <col min="32" max="32" width="11.5546875" style="206"/>
     <col min="34" max="35" width="11.5546875" style="206"/>
-    <col min="41" max="44" width="11.5546875" style="206"/>
+    <col min="41" max="43" width="11.5546875" style="206"/>
+    <col min="44" max="44" width="19.6640625" style="206" customWidth="1"/>
     <col min="262" max="262" width="19.21875" customWidth="1"/>
     <col min="263" max="263" width="51.109375" customWidth="1"/>
     <col min="264" max="264" width="25.5546875" customWidth="1"/>
@@ -7168,7 +7169,7 @@
       <c r="B2" s="454" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="462">
+      <c r="C2" s="523">
         <v>11</v>
       </c>
       <c r="D2" s="296" t="s">
@@ -7296,7 +7297,7 @@
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="457"/>
       <c r="B3" s="454"/>
-      <c r="C3" s="463"/>
+      <c r="C3" s="524"/>
       <c r="D3" s="296"/>
       <c r="E3" s="17"/>
       <c r="F3" s="224"/>
@@ -7388,7 +7389,7 @@
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
       <c r="B4" s="454"/>
-      <c r="C4" s="464"/>
+      <c r="C4" s="525"/>
       <c r="D4" s="297"/>
       <c r="E4" s="209"/>
       <c r="F4" s="225"/>
@@ -7484,7 +7485,7 @@
       <c r="B5" s="454" t="s">
         <v>902</v>
       </c>
-      <c r="C5" s="462">
+      <c r="C5" s="523">
         <v>12</v>
       </c>
       <c r="D5" s="296" t="s">
@@ -7610,7 +7611,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="457"/>
       <c r="B6" s="454"/>
-      <c r="C6" s="463"/>
+      <c r="C6" s="524"/>
       <c r="D6" s="296"/>
       <c r="E6" s="34"/>
       <c r="F6" s="226"/>
@@ -7700,7 +7701,7 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
       <c r="B7" s="454"/>
-      <c r="C7" s="463"/>
+      <c r="C7" s="524"/>
       <c r="D7" s="296"/>
       <c r="E7" s="34"/>
       <c r="F7" s="226"/>
@@ -7790,7 +7791,7 @@
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
       <c r="B8" s="454"/>
-      <c r="C8" s="463"/>
+      <c r="C8" s="524"/>
       <c r="D8" s="296"/>
       <c r="E8" s="53"/>
       <c r="F8" s="227"/>
@@ -7882,7 +7883,7 @@
       <c r="B9" s="454" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="463"/>
+      <c r="C9" s="524"/>
       <c r="D9" s="296" t="s">
         <v>736</v>
       </c>
@@ -8004,7 +8005,7 @@
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="457"/>
       <c r="B10" s="454"/>
-      <c r="C10" s="463"/>
+      <c r="C10" s="524"/>
       <c r="D10" s="296"/>
       <c r="E10" s="34"/>
       <c r="F10" s="226"/>
@@ -8092,7 +8093,7 @@
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
       <c r="B11" s="454"/>
-      <c r="C11" s="463"/>
+      <c r="C11" s="524"/>
       <c r="D11" s="296"/>
       <c r="E11" s="34"/>
       <c r="F11" s="226"/>
@@ -8180,7 +8181,7 @@
     <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
       <c r="B12" s="454"/>
-      <c r="C12" s="464"/>
+      <c r="C12" s="525"/>
       <c r="D12" s="297"/>
       <c r="E12" s="38"/>
       <c r="F12" s="228"/>
@@ -8270,7 +8271,7 @@
       <c r="B13" s="454" t="s">
         <v>904</v>
       </c>
-      <c r="C13" s="462">
+      <c r="C13" s="523">
         <v>13</v>
       </c>
       <c r="D13" s="296" t="s">
@@ -8394,7 +8395,7 @@
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="457"/>
       <c r="B14" s="454"/>
-      <c r="C14" s="463"/>
+      <c r="C14" s="524"/>
       <c r="D14" s="296"/>
       <c r="E14" s="34"/>
       <c r="F14" s="226"/>
@@ -8482,7 +8483,7 @@
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
       <c r="B15" s="454"/>
-      <c r="C15" s="463"/>
+      <c r="C15" s="524"/>
       <c r="D15" s="296"/>
       <c r="E15" s="34"/>
       <c r="F15" s="226"/>
@@ -8570,7 +8571,7 @@
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
       <c r="B16" s="454"/>
-      <c r="C16" s="463"/>
+      <c r="C16" s="524"/>
       <c r="D16" s="296"/>
       <c r="E16" s="34"/>
       <c r="F16" s="226"/>
@@ -8658,7 +8659,7 @@
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
       <c r="B17" s="454"/>
-      <c r="C17" s="463"/>
+      <c r="C17" s="524"/>
       <c r="D17" s="296"/>
       <c r="E17" s="53"/>
       <c r="F17" s="227"/>
@@ -8748,7 +8749,7 @@
       <c r="B18" s="454" t="s">
         <v>905</v>
       </c>
-      <c r="C18" s="463"/>
+      <c r="C18" s="524"/>
       <c r="D18" s="296" t="s">
         <v>736</v>
       </c>
@@ -8868,7 +8869,7 @@
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="457"/>
       <c r="B19" s="454"/>
-      <c r="C19" s="463"/>
+      <c r="C19" s="524"/>
       <c r="D19" s="296"/>
       <c r="E19" s="34"/>
       <c r="F19" s="226"/>
@@ -8956,7 +8957,7 @@
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
       <c r="B20" s="454"/>
-      <c r="C20" s="463"/>
+      <c r="C20" s="524"/>
       <c r="D20" s="296"/>
       <c r="E20" s="34"/>
       <c r="F20" s="226"/>
@@ -9044,7 +9045,7 @@
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
       <c r="B21" s="454"/>
-      <c r="C21" s="463"/>
+      <c r="C21" s="524"/>
       <c r="D21" s="296"/>
       <c r="E21" s="34"/>
       <c r="F21" s="226"/>
@@ -9132,7 +9133,7 @@
     <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
       <c r="B22" s="454"/>
-      <c r="C22" s="464"/>
+      <c r="C22" s="525"/>
       <c r="D22" s="297"/>
       <c r="E22" s="38"/>
       <c r="F22" s="228"/>
@@ -9224,7 +9225,7 @@
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="465">
+      <c r="C23" s="526">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9352,7 +9353,7 @@
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="466"/>
+      <c r="C24" s="527"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9444,7 +9445,7 @@
     <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="467"/>
+      <c r="C25" s="528"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9540,7 +9541,7 @@
       <c r="B26" s="454" t="s">
         <v>907</v>
       </c>
-      <c r="C26" s="459">
+      <c r="C26" s="502">
         <v>22</v>
       </c>
       <c r="D26" s="298" t="s">
@@ -9664,7 +9665,7 @@
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="457"/>
       <c r="B27" s="454"/>
-      <c r="C27" s="460"/>
+      <c r="C27" s="503"/>
       <c r="D27" s="298"/>
       <c r="E27" s="73"/>
       <c r="F27" s="230"/>
@@ -9752,7 +9753,7 @@
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
       <c r="B28" s="454"/>
-      <c r="C28" s="460"/>
+      <c r="C28" s="503"/>
       <c r="D28" s="298"/>
       <c r="E28" s="73"/>
       <c r="F28" s="230"/>
@@ -9840,7 +9841,7 @@
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
       <c r="B29" s="454"/>
-      <c r="C29" s="460"/>
+      <c r="C29" s="503"/>
       <c r="D29" s="298"/>
       <c r="E29" s="73"/>
       <c r="F29" s="230"/>
@@ -9930,7 +9931,7 @@
     <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
       <c r="B30" s="454"/>
-      <c r="C30" s="461"/>
+      <c r="C30" s="504"/>
       <c r="D30" s="311"/>
       <c r="E30" s="74"/>
       <c r="F30" s="231"/>
@@ -10020,7 +10021,7 @@
       <c r="B31" s="454" t="s">
         <v>908</v>
       </c>
-      <c r="C31" s="459">
+      <c r="C31" s="502">
         <v>23</v>
       </c>
       <c r="D31" s="298" t="s">
@@ -10148,7 +10149,7 @@
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="457"/>
       <c r="B32" s="454"/>
-      <c r="C32" s="460"/>
+      <c r="C32" s="503"/>
       <c r="D32" s="298"/>
       <c r="E32" s="73"/>
       <c r="F32" s="230"/>
@@ -10240,7 +10241,7 @@
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
       <c r="B33" s="454"/>
-      <c r="C33" s="460"/>
+      <c r="C33" s="503"/>
       <c r="D33" s="298"/>
       <c r="E33" s="73"/>
       <c r="F33" s="230"/>
@@ -10332,7 +10333,7 @@
     <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
       <c r="B34" s="454"/>
-      <c r="C34" s="461"/>
+      <c r="C34" s="504"/>
       <c r="D34" s="311"/>
       <c r="E34" s="74"/>
       <c r="F34" s="231"/>
@@ -10428,7 +10429,7 @@
       <c r="B35" s="454" t="s">
         <v>909</v>
       </c>
-      <c r="C35" s="459">
+      <c r="C35" s="502">
         <v>24</v>
       </c>
       <c r="D35" s="298" t="s">
@@ -10550,7 +10551,7 @@
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="457"/>
       <c r="B36" s="454"/>
-      <c r="C36" s="460"/>
+      <c r="C36" s="503"/>
       <c r="D36" s="298"/>
       <c r="E36" s="73"/>
       <c r="F36" s="230"/>
@@ -10638,7 +10639,7 @@
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
       <c r="B37" s="454"/>
-      <c r="C37" s="460"/>
+      <c r="C37" s="503"/>
       <c r="D37" s="298"/>
       <c r="E37" s="73"/>
       <c r="F37" s="230"/>
@@ -10726,7 +10727,7 @@
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
       <c r="B38" s="454"/>
-      <c r="C38" s="460"/>
+      <c r="C38" s="503"/>
       <c r="D38" s="298"/>
       <c r="E38" s="77"/>
       <c r="F38" s="232"/>
@@ -10818,7 +10819,7 @@
       <c r="B39" s="454" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="460"/>
+      <c r="C39" s="503"/>
       <c r="D39" s="298" t="s">
         <v>737</v>
       </c>
@@ -10940,7 +10941,7 @@
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="457"/>
       <c r="B40" s="454"/>
-      <c r="C40" s="460"/>
+      <c r="C40" s="503"/>
       <c r="D40" s="298"/>
       <c r="E40" s="73"/>
       <c r="F40" s="230"/>
@@ -11028,7 +11029,7 @@
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
       <c r="B41" s="454"/>
-      <c r="C41" s="460"/>
+      <c r="C41" s="503"/>
       <c r="D41" s="298"/>
       <c r="E41" s="73"/>
       <c r="F41" s="230"/>
@@ -11116,7 +11117,7 @@
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
       <c r="B42" s="454"/>
-      <c r="C42" s="460"/>
+      <c r="C42" s="503"/>
       <c r="D42" s="298"/>
       <c r="E42" s="73"/>
       <c r="F42" s="230"/>
@@ -11204,7 +11205,7 @@
     <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
       <c r="B43" s="454"/>
-      <c r="C43" s="461"/>
+      <c r="C43" s="504"/>
       <c r="D43" s="311"/>
       <c r="E43" s="74"/>
       <c r="F43" s="231"/>
@@ -11294,7 +11295,7 @@
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="471">
+      <c r="C44" s="505">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11420,7 +11421,7 @@
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="472"/>
+      <c r="C45" s="506"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11512,7 +11513,7 @@
     <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="473"/>
+      <c r="C46" s="507"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11608,7 +11609,7 @@
       <c r="B47" s="454" t="s">
         <v>912</v>
       </c>
-      <c r="C47" s="474">
+      <c r="C47" s="508">
         <v>32</v>
       </c>
       <c r="D47" s="299" t="s">
@@ -11734,7 +11735,7 @@
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="457"/>
       <c r="B48" s="454"/>
-      <c r="C48" s="475"/>
+      <c r="C48" s="509"/>
       <c r="D48" s="299"/>
       <c r="E48" s="84"/>
       <c r="F48" s="235"/>
@@ -11824,7 +11825,7 @@
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
       <c r="B49" s="454"/>
-      <c r="C49" s="475"/>
+      <c r="C49" s="509"/>
       <c r="D49" s="299"/>
       <c r="E49" s="84"/>
       <c r="F49" s="235"/>
@@ -11914,7 +11915,7 @@
     <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="476"/>
+      <c r="C50" s="510"/>
       <c r="D50" s="312"/>
       <c r="E50" s="85"/>
       <c r="F50" s="236"/>
@@ -12008,7 +12009,7 @@
       <c r="B51" s="454" t="s">
         <v>913</v>
       </c>
-      <c r="C51" s="474">
+      <c r="C51" s="508">
         <v>33</v>
       </c>
       <c r="D51" s="299" t="s">
@@ -12136,7 +12137,7 @@
     <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="457"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="475"/>
+      <c r="C52" s="509"/>
       <c r="D52" s="299"/>
       <c r="E52" s="84"/>
       <c r="F52" s="235"/>
@@ -12228,7 +12229,7 @@
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
       <c r="B53" s="454"/>
-      <c r="C53" s="475"/>
+      <c r="C53" s="509"/>
       <c r="D53" s="299"/>
       <c r="E53" s="84"/>
       <c r="F53" s="235"/>
@@ -12316,7 +12317,7 @@
     <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
       <c r="B54" s="454"/>
-      <c r="C54" s="476"/>
+      <c r="C54" s="510"/>
       <c r="D54" s="312"/>
       <c r="E54" s="85"/>
       <c r="F54" s="236"/>
@@ -12406,7 +12407,7 @@
       <c r="B55" s="454" t="s">
         <v>914</v>
       </c>
-      <c r="C55" s="474">
+      <c r="C55" s="508">
         <v>34</v>
       </c>
       <c r="D55" s="299" t="s">
@@ -12528,7 +12529,7 @@
     <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="457"/>
       <c r="B56" s="454"/>
-      <c r="C56" s="475"/>
+      <c r="C56" s="509"/>
       <c r="D56" s="299"/>
       <c r="E56" s="84"/>
       <c r="F56" s="235"/>
@@ -12616,7 +12617,7 @@
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
       <c r="B57" s="454"/>
-      <c r="C57" s="475"/>
+      <c r="C57" s="509"/>
       <c r="D57" s="299"/>
       <c r="E57" s="84"/>
       <c r="F57" s="235"/>
@@ -12704,7 +12705,7 @@
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
       <c r="B58" s="454"/>
-      <c r="C58" s="475"/>
+      <c r="C58" s="509"/>
       <c r="D58" s="299"/>
       <c r="E58" s="84"/>
       <c r="F58" s="235"/>
@@ -12792,7 +12793,7 @@
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
       <c r="B59" s="454"/>
-      <c r="C59" s="475"/>
+      <c r="C59" s="509"/>
       <c r="D59" s="299"/>
       <c r="E59" s="89"/>
       <c r="F59" s="237"/>
@@ -12884,7 +12885,7 @@
       <c r="B60" s="454" t="s">
         <v>915</v>
       </c>
-      <c r="C60" s="475"/>
+      <c r="C60" s="509"/>
       <c r="D60" s="299" t="s">
         <v>738</v>
       </c>
@@ -13006,7 +13007,7 @@
     <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="457"/>
       <c r="B61" s="454"/>
-      <c r="C61" s="475"/>
+      <c r="C61" s="509"/>
       <c r="D61" s="299"/>
       <c r="E61" s="84"/>
       <c r="F61" s="235"/>
@@ -13094,7 +13095,7 @@
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
       <c r="B62" s="454"/>
-      <c r="C62" s="475"/>
+      <c r="C62" s="509"/>
       <c r="D62" s="299"/>
       <c r="E62" s="84"/>
       <c r="F62" s="235"/>
@@ -13182,7 +13183,7 @@
     <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
       <c r="B63" s="454"/>
-      <c r="C63" s="476"/>
+      <c r="C63" s="510"/>
       <c r="D63" s="312"/>
       <c r="E63" s="85"/>
       <c r="F63" s="236"/>
@@ -13274,7 +13275,7 @@
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="477">
+      <c r="C64" s="511">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13400,7 +13401,7 @@
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="478"/>
+      <c r="C65" s="512"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13492,7 +13493,7 @@
     <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="479"/>
+      <c r="C66" s="513"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13588,7 +13589,7 @@
       <c r="B67" s="454" t="s">
         <v>917</v>
       </c>
-      <c r="C67" s="480">
+      <c r="C67" s="514">
         <v>42</v>
       </c>
       <c r="D67" s="300" t="s">
@@ -13714,7 +13715,7 @@
     <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="457"/>
       <c r="B68" s="454"/>
-      <c r="C68" s="481"/>
+      <c r="C68" s="515"/>
       <c r="D68" s="300"/>
       <c r="E68" s="96"/>
       <c r="F68" s="238"/>
@@ -13804,7 +13805,7 @@
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
       <c r="B69" s="454"/>
-      <c r="C69" s="481"/>
+      <c r="C69" s="515"/>
       <c r="D69" s="300"/>
       <c r="E69" s="100"/>
       <c r="F69" s="240"/>
@@ -13898,7 +13899,7 @@
       <c r="B70" s="454" t="s">
         <v>918</v>
       </c>
-      <c r="C70" s="481"/>
+      <c r="C70" s="515"/>
       <c r="D70" s="300" t="s">
         <v>739</v>
       </c>
@@ -14018,7 +14019,7 @@
     <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="457"/>
       <c r="B71" s="454"/>
-      <c r="C71" s="481"/>
+      <c r="C71" s="515"/>
       <c r="D71" s="300"/>
       <c r="E71" s="96"/>
       <c r="F71" s="238"/>
@@ -14106,7 +14107,7 @@
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
       <c r="B72" s="454"/>
-      <c r="C72" s="481"/>
+      <c r="C72" s="515"/>
       <c r="D72" s="300"/>
       <c r="E72" s="96"/>
       <c r="F72" s="238"/>
@@ -14194,7 +14195,7 @@
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
       <c r="B73" s="454"/>
-      <c r="C73" s="481"/>
+      <c r="C73" s="515"/>
       <c r="D73" s="300"/>
       <c r="E73" s="96"/>
       <c r="F73" s="238"/>
@@ -14282,7 +14283,7 @@
     <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
       <c r="B74" s="454"/>
-      <c r="C74" s="482"/>
+      <c r="C74" s="516"/>
       <c r="D74" s="313"/>
       <c r="E74" s="97"/>
       <c r="F74" s="239"/>
@@ -14374,7 +14375,7 @@
       <c r="B75" s="454" t="s">
         <v>919</v>
       </c>
-      <c r="C75" s="480">
+      <c r="C75" s="514">
         <v>43</v>
       </c>
       <c r="D75" s="300" t="s">
@@ -14498,7 +14499,7 @@
     <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="457"/>
       <c r="B76" s="454"/>
-      <c r="C76" s="481"/>
+      <c r="C76" s="515"/>
       <c r="D76" s="300"/>
       <c r="E76" s="96"/>
       <c r="F76" s="238"/>
@@ -14586,7 +14587,7 @@
     <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
       <c r="B77" s="454"/>
-      <c r="C77" s="481"/>
+      <c r="C77" s="515"/>
       <c r="D77" s="300"/>
       <c r="E77" s="96"/>
       <c r="F77" s="238"/>
@@ -14674,7 +14675,7 @@
     <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
       <c r="B78" s="454"/>
-      <c r="C78" s="481"/>
+      <c r="C78" s="515"/>
       <c r="D78" s="300"/>
       <c r="E78" s="96"/>
       <c r="F78" s="238"/>
@@ -14762,7 +14763,7 @@
     <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
       <c r="B79" s="454"/>
-      <c r="C79" s="481"/>
+      <c r="C79" s="515"/>
       <c r="D79" s="300"/>
       <c r="E79" s="100"/>
       <c r="F79" s="240"/>
@@ -14854,7 +14855,7 @@
       <c r="B80" s="454" t="s">
         <v>920</v>
       </c>
-      <c r="C80" s="481"/>
+      <c r="C80" s="515"/>
       <c r="D80" s="300" t="s">
         <v>739</v>
       </c>
@@ -14972,7 +14973,7 @@
     <row r="81" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A81" s="457"/>
       <c r="B81" s="454"/>
-      <c r="C81" s="481"/>
+      <c r="C81" s="515"/>
       <c r="D81" s="300"/>
       <c r="E81" s="96"/>
       <c r="F81" s="238"/>
@@ -15060,7 +15061,7 @@
     <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
       <c r="B82" s="454"/>
-      <c r="C82" s="482"/>
+      <c r="C82" s="516"/>
       <c r="D82" s="313"/>
       <c r="E82" s="97"/>
       <c r="F82" s="239"/>
@@ -15150,7 +15151,7 @@
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="483">
+      <c r="C83" s="517">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -15278,7 +15279,7 @@
     <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="484"/>
+      <c r="C84" s="518"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -15370,7 +15371,7 @@
     <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="485"/>
+      <c r="C85" s="519"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15464,7 +15465,7 @@
       <c r="B86" s="454" t="s">
         <v>922</v>
       </c>
-      <c r="C86" s="486">
+      <c r="C86" s="520">
         <v>52</v>
       </c>
       <c r="D86" s="301" t="s">
@@ -15590,7 +15591,7 @@
     <row r="87" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A87" s="457"/>
       <c r="B87" s="454"/>
-      <c r="C87" s="487"/>
+      <c r="C87" s="521"/>
       <c r="D87" s="301"/>
       <c r="E87" s="110"/>
       <c r="F87" s="241"/>
@@ -15682,7 +15683,7 @@
     <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
       <c r="B88" s="454"/>
-      <c r="C88" s="487"/>
+      <c r="C88" s="521"/>
       <c r="D88" s="301"/>
       <c r="E88" s="110"/>
       <c r="F88" s="241"/>
@@ -15774,7 +15775,7 @@
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
       <c r="B89" s="454"/>
-      <c r="C89" s="487"/>
+      <c r="C89" s="521"/>
       <c r="D89" s="301"/>
       <c r="E89" s="115"/>
       <c r="F89" s="243"/>
@@ -15870,7 +15871,7 @@
       <c r="B90" s="454" t="s">
         <v>923</v>
       </c>
-      <c r="C90" s="487"/>
+      <c r="C90" s="521"/>
       <c r="D90" s="301" t="s">
         <v>740</v>
       </c>
@@ -15994,7 +15995,7 @@
     <row r="91" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A91" s="457"/>
       <c r="B91" s="454"/>
-      <c r="C91" s="487"/>
+      <c r="C91" s="521"/>
       <c r="D91" s="301"/>
       <c r="E91" s="110"/>
       <c r="F91" s="241"/>
@@ -16084,7 +16085,7 @@
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
       <c r="B92" s="454"/>
-      <c r="C92" s="487"/>
+      <c r="C92" s="521"/>
       <c r="D92" s="301"/>
       <c r="E92" s="110"/>
       <c r="F92" s="241"/>
@@ -16174,7 +16175,7 @@
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
       <c r="B93" s="454"/>
-      <c r="C93" s="487"/>
+      <c r="C93" s="521"/>
       <c r="D93" s="301"/>
       <c r="E93" s="115"/>
       <c r="F93" s="243"/>
@@ -16268,7 +16269,7 @@
       <c r="B94" s="454" t="s">
         <v>924</v>
       </c>
-      <c r="C94" s="487"/>
+      <c r="C94" s="521"/>
       <c r="D94" s="301" t="s">
         <v>740</v>
       </c>
@@ -16392,7 +16393,7 @@
     <row r="95" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A95" s="457"/>
       <c r="B95" s="454"/>
-      <c r="C95" s="487"/>
+      <c r="C95" s="521"/>
       <c r="D95" s="301"/>
       <c r="E95" s="110"/>
       <c r="F95" s="241"/>
@@ -16482,7 +16483,7 @@
     <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
       <c r="B96" s="454"/>
-      <c r="C96" s="487"/>
+      <c r="C96" s="521"/>
       <c r="D96" s="301"/>
       <c r="E96" s="110"/>
       <c r="F96" s="241"/>
@@ -16572,7 +16573,7 @@
     <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
       <c r="B97" s="454"/>
-      <c r="C97" s="488"/>
+      <c r="C97" s="522"/>
       <c r="D97" s="314"/>
       <c r="E97" s="111"/>
       <c r="F97" s="242"/>
@@ -16666,7 +16667,7 @@
       <c r="B98" s="454" t="s">
         <v>925</v>
       </c>
-      <c r="C98" s="486">
+      <c r="C98" s="520">
         <v>53</v>
       </c>
       <c r="D98" s="301" t="s">
@@ -16790,7 +16791,7 @@
     <row r="99" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A99" s="457"/>
       <c r="B99" s="454"/>
-      <c r="C99" s="487"/>
+      <c r="C99" s="521"/>
       <c r="D99" s="301"/>
       <c r="E99" s="110"/>
       <c r="F99" s="241"/>
@@ -16880,7 +16881,7 @@
     <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
       <c r="B100" s="454"/>
-      <c r="C100" s="487"/>
+      <c r="C100" s="521"/>
       <c r="D100" s="301"/>
       <c r="E100" s="110"/>
       <c r="F100" s="241"/>
@@ -16968,7 +16969,7 @@
     <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
       <c r="B101" s="454"/>
-      <c r="C101" s="488"/>
+      <c r="C101" s="522"/>
       <c r="D101" s="301"/>
       <c r="E101" s="111"/>
       <c r="F101" s="242"/>
@@ -17062,7 +17063,7 @@
       <c r="B102" s="454" t="s">
         <v>926</v>
       </c>
-      <c r="C102" s="468">
+      <c r="C102" s="478">
         <v>61</v>
       </c>
       <c r="D102" s="323" t="s">
@@ -17182,7 +17183,7 @@
     <row r="103" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A103" s="457"/>
       <c r="B103" s="454"/>
-      <c r="C103" s="469"/>
+      <c r="C103" s="479"/>
       <c r="D103" s="323"/>
       <c r="E103" s="329"/>
       <c r="F103" s="330"/>
@@ -17270,7 +17271,7 @@
     <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
       <c r="B104" s="454"/>
-      <c r="C104" s="469"/>
+      <c r="C104" s="479"/>
       <c r="D104" s="323"/>
       <c r="E104" s="329"/>
       <c r="F104" s="330"/>
@@ -17358,7 +17359,7 @@
     <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
       <c r="B105" s="454"/>
-      <c r="C105" s="470"/>
+      <c r="C105" s="480"/>
       <c r="D105" s="331"/>
       <c r="E105" s="332"/>
       <c r="F105" s="333"/>
@@ -17450,7 +17451,7 @@
       <c r="B106" s="454" t="s">
         <v>927</v>
       </c>
-      <c r="C106" s="468">
+      <c r="C106" s="478">
         <v>62</v>
       </c>
       <c r="D106" s="323" t="s">
@@ -17574,7 +17575,7 @@
     <row r="107" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A107" s="457"/>
       <c r="B107" s="454"/>
-      <c r="C107" s="469"/>
+      <c r="C107" s="479"/>
       <c r="D107" s="323"/>
       <c r="E107" s="329"/>
       <c r="F107" s="330"/>
@@ -17662,7 +17663,7 @@
     <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
       <c r="B108" s="454"/>
-      <c r="C108" s="469"/>
+      <c r="C108" s="479"/>
       <c r="D108" s="323"/>
       <c r="E108" s="329"/>
       <c r="F108" s="330"/>
@@ -17750,7 +17751,7 @@
     <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
       <c r="B109" s="454"/>
-      <c r="C109" s="469"/>
+      <c r="C109" s="479"/>
       <c r="D109" s="323"/>
       <c r="E109" s="338"/>
       <c r="F109" s="339"/>
@@ -17842,7 +17843,7 @@
       <c r="B110" s="454" t="s">
         <v>928</v>
       </c>
-      <c r="C110" s="469"/>
+      <c r="C110" s="479"/>
       <c r="D110" s="323" t="s">
         <v>741</v>
       </c>
@@ -17964,7 +17965,7 @@
     <row r="111" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A111" s="457"/>
       <c r="B111" s="454"/>
-      <c r="C111" s="469"/>
+      <c r="C111" s="479"/>
       <c r="D111" s="323"/>
       <c r="E111" s="329"/>
       <c r="F111" s="330"/>
@@ -18052,7 +18053,7 @@
     <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
       <c r="B112" s="454"/>
-      <c r="C112" s="469"/>
+      <c r="C112" s="479"/>
       <c r="D112" s="323"/>
       <c r="E112" s="329"/>
       <c r="F112" s="330"/>
@@ -18140,7 +18141,7 @@
     <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
       <c r="B113" s="454"/>
-      <c r="C113" s="469"/>
+      <c r="C113" s="479"/>
       <c r="D113" s="323"/>
       <c r="E113" s="329"/>
       <c r="F113" s="330"/>
@@ -18228,7 +18229,7 @@
     <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
       <c r="B114" s="454"/>
-      <c r="C114" s="470"/>
+      <c r="C114" s="480"/>
       <c r="D114" s="331"/>
       <c r="E114" s="332"/>
       <c r="F114" s="333"/>
@@ -18318,7 +18319,7 @@
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="492">
+      <c r="C115" s="481">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -18442,7 +18443,7 @@
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="493"/>
+      <c r="C116" s="482"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -18530,7 +18531,7 @@
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="493"/>
+      <c r="C117" s="482"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18618,7 +18619,7 @@
     <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="493"/>
+      <c r="C118" s="482"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18710,7 +18711,7 @@
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="493"/>
+      <c r="C119" s="482"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18830,7 +18831,7 @@
     <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="493"/>
+      <c r="C120" s="482"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18918,7 +18919,7 @@
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="493"/>
+      <c r="C121" s="482"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -19006,7 +19007,7 @@
     <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="494"/>
+      <c r="C122" s="483"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -19098,7 +19099,7 @@
       <c r="B123" s="454" t="s">
         <v>931</v>
       </c>
-      <c r="C123" s="495">
+      <c r="C123" s="484">
         <v>72</v>
       </c>
       <c r="D123" s="302" t="s">
@@ -19220,7 +19221,7 @@
     <row r="124" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A124" s="457"/>
       <c r="B124" s="454"/>
-      <c r="C124" s="496"/>
+      <c r="C124" s="485"/>
       <c r="D124" s="302"/>
       <c r="E124" s="125"/>
       <c r="F124" s="244"/>
@@ -19308,7 +19309,7 @@
     <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
       <c r="B125" s="454"/>
-      <c r="C125" s="496"/>
+      <c r="C125" s="485"/>
       <c r="D125" s="302"/>
       <c r="E125" s="125"/>
       <c r="F125" s="244"/>
@@ -19396,7 +19397,7 @@
     <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
       <c r="B126" s="454"/>
-      <c r="C126" s="496"/>
+      <c r="C126" s="485"/>
       <c r="D126" s="302"/>
       <c r="E126" s="125"/>
       <c r="F126" s="244"/>
@@ -19484,7 +19485,7 @@
     <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
       <c r="B127" s="454"/>
-      <c r="C127" s="496"/>
+      <c r="C127" s="485"/>
       <c r="D127" s="302"/>
       <c r="E127" s="126"/>
       <c r="F127" s="245"/>
@@ -19576,7 +19577,7 @@
       <c r="B128" s="454" t="s">
         <v>932</v>
       </c>
-      <c r="C128" s="496"/>
+      <c r="C128" s="485"/>
       <c r="D128" s="302" t="s">
         <v>742</v>
       </c>
@@ -19700,7 +19701,7 @@
     <row r="129" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A129" s="457"/>
       <c r="B129" s="454"/>
-      <c r="C129" s="496"/>
+      <c r="C129" s="485"/>
       <c r="D129" s="302"/>
       <c r="E129" s="125"/>
       <c r="F129" s="244"/>
@@ -19792,7 +19793,7 @@
     <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
       <c r="B130" s="454"/>
-      <c r="C130" s="496"/>
+      <c r="C130" s="485"/>
       <c r="D130" s="302"/>
       <c r="E130" s="125"/>
       <c r="F130" s="244"/>
@@ -19884,7 +19885,7 @@
     <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
       <c r="B131" s="454"/>
-      <c r="C131" s="497"/>
+      <c r="C131" s="486"/>
       <c r="D131" s="315"/>
       <c r="E131" s="129"/>
       <c r="F131" s="246"/>
@@ -19972,7 +19973,7 @@
       <c r="B132" s="454" t="s">
         <v>933</v>
       </c>
-      <c r="C132" s="495">
+      <c r="C132" s="484">
         <v>73</v>
       </c>
       <c r="D132" s="302" t="s">
@@ -20096,7 +20097,7 @@
     <row r="133" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A133" s="457"/>
       <c r="B133" s="454"/>
-      <c r="C133" s="496"/>
+      <c r="C133" s="485"/>
       <c r="D133" s="302"/>
       <c r="E133" s="125"/>
       <c r="F133" s="244"/>
@@ -20184,7 +20185,7 @@
     <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
       <c r="B134" s="454"/>
-      <c r="C134" s="496"/>
+      <c r="C134" s="485"/>
       <c r="D134" s="302"/>
       <c r="E134" s="125"/>
       <c r="F134" s="244"/>
@@ -20272,7 +20273,7 @@
     <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
       <c r="B135" s="454"/>
-      <c r="C135" s="496"/>
+      <c r="C135" s="485"/>
       <c r="D135" s="302"/>
       <c r="E135" s="126"/>
       <c r="F135" s="245"/>
@@ -20364,7 +20365,7 @@
       <c r="B136" s="454" t="s">
         <v>934</v>
       </c>
-      <c r="C136" s="496"/>
+      <c r="C136" s="485"/>
       <c r="D136" s="302" t="s">
         <v>742</v>
       </c>
@@ -20486,7 +20487,7 @@
     <row r="137" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A137" s="457"/>
       <c r="B137" s="454"/>
-      <c r="C137" s="496"/>
+      <c r="C137" s="485"/>
       <c r="D137" s="302"/>
       <c r="E137" s="125"/>
       <c r="F137" s="244"/>
@@ -20574,7 +20575,7 @@
     <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
       <c r="B138" s="454"/>
-      <c r="C138" s="496"/>
+      <c r="C138" s="485"/>
       <c r="D138" s="302"/>
       <c r="E138" s="125"/>
       <c r="F138" s="244"/>
@@ -20662,7 +20663,7 @@
     <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
       <c r="B139" s="454"/>
-      <c r="C139" s="496"/>
+      <c r="C139" s="485"/>
       <c r="D139" s="302"/>
       <c r="E139" s="125"/>
       <c r="F139" s="244"/>
@@ -20750,7 +20751,7 @@
     <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
       <c r="B140" s="454"/>
-      <c r="C140" s="497"/>
+      <c r="C140" s="486"/>
       <c r="D140" s="315"/>
       <c r="E140" s="129"/>
       <c r="F140" s="246"/>
@@ -20840,7 +20841,7 @@
       <c r="B141" s="454" t="s">
         <v>935</v>
       </c>
-      <c r="C141" s="498">
+      <c r="C141" s="487">
         <v>74</v>
       </c>
       <c r="D141" s="302" t="s">
@@ -20962,7 +20963,7 @@
     <row r="142" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A142" s="457"/>
       <c r="B142" s="454"/>
-      <c r="C142" s="499"/>
+      <c r="C142" s="488"/>
       <c r="D142" s="303"/>
       <c r="E142" s="125"/>
       <c r="F142" s="244"/>
@@ -21050,7 +21051,7 @@
     <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
       <c r="B143" s="454"/>
-      <c r="C143" s="499"/>
+      <c r="C143" s="488"/>
       <c r="D143" s="303"/>
       <c r="E143" s="125"/>
       <c r="F143" s="244"/>
@@ -21138,7 +21139,7 @@
     <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
       <c r="B144" s="454"/>
-      <c r="C144" s="499"/>
+      <c r="C144" s="488"/>
       <c r="D144" s="303"/>
       <c r="E144" s="125"/>
       <c r="F144" s="244"/>
@@ -21226,7 +21227,7 @@
     <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
       <c r="B145" s="454"/>
-      <c r="C145" s="499"/>
+      <c r="C145" s="488"/>
       <c r="D145" s="303"/>
       <c r="E145" s="126"/>
       <c r="F145" s="245"/>
@@ -21318,7 +21319,7 @@
       <c r="B146" s="454" t="s">
         <v>936</v>
       </c>
-      <c r="C146" s="499"/>
+      <c r="C146" s="488"/>
       <c r="D146" s="302" t="s">
         <v>742</v>
       </c>
@@ -21440,7 +21441,7 @@
     <row r="147" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A147" s="457"/>
       <c r="B147" s="454"/>
-      <c r="C147" s="499"/>
+      <c r="C147" s="488"/>
       <c r="D147" s="303"/>
       <c r="E147" s="125"/>
       <c r="F147" s="244"/>
@@ -21528,7 +21529,7 @@
     <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
       <c r="B148" s="454"/>
-      <c r="C148" s="499"/>
+      <c r="C148" s="488"/>
       <c r="D148" s="303"/>
       <c r="E148" s="125"/>
       <c r="F148" s="244"/>
@@ -21616,7 +21617,7 @@
     <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
       <c r="B149" s="454"/>
-      <c r="C149" s="500"/>
+      <c r="C149" s="489"/>
       <c r="D149" s="316"/>
       <c r="E149" s="129"/>
       <c r="F149" s="246"/>
@@ -21708,7 +21709,7 @@
       <c r="B150" s="454" t="s">
         <v>937</v>
       </c>
-      <c r="C150" s="495">
+      <c r="C150" s="484">
         <v>75</v>
       </c>
       <c r="D150" s="302" t="s">
@@ -21830,7 +21831,7 @@
     <row r="151" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A151" s="457"/>
       <c r="B151" s="454"/>
-      <c r="C151" s="496"/>
+      <c r="C151" s="485"/>
       <c r="D151" s="302"/>
       <c r="E151" s="125"/>
       <c r="F151" s="244"/>
@@ -21918,7 +21919,7 @@
     <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
       <c r="B152" s="454"/>
-      <c r="C152" s="496"/>
+      <c r="C152" s="485"/>
       <c r="D152" s="302"/>
       <c r="E152" s="125"/>
       <c r="F152" s="244"/>
@@ -22006,7 +22007,7 @@
     <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
       <c r="B153" s="454"/>
-      <c r="C153" s="496"/>
+      <c r="C153" s="485"/>
       <c r="D153" s="302"/>
       <c r="E153" s="126"/>
       <c r="F153" s="245"/>
@@ -22098,7 +22099,7 @@
       <c r="B154" s="454" t="s">
         <v>938</v>
       </c>
-      <c r="C154" s="496"/>
+      <c r="C154" s="485"/>
       <c r="D154" s="302" t="s">
         <v>742</v>
       </c>
@@ -22218,7 +22219,7 @@
     <row r="155" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A155" s="457"/>
       <c r="B155" s="454"/>
-      <c r="C155" s="496"/>
+      <c r="C155" s="485"/>
       <c r="D155" s="302"/>
       <c r="E155" s="125"/>
       <c r="F155" s="244"/>
@@ -22306,7 +22307,7 @@
     <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
       <c r="B156" s="454"/>
-      <c r="C156" s="496"/>
+      <c r="C156" s="485"/>
       <c r="D156" s="302"/>
       <c r="E156" s="125"/>
       <c r="F156" s="244"/>
@@ -22394,7 +22395,7 @@
     <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
       <c r="B157" s="454"/>
-      <c r="C157" s="496"/>
+      <c r="C157" s="485"/>
       <c r="D157" s="302"/>
       <c r="E157" s="125"/>
       <c r="F157" s="244"/>
@@ -22482,7 +22483,7 @@
     <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
       <c r="B158" s="454"/>
-      <c r="C158" s="497"/>
+      <c r="C158" s="486"/>
       <c r="D158" s="315"/>
       <c r="E158" s="129"/>
       <c r="F158" s="246"/>
@@ -22572,7 +22573,7 @@
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="501">
+      <c r="C159" s="490">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22696,7 +22697,7 @@
     <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="502"/>
+      <c r="C160" s="491"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22784,7 +22785,7 @@
     <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="502"/>
+      <c r="C161" s="491"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22872,7 +22873,7 @@
     <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="502"/>
+      <c r="C162" s="491"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22964,7 +22965,7 @@
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="502"/>
+      <c r="C163" s="491"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -23086,7 +23087,7 @@
     <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="502"/>
+      <c r="C164" s="491"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -23174,7 +23175,7 @@
     <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="502"/>
+      <c r="C165" s="491"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -23262,7 +23263,7 @@
     <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="502"/>
+      <c r="C166" s="491"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -23354,7 +23355,7 @@
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="502"/>
+      <c r="C167" s="491"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -23476,7 +23477,7 @@
     <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="502"/>
+      <c r="C168" s="491"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -23564,7 +23565,7 @@
     <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="502"/>
+      <c r="C169" s="491"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -23652,7 +23653,7 @@
     <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="503"/>
+      <c r="C170" s="492"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23744,7 +23745,7 @@
       <c r="B171" s="454" t="s">
         <v>942</v>
       </c>
-      <c r="C171" s="504">
+      <c r="C171" s="493">
         <v>82</v>
       </c>
       <c r="D171" s="304" t="s">
@@ -23868,7 +23869,7 @@
     <row r="172" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A172" s="457"/>
       <c r="B172" s="454"/>
-      <c r="C172" s="505"/>
+      <c r="C172" s="494"/>
       <c r="D172" s="304"/>
       <c r="E172" s="137"/>
       <c r="F172" s="247"/>
@@ -23956,7 +23957,7 @@
     <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
       <c r="B173" s="454"/>
-      <c r="C173" s="505"/>
+      <c r="C173" s="494"/>
       <c r="D173" s="304"/>
       <c r="E173" s="137"/>
       <c r="F173" s="247"/>
@@ -24044,7 +24045,7 @@
     <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
       <c r="B174" s="454"/>
-      <c r="C174" s="505"/>
+      <c r="C174" s="494"/>
       <c r="D174" s="304"/>
       <c r="E174" s="138"/>
       <c r="F174" s="248"/>
@@ -24138,7 +24139,7 @@
       <c r="B175" s="454" t="s">
         <v>943</v>
       </c>
-      <c r="C175" s="505"/>
+      <c r="C175" s="494"/>
       <c r="D175" s="304" t="s">
         <v>743</v>
       </c>
@@ -24260,7 +24261,7 @@
     <row r="176" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A176" s="457"/>
       <c r="B176" s="454"/>
-      <c r="C176" s="505"/>
+      <c r="C176" s="494"/>
       <c r="D176" s="304"/>
       <c r="E176" s="137"/>
       <c r="F176" s="247"/>
@@ -24354,7 +24355,7 @@
     <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
       <c r="B177" s="454"/>
-      <c r="C177" s="505"/>
+      <c r="C177" s="494"/>
       <c r="D177" s="304"/>
       <c r="E177" s="137"/>
       <c r="F177" s="247"/>
@@ -24446,7 +24447,7 @@
     <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
       <c r="B178" s="454"/>
-      <c r="C178" s="505"/>
+      <c r="C178" s="494"/>
       <c r="D178" s="304"/>
       <c r="E178" s="138"/>
       <c r="F178" s="248"/>
@@ -24540,7 +24541,7 @@
       <c r="B179" s="454" t="s">
         <v>944</v>
       </c>
-      <c r="C179" s="505"/>
+      <c r="C179" s="494"/>
       <c r="D179" s="304" t="s">
         <v>743</v>
       </c>
@@ -24662,7 +24663,7 @@
     <row r="180" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A180" s="457"/>
       <c r="B180" s="454"/>
-      <c r="C180" s="505"/>
+      <c r="C180" s="494"/>
       <c r="D180" s="304"/>
       <c r="E180" s="137"/>
       <c r="F180" s="247"/>
@@ -24750,7 +24751,7 @@
     <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
       <c r="B181" s="454"/>
-      <c r="C181" s="505"/>
+      <c r="C181" s="494"/>
       <c r="D181" s="304"/>
       <c r="E181" s="137"/>
       <c r="F181" s="247"/>
@@ -24838,7 +24839,7 @@
     <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
       <c r="B182" s="454"/>
-      <c r="C182" s="505"/>
+      <c r="C182" s="494"/>
       <c r="D182" s="304"/>
       <c r="E182" s="137"/>
       <c r="F182" s="247"/>
@@ -24926,7 +24927,7 @@
     <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
       <c r="B183" s="454"/>
-      <c r="C183" s="506"/>
+      <c r="C183" s="495"/>
       <c r="D183" s="317"/>
       <c r="E183" s="141"/>
       <c r="F183" s="249"/>
@@ -25018,7 +25019,7 @@
       <c r="B184" s="454">
         <v>831</v>
       </c>
-      <c r="C184" s="504">
+      <c r="C184" s="493">
         <v>83</v>
       </c>
       <c r="D184" s="304" t="s">
@@ -25142,7 +25143,7 @@
     <row r="185" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A185" s="457"/>
       <c r="B185" s="454"/>
-      <c r="C185" s="505"/>
+      <c r="C185" s="494"/>
       <c r="D185" s="304"/>
       <c r="E185" s="137"/>
       <c r="F185" s="247"/>
@@ -25232,7 +25233,7 @@
     <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
       <c r="B186" s="454"/>
-      <c r="C186" s="505"/>
+      <c r="C186" s="494"/>
       <c r="D186" s="304"/>
       <c r="E186" s="137"/>
       <c r="F186" s="247"/>
@@ -25320,7 +25321,7 @@
     <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
       <c r="B187" s="454"/>
-      <c r="C187" s="505"/>
+      <c r="C187" s="494"/>
       <c r="D187" s="304"/>
       <c r="E187" s="138"/>
       <c r="F187" s="248"/>
@@ -25414,7 +25415,7 @@
       <c r="B188" s="454" t="s">
         <v>945</v>
       </c>
-      <c r="C188" s="505"/>
+      <c r="C188" s="494"/>
       <c r="D188" s="304" t="s">
         <v>743</v>
       </c>
@@ -25534,7 +25535,7 @@
     <row r="189" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A189" s="457"/>
       <c r="B189" s="454"/>
-      <c r="C189" s="505"/>
+      <c r="C189" s="494"/>
       <c r="D189" s="304"/>
       <c r="E189" s="137"/>
       <c r="F189" s="247"/>
@@ -25622,7 +25623,7 @@
     <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
       <c r="B190" s="454"/>
-      <c r="C190" s="505"/>
+      <c r="C190" s="494"/>
       <c r="D190" s="304"/>
       <c r="E190" s="137"/>
       <c r="F190" s="247"/>
@@ -25710,7 +25711,7 @@
     <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
       <c r="B191" s="454"/>
-      <c r="C191" s="506"/>
+      <c r="C191" s="495"/>
       <c r="D191" s="317"/>
       <c r="E191" s="141"/>
       <c r="F191" s="249"/>
@@ -25800,7 +25801,7 @@
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="507">
+      <c r="C192" s="496">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25922,7 +25923,7 @@
     <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="508"/>
+      <c r="C193" s="497"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -26010,7 +26011,7 @@
     <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="508"/>
+      <c r="C194" s="497"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -26098,7 +26099,7 @@
     <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="508"/>
+      <c r="C195" s="497"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -26190,7 +26191,7 @@
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="508"/>
+      <c r="C196" s="497"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -26310,7 +26311,7 @@
     <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="508"/>
+      <c r="C197" s="497"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -26398,7 +26399,7 @@
     <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="508"/>
+      <c r="C198" s="497"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -26486,7 +26487,7 @@
     <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="509"/>
+      <c r="C199" s="498"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -26578,7 +26579,7 @@
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="510">
+      <c r="C200" s="499">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -26704,7 +26705,7 @@
     <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="511"/>
+      <c r="C201" s="500"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -26796,7 +26797,7 @@
     <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="511"/>
+      <c r="C202" s="500"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26890,7 +26891,7 @@
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="511"/>
+      <c r="C203" s="500"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -27016,7 +27017,7 @@
     <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="511"/>
+      <c r="C204" s="500"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -27108,7 +27109,7 @@
     <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="511"/>
+      <c r="C205" s="500"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -27202,7 +27203,7 @@
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="511"/>
+      <c r="C206" s="500"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -27328,7 +27329,7 @@
     <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="511"/>
+      <c r="C207" s="500"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -27416,7 +27417,7 @@
     <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="512"/>
+      <c r="C208" s="501"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -27512,7 +27513,7 @@
       <c r="B209" s="454" t="s">
         <v>951</v>
       </c>
-      <c r="C209" s="489">
+      <c r="C209" s="475">
         <v>101</v>
       </c>
       <c r="D209" s="306" t="s">
@@ -27640,7 +27641,7 @@
     <row r="210" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A210" s="457"/>
       <c r="B210" s="454"/>
-      <c r="C210" s="490"/>
+      <c r="C210" s="476"/>
       <c r="D210" s="306"/>
       <c r="E210" s="163"/>
       <c r="F210" s="253"/>
@@ -27732,7 +27733,7 @@
     <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
       <c r="B211" s="454"/>
-      <c r="C211" s="490"/>
+      <c r="C211" s="476"/>
       <c r="D211" s="306"/>
       <c r="E211" s="163"/>
       <c r="F211" s="253"/>
@@ -27824,7 +27825,7 @@
     <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
       <c r="B212" s="454"/>
-      <c r="C212" s="490"/>
+      <c r="C212" s="476"/>
       <c r="D212" s="306"/>
       <c r="E212" s="164"/>
       <c r="F212" s="254"/>
@@ -27918,7 +27919,7 @@
       <c r="B213" s="454" t="s">
         <v>952</v>
       </c>
-      <c r="C213" s="490"/>
+      <c r="C213" s="476"/>
       <c r="D213" s="306" t="s">
         <v>745</v>
       </c>
@@ -28044,7 +28045,7 @@
     <row r="214" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A214" s="457"/>
       <c r="B214" s="454"/>
-      <c r="C214" s="490"/>
+      <c r="C214" s="476"/>
       <c r="D214" s="306"/>
       <c r="E214" s="163"/>
       <c r="F214" s="253"/>
@@ -28136,7 +28137,7 @@
     <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
       <c r="B215" s="454"/>
-      <c r="C215" s="491"/>
+      <c r="C215" s="477"/>
       <c r="D215" s="319"/>
       <c r="E215" s="166"/>
       <c r="F215" s="255"/>
@@ -28232,7 +28233,7 @@
       <c r="B216" s="454" t="s">
         <v>953</v>
       </c>
-      <c r="C216" s="513">
+      <c r="C216" s="459">
         <v>102</v>
       </c>
       <c r="D216" s="307" t="s">
@@ -28360,7 +28361,7 @@
     <row r="217" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A217" s="457"/>
       <c r="B217" s="454"/>
-      <c r="C217" s="514"/>
+      <c r="C217" s="460"/>
       <c r="D217" s="307"/>
       <c r="E217" s="174"/>
       <c r="F217" s="256"/>
@@ -28452,7 +28453,7 @@
     <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
       <c r="B218" s="454"/>
-      <c r="C218" s="514"/>
+      <c r="C218" s="460"/>
       <c r="D218" s="307"/>
       <c r="E218" s="174"/>
       <c r="F218" s="256"/>
@@ -28544,7 +28545,7 @@
     <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
       <c r="B219" s="454"/>
-      <c r="C219" s="515"/>
+      <c r="C219" s="461"/>
       <c r="D219" s="320"/>
       <c r="E219" s="175"/>
       <c r="F219" s="257"/>
@@ -28640,7 +28641,7 @@
       <c r="B220" s="454" t="s">
         <v>954</v>
       </c>
-      <c r="C220" s="513">
+      <c r="C220" s="459">
         <v>103</v>
       </c>
       <c r="D220" s="307" t="s">
@@ -28764,7 +28765,7 @@
     <row r="221" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A221" s="457"/>
       <c r="B221" s="454"/>
-      <c r="C221" s="514"/>
+      <c r="C221" s="460"/>
       <c r="D221" s="307"/>
       <c r="E221" s="174"/>
       <c r="F221" s="256"/>
@@ -28854,7 +28855,7 @@
     <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
       <c r="B222" s="454"/>
-      <c r="C222" s="514"/>
+      <c r="C222" s="460"/>
       <c r="D222" s="307"/>
       <c r="E222" s="178"/>
       <c r="F222" s="258"/>
@@ -28948,7 +28949,7 @@
       <c r="B223" s="454" t="s">
         <v>955</v>
       </c>
-      <c r="C223" s="514"/>
+      <c r="C223" s="460"/>
       <c r="D223" s="307" t="s">
         <v>745</v>
       </c>
@@ -29074,7 +29075,7 @@
     <row r="224" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A224" s="457"/>
       <c r="B224" s="454"/>
-      <c r="C224" s="514"/>
+      <c r="C224" s="460"/>
       <c r="D224" s="307"/>
       <c r="E224" s="174"/>
       <c r="F224" s="256"/>
@@ -29166,7 +29167,7 @@
     <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
       <c r="B225" s="454"/>
-      <c r="C225" s="514"/>
+      <c r="C225" s="460"/>
       <c r="D225" s="307"/>
       <c r="E225" s="174"/>
       <c r="F225" s="256"/>
@@ -29258,7 +29259,7 @@
     <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
       <c r="B226" s="454"/>
-      <c r="C226" s="515"/>
+      <c r="C226" s="461"/>
       <c r="D226" s="320"/>
       <c r="E226" s="175"/>
       <c r="F226" s="257"/>
@@ -29348,7 +29349,7 @@
       <c r="B227" s="454" t="s">
         <v>956</v>
       </c>
-      <c r="C227" s="513">
+      <c r="C227" s="459">
         <v>104</v>
       </c>
       <c r="D227" s="307" t="s">
@@ -29472,7 +29473,7 @@
     <row r="228" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A228" s="457"/>
       <c r="B228" s="454"/>
-      <c r="C228" s="514"/>
+      <c r="C228" s="460"/>
       <c r="D228" s="307"/>
       <c r="E228" s="174"/>
       <c r="F228" s="256"/>
@@ -29560,7 +29561,7 @@
     <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
       <c r="B229" s="454"/>
-      <c r="C229" s="514"/>
+      <c r="C229" s="460"/>
       <c r="D229" s="307"/>
       <c r="E229" s="174"/>
       <c r="F229" s="256"/>
@@ -29648,7 +29649,7 @@
     <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
       <c r="B230" s="454"/>
-      <c r="C230" s="514"/>
+      <c r="C230" s="460"/>
       <c r="D230" s="307"/>
       <c r="E230" s="178"/>
       <c r="F230" s="258"/>
@@ -29740,7 +29741,7 @@
       <c r="B231" s="454" t="s">
         <v>957</v>
       </c>
-      <c r="C231" s="514"/>
+      <c r="C231" s="460"/>
       <c r="D231" s="307" t="s">
         <v>745</v>
       </c>
@@ -29862,7 +29863,7 @@
     <row r="232" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A232" s="457"/>
       <c r="B232" s="454"/>
-      <c r="C232" s="514"/>
+      <c r="C232" s="460"/>
       <c r="D232" s="307"/>
       <c r="E232" s="174"/>
       <c r="F232" s="256"/>
@@ -29950,7 +29951,7 @@
     <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
       <c r="B233" s="454"/>
-      <c r="C233" s="514"/>
+      <c r="C233" s="460"/>
       <c r="D233" s="307"/>
       <c r="E233" s="174"/>
       <c r="F233" s="256"/>
@@ -30038,7 +30039,7 @@
     <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
       <c r="B234" s="454"/>
-      <c r="C234" s="515"/>
+      <c r="C234" s="461"/>
       <c r="D234" s="320"/>
       <c r="E234" s="175"/>
       <c r="F234" s="257"/>
@@ -30126,7 +30127,7 @@
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="522">
+      <c r="C235" s="468">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -30250,7 +30251,7 @@
     <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="523"/>
+      <c r="C236" s="469"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -30338,7 +30339,7 @@
     <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="523"/>
+      <c r="C237" s="469"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -30426,7 +30427,7 @@
     <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="524"/>
+      <c r="C238" s="470"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -30516,7 +30517,7 @@
       <c r="B239" s="454" t="s">
         <v>959</v>
       </c>
-      <c r="C239" s="525">
+      <c r="C239" s="471">
         <v>106</v>
       </c>
       <c r="D239" s="308" t="s">
@@ -30640,7 +30641,7 @@
     <row r="240" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A240" s="457"/>
       <c r="B240" s="454"/>
-      <c r="C240" s="526"/>
+      <c r="C240" s="472"/>
       <c r="D240" s="308"/>
       <c r="E240" s="185"/>
       <c r="F240" s="259"/>
@@ -30728,7 +30729,7 @@
     <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
       <c r="B241" s="454"/>
-      <c r="C241" s="526"/>
+      <c r="C241" s="472"/>
       <c r="D241" s="308"/>
       <c r="E241" s="185"/>
       <c r="F241" s="259"/>
@@ -30816,7 +30817,7 @@
     <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
       <c r="B242" s="454"/>
-      <c r="C242" s="526"/>
+      <c r="C242" s="472"/>
       <c r="D242" s="308"/>
       <c r="E242" s="189"/>
       <c r="F242" s="261"/>
@@ -30906,7 +30907,7 @@
       <c r="B243" s="454" t="s">
         <v>960</v>
       </c>
-      <c r="C243" s="526"/>
+      <c r="C243" s="472"/>
       <c r="D243" s="308" t="s">
         <v>745</v>
       </c>
@@ -31028,7 +31029,7 @@
     <row r="244" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A244" s="457"/>
       <c r="B244" s="454"/>
-      <c r="C244" s="526"/>
+      <c r="C244" s="472"/>
       <c r="D244" s="308"/>
       <c r="E244" s="185"/>
       <c r="F244" s="259"/>
@@ -31116,7 +31117,7 @@
     <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
       <c r="B245" s="454"/>
-      <c r="C245" s="526"/>
+      <c r="C245" s="472"/>
       <c r="D245" s="308"/>
       <c r="E245" s="185"/>
       <c r="F245" s="259"/>
@@ -31204,7 +31205,7 @@
     <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
       <c r="B246" s="454"/>
-      <c r="C246" s="526"/>
+      <c r="C246" s="472"/>
       <c r="D246" s="308"/>
       <c r="E246" s="185"/>
       <c r="F246" s="259"/>
@@ -31292,7 +31293,7 @@
     <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
       <c r="B247" s="454"/>
-      <c r="C247" s="526"/>
+      <c r="C247" s="472"/>
       <c r="D247" s="308"/>
       <c r="E247" s="181"/>
       <c r="F247" s="181"/>
@@ -31390,7 +31391,7 @@
       <c r="B248" s="454" t="s">
         <v>961</v>
       </c>
-      <c r="C248" s="527"/>
+      <c r="C248" s="473"/>
       <c r="D248" s="308" t="s">
         <v>745</v>
       </c>
@@ -31506,7 +31507,7 @@
     <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
       <c r="B249" s="454"/>
-      <c r="C249" s="526"/>
+      <c r="C249" s="472"/>
       <c r="D249" s="308"/>
       <c r="E249" s="185"/>
       <c r="F249" s="259"/>
@@ -31596,7 +31597,7 @@
     <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
       <c r="B250" s="454"/>
-      <c r="C250" s="526"/>
+      <c r="C250" s="472"/>
       <c r="D250" s="308"/>
       <c r="E250" s="185"/>
       <c r="F250" s="259"/>
@@ -31686,7 +31687,7 @@
     <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
       <c r="B251" s="454"/>
-      <c r="C251" s="526"/>
+      <c r="C251" s="472"/>
       <c r="D251" s="308"/>
       <c r="E251" s="189"/>
       <c r="F251" s="261"/>
@@ -31780,7 +31781,7 @@
       <c r="B252" s="454" t="s">
         <v>962</v>
       </c>
-      <c r="C252" s="526"/>
+      <c r="C252" s="472"/>
       <c r="D252" s="308" t="s">
         <v>745</v>
       </c>
@@ -31902,7 +31903,7 @@
     <row r="253" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A253" s="457"/>
       <c r="B253" s="454"/>
-      <c r="C253" s="526"/>
+      <c r="C253" s="472"/>
       <c r="D253" s="308"/>
       <c r="E253" s="185"/>
       <c r="F253" s="259"/>
@@ -31990,7 +31991,7 @@
     <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
       <c r="B254" s="454"/>
-      <c r="C254" s="526"/>
+      <c r="C254" s="472"/>
       <c r="D254" s="308"/>
       <c r="E254" s="185"/>
       <c r="F254" s="259"/>
@@ -32078,7 +32079,7 @@
     <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
       <c r="B255" s="454"/>
-      <c r="C255" s="526"/>
+      <c r="C255" s="472"/>
       <c r="D255" s="308"/>
       <c r="E255" s="185"/>
       <c r="F255" s="259"/>
@@ -32166,7 +32167,7 @@
     <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
       <c r="B256" s="454"/>
-      <c r="C256" s="528"/>
+      <c r="C256" s="474"/>
       <c r="D256" s="321"/>
       <c r="E256" s="186"/>
       <c r="F256" s="260"/>
@@ -32258,7 +32259,7 @@
       <c r="B257" s="454" t="s">
         <v>963</v>
       </c>
-      <c r="C257" s="513">
+      <c r="C257" s="459">
         <v>107</v>
       </c>
       <c r="D257" s="307" t="s">
@@ -32382,7 +32383,7 @@
     <row r="258" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A258" s="457"/>
       <c r="B258" s="454"/>
-      <c r="C258" s="514"/>
+      <c r="C258" s="460"/>
       <c r="D258" s="307"/>
       <c r="E258" s="174"/>
       <c r="F258" s="256"/>
@@ -32472,7 +32473,7 @@
     <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
       <c r="B259" s="454"/>
-      <c r="C259" s="514"/>
+      <c r="C259" s="460"/>
       <c r="D259" s="307"/>
       <c r="E259" s="174"/>
       <c r="F259" s="256"/>
@@ -32562,7 +32563,7 @@
     <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
       <c r="B260" s="454"/>
-      <c r="C260" s="514"/>
+      <c r="C260" s="460"/>
       <c r="D260" s="307"/>
       <c r="E260" s="178"/>
       <c r="F260" s="258"/>
@@ -32654,7 +32655,7 @@
       <c r="B261" s="454" t="s">
         <v>964</v>
       </c>
-      <c r="C261" s="514"/>
+      <c r="C261" s="460"/>
       <c r="D261" s="307" t="s">
         <v>745</v>
       </c>
@@ -32776,7 +32777,7 @@
     <row r="262" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A262" s="457"/>
       <c r="B262" s="454"/>
-      <c r="C262" s="514"/>
+      <c r="C262" s="460"/>
       <c r="D262" s="307"/>
       <c r="E262" s="174"/>
       <c r="F262" s="256"/>
@@ -32862,7 +32863,7 @@
     <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
       <c r="B263" s="454"/>
-      <c r="C263" s="515"/>
+      <c r="C263" s="461"/>
       <c r="D263" s="320"/>
       <c r="E263" s="175"/>
       <c r="F263" s="257"/>
@@ -32952,7 +32953,7 @@
       <c r="B264" s="454" t="s">
         <v>965</v>
       </c>
-      <c r="C264" s="513">
+      <c r="C264" s="459">
         <v>108</v>
       </c>
       <c r="D264" s="307" t="s">
@@ -33078,7 +33079,7 @@
     <row r="265" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A265" s="457"/>
       <c r="B265" s="454"/>
-      <c r="C265" s="514"/>
+      <c r="C265" s="460"/>
       <c r="D265" s="307"/>
       <c r="E265" s="174"/>
       <c r="F265" s="256"/>
@@ -33168,7 +33169,7 @@
     <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
       <c r="B266" s="454"/>
-      <c r="C266" s="514"/>
+      <c r="C266" s="460"/>
       <c r="D266" s="307"/>
       <c r="E266" s="174"/>
       <c r="F266" s="256"/>
@@ -33258,7 +33259,7 @@
     <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
       <c r="B267" s="454"/>
-      <c r="C267" s="515"/>
+      <c r="C267" s="461"/>
       <c r="D267" s="320"/>
       <c r="E267" s="175"/>
       <c r="F267" s="257"/>
@@ -33352,7 +33353,7 @@
       <c r="B268" s="454" t="s">
         <v>966</v>
       </c>
-      <c r="C268" s="513">
+      <c r="C268" s="459">
         <v>109</v>
       </c>
       <c r="D268" s="307" t="s">
@@ -33480,7 +33481,7 @@
     <row r="269" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A269" s="457"/>
       <c r="B269" s="454"/>
-      <c r="C269" s="514"/>
+      <c r="C269" s="460"/>
       <c r="D269" s="307"/>
       <c r="E269" s="174"/>
       <c r="F269" s="256"/>
@@ -33572,7 +33573,7 @@
     <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
       <c r="B270" s="454"/>
-      <c r="C270" s="515"/>
+      <c r="C270" s="461"/>
       <c r="D270" s="320"/>
       <c r="E270" s="175"/>
       <c r="F270" s="257"/>
@@ -33668,7 +33669,7 @@
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="516">
+      <c r="C271" s="462">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -33796,7 +33797,7 @@
     <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="517"/>
+      <c r="C272" s="463"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -33886,7 +33887,7 @@
     <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="517"/>
+      <c r="C273" s="463"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -33980,7 +33981,7 @@
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="517"/>
+      <c r="C274" s="463"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -34098,7 +34099,7 @@
     <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="517"/>
+      <c r="C275" s="463"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -34194,7 +34195,7 @@
     <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="517"/>
+      <c r="C276" s="463"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -34284,7 +34285,7 @@
     <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="518"/>
+      <c r="C277" s="464"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -34378,7 +34379,7 @@
       <c r="B278" s="454" t="s">
         <v>969</v>
       </c>
-      <c r="C278" s="519">
+      <c r="C278" s="465">
         <v>112</v>
       </c>
       <c r="D278" s="309" t="s">
@@ -34502,7 +34503,7 @@
     <row r="279" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A279" s="457"/>
       <c r="B279" s="454"/>
-      <c r="C279" s="520"/>
+      <c r="C279" s="466"/>
       <c r="D279" s="309"/>
       <c r="E279" s="197"/>
       <c r="F279" s="262"/>
@@ -34590,7 +34591,7 @@
     <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
       <c r="B280" s="454"/>
-      <c r="C280" s="520"/>
+      <c r="C280" s="466"/>
       <c r="D280" s="309"/>
       <c r="E280" s="197"/>
       <c r="F280" s="262"/>
@@ -34678,7 +34679,7 @@
     <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
       <c r="B281" s="455"/>
-      <c r="C281" s="521"/>
+      <c r="C281" s="467"/>
       <c r="D281" s="322"/>
       <c r="E281" s="201"/>
       <c r="F281" s="264"/>
@@ -34765,16 +34766,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C264:C267"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="C271:C277"/>
-    <mergeCell ref="C278:C281"/>
-    <mergeCell ref="C216:C219"/>
-    <mergeCell ref="C220:C226"/>
-    <mergeCell ref="C227:C234"/>
-    <mergeCell ref="C235:C238"/>
-    <mergeCell ref="C239:C256"/>
-    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="C13:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="C35:C43"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="C55:C63"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="C67:C74"/>
+    <mergeCell ref="C75:C82"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="C86:C97"/>
+    <mergeCell ref="C98:C101"/>
     <mergeCell ref="C209:C215"/>
     <mergeCell ref="C106:C114"/>
     <mergeCell ref="C115:C122"/>
@@ -34787,24 +34796,16 @@
     <mergeCell ref="C184:C191"/>
     <mergeCell ref="C192:C199"/>
     <mergeCell ref="C200:C208"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="C35:C43"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="C47:C50"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="C55:C63"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="C67:C74"/>
-    <mergeCell ref="C75:C82"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="C86:C97"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="C13:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C264:C267"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="C271:C277"/>
+    <mergeCell ref="C278:C281"/>
+    <mergeCell ref="C216:C219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="C235:C238"/>
+    <mergeCell ref="C239:C256"/>
+    <mergeCell ref="C257:C263"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47056976-65D7-465A-A358-2EE1CB91D610}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD2F744-E413-4338-98E7-C3781CB965C0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4478,7 +4478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="529">
+  <cellXfs count="537">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5644,6 +5644,168 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5692,167 +5854,29 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="40" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="52" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="47" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="46" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6206,7 +6230,7 @@
     <col min="32" max="32" width="11.5546875" style="206"/>
     <col min="34" max="35" width="11.5546875" style="206"/>
     <col min="41" max="43" width="11.5546875" style="206"/>
-    <col min="44" max="44" width="19.6640625" style="206" customWidth="1"/>
+    <col min="44" max="44" width="19.6640625" style="207" customWidth="1"/>
     <col min="262" max="262" width="19.21875" customWidth="1"/>
     <col min="263" max="263" width="51.109375" customWidth="1"/>
     <col min="264" max="264" width="25.5546875" customWidth="1"/>
@@ -7169,7 +7193,7 @@
       <c r="B2" s="454" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="523">
+      <c r="C2" s="462">
         <v>11</v>
       </c>
       <c r="D2" s="296" t="s">
@@ -7290,14 +7314,14 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
-      <c r="AR2" s="33" t="s">
+      <c r="AR2" s="529" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" s="457"/>
       <c r="B3" s="454"/>
-      <c r="C3" s="524"/>
+      <c r="C3" s="463"/>
       <c r="D3" s="296"/>
       <c r="E3" s="17"/>
       <c r="F3" s="224"/>
@@ -7382,14 +7406,14 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
-      <c r="AR3" s="37" t="s">
+      <c r="AR3" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="457"/>
       <c r="B4" s="454"/>
-      <c r="C4" s="525"/>
+      <c r="C4" s="464"/>
       <c r="D4" s="297"/>
       <c r="E4" s="209"/>
       <c r="F4" s="225"/>
@@ -7474,7 +7498,7 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
-      <c r="AR4" s="51" t="s">
+      <c r="AR4" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7485,7 +7509,7 @@
       <c r="B5" s="454" t="s">
         <v>902</v>
       </c>
-      <c r="C5" s="523">
+      <c r="C5" s="462">
         <v>12</v>
       </c>
       <c r="D5" s="296" t="s">
@@ -7604,14 +7628,14 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
-      <c r="AR5" s="33" t="s">
+      <c r="AR5" s="529" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="457"/>
       <c r="B6" s="454"/>
-      <c r="C6" s="524"/>
+      <c r="C6" s="463"/>
       <c r="D6" s="296"/>
       <c r="E6" s="34"/>
       <c r="F6" s="226"/>
@@ -7694,14 +7718,14 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
-      <c r="AR6" s="52" t="s">
+      <c r="AR6" s="532" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="457"/>
       <c r="B7" s="454"/>
-      <c r="C7" s="524"/>
+      <c r="C7" s="463"/>
       <c r="D7" s="296"/>
       <c r="E7" s="34"/>
       <c r="F7" s="226"/>
@@ -7784,14 +7808,14 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
-      <c r="AR7" s="37" t="s">
+      <c r="AR7" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="457"/>
       <c r="B8" s="454"/>
-      <c r="C8" s="524"/>
+      <c r="C8" s="463"/>
       <c r="D8" s="296"/>
       <c r="E8" s="53"/>
       <c r="F8" s="227"/>
@@ -7872,7 +7896,7 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
-      <c r="AR8" s="66" t="s">
+      <c r="AR8" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7883,7 +7907,7 @@
       <c r="B9" s="454" t="s">
         <v>903</v>
       </c>
-      <c r="C9" s="524"/>
+      <c r="C9" s="463"/>
       <c r="D9" s="296" t="s">
         <v>736</v>
       </c>
@@ -7998,14 +8022,14 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
-      <c r="AR9" s="33" t="s">
+      <c r="AR9" s="529" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="457"/>
       <c r="B10" s="454"/>
-      <c r="C10" s="524"/>
+      <c r="C10" s="463"/>
       <c r="D10" s="296"/>
       <c r="E10" s="34"/>
       <c r="F10" s="226"/>
@@ -8086,14 +8110,14 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
-      <c r="AR10" s="52" t="s">
+      <c r="AR10" s="532" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="457"/>
       <c r="B11" s="454"/>
-      <c r="C11" s="524"/>
+      <c r="C11" s="463"/>
       <c r="D11" s="296"/>
       <c r="E11" s="34"/>
       <c r="F11" s="226"/>
@@ -8174,14 +8198,14 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
-      <c r="AR11" s="37" t="s">
+      <c r="AR11" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="457"/>
       <c r="B12" s="454"/>
-      <c r="C12" s="525"/>
+      <c r="C12" s="464"/>
       <c r="D12" s="297"/>
       <c r="E12" s="38"/>
       <c r="F12" s="228"/>
@@ -8260,7 +8284,7 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
-      <c r="AR12" s="51" t="s">
+      <c r="AR12" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8271,7 +8295,7 @@
       <c r="B13" s="454" t="s">
         <v>904</v>
       </c>
-      <c r="C13" s="523">
+      <c r="C13" s="462">
         <v>13</v>
       </c>
       <c r="D13" s="296" t="s">
@@ -8388,14 +8412,14 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
-      <c r="AR13" s="33" t="s">
+      <c r="AR13" s="529" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="457"/>
       <c r="B14" s="454"/>
-      <c r="C14" s="524"/>
+      <c r="C14" s="463"/>
       <c r="D14" s="296"/>
       <c r="E14" s="34"/>
       <c r="F14" s="226"/>
@@ -8476,14 +8500,14 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
-      <c r="AR14" s="37" t="s">
+      <c r="AR14" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="457"/>
       <c r="B15" s="454"/>
-      <c r="C15" s="524"/>
+      <c r="C15" s="463"/>
       <c r="D15" s="296"/>
       <c r="E15" s="34"/>
       <c r="F15" s="226"/>
@@ -8564,14 +8588,14 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
-      <c r="AR15" s="52" t="s">
+      <c r="AR15" s="532" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="457"/>
       <c r="B16" s="454"/>
-      <c r="C16" s="524"/>
+      <c r="C16" s="463"/>
       <c r="D16" s="296"/>
       <c r="E16" s="34"/>
       <c r="F16" s="226"/>
@@ -8652,14 +8676,14 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
-      <c r="AR16" s="37" t="s">
+      <c r="AR16" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="457"/>
       <c r="B17" s="454"/>
-      <c r="C17" s="524"/>
+      <c r="C17" s="463"/>
       <c r="D17" s="296"/>
       <c r="E17" s="53"/>
       <c r="F17" s="227"/>
@@ -8738,7 +8762,7 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
-      <c r="AR17" s="66" t="s">
+      <c r="AR17" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8749,7 +8773,7 @@
       <c r="B18" s="454" t="s">
         <v>905</v>
       </c>
-      <c r="C18" s="524"/>
+      <c r="C18" s="463"/>
       <c r="D18" s="296" t="s">
         <v>736</v>
       </c>
@@ -8862,14 +8886,14 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
-      <c r="AR18" s="33" t="s">
+      <c r="AR18" s="529" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="457"/>
       <c r="B19" s="454"/>
-      <c r="C19" s="524"/>
+      <c r="C19" s="463"/>
       <c r="D19" s="296"/>
       <c r="E19" s="34"/>
       <c r="F19" s="226"/>
@@ -8950,14 +8974,14 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
-      <c r="AR19" s="37" t="s">
+      <c r="AR19" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="457"/>
       <c r="B20" s="454"/>
-      <c r="C20" s="524"/>
+      <c r="C20" s="463"/>
       <c r="D20" s="296"/>
       <c r="E20" s="34"/>
       <c r="F20" s="226"/>
@@ -9038,14 +9062,14 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
-      <c r="AR20" s="52" t="s">
+      <c r="AR20" s="532" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="457"/>
       <c r="B21" s="454"/>
-      <c r="C21" s="524"/>
+      <c r="C21" s="463"/>
       <c r="D21" s="296"/>
       <c r="E21" s="34"/>
       <c r="F21" s="226"/>
@@ -9126,14 +9150,14 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
-      <c r="AR21" s="37" t="s">
+      <c r="AR21" s="530" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="457"/>
       <c r="B22" s="454"/>
-      <c r="C22" s="525"/>
+      <c r="C22" s="464"/>
       <c r="D22" s="297"/>
       <c r="E22" s="38"/>
       <c r="F22" s="228"/>
@@ -9214,7 +9238,7 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" s="51" t="s">
+      <c r="AR22" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9225,7 +9249,7 @@
       <c r="B23" s="454" t="s">
         <v>906</v>
       </c>
-      <c r="C23" s="526">
+      <c r="C23" s="465">
         <v>21</v>
       </c>
       <c r="D23" s="298" t="s">
@@ -9346,14 +9370,14 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
-      <c r="AR23" s="33" t="s">
+      <c r="AR23" s="529" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="457"/>
       <c r="B24" s="454"/>
-      <c r="C24" s="527"/>
+      <c r="C24" s="466"/>
       <c r="D24" s="298"/>
       <c r="E24" s="73"/>
       <c r="F24" s="230"/>
@@ -9438,14 +9462,14 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
-      <c r="AR24" s="37" t="s">
+      <c r="AR24" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="25" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="457"/>
       <c r="B25" s="454"/>
-      <c r="C25" s="528"/>
+      <c r="C25" s="467"/>
       <c r="D25" s="311"/>
       <c r="E25" s="74"/>
       <c r="F25" s="231"/>
@@ -9530,7 +9554,7 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
-      <c r="AR25" s="51" t="s">
+      <c r="AR25" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9541,7 +9565,7 @@
       <c r="B26" s="454" t="s">
         <v>907</v>
       </c>
-      <c r="C26" s="502">
+      <c r="C26" s="459">
         <v>22</v>
       </c>
       <c r="D26" s="298" t="s">
@@ -9658,14 +9682,14 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
-      <c r="AR26" s="33" t="s">
+      <c r="AR26" s="529" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="457"/>
       <c r="B27" s="454"/>
-      <c r="C27" s="503"/>
+      <c r="C27" s="460"/>
       <c r="D27" s="298"/>
       <c r="E27" s="73"/>
       <c r="F27" s="230"/>
@@ -9746,14 +9770,14 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
-      <c r="AR27" s="37" t="s">
+      <c r="AR27" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="457"/>
       <c r="B28" s="454"/>
-      <c r="C28" s="503"/>
+      <c r="C28" s="460"/>
       <c r="D28" s="298"/>
       <c r="E28" s="73"/>
       <c r="F28" s="230"/>
@@ -9834,14 +9858,14 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
-      <c r="AR28" s="52" t="s">
+      <c r="AR28" s="532" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="457"/>
       <c r="B29" s="454"/>
-      <c r="C29" s="503"/>
+      <c r="C29" s="460"/>
       <c r="D29" s="298"/>
       <c r="E29" s="73"/>
       <c r="F29" s="230"/>
@@ -9924,14 +9948,14 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
-      <c r="AR29" s="37" t="s">
+      <c r="AR29" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="30" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="457"/>
       <c r="B30" s="454"/>
-      <c r="C30" s="504"/>
+      <c r="C30" s="461"/>
       <c r="D30" s="311"/>
       <c r="E30" s="74"/>
       <c r="F30" s="231"/>
@@ -10010,7 +10034,7 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" s="51" t="s">
+      <c r="AR30" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10021,7 +10045,7 @@
       <c r="B31" s="454" t="s">
         <v>908</v>
       </c>
-      <c r="C31" s="502">
+      <c r="C31" s="459">
         <v>23</v>
       </c>
       <c r="D31" s="298" t="s">
@@ -10142,14 +10166,14 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
-      <c r="AR31" s="33" t="s">
+      <c r="AR31" s="529" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="457"/>
       <c r="B32" s="454"/>
-      <c r="C32" s="503"/>
+      <c r="C32" s="460"/>
       <c r="D32" s="298"/>
       <c r="E32" s="73"/>
       <c r="F32" s="230"/>
@@ -10234,14 +10258,14 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
-      <c r="AR32" s="52" t="s">
+      <c r="AR32" s="532" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="457"/>
       <c r="B33" s="454"/>
-      <c r="C33" s="503"/>
+      <c r="C33" s="460"/>
       <c r="D33" s="298"/>
       <c r="E33" s="73"/>
       <c r="F33" s="230"/>
@@ -10326,14 +10350,14 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
-      <c r="AR33" s="37" t="s">
+      <c r="AR33" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="34" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="457"/>
       <c r="B34" s="454"/>
-      <c r="C34" s="504"/>
+      <c r="C34" s="461"/>
       <c r="D34" s="311"/>
       <c r="E34" s="74"/>
       <c r="F34" s="231"/>
@@ -10418,7 +10442,7 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
-      <c r="AR34" s="51" t="s">
+      <c r="AR34" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10429,7 +10453,7 @@
       <c r="B35" s="454" t="s">
         <v>909</v>
       </c>
-      <c r="C35" s="502">
+      <c r="C35" s="459">
         <v>24</v>
       </c>
       <c r="D35" s="298" t="s">
@@ -10544,14 +10568,14 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
-      <c r="AR35" s="33" t="s">
+      <c r="AR35" s="529" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="457"/>
       <c r="B36" s="454"/>
-      <c r="C36" s="503"/>
+      <c r="C36" s="460"/>
       <c r="D36" s="298"/>
       <c r="E36" s="73"/>
       <c r="F36" s="230"/>
@@ -10632,14 +10656,14 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
-      <c r="AR36" s="52" t="s">
+      <c r="AR36" s="532" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="457"/>
       <c r="B37" s="454"/>
-      <c r="C37" s="503"/>
+      <c r="C37" s="460"/>
       <c r="D37" s="298"/>
       <c r="E37" s="73"/>
       <c r="F37" s="230"/>
@@ -10720,14 +10744,14 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
-      <c r="AR37" s="37" t="s">
+      <c r="AR37" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="457"/>
       <c r="B38" s="454"/>
-      <c r="C38" s="503"/>
+      <c r="C38" s="460"/>
       <c r="D38" s="298"/>
       <c r="E38" s="77"/>
       <c r="F38" s="232"/>
@@ -10808,7 +10832,7 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
-      <c r="AR38" s="66" t="s">
+      <c r="AR38" s="533" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10819,7 +10843,7 @@
       <c r="B39" s="454" t="s">
         <v>910</v>
       </c>
-      <c r="C39" s="503"/>
+      <c r="C39" s="460"/>
       <c r="D39" s="298" t="s">
         <v>737</v>
       </c>
@@ -10934,14 +10958,14 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
-      <c r="AR39" s="33" t="s">
+      <c r="AR39" s="529" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="457"/>
       <c r="B40" s="454"/>
-      <c r="C40" s="503"/>
+      <c r="C40" s="460"/>
       <c r="D40" s="298"/>
       <c r="E40" s="73"/>
       <c r="F40" s="230"/>
@@ -11022,14 +11046,14 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
-      <c r="AR40" s="37" t="s">
+      <c r="AR40" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="457"/>
       <c r="B41" s="454"/>
-      <c r="C41" s="503"/>
+      <c r="C41" s="460"/>
       <c r="D41" s="298"/>
       <c r="E41" s="73"/>
       <c r="F41" s="230"/>
@@ -11110,14 +11134,14 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
-      <c r="AR41" s="52" t="s">
+      <c r="AR41" s="532" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="457"/>
       <c r="B42" s="454"/>
-      <c r="C42" s="503"/>
+      <c r="C42" s="460"/>
       <c r="D42" s="298"/>
       <c r="E42" s="73"/>
       <c r="F42" s="230"/>
@@ -11198,14 +11222,14 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
-      <c r="AR42" s="37" t="s">
+      <c r="AR42" s="530" t="s">
         <v>971</v>
       </c>
     </row>
     <row r="43" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="457"/>
       <c r="B43" s="454"/>
-      <c r="C43" s="504"/>
+      <c r="C43" s="461"/>
       <c r="D43" s="311"/>
       <c r="E43" s="74"/>
       <c r="F43" s="231"/>
@@ -11284,7 +11308,7 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
-      <c r="AR43" s="51" t="s">
+      <c r="AR43" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11295,7 +11319,7 @@
       <c r="B44" s="454" t="s">
         <v>911</v>
       </c>
-      <c r="C44" s="505">
+      <c r="C44" s="471">
         <v>31</v>
       </c>
       <c r="D44" s="299" t="s">
@@ -11414,14 +11438,14 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
-      <c r="AR44" s="33" t="s">
+      <c r="AR44" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="457"/>
       <c r="B45" s="454"/>
-      <c r="C45" s="506"/>
+      <c r="C45" s="472"/>
       <c r="D45" s="299"/>
       <c r="E45" s="84"/>
       <c r="F45" s="235"/>
@@ -11506,14 +11530,14 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
-      <c r="AR45" s="37" t="s">
+      <c r="AR45" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="46" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="457"/>
       <c r="B46" s="454"/>
-      <c r="C46" s="507"/>
+      <c r="C46" s="473"/>
       <c r="D46" s="312"/>
       <c r="E46" s="85"/>
       <c r="F46" s="236"/>
@@ -11598,7 +11622,7 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
-      <c r="AR46" s="51" t="s">
+      <c r="AR46" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11609,7 +11633,7 @@
       <c r="B47" s="454" t="s">
         <v>912</v>
       </c>
-      <c r="C47" s="508">
+      <c r="C47" s="474">
         <v>32</v>
       </c>
       <c r="D47" s="299" t="s">
@@ -11728,14 +11752,14 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
-      <c r="AR47" s="33" t="s">
+      <c r="AR47" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="457"/>
       <c r="B48" s="454"/>
-      <c r="C48" s="509"/>
+      <c r="C48" s="475"/>
       <c r="D48" s="299"/>
       <c r="E48" s="84"/>
       <c r="F48" s="235"/>
@@ -11818,14 +11842,14 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
-      <c r="AR48" s="52" t="s">
+      <c r="AR48" s="532" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="457"/>
       <c r="B49" s="454"/>
-      <c r="C49" s="509"/>
+      <c r="C49" s="475"/>
       <c r="D49" s="299"/>
       <c r="E49" s="84"/>
       <c r="F49" s="235"/>
@@ -11908,14 +11932,14 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
-      <c r="AR49" s="37" t="s">
+      <c r="AR49" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="50" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="457"/>
       <c r="B50" s="454"/>
-      <c r="C50" s="510"/>
+      <c r="C50" s="476"/>
       <c r="D50" s="312"/>
       <c r="E50" s="85"/>
       <c r="F50" s="236"/>
@@ -11998,7 +12022,7 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
-      <c r="AR50" s="51" t="s">
+      <c r="AR50" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12009,7 +12033,7 @@
       <c r="B51" s="454" t="s">
         <v>913</v>
       </c>
-      <c r="C51" s="508">
+      <c r="C51" s="474">
         <v>33</v>
       </c>
       <c r="D51" s="299" t="s">
@@ -12130,14 +12154,14 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
-      <c r="AR51" s="33" t="s">
+      <c r="AR51" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="457"/>
       <c r="B52" s="454"/>
-      <c r="C52" s="509"/>
+      <c r="C52" s="475"/>
       <c r="D52" s="299"/>
       <c r="E52" s="84"/>
       <c r="F52" s="235"/>
@@ -12222,14 +12246,14 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
-      <c r="AR52" s="52" t="s">
+      <c r="AR52" s="532" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="457"/>
       <c r="B53" s="454"/>
-      <c r="C53" s="509"/>
+      <c r="C53" s="475"/>
       <c r="D53" s="299"/>
       <c r="E53" s="84"/>
       <c r="F53" s="235"/>
@@ -12310,14 +12334,14 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
-      <c r="AR53" s="37" t="s">
+      <c r="AR53" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="54" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="457"/>
       <c r="B54" s="454"/>
-      <c r="C54" s="510"/>
+      <c r="C54" s="476"/>
       <c r="D54" s="312"/>
       <c r="E54" s="85"/>
       <c r="F54" s="236"/>
@@ -12396,7 +12420,7 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
-      <c r="AR54" s="51" t="s">
+      <c r="AR54" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12407,7 +12431,7 @@
       <c r="B55" s="454" t="s">
         <v>914</v>
       </c>
-      <c r="C55" s="508">
+      <c r="C55" s="474">
         <v>34</v>
       </c>
       <c r="D55" s="299" t="s">
@@ -12522,14 +12546,14 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
-      <c r="AR55" s="33" t="s">
+      <c r="AR55" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="457"/>
       <c r="B56" s="454"/>
-      <c r="C56" s="509"/>
+      <c r="C56" s="475"/>
       <c r="D56" s="299"/>
       <c r="E56" s="84"/>
       <c r="F56" s="235"/>
@@ -12610,14 +12634,14 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
-      <c r="AR56" s="37" t="s">
+      <c r="AR56" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="457"/>
       <c r="B57" s="454"/>
-      <c r="C57" s="509"/>
+      <c r="C57" s="475"/>
       <c r="D57" s="299"/>
       <c r="E57" s="84"/>
       <c r="F57" s="235"/>
@@ -12698,14 +12722,14 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
-      <c r="AR57" s="52" t="s">
+      <c r="AR57" s="532" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="457"/>
       <c r="B58" s="454"/>
-      <c r="C58" s="509"/>
+      <c r="C58" s="475"/>
       <c r="D58" s="299"/>
       <c r="E58" s="84"/>
       <c r="F58" s="235"/>
@@ -12786,14 +12810,14 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
-      <c r="AR58" s="37" t="s">
+      <c r="AR58" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="457"/>
       <c r="B59" s="454"/>
-      <c r="C59" s="509"/>
+      <c r="C59" s="475"/>
       <c r="D59" s="299"/>
       <c r="E59" s="89"/>
       <c r="F59" s="237"/>
@@ -12874,7 +12898,7 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
-      <c r="AR59" s="66" t="s">
+      <c r="AR59" s="533" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12885,7 +12909,7 @@
       <c r="B60" s="454" t="s">
         <v>915</v>
       </c>
-      <c r="C60" s="509"/>
+      <c r="C60" s="475"/>
       <c r="D60" s="299" t="s">
         <v>738</v>
       </c>
@@ -13000,14 +13024,14 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
-      <c r="AR60" s="33" t="s">
+      <c r="AR60" s="529" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="457"/>
       <c r="B61" s="454"/>
-      <c r="C61" s="509"/>
+      <c r="C61" s="475"/>
       <c r="D61" s="299"/>
       <c r="E61" s="84"/>
       <c r="F61" s="235"/>
@@ -13088,14 +13112,14 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
-      <c r="AR61" s="52" t="s">
+      <c r="AR61" s="532" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="457"/>
       <c r="B62" s="454"/>
-      <c r="C62" s="509"/>
+      <c r="C62" s="475"/>
       <c r="D62" s="299"/>
       <c r="E62" s="84"/>
       <c r="F62" s="235"/>
@@ -13176,14 +13200,14 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
-      <c r="AR62" s="37" t="s">
+      <c r="AR62" s="530" t="s">
         <v>972</v>
       </c>
     </row>
     <row r="63" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="457"/>
       <c r="B63" s="454"/>
-      <c r="C63" s="510"/>
+      <c r="C63" s="476"/>
       <c r="D63" s="312"/>
       <c r="E63" s="85"/>
       <c r="F63" s="236"/>
@@ -13264,7 +13288,7 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
-      <c r="AR63" s="51" t="s">
+      <c r="AR63" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13275,7 +13299,7 @@
       <c r="B64" s="454" t="s">
         <v>916</v>
       </c>
-      <c r="C64" s="511">
+      <c r="C64" s="477">
         <v>41</v>
       </c>
       <c r="D64" s="300" t="s">
@@ -13394,14 +13418,14 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
-      <c r="AR64" s="33" t="s">
+      <c r="AR64" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="457"/>
       <c r="B65" s="454"/>
-      <c r="C65" s="512"/>
+      <c r="C65" s="478"/>
       <c r="D65" s="300"/>
       <c r="E65" s="96"/>
       <c r="F65" s="238"/>
@@ -13486,14 +13510,14 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
-      <c r="AR65" s="37" t="s">
+      <c r="AR65" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="66" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="457"/>
       <c r="B66" s="454"/>
-      <c r="C66" s="513"/>
+      <c r="C66" s="479"/>
       <c r="D66" s="313"/>
       <c r="E66" s="97"/>
       <c r="F66" s="239"/>
@@ -13578,7 +13602,7 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
-      <c r="AR66" s="51" t="s">
+      <c r="AR66" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13589,7 +13613,7 @@
       <c r="B67" s="454" t="s">
         <v>917</v>
       </c>
-      <c r="C67" s="514">
+      <c r="C67" s="480">
         <v>42</v>
       </c>
       <c r="D67" s="300" t="s">
@@ -13708,14 +13732,14 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
-      <c r="AR67" s="33" t="s">
+      <c r="AR67" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="457"/>
       <c r="B68" s="454"/>
-      <c r="C68" s="515"/>
+      <c r="C68" s="481"/>
       <c r="D68" s="300"/>
       <c r="E68" s="96"/>
       <c r="F68" s="238"/>
@@ -13798,14 +13822,14 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
-      <c r="AR68" s="37" t="s">
+      <c r="AR68" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="457"/>
       <c r="B69" s="454"/>
-      <c r="C69" s="515"/>
+      <c r="C69" s="481"/>
       <c r="D69" s="300"/>
       <c r="E69" s="100"/>
       <c r="F69" s="240"/>
@@ -13888,7 +13912,7 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
-      <c r="AR69" s="66" t="s">
+      <c r="AR69" s="533" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13899,7 +13923,7 @@
       <c r="B70" s="454" t="s">
         <v>918</v>
       </c>
-      <c r="C70" s="515"/>
+      <c r="C70" s="481"/>
       <c r="D70" s="300" t="s">
         <v>739</v>
       </c>
@@ -14012,14 +14036,14 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
-      <c r="AR70" s="33" t="s">
+      <c r="AR70" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="457"/>
       <c r="B71" s="454"/>
-      <c r="C71" s="515"/>
+      <c r="C71" s="481"/>
       <c r="D71" s="300"/>
       <c r="E71" s="96"/>
       <c r="F71" s="238"/>
@@ -14100,14 +14124,14 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
-      <c r="AR71" s="52" t="s">
+      <c r="AR71" s="532" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="457"/>
       <c r="B72" s="454"/>
-      <c r="C72" s="515"/>
+      <c r="C72" s="481"/>
       <c r="D72" s="300"/>
       <c r="E72" s="96"/>
       <c r="F72" s="238"/>
@@ -14188,14 +14212,14 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
-      <c r="AR72" s="103" t="s">
+      <c r="AR72" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="457"/>
       <c r="B73" s="454"/>
-      <c r="C73" s="515"/>
+      <c r="C73" s="481"/>
       <c r="D73" s="300"/>
       <c r="E73" s="96"/>
       <c r="F73" s="238"/>
@@ -14276,14 +14300,14 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
-      <c r="AR73" s="37" t="s">
+      <c r="AR73" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="74" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="457"/>
       <c r="B74" s="454"/>
-      <c r="C74" s="516"/>
+      <c r="C74" s="482"/>
       <c r="D74" s="313"/>
       <c r="E74" s="97"/>
       <c r="F74" s="239"/>
@@ -14364,7 +14388,7 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
-      <c r="AR74" s="51" t="s">
+      <c r="AR74" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14375,7 +14399,7 @@
       <c r="B75" s="454" t="s">
         <v>919</v>
       </c>
-      <c r="C75" s="514">
+      <c r="C75" s="480">
         <v>43</v>
       </c>
       <c r="D75" s="300" t="s">
@@ -14492,14 +14516,14 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
-      <c r="AR75" s="33" t="s">
+      <c r="AR75" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="76" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A76" s="457"/>
       <c r="B76" s="454"/>
-      <c r="C76" s="515"/>
+      <c r="C76" s="481"/>
       <c r="D76" s="300"/>
       <c r="E76" s="96"/>
       <c r="F76" s="238"/>
@@ -14580,14 +14604,14 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
-      <c r="AR76" s="37" t="s">
+      <c r="AR76" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="77" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A77" s="457"/>
       <c r="B77" s="454"/>
-      <c r="C77" s="515"/>
+      <c r="C77" s="481"/>
       <c r="D77" s="300"/>
       <c r="E77" s="96"/>
       <c r="F77" s="238"/>
@@ -14668,14 +14692,14 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
-      <c r="AR77" s="52" t="s">
+      <c r="AR77" s="532" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A78" s="457"/>
       <c r="B78" s="454"/>
-      <c r="C78" s="515"/>
+      <c r="C78" s="481"/>
       <c r="D78" s="300"/>
       <c r="E78" s="96"/>
       <c r="F78" s="238"/>
@@ -14756,14 +14780,14 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
-      <c r="AR78" s="37" t="s">
+      <c r="AR78" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="79" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A79" s="457"/>
       <c r="B79" s="454"/>
-      <c r="C79" s="515"/>
+      <c r="C79" s="481"/>
       <c r="D79" s="300"/>
       <c r="E79" s="100"/>
       <c r="F79" s="240"/>
@@ -14844,7 +14868,7 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
-      <c r="AR79" s="66" t="s">
+      <c r="AR79" s="533" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14855,7 +14879,7 @@
       <c r="B80" s="454" t="s">
         <v>920</v>
       </c>
-      <c r="C80" s="515"/>
+      <c r="C80" s="481"/>
       <c r="D80" s="300" t="s">
         <v>739</v>
       </c>
@@ -14966,14 +14990,14 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
-      <c r="AR80" s="33" t="s">
+      <c r="AR80" s="529" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="81" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A81" s="457"/>
       <c r="B81" s="454"/>
-      <c r="C81" s="515"/>
+      <c r="C81" s="481"/>
       <c r="D81" s="300"/>
       <c r="E81" s="96"/>
       <c r="F81" s="238"/>
@@ -15054,14 +15078,14 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
-      <c r="AR81" s="37" t="s">
+      <c r="AR81" s="530" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="82" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="457"/>
       <c r="B82" s="454"/>
-      <c r="C82" s="516"/>
+      <c r="C82" s="482"/>
       <c r="D82" s="313"/>
       <c r="E82" s="97"/>
       <c r="F82" s="239"/>
@@ -15140,7 +15164,7 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
-      <c r="AR82" s="51" t="s">
+      <c r="AR82" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15151,7 +15175,7 @@
       <c r="B83" s="454" t="s">
         <v>921</v>
       </c>
-      <c r="C83" s="517">
+      <c r="C83" s="483">
         <v>51</v>
       </c>
       <c r="D83" s="301" t="s">
@@ -15272,14 +15296,14 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
-      <c r="AR83" s="33" t="s">
+      <c r="AR83" s="529" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="84" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A84" s="457"/>
       <c r="B84" s="454"/>
-      <c r="C84" s="518"/>
+      <c r="C84" s="484"/>
       <c r="D84" s="301"/>
       <c r="E84" s="110"/>
       <c r="F84" s="241"/>
@@ -15364,14 +15388,14 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
-      <c r="AR84" s="37" t="s">
+      <c r="AR84" s="530" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="85" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="457"/>
       <c r="B85" s="454"/>
-      <c r="C85" s="519"/>
+      <c r="C85" s="485"/>
       <c r="D85" s="314"/>
       <c r="E85" s="111"/>
       <c r="F85" s="242"/>
@@ -15454,7 +15478,7 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
-      <c r="AR85" s="51" t="s">
+      <c r="AR85" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15465,7 +15489,7 @@
       <c r="B86" s="454" t="s">
         <v>922</v>
       </c>
-      <c r="C86" s="520">
+      <c r="C86" s="486">
         <v>52</v>
       </c>
       <c r="D86" s="301" t="s">
@@ -15584,14 +15608,14 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
-      <c r="AR86" s="33" t="s">
+      <c r="AR86" s="529" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="87" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A87" s="457"/>
       <c r="B87" s="454"/>
-      <c r="C87" s="521"/>
+      <c r="C87" s="487"/>
       <c r="D87" s="301"/>
       <c r="E87" s="110"/>
       <c r="F87" s="241"/>
@@ -15676,14 +15700,14 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
-      <c r="AR87" s="52" t="s">
+      <c r="AR87" s="532" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="88" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A88" s="457"/>
       <c r="B88" s="454"/>
-      <c r="C88" s="521"/>
+      <c r="C88" s="487"/>
       <c r="D88" s="301"/>
       <c r="E88" s="110"/>
       <c r="F88" s="241"/>
@@ -15768,14 +15792,14 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
-      <c r="AR88" s="37" t="s">
+      <c r="AR88" s="530" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="89" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A89" s="457"/>
       <c r="B89" s="454"/>
-      <c r="C89" s="521"/>
+      <c r="C89" s="487"/>
       <c r="D89" s="301"/>
       <c r="E89" s="115"/>
       <c r="F89" s="243"/>
@@ -15860,7 +15884,7 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
-      <c r="AR89" s="66" t="s">
+      <c r="AR89" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15871,7 +15895,7 @@
       <c r="B90" s="454" t="s">
         <v>923</v>
       </c>
-      <c r="C90" s="521"/>
+      <c r="C90" s="487"/>
       <c r="D90" s="301" t="s">
         <v>740</v>
       </c>
@@ -15988,14 +16012,14 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
-      <c r="AR90" s="33" t="s">
+      <c r="AR90" s="529" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="91" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A91" s="457"/>
       <c r="B91" s="454"/>
-      <c r="C91" s="521"/>
+      <c r="C91" s="487"/>
       <c r="D91" s="301"/>
       <c r="E91" s="110"/>
       <c r="F91" s="241"/>
@@ -16078,14 +16102,14 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
-      <c r="AR91" s="52" t="s">
+      <c r="AR91" s="532" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="92" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A92" s="457"/>
       <c r="B92" s="454"/>
-      <c r="C92" s="521"/>
+      <c r="C92" s="487"/>
       <c r="D92" s="301"/>
       <c r="E92" s="110"/>
       <c r="F92" s="241"/>
@@ -16168,14 +16192,14 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
-      <c r="AR92" s="37" t="s">
+      <c r="AR92" s="530" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="93" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A93" s="457"/>
       <c r="B93" s="454"/>
-      <c r="C93" s="521"/>
+      <c r="C93" s="487"/>
       <c r="D93" s="301"/>
       <c r="E93" s="115"/>
       <c r="F93" s="243"/>
@@ -16258,7 +16282,7 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
-      <c r="AR93" s="66" t="s">
+      <c r="AR93" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16269,7 +16293,7 @@
       <c r="B94" s="454" t="s">
         <v>924</v>
       </c>
-      <c r="C94" s="521"/>
+      <c r="C94" s="487"/>
       <c r="D94" s="301" t="s">
         <v>740</v>
       </c>
@@ -16386,14 +16410,14 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR94" s="118" t="s">
+      <c r="AR94" s="534" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="95" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A95" s="457"/>
       <c r="B95" s="454"/>
-      <c r="C95" s="521"/>
+      <c r="C95" s="487"/>
       <c r="D95" s="301"/>
       <c r="E95" s="110"/>
       <c r="F95" s="241"/>
@@ -16476,14 +16500,14 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
-      <c r="AR95" s="52" t="s">
+      <c r="AR95" s="532" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="96" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A96" s="457"/>
       <c r="B96" s="454"/>
-      <c r="C96" s="521"/>
+      <c r="C96" s="487"/>
       <c r="D96" s="301"/>
       <c r="E96" s="110"/>
       <c r="F96" s="241"/>
@@ -16566,14 +16590,14 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
-      <c r="AR96" s="37" t="s">
+      <c r="AR96" s="530" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="97" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="457"/>
       <c r="B97" s="454"/>
-      <c r="C97" s="522"/>
+      <c r="C97" s="488"/>
       <c r="D97" s="314"/>
       <c r="E97" s="111"/>
       <c r="F97" s="242"/>
@@ -16656,7 +16680,7 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
-      <c r="AR97" s="51" t="s">
+      <c r="AR97" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16667,7 +16691,7 @@
       <c r="B98" s="454" t="s">
         <v>925</v>
       </c>
-      <c r="C98" s="520">
+      <c r="C98" s="486">
         <v>53</v>
       </c>
       <c r="D98" s="301" t="s">
@@ -16784,14 +16808,14 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
-      <c r="AR98" s="33" t="s">
+      <c r="AR98" s="529" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="99" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A99" s="457"/>
       <c r="B99" s="454"/>
-      <c r="C99" s="521"/>
+      <c r="C99" s="487"/>
       <c r="D99" s="301"/>
       <c r="E99" s="110"/>
       <c r="F99" s="241"/>
@@ -16874,14 +16898,14 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
-      <c r="AR99" s="52" t="s">
+      <c r="AR99" s="532" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="100" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A100" s="457"/>
       <c r="B100" s="454"/>
-      <c r="C100" s="521"/>
+      <c r="C100" s="487"/>
       <c r="D100" s="301"/>
       <c r="E100" s="110"/>
       <c r="F100" s="241"/>
@@ -16962,14 +16986,14 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
-      <c r="AR100" s="37" t="s">
+      <c r="AR100" s="530" t="s">
         <v>974</v>
       </c>
     </row>
     <row r="101" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="457"/>
       <c r="B101" s="454"/>
-      <c r="C101" s="522"/>
+      <c r="C101" s="488"/>
       <c r="D101" s="301"/>
       <c r="E101" s="111"/>
       <c r="F101" s="242"/>
@@ -17052,7 +17076,7 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
-      <c r="AR101" s="51" t="s">
+      <c r="AR101" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17063,7 +17087,7 @@
       <c r="B102" s="454" t="s">
         <v>926</v>
       </c>
-      <c r="C102" s="478">
+      <c r="C102" s="468">
         <v>61</v>
       </c>
       <c r="D102" s="323" t="s">
@@ -17176,14 +17200,14 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
-      <c r="AR102" s="33" t="s">
+      <c r="AR102" s="529" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="103" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A103" s="457"/>
       <c r="B103" s="454"/>
-      <c r="C103" s="479"/>
+      <c r="C103" s="469"/>
       <c r="D103" s="323"/>
       <c r="E103" s="329"/>
       <c r="F103" s="330"/>
@@ -17264,14 +17288,14 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
-      <c r="AR103" s="52" t="s">
+      <c r="AR103" s="532" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="104" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A104" s="457"/>
       <c r="B104" s="454"/>
-      <c r="C104" s="479"/>
+      <c r="C104" s="469"/>
       <c r="D104" s="323"/>
       <c r="E104" s="329"/>
       <c r="F104" s="330"/>
@@ -17352,14 +17376,14 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
-      <c r="AR104" s="37" t="s">
+      <c r="AR104" s="530" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="105" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="457"/>
       <c r="B105" s="454"/>
-      <c r="C105" s="480"/>
+      <c r="C105" s="470"/>
       <c r="D105" s="331"/>
       <c r="E105" s="332"/>
       <c r="F105" s="333"/>
@@ -17440,7 +17464,7 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
-      <c r="AR105" s="51" t="s">
+      <c r="AR105" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17451,7 +17475,7 @@
       <c r="B106" s="454" t="s">
         <v>927</v>
       </c>
-      <c r="C106" s="478">
+      <c r="C106" s="468">
         <v>62</v>
       </c>
       <c r="D106" s="323" t="s">
@@ -17568,14 +17592,14 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
-      <c r="AR106" s="33" t="s">
+      <c r="AR106" s="529" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="107" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A107" s="457"/>
       <c r="B107" s="454"/>
-      <c r="C107" s="479"/>
+      <c r="C107" s="469"/>
       <c r="D107" s="323"/>
       <c r="E107" s="329"/>
       <c r="F107" s="330"/>
@@ -17656,14 +17680,14 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
-      <c r="AR107" s="52" t="s">
+      <c r="AR107" s="532" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="108" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A108" s="457"/>
       <c r="B108" s="454"/>
-      <c r="C108" s="479"/>
+      <c r="C108" s="469"/>
       <c r="D108" s="323"/>
       <c r="E108" s="329"/>
       <c r="F108" s="330"/>
@@ -17744,14 +17768,14 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
-      <c r="AR108" s="37" t="s">
+      <c r="AR108" s="530" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="109" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A109" s="457"/>
       <c r="B109" s="454"/>
-      <c r="C109" s="479"/>
+      <c r="C109" s="469"/>
       <c r="D109" s="323"/>
       <c r="E109" s="338"/>
       <c r="F109" s="339"/>
@@ -17832,7 +17856,7 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
-      <c r="AR109" s="66" t="s">
+      <c r="AR109" s="533" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17843,7 +17867,7 @@
       <c r="B110" s="454" t="s">
         <v>928</v>
       </c>
-      <c r="C110" s="479"/>
+      <c r="C110" s="469"/>
       <c r="D110" s="323" t="s">
         <v>741</v>
       </c>
@@ -17958,14 +17982,14 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
-      <c r="AR110" s="33" t="s">
+      <c r="AR110" s="529" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="111" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A111" s="457"/>
       <c r="B111" s="454"/>
-      <c r="C111" s="479"/>
+      <c r="C111" s="469"/>
       <c r="D111" s="323"/>
       <c r="E111" s="329"/>
       <c r="F111" s="330"/>
@@ -18046,14 +18070,14 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
-      <c r="AR111" s="37" t="s">
+      <c r="AR111" s="530" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="112" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A112" s="457"/>
       <c r="B112" s="454"/>
-      <c r="C112" s="479"/>
+      <c r="C112" s="469"/>
       <c r="D112" s="323"/>
       <c r="E112" s="329"/>
       <c r="F112" s="330"/>
@@ -18134,14 +18158,14 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
-      <c r="AR112" s="52" t="s">
+      <c r="AR112" s="532" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="113" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A113" s="457"/>
       <c r="B113" s="454"/>
-      <c r="C113" s="479"/>
+      <c r="C113" s="469"/>
       <c r="D113" s="323"/>
       <c r="E113" s="329"/>
       <c r="F113" s="330"/>
@@ -18222,14 +18246,14 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
-      <c r="AR113" s="37" t="s">
+      <c r="AR113" s="530" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="114" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="457"/>
       <c r="B114" s="454"/>
-      <c r="C114" s="480"/>
+      <c r="C114" s="470"/>
       <c r="D114" s="331"/>
       <c r="E114" s="332"/>
       <c r="F114" s="333"/>
@@ -18308,7 +18332,7 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
-      <c r="AR114" s="51" t="s">
+      <c r="AR114" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18319,7 +18343,7 @@
       <c r="B115" s="454" t="s">
         <v>929</v>
       </c>
-      <c r="C115" s="481">
+      <c r="C115" s="492">
         <v>71</v>
       </c>
       <c r="D115" s="302" t="s">
@@ -18436,14 +18460,14 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR115" s="118" t="s">
+      <c r="AR115" s="534" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="116" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A116" s="457"/>
       <c r="B116" s="454"/>
-      <c r="C116" s="482"/>
+      <c r="C116" s="493"/>
       <c r="D116" s="302"/>
       <c r="E116" s="125"/>
       <c r="F116" s="244"/>
@@ -18524,14 +18548,14 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
-      <c r="AR116" s="52" t="s">
+      <c r="AR116" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="117" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A117" s="457"/>
       <c r="B117" s="454"/>
-      <c r="C117" s="482"/>
+      <c r="C117" s="493"/>
       <c r="D117" s="302"/>
       <c r="E117" s="125"/>
       <c r="F117" s="244"/>
@@ -18612,14 +18636,14 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
-      <c r="AR117" s="37" t="s">
+      <c r="AR117" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="118" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A118" s="457"/>
       <c r="B118" s="454"/>
-      <c r="C118" s="482"/>
+      <c r="C118" s="493"/>
       <c r="D118" s="302"/>
       <c r="E118" s="126"/>
       <c r="F118" s="245"/>
@@ -18700,7 +18724,7 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
-      <c r="AR118" s="66" t="s">
+      <c r="AR118" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18711,7 +18735,7 @@
       <c r="B119" s="454" t="s">
         <v>930</v>
       </c>
-      <c r="C119" s="482"/>
+      <c r="C119" s="493"/>
       <c r="D119" s="302" t="s">
         <v>742</v>
       </c>
@@ -18824,14 +18848,14 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
-      <c r="AR119" s="33" t="s">
+      <c r="AR119" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="120" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A120" s="457"/>
       <c r="B120" s="454"/>
-      <c r="C120" s="482"/>
+      <c r="C120" s="493"/>
       <c r="D120" s="302"/>
       <c r="E120" s="125"/>
       <c r="F120" s="244"/>
@@ -18912,14 +18936,14 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
-      <c r="AR120" s="52" t="s">
+      <c r="AR120" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="121" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A121" s="457"/>
       <c r="B121" s="454"/>
-      <c r="C121" s="482"/>
+      <c r="C121" s="493"/>
       <c r="D121" s="302"/>
       <c r="E121" s="125"/>
       <c r="F121" s="244"/>
@@ -19000,14 +19024,14 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
-      <c r="AR121" s="37" t="s">
+      <c r="AR121" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="122" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="457"/>
       <c r="B122" s="454"/>
-      <c r="C122" s="483"/>
+      <c r="C122" s="494"/>
       <c r="D122" s="315"/>
       <c r="E122" s="129"/>
       <c r="F122" s="246"/>
@@ -19088,7 +19112,7 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
-      <c r="AR122" s="51" t="s">
+      <c r="AR122" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19099,7 +19123,7 @@
       <c r="B123" s="454" t="s">
         <v>931</v>
       </c>
-      <c r="C123" s="484">
+      <c r="C123" s="495">
         <v>72</v>
       </c>
       <c r="D123" s="302" t="s">
@@ -19214,14 +19238,14 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
-      <c r="AR123" s="33" t="s">
+      <c r="AR123" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="124" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A124" s="457"/>
       <c r="B124" s="454"/>
-      <c r="C124" s="485"/>
+      <c r="C124" s="496"/>
       <c r="D124" s="302"/>
       <c r="E124" s="125"/>
       <c r="F124" s="244"/>
@@ -19302,14 +19326,14 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
-      <c r="AR124" s="37" t="s">
+      <c r="AR124" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="125" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A125" s="457"/>
       <c r="B125" s="454"/>
-      <c r="C125" s="485"/>
+      <c r="C125" s="496"/>
       <c r="D125" s="302"/>
       <c r="E125" s="125"/>
       <c r="F125" s="244"/>
@@ -19390,14 +19414,14 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
-      <c r="AR125" s="52" t="s">
+      <c r="AR125" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="126" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A126" s="457"/>
       <c r="B126" s="454"/>
-      <c r="C126" s="485"/>
+      <c r="C126" s="496"/>
       <c r="D126" s="302"/>
       <c r="E126" s="125"/>
       <c r="F126" s="244"/>
@@ -19478,14 +19502,14 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
-      <c r="AR126" s="37" t="s">
+      <c r="AR126" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="127" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A127" s="457"/>
       <c r="B127" s="454"/>
-      <c r="C127" s="485"/>
+      <c r="C127" s="496"/>
       <c r="D127" s="302"/>
       <c r="E127" s="126"/>
       <c r="F127" s="245"/>
@@ -19566,7 +19590,7 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
-      <c r="AR127" s="66" t="s">
+      <c r="AR127" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19577,7 +19601,7 @@
       <c r="B128" s="454" t="s">
         <v>932</v>
       </c>
-      <c r="C128" s="485"/>
+      <c r="C128" s="496"/>
       <c r="D128" s="302" t="s">
         <v>742</v>
       </c>
@@ -19694,14 +19718,14 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
-      <c r="AR128" s="33" t="s">
+      <c r="AR128" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="129" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A129" s="457"/>
       <c r="B129" s="454"/>
-      <c r="C129" s="485"/>
+      <c r="C129" s="496"/>
       <c r="D129" s="302"/>
       <c r="E129" s="125"/>
       <c r="F129" s="244"/>
@@ -19786,14 +19810,14 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
-      <c r="AR129" s="52" t="s">
+      <c r="AR129" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="130" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A130" s="457"/>
       <c r="B130" s="454"/>
-      <c r="C130" s="485"/>
+      <c r="C130" s="496"/>
       <c r="D130" s="302"/>
       <c r="E130" s="125"/>
       <c r="F130" s="244"/>
@@ -19878,14 +19902,14 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
-      <c r="AR130" s="37" t="s">
+      <c r="AR130" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="131" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="457"/>
       <c r="B131" s="454"/>
-      <c r="C131" s="486"/>
+      <c r="C131" s="497"/>
       <c r="D131" s="315"/>
       <c r="E131" s="129"/>
       <c r="F131" s="246"/>
@@ -19962,7 +19986,7 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
-      <c r="AR131" s="51" t="s">
+      <c r="AR131" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19973,7 +19997,7 @@
       <c r="B132" s="454" t="s">
         <v>933</v>
       </c>
-      <c r="C132" s="484">
+      <c r="C132" s="495">
         <v>73</v>
       </c>
       <c r="D132" s="302" t="s">
@@ -20090,14 +20114,14 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR132" s="118" t="s">
+      <c r="AR132" s="534" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="133" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A133" s="457"/>
       <c r="B133" s="454"/>
-      <c r="C133" s="485"/>
+      <c r="C133" s="496"/>
       <c r="D133" s="302"/>
       <c r="E133" s="125"/>
       <c r="F133" s="244"/>
@@ -20178,14 +20202,14 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
-      <c r="AR133" s="52" t="s">
+      <c r="AR133" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="134" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A134" s="457"/>
       <c r="B134" s="454"/>
-      <c r="C134" s="485"/>
+      <c r="C134" s="496"/>
       <c r="D134" s="302"/>
       <c r="E134" s="125"/>
       <c r="F134" s="244"/>
@@ -20266,14 +20290,14 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
-      <c r="AR134" s="37" t="s">
+      <c r="AR134" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="135" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A135" s="457"/>
       <c r="B135" s="454"/>
-      <c r="C135" s="485"/>
+      <c r="C135" s="496"/>
       <c r="D135" s="302"/>
       <c r="E135" s="126"/>
       <c r="F135" s="245"/>
@@ -20354,7 +20378,7 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
-      <c r="AR135" s="66" t="s">
+      <c r="AR135" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20365,7 +20389,7 @@
       <c r="B136" s="454" t="s">
         <v>934</v>
       </c>
-      <c r="C136" s="485"/>
+      <c r="C136" s="496"/>
       <c r="D136" s="302" t="s">
         <v>742</v>
       </c>
@@ -20480,14 +20504,14 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
-      <c r="AR136" s="33" t="s">
+      <c r="AR136" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="137" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A137" s="457"/>
       <c r="B137" s="454"/>
-      <c r="C137" s="485"/>
+      <c r="C137" s="496"/>
       <c r="D137" s="302"/>
       <c r="E137" s="125"/>
       <c r="F137" s="244"/>
@@ -20568,14 +20592,14 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
-      <c r="AR137" s="37" t="s">
+      <c r="AR137" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="138" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A138" s="457"/>
       <c r="B138" s="454"/>
-      <c r="C138" s="485"/>
+      <c r="C138" s="496"/>
       <c r="D138" s="302"/>
       <c r="E138" s="125"/>
       <c r="F138" s="244"/>
@@ -20656,14 +20680,14 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
-      <c r="AR138" s="52" t="s">
+      <c r="AR138" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="139" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A139" s="457"/>
       <c r="B139" s="454"/>
-      <c r="C139" s="485"/>
+      <c r="C139" s="496"/>
       <c r="D139" s="302"/>
       <c r="E139" s="125"/>
       <c r="F139" s="244"/>
@@ -20744,14 +20768,14 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
-      <c r="AR139" s="37" t="s">
+      <c r="AR139" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="140" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="457"/>
       <c r="B140" s="454"/>
-      <c r="C140" s="486"/>
+      <c r="C140" s="497"/>
       <c r="D140" s="315"/>
       <c r="E140" s="129"/>
       <c r="F140" s="246"/>
@@ -20830,7 +20854,7 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
-      <c r="AR140" s="51" t="s">
+      <c r="AR140" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20841,7 +20865,7 @@
       <c r="B141" s="454" t="s">
         <v>935</v>
       </c>
-      <c r="C141" s="487">
+      <c r="C141" s="498">
         <v>74</v>
       </c>
       <c r="D141" s="302" t="s">
@@ -20956,14 +20980,14 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
-      <c r="AR141" s="33" t="s">
+      <c r="AR141" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="142" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A142" s="457"/>
       <c r="B142" s="454"/>
-      <c r="C142" s="488"/>
+      <c r="C142" s="499"/>
       <c r="D142" s="303"/>
       <c r="E142" s="125"/>
       <c r="F142" s="244"/>
@@ -21044,14 +21068,14 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
-      <c r="AR142" s="37" t="s">
+      <c r="AR142" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="143" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A143" s="457"/>
       <c r="B143" s="454"/>
-      <c r="C143" s="488"/>
+      <c r="C143" s="499"/>
       <c r="D143" s="303"/>
       <c r="E143" s="125"/>
       <c r="F143" s="244"/>
@@ -21132,14 +21156,14 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
-      <c r="AR143" s="52" t="s">
+      <c r="AR143" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="144" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A144" s="457"/>
       <c r="B144" s="454"/>
-      <c r="C144" s="488"/>
+      <c r="C144" s="499"/>
       <c r="D144" s="303"/>
       <c r="E144" s="125"/>
       <c r="F144" s="244"/>
@@ -21220,14 +21244,14 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
-      <c r="AR144" s="37" t="s">
+      <c r="AR144" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="145" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A145" s="457"/>
       <c r="B145" s="454"/>
-      <c r="C145" s="488"/>
+      <c r="C145" s="499"/>
       <c r="D145" s="303"/>
       <c r="E145" s="126"/>
       <c r="F145" s="245"/>
@@ -21308,7 +21332,7 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
-      <c r="AR145" s="66" t="s">
+      <c r="AR145" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21319,7 +21343,7 @@
       <c r="B146" s="454" t="s">
         <v>936</v>
       </c>
-      <c r="C146" s="488"/>
+      <c r="C146" s="499"/>
       <c r="D146" s="302" t="s">
         <v>742</v>
       </c>
@@ -21434,14 +21458,14 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
-      <c r="AR146" s="33" t="s">
+      <c r="AR146" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="147" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A147" s="457"/>
       <c r="B147" s="454"/>
-      <c r="C147" s="488"/>
+      <c r="C147" s="499"/>
       <c r="D147" s="303"/>
       <c r="E147" s="125"/>
       <c r="F147" s="244"/>
@@ -21522,14 +21546,14 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
-      <c r="AR147" s="52" t="s">
+      <c r="AR147" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="148" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A148" s="457"/>
       <c r="B148" s="454"/>
-      <c r="C148" s="488"/>
+      <c r="C148" s="499"/>
       <c r="D148" s="303"/>
       <c r="E148" s="125"/>
       <c r="F148" s="244"/>
@@ -21610,14 +21634,14 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
-      <c r="AR148" s="37" t="s">
+      <c r="AR148" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="149" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="457"/>
       <c r="B149" s="454"/>
-      <c r="C149" s="489"/>
+      <c r="C149" s="500"/>
       <c r="D149" s="316"/>
       <c r="E149" s="129"/>
       <c r="F149" s="246"/>
@@ -21698,7 +21722,7 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
-      <c r="AR149" s="51" t="s">
+      <c r="AR149" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21709,7 +21733,7 @@
       <c r="B150" s="454" t="s">
         <v>937</v>
       </c>
-      <c r="C150" s="484">
+      <c r="C150" s="495">
         <v>75</v>
       </c>
       <c r="D150" s="302" t="s">
@@ -21824,14 +21848,14 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
-      <c r="AR150" s="33" t="s">
+      <c r="AR150" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="151" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A151" s="457"/>
       <c r="B151" s="454"/>
-      <c r="C151" s="485"/>
+      <c r="C151" s="496"/>
       <c r="D151" s="302"/>
       <c r="E151" s="125"/>
       <c r="F151" s="244"/>
@@ -21912,14 +21936,14 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
-      <c r="AR151" s="52" t="s">
+      <c r="AR151" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="152" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A152" s="457"/>
       <c r="B152" s="454"/>
-      <c r="C152" s="485"/>
+      <c r="C152" s="496"/>
       <c r="D152" s="302"/>
       <c r="E152" s="125"/>
       <c r="F152" s="244"/>
@@ -22000,14 +22024,14 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
-      <c r="AR152" s="37" t="s">
+      <c r="AR152" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="153" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A153" s="457"/>
       <c r="B153" s="454"/>
-      <c r="C153" s="485"/>
+      <c r="C153" s="496"/>
       <c r="D153" s="302"/>
       <c r="E153" s="126"/>
       <c r="F153" s="245"/>
@@ -22088,7 +22112,7 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
-      <c r="AR153" s="66" t="s">
+      <c r="AR153" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22099,7 +22123,7 @@
       <c r="B154" s="454" t="s">
         <v>938</v>
       </c>
-      <c r="C154" s="485"/>
+      <c r="C154" s="496"/>
       <c r="D154" s="302" t="s">
         <v>742</v>
       </c>
@@ -22212,14 +22236,14 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
-      <c r="AR154" s="33" t="s">
+      <c r="AR154" s="529" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="155" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A155" s="457"/>
       <c r="B155" s="454"/>
-      <c r="C155" s="485"/>
+      <c r="C155" s="496"/>
       <c r="D155" s="302"/>
       <c r="E155" s="125"/>
       <c r="F155" s="244"/>
@@ -22300,14 +22324,14 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
-      <c r="AR155" s="37" t="s">
+      <c r="AR155" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="156" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A156" s="457"/>
       <c r="B156" s="454"/>
-      <c r="C156" s="485"/>
+      <c r="C156" s="496"/>
       <c r="D156" s="302"/>
       <c r="E156" s="125"/>
       <c r="F156" s="244"/>
@@ -22388,14 +22412,14 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
-      <c r="AR156" s="52" t="s">
+      <c r="AR156" s="532" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="157" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A157" s="457"/>
       <c r="B157" s="454"/>
-      <c r="C157" s="485"/>
+      <c r="C157" s="496"/>
       <c r="D157" s="302"/>
       <c r="E157" s="125"/>
       <c r="F157" s="244"/>
@@ -22476,14 +22500,14 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
-      <c r="AR157" s="37" t="s">
+      <c r="AR157" s="530" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="158" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="457"/>
       <c r="B158" s="454"/>
-      <c r="C158" s="486"/>
+      <c r="C158" s="497"/>
       <c r="D158" s="315"/>
       <c r="E158" s="129"/>
       <c r="F158" s="246"/>
@@ -22562,7 +22586,7 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
-      <c r="AR158" s="51" t="s">
+      <c r="AR158" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22573,7 +22597,7 @@
       <c r="B159" s="454" t="s">
         <v>939</v>
       </c>
-      <c r="C159" s="490">
+      <c r="C159" s="501">
         <v>81</v>
       </c>
       <c r="D159" s="304" t="s">
@@ -22690,14 +22714,14 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
-      <c r="AR159" s="33" t="s">
+      <c r="AR159" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="160" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A160" s="457"/>
       <c r="B160" s="454"/>
-      <c r="C160" s="491"/>
+      <c r="C160" s="502"/>
       <c r="D160" s="304"/>
       <c r="E160" s="137"/>
       <c r="F160" s="247"/>
@@ -22778,14 +22802,14 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
-      <c r="AR160" s="52" t="s">
+      <c r="AR160" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="161" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A161" s="457"/>
       <c r="B161" s="454"/>
-      <c r="C161" s="491"/>
+      <c r="C161" s="502"/>
       <c r="D161" s="304"/>
       <c r="E161" s="137"/>
       <c r="F161" s="247"/>
@@ -22866,14 +22890,14 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
-      <c r="AR161" s="37" t="s">
+      <c r="AR161" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="162" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A162" s="457"/>
       <c r="B162" s="454"/>
-      <c r="C162" s="491"/>
+      <c r="C162" s="502"/>
       <c r="D162" s="304"/>
       <c r="E162" s="138"/>
       <c r="F162" s="248"/>
@@ -22954,7 +22978,7 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
-      <c r="AR162" s="66" t="s">
+      <c r="AR162" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22965,7 +22989,7 @@
       <c r="B163" s="454" t="s">
         <v>940</v>
       </c>
-      <c r="C163" s="491"/>
+      <c r="C163" s="502"/>
       <c r="D163" s="304" t="s">
         <v>743</v>
       </c>
@@ -23080,14 +23104,14 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
-      <c r="AR163" s="33" t="s">
+      <c r="AR163" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="164" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A164" s="457"/>
       <c r="B164" s="454"/>
-      <c r="C164" s="491"/>
+      <c r="C164" s="502"/>
       <c r="D164" s="304"/>
       <c r="E164" s="137"/>
       <c r="F164" s="247"/>
@@ -23168,14 +23192,14 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
-      <c r="AR164" s="52" t="s">
+      <c r="AR164" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="165" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A165" s="457"/>
       <c r="B165" s="454"/>
-      <c r="C165" s="491"/>
+      <c r="C165" s="502"/>
       <c r="D165" s="304"/>
       <c r="E165" s="137"/>
       <c r="F165" s="247"/>
@@ -23256,14 +23280,14 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
-      <c r="AR165" s="37" t="s">
+      <c r="AR165" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="166" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A166" s="457"/>
       <c r="B166" s="454"/>
-      <c r="C166" s="491"/>
+      <c r="C166" s="502"/>
       <c r="D166" s="304"/>
       <c r="E166" s="138"/>
       <c r="F166" s="248"/>
@@ -23344,7 +23368,7 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
-      <c r="AR166" s="66" t="s">
+      <c r="AR166" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23355,7 +23379,7 @@
       <c r="B167" s="454" t="s">
         <v>941</v>
       </c>
-      <c r="C167" s="491"/>
+      <c r="C167" s="502"/>
       <c r="D167" s="304" t="s">
         <v>743</v>
       </c>
@@ -23470,14 +23494,14 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
-      <c r="AR167" s="33" t="s">
+      <c r="AR167" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="168" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A168" s="457"/>
       <c r="B168" s="454"/>
-      <c r="C168" s="491"/>
+      <c r="C168" s="502"/>
       <c r="D168" s="304"/>
       <c r="E168" s="137"/>
       <c r="F168" s="247"/>
@@ -23558,14 +23582,14 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
-      <c r="AR168" s="52" t="s">
+      <c r="AR168" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="169" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A169" s="457"/>
       <c r="B169" s="454"/>
-      <c r="C169" s="491"/>
+      <c r="C169" s="502"/>
       <c r="D169" s="304"/>
       <c r="E169" s="137"/>
       <c r="F169" s="247"/>
@@ -23646,14 +23670,14 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
-      <c r="AR169" s="103" t="s">
+      <c r="AR169" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="170" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="457"/>
       <c r="B170" s="454"/>
-      <c r="C170" s="492"/>
+      <c r="C170" s="503"/>
       <c r="D170" s="317"/>
       <c r="E170" s="141"/>
       <c r="F170" s="249"/>
@@ -23734,7 +23758,7 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
-      <c r="AR170" s="51" t="s">
+      <c r="AR170" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23745,7 +23769,7 @@
       <c r="B171" s="454" t="s">
         <v>942</v>
       </c>
-      <c r="C171" s="493">
+      <c r="C171" s="504">
         <v>82</v>
       </c>
       <c r="D171" s="304" t="s">
@@ -23862,14 +23886,14 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR171" s="118" t="s">
+      <c r="AR171" s="534" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="172" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A172" s="457"/>
       <c r="B172" s="454"/>
-      <c r="C172" s="494"/>
+      <c r="C172" s="505"/>
       <c r="D172" s="304"/>
       <c r="E172" s="137"/>
       <c r="F172" s="247"/>
@@ -23950,14 +23974,14 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
-      <c r="AR172" s="37" t="s">
+      <c r="AR172" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="173" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A173" s="457"/>
       <c r="B173" s="454"/>
-      <c r="C173" s="494"/>
+      <c r="C173" s="505"/>
       <c r="D173" s="304"/>
       <c r="E173" s="137"/>
       <c r="F173" s="247"/>
@@ -24038,14 +24062,14 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
-      <c r="AR173" s="52" t="s">
+      <c r="AR173" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="174" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A174" s="457"/>
       <c r="B174" s="454"/>
-      <c r="C174" s="494"/>
+      <c r="C174" s="505"/>
       <c r="D174" s="304"/>
       <c r="E174" s="138"/>
       <c r="F174" s="248"/>
@@ -24128,7 +24152,7 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
-      <c r="AR174" s="66" t="s">
+      <c r="AR174" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24139,7 +24163,7 @@
       <c r="B175" s="454" t="s">
         <v>943</v>
       </c>
-      <c r="C175" s="494"/>
+      <c r="C175" s="505"/>
       <c r="D175" s="304" t="s">
         <v>743</v>
       </c>
@@ -24254,14 +24278,14 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
-      <c r="AR175" s="33" t="s">
+      <c r="AR175" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="176" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A176" s="457"/>
       <c r="B176" s="454"/>
-      <c r="C176" s="494"/>
+      <c r="C176" s="505"/>
       <c r="D176" s="304"/>
       <c r="E176" s="137"/>
       <c r="F176" s="247"/>
@@ -24348,14 +24372,14 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
-      <c r="AR176" s="37" t="s">
+      <c r="AR176" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="177" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A177" s="457"/>
       <c r="B177" s="454"/>
-      <c r="C177" s="494"/>
+      <c r="C177" s="505"/>
       <c r="D177" s="304"/>
       <c r="E177" s="137"/>
       <c r="F177" s="247"/>
@@ -24440,14 +24464,14 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
-      <c r="AR177" s="52" t="s">
+      <c r="AR177" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="178" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A178" s="457"/>
       <c r="B178" s="454"/>
-      <c r="C178" s="494"/>
+      <c r="C178" s="505"/>
       <c r="D178" s="304"/>
       <c r="E178" s="138"/>
       <c r="F178" s="248"/>
@@ -24530,7 +24554,7 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
-      <c r="AR178" s="66" t="s">
+      <c r="AR178" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24541,7 +24565,7 @@
       <c r="B179" s="454" t="s">
         <v>944</v>
       </c>
-      <c r="C179" s="494"/>
+      <c r="C179" s="505"/>
       <c r="D179" s="304" t="s">
         <v>743</v>
       </c>
@@ -24656,14 +24680,14 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR179" s="118" t="s">
+      <c r="AR179" s="534" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="180" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A180" s="457"/>
       <c r="B180" s="454"/>
-      <c r="C180" s="494"/>
+      <c r="C180" s="505"/>
       <c r="D180" s="304"/>
       <c r="E180" s="137"/>
       <c r="F180" s="247"/>
@@ -24744,14 +24768,14 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
-      <c r="AR180" s="37" t="s">
+      <c r="AR180" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="181" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A181" s="457"/>
       <c r="B181" s="454"/>
-      <c r="C181" s="494"/>
+      <c r="C181" s="505"/>
       <c r="D181" s="304"/>
       <c r="E181" s="137"/>
       <c r="F181" s="247"/>
@@ -24832,14 +24856,14 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
-      <c r="AR181" s="52" t="s">
+      <c r="AR181" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="182" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A182" s="457"/>
       <c r="B182" s="454"/>
-      <c r="C182" s="494"/>
+      <c r="C182" s="505"/>
       <c r="D182" s="304"/>
       <c r="E182" s="137"/>
       <c r="F182" s="247"/>
@@ -24920,14 +24944,14 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
-      <c r="AR182" s="37" t="s">
+      <c r="AR182" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="183" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="457"/>
       <c r="B183" s="454"/>
-      <c r="C183" s="495"/>
+      <c r="C183" s="506"/>
       <c r="D183" s="317"/>
       <c r="E183" s="141"/>
       <c r="F183" s="249"/>
@@ -25008,7 +25032,7 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
-      <c r="AR183" s="51" t="s">
+      <c r="AR183" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25019,7 +25043,7 @@
       <c r="B184" s="454">
         <v>831</v>
       </c>
-      <c r="C184" s="493">
+      <c r="C184" s="504">
         <v>83</v>
       </c>
       <c r="D184" s="304" t="s">
@@ -25136,14 +25160,14 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
-      <c r="AR184" s="33" t="s">
+      <c r="AR184" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="185" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A185" s="457"/>
       <c r="B185" s="454"/>
-      <c r="C185" s="494"/>
+      <c r="C185" s="505"/>
       <c r="D185" s="304"/>
       <c r="E185" s="137"/>
       <c r="F185" s="247"/>
@@ -25226,14 +25250,14 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
-      <c r="AR185" s="37" t="s">
+      <c r="AR185" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="186" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A186" s="457"/>
       <c r="B186" s="454"/>
-      <c r="C186" s="494"/>
+      <c r="C186" s="505"/>
       <c r="D186" s="304"/>
       <c r="E186" s="137"/>
       <c r="F186" s="247"/>
@@ -25314,14 +25338,14 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
-      <c r="AR186" s="37" t="s">
+      <c r="AR186" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="187" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A187" s="457"/>
       <c r="B187" s="454"/>
-      <c r="C187" s="494"/>
+      <c r="C187" s="505"/>
       <c r="D187" s="304"/>
       <c r="E187" s="138"/>
       <c r="F187" s="248"/>
@@ -25404,7 +25428,7 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
-      <c r="AR187" s="119" t="s">
+      <c r="AR187" s="535" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25415,7 +25439,7 @@
       <c r="B188" s="454" t="s">
         <v>945</v>
       </c>
-      <c r="C188" s="494"/>
+      <c r="C188" s="505"/>
       <c r="D188" s="304" t="s">
         <v>743</v>
       </c>
@@ -25528,14 +25552,14 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
-      <c r="AR188" s="33" t="s">
+      <c r="AR188" s="529" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="189" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A189" s="457"/>
       <c r="B189" s="454"/>
-      <c r="C189" s="494"/>
+      <c r="C189" s="505"/>
       <c r="D189" s="304"/>
       <c r="E189" s="137"/>
       <c r="F189" s="247"/>
@@ -25616,14 +25640,14 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
-      <c r="AR189" s="52" t="s">
+      <c r="AR189" s="532" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="190" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A190" s="457"/>
       <c r="B190" s="454"/>
-      <c r="C190" s="494"/>
+      <c r="C190" s="505"/>
       <c r="D190" s="304"/>
       <c r="E190" s="137"/>
       <c r="F190" s="247"/>
@@ -25704,14 +25728,14 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
-      <c r="AR190" s="37" t="s">
+      <c r="AR190" s="530" t="s">
         <v>977</v>
       </c>
     </row>
     <row r="191" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="457"/>
       <c r="B191" s="454"/>
-      <c r="C191" s="495"/>
+      <c r="C191" s="506"/>
       <c r="D191" s="317"/>
       <c r="E191" s="141"/>
       <c r="F191" s="249"/>
@@ -25790,7 +25814,7 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
-      <c r="AR191" s="51" t="s">
+      <c r="AR191" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25801,7 +25825,7 @@
       <c r="B192" s="454" t="s">
         <v>946</v>
       </c>
-      <c r="C192" s="496">
+      <c r="C192" s="507">
         <v>91</v>
       </c>
       <c r="D192" s="305" t="s">
@@ -25916,14 +25940,14 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
-      <c r="AR192" s="33" t="s">
+      <c r="AR192" s="529" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="193" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A193" s="457"/>
       <c r="B193" s="454"/>
-      <c r="C193" s="497"/>
+      <c r="C193" s="508"/>
       <c r="D193" s="305"/>
       <c r="E193" s="152"/>
       <c r="F193" s="250"/>
@@ -26004,14 +26028,14 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
-      <c r="AR193" s="52" t="s">
+      <c r="AR193" s="532" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="194" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A194" s="457"/>
       <c r="B194" s="454"/>
-      <c r="C194" s="497"/>
+      <c r="C194" s="508"/>
       <c r="D194" s="305"/>
       <c r="E194" s="152"/>
       <c r="F194" s="250"/>
@@ -26092,14 +26116,14 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
-      <c r="AR194" s="37" t="s">
+      <c r="AR194" s="530" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="195" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A195" s="457"/>
       <c r="B195" s="454"/>
-      <c r="C195" s="497"/>
+      <c r="C195" s="508"/>
       <c r="D195" s="305"/>
       <c r="E195" s="153"/>
       <c r="F195" s="251"/>
@@ -26180,7 +26204,7 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
-      <c r="AR195" s="66" t="s">
+      <c r="AR195" s="533" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26191,7 +26215,7 @@
       <c r="B196" s="454" t="s">
         <v>947</v>
       </c>
-      <c r="C196" s="497"/>
+      <c r="C196" s="508"/>
       <c r="D196" s="305" t="s">
         <v>744</v>
       </c>
@@ -26304,14 +26328,14 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
-      <c r="AR196" s="33" t="s">
+      <c r="AR196" s="529" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="197" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A197" s="457"/>
       <c r="B197" s="454"/>
-      <c r="C197" s="497"/>
+      <c r="C197" s="508"/>
       <c r="D197" s="305"/>
       <c r="E197" s="152"/>
       <c r="F197" s="250"/>
@@ -26392,14 +26416,14 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
-      <c r="AR197" s="52" t="s">
+      <c r="AR197" s="532" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="198" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A198" s="457"/>
       <c r="B198" s="454"/>
-      <c r="C198" s="497"/>
+      <c r="C198" s="508"/>
       <c r="D198" s="305"/>
       <c r="E198" s="152"/>
       <c r="F198" s="250"/>
@@ -26480,14 +26504,14 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
-      <c r="AR198" s="37" t="s">
+      <c r="AR198" s="530" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="199" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="457"/>
       <c r="B199" s="454"/>
-      <c r="C199" s="498"/>
+      <c r="C199" s="509"/>
       <c r="D199" s="318"/>
       <c r="E199" s="155"/>
       <c r="F199" s="252"/>
@@ -26568,7 +26592,7 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
-      <c r="AR199" s="51" t="s">
+      <c r="AR199" s="531" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26579,7 +26603,7 @@
       <c r="B200" s="454" t="s">
         <v>948</v>
       </c>
-      <c r="C200" s="499">
+      <c r="C200" s="510">
         <v>100</v>
       </c>
       <c r="D200" s="306" t="s">
@@ -26698,14 +26722,14 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
-      <c r="AR200" s="33" t="s">
+      <c r="AR200" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="201" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A201" s="457"/>
       <c r="B201" s="454"/>
-      <c r="C201" s="500"/>
+      <c r="C201" s="511"/>
       <c r="D201" s="306"/>
       <c r="E201" s="163"/>
       <c r="F201" s="253"/>
@@ -26790,14 +26814,14 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
-      <c r="AR201" s="37" t="s">
+      <c r="AR201" s="530" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="202" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A202" s="457"/>
       <c r="B202" s="454"/>
-      <c r="C202" s="500"/>
+      <c r="C202" s="511"/>
       <c r="D202" s="306"/>
       <c r="E202" s="164"/>
       <c r="F202" s="254"/>
@@ -26880,7 +26904,7 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
-      <c r="AR202" s="119" t="s">
+      <c r="AR202" s="535" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26891,7 +26915,7 @@
       <c r="B203" s="454" t="s">
         <v>949</v>
       </c>
-      <c r="C203" s="500"/>
+      <c r="C203" s="511"/>
       <c r="D203" s="306" t="s">
         <v>745</v>
       </c>
@@ -27010,14 +27034,14 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
-      <c r="AR203" s="33" t="s">
+      <c r="AR203" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="204" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A204" s="457"/>
       <c r="B204" s="454"/>
-      <c r="C204" s="500"/>
+      <c r="C204" s="511"/>
       <c r="D204" s="306"/>
       <c r="E204" s="163"/>
       <c r="F204" s="253"/>
@@ -27102,14 +27126,14 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
-      <c r="AR204" s="37" t="s">
+      <c r="AR204" s="530" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="205" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A205" s="457"/>
       <c r="B205" s="454"/>
-      <c r="C205" s="500"/>
+      <c r="C205" s="511"/>
       <c r="D205" s="306"/>
       <c r="E205" s="164"/>
       <c r="F205" s="254"/>
@@ -27192,7 +27216,7 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
-      <c r="AR205" s="66" t="s">
+      <c r="AR205" s="533" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27203,7 +27227,7 @@
       <c r="B206" s="454" t="s">
         <v>950</v>
       </c>
-      <c r="C206" s="500"/>
+      <c r="C206" s="511"/>
       <c r="D206" s="306" t="s">
         <v>745</v>
       </c>
@@ -27322,14 +27346,14 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
-      <c r="AR206" s="33" t="s">
+      <c r="AR206" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="207" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A207" s="457"/>
       <c r="B207" s="454"/>
-      <c r="C207" s="500"/>
+      <c r="C207" s="511"/>
       <c r="D207" s="306"/>
       <c r="E207" s="163"/>
       <c r="F207" s="253"/>
@@ -27410,14 +27434,14 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
-      <c r="AR207" s="37" t="s">
+      <c r="AR207" s="530" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="208" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="457"/>
       <c r="B208" s="454"/>
-      <c r="C208" s="501"/>
+      <c r="C208" s="512"/>
       <c r="D208" s="319"/>
       <c r="E208" s="166"/>
       <c r="F208" s="255"/>
@@ -27502,7 +27526,7 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
-      <c r="AR208" s="51" t="s">
+      <c r="AR208" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27513,7 +27537,7 @@
       <c r="B209" s="454" t="s">
         <v>951</v>
       </c>
-      <c r="C209" s="475">
+      <c r="C209" s="489">
         <v>101</v>
       </c>
       <c r="D209" s="306" t="s">
@@ -27634,14 +27658,14 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
-      <c r="AR209" s="33" t="s">
+      <c r="AR209" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="210" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A210" s="457"/>
       <c r="B210" s="454"/>
-      <c r="C210" s="476"/>
+      <c r="C210" s="490"/>
       <c r="D210" s="306"/>
       <c r="E210" s="163"/>
       <c r="F210" s="253"/>
@@ -27726,14 +27750,14 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
-      <c r="AR210" s="52" t="s">
+      <c r="AR210" s="532" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="211" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A211" s="457"/>
       <c r="B211" s="454"/>
-      <c r="C211" s="476"/>
+      <c r="C211" s="490"/>
       <c r="D211" s="306"/>
       <c r="E211" s="163"/>
       <c r="F211" s="253"/>
@@ -27818,14 +27842,14 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
-      <c r="AR211" s="37" t="s">
+      <c r="AR211" s="530" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="212" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A212" s="457"/>
       <c r="B212" s="454"/>
-      <c r="C212" s="476"/>
+      <c r="C212" s="490"/>
       <c r="D212" s="306"/>
       <c r="E212" s="164"/>
       <c r="F212" s="254"/>
@@ -27908,7 +27932,7 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
-      <c r="AR212" s="66" t="s">
+      <c r="AR212" s="533" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27919,7 +27943,7 @@
       <c r="B213" s="454" t="s">
         <v>952</v>
       </c>
-      <c r="C213" s="476"/>
+      <c r="C213" s="490"/>
       <c r="D213" s="306" t="s">
         <v>745</v>
       </c>
@@ -28038,14 +28062,14 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
-      <c r="AR213" s="33" t="s">
+      <c r="AR213" s="529" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="214" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A214" s="457"/>
       <c r="B214" s="454"/>
-      <c r="C214" s="476"/>
+      <c r="C214" s="490"/>
       <c r="D214" s="306"/>
       <c r="E214" s="163"/>
       <c r="F214" s="253"/>
@@ -28130,14 +28154,14 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
-      <c r="AR214" s="37" t="s">
+      <c r="AR214" s="530" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="215" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="457"/>
       <c r="B215" s="454"/>
-      <c r="C215" s="477"/>
+      <c r="C215" s="491"/>
       <c r="D215" s="319"/>
       <c r="E215" s="166"/>
       <c r="F215" s="255"/>
@@ -28222,7 +28246,7 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
-      <c r="AR215" s="51" t="s">
+      <c r="AR215" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28233,7 +28257,7 @@
       <c r="B216" s="454" t="s">
         <v>953</v>
       </c>
-      <c r="C216" s="459">
+      <c r="C216" s="513">
         <v>102</v>
       </c>
       <c r="D216" s="307" t="s">
@@ -28354,14 +28378,14 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
-      <c r="AR216" s="33" t="s">
+      <c r="AR216" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="217" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A217" s="457"/>
       <c r="B217" s="454"/>
-      <c r="C217" s="460"/>
+      <c r="C217" s="514"/>
       <c r="D217" s="307"/>
       <c r="E217" s="174"/>
       <c r="F217" s="256"/>
@@ -28446,14 +28470,14 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
-      <c r="AR217" s="52" t="s">
+      <c r="AR217" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="218" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A218" s="457"/>
       <c r="B218" s="454"/>
-      <c r="C218" s="460"/>
+      <c r="C218" s="514"/>
       <c r="D218" s="307"/>
       <c r="E218" s="174"/>
       <c r="F218" s="256"/>
@@ -28538,14 +28562,14 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
-      <c r="AR218" s="37" t="s">
+      <c r="AR218" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="219" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="457"/>
       <c r="B219" s="454"/>
-      <c r="C219" s="461"/>
+      <c r="C219" s="515"/>
       <c r="D219" s="320"/>
       <c r="E219" s="175"/>
       <c r="F219" s="257"/>
@@ -28630,7 +28654,7 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
-      <c r="AR219" s="51" t="s">
+      <c r="AR219" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28641,7 +28665,7 @@
       <c r="B220" s="454" t="s">
         <v>954</v>
       </c>
-      <c r="C220" s="459">
+      <c r="C220" s="513">
         <v>103</v>
       </c>
       <c r="D220" s="307" t="s">
@@ -28758,14 +28782,14 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
-      <c r="AR220" s="33" t="s">
+      <c r="AR220" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="221" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A221" s="457"/>
       <c r="B221" s="454"/>
-      <c r="C221" s="460"/>
+      <c r="C221" s="514"/>
       <c r="D221" s="307"/>
       <c r="E221" s="174"/>
       <c r="F221" s="256"/>
@@ -28848,14 +28872,14 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
-      <c r="AR221" s="37" t="s">
+      <c r="AR221" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="222" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A222" s="457"/>
       <c r="B222" s="454"/>
-      <c r="C222" s="460"/>
+      <c r="C222" s="514"/>
       <c r="D222" s="307"/>
       <c r="E222" s="178"/>
       <c r="F222" s="258"/>
@@ -28938,7 +28962,7 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
-      <c r="AR222" s="66" t="s">
+      <c r="AR222" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28949,7 +28973,7 @@
       <c r="B223" s="454" t="s">
         <v>955</v>
       </c>
-      <c r="C223" s="460"/>
+      <c r="C223" s="514"/>
       <c r="D223" s="307" t="s">
         <v>745</v>
       </c>
@@ -29068,14 +29092,14 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
-      <c r="AR223" s="33" t="s">
+      <c r="AR223" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="224" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A224" s="457"/>
       <c r="B224" s="454"/>
-      <c r="C224" s="460"/>
+      <c r="C224" s="514"/>
       <c r="D224" s="307"/>
       <c r="E224" s="174"/>
       <c r="F224" s="256"/>
@@ -29160,14 +29184,14 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
-      <c r="AR224" s="52" t="s">
+      <c r="AR224" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="225" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A225" s="457"/>
       <c r="B225" s="454"/>
-      <c r="C225" s="460"/>
+      <c r="C225" s="514"/>
       <c r="D225" s="307"/>
       <c r="E225" s="174"/>
       <c r="F225" s="256"/>
@@ -29252,14 +29276,14 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
-      <c r="AR225" s="37" t="s">
+      <c r="AR225" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="226" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="457"/>
       <c r="B226" s="454"/>
-      <c r="C226" s="461"/>
+      <c r="C226" s="515"/>
       <c r="D226" s="320"/>
       <c r="E226" s="175"/>
       <c r="F226" s="257"/>
@@ -29338,7 +29362,7 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
-      <c r="AR226" s="51" t="s">
+      <c r="AR226" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29349,7 +29373,7 @@
       <c r="B227" s="454" t="s">
         <v>956</v>
       </c>
-      <c r="C227" s="459">
+      <c r="C227" s="513">
         <v>104</v>
       </c>
       <c r="D227" s="307" t="s">
@@ -29466,14 +29490,14 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
-      <c r="AR227" s="33" t="s">
+      <c r="AR227" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="228" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A228" s="457"/>
       <c r="B228" s="454"/>
-      <c r="C228" s="460"/>
+      <c r="C228" s="514"/>
       <c r="D228" s="307"/>
       <c r="E228" s="174"/>
       <c r="F228" s="256"/>
@@ -29554,14 +29578,14 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
-      <c r="AR228" s="52" t="s">
+      <c r="AR228" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="229" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A229" s="457"/>
       <c r="B229" s="454"/>
-      <c r="C229" s="460"/>
+      <c r="C229" s="514"/>
       <c r="D229" s="307"/>
       <c r="E229" s="174"/>
       <c r="F229" s="256"/>
@@ -29642,14 +29666,14 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
-      <c r="AR229" s="37" t="s">
+      <c r="AR229" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="230" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A230" s="457"/>
       <c r="B230" s="454"/>
-      <c r="C230" s="460"/>
+      <c r="C230" s="514"/>
       <c r="D230" s="307"/>
       <c r="E230" s="178"/>
       <c r="F230" s="258"/>
@@ -29730,7 +29754,7 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
-      <c r="AR230" s="66" t="s">
+      <c r="AR230" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29741,7 +29765,7 @@
       <c r="B231" s="454" t="s">
         <v>957</v>
       </c>
-      <c r="C231" s="460"/>
+      <c r="C231" s="514"/>
       <c r="D231" s="307" t="s">
         <v>745</v>
       </c>
@@ -29856,14 +29880,14 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
-      <c r="AR231" s="33" t="s">
+      <c r="AR231" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="232" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A232" s="457"/>
       <c r="B232" s="454"/>
-      <c r="C232" s="460"/>
+      <c r="C232" s="514"/>
       <c r="D232" s="307"/>
       <c r="E232" s="174"/>
       <c r="F232" s="256"/>
@@ -29944,14 +29968,14 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
-      <c r="AR232" s="52" t="s">
+      <c r="AR232" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="233" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A233" s="457"/>
       <c r="B233" s="454"/>
-      <c r="C233" s="460"/>
+      <c r="C233" s="514"/>
       <c r="D233" s="307"/>
       <c r="E233" s="174"/>
       <c r="F233" s="256"/>
@@ -30032,14 +30056,14 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
-      <c r="AR233" s="37" t="s">
+      <c r="AR233" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="234" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="457"/>
       <c r="B234" s="454"/>
-      <c r="C234" s="461"/>
+      <c r="C234" s="515"/>
       <c r="D234" s="320"/>
       <c r="E234" s="175"/>
       <c r="F234" s="257"/>
@@ -30116,7 +30140,7 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
-      <c r="AR234" s="51" t="s">
+      <c r="AR234" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30127,7 +30151,7 @@
       <c r="B235" s="454" t="s">
         <v>958</v>
       </c>
-      <c r="C235" s="468">
+      <c r="C235" s="522">
         <v>105</v>
       </c>
       <c r="D235" s="308" t="s">
@@ -30244,14 +30268,14 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
-      <c r="AR235" s="33" t="s">
+      <c r="AR235" s="529" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="236" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A236" s="457"/>
       <c r="B236" s="454"/>
-      <c r="C236" s="469"/>
+      <c r="C236" s="523"/>
       <c r="D236" s="308"/>
       <c r="E236" s="185"/>
       <c r="F236" s="259"/>
@@ -30332,14 +30356,14 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
-      <c r="AR236" s="52" t="s">
+      <c r="AR236" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="237" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A237" s="457"/>
       <c r="B237" s="454"/>
-      <c r="C237" s="469"/>
+      <c r="C237" s="523"/>
       <c r="D237" s="308"/>
       <c r="E237" s="185"/>
       <c r="F237" s="259"/>
@@ -30420,14 +30444,14 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
-      <c r="AR237" s="37" t="s">
+      <c r="AR237" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="238" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="457"/>
       <c r="B238" s="454"/>
-      <c r="C238" s="470"/>
+      <c r="C238" s="524"/>
       <c r="D238" s="321"/>
       <c r="E238" s="186"/>
       <c r="F238" s="260"/>
@@ -30506,7 +30530,7 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
-      <c r="AR238" s="51" t="s">
+      <c r="AR238" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30517,7 +30541,7 @@
       <c r="B239" s="454" t="s">
         <v>959</v>
       </c>
-      <c r="C239" s="471">
+      <c r="C239" s="525">
         <v>106</v>
       </c>
       <c r="D239" s="308" t="s">
@@ -30634,14 +30658,14 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
-      <c r="AR239" s="33" t="s">
+      <c r="AR239" s="529" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="240" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A240" s="457"/>
       <c r="B240" s="454"/>
-      <c r="C240" s="472"/>
+      <c r="C240" s="526"/>
       <c r="D240" s="308"/>
       <c r="E240" s="185"/>
       <c r="F240" s="259"/>
@@ -30722,14 +30746,14 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
-      <c r="AR240" s="52" t="s">
+      <c r="AR240" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="241" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A241" s="457"/>
       <c r="B241" s="454"/>
-      <c r="C241" s="472"/>
+      <c r="C241" s="526"/>
       <c r="D241" s="308"/>
       <c r="E241" s="185"/>
       <c r="F241" s="259"/>
@@ -30810,14 +30834,14 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
-      <c r="AR241" s="37" t="s">
+      <c r="AR241" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="242" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A242" s="457"/>
       <c r="B242" s="454"/>
-      <c r="C242" s="472"/>
+      <c r="C242" s="526"/>
       <c r="D242" s="308"/>
       <c r="E242" s="189"/>
       <c r="F242" s="261"/>
@@ -30896,7 +30920,7 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
-      <c r="AR242" s="66" t="s">
+      <c r="AR242" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30907,7 +30931,7 @@
       <c r="B243" s="454" t="s">
         <v>960</v>
       </c>
-      <c r="C243" s="472"/>
+      <c r="C243" s="526"/>
       <c r="D243" s="308" t="s">
         <v>745</v>
       </c>
@@ -31022,14 +31046,14 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
-      <c r="AR243" s="33" t="s">
+      <c r="AR243" s="529" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="244" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A244" s="457"/>
       <c r="B244" s="454"/>
-      <c r="C244" s="472"/>
+      <c r="C244" s="526"/>
       <c r="D244" s="308"/>
       <c r="E244" s="185"/>
       <c r="F244" s="259"/>
@@ -31110,14 +31134,14 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
-      <c r="AR244" s="37" t="s">
+      <c r="AR244" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="245" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A245" s="457"/>
       <c r="B245" s="454"/>
-      <c r="C245" s="472"/>
+      <c r="C245" s="526"/>
       <c r="D245" s="308"/>
       <c r="E245" s="185"/>
       <c r="F245" s="259"/>
@@ -31198,14 +31222,14 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
-      <c r="AR245" s="52" t="s">
+      <c r="AR245" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="246" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A246" s="457"/>
       <c r="B246" s="454"/>
-      <c r="C246" s="472"/>
+      <c r="C246" s="526"/>
       <c r="D246" s="308"/>
       <c r="E246" s="185"/>
       <c r="F246" s="259"/>
@@ -31286,14 +31310,14 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
-      <c r="AR246" s="66" t="s">
+      <c r="AR246" s="533" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="247" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A247" s="457"/>
       <c r="B247" s="454"/>
-      <c r="C247" s="472"/>
+      <c r="C247" s="526"/>
       <c r="D247" s="308"/>
       <c r="E247" s="181"/>
       <c r="F247" s="181"/>
@@ -31380,7 +31404,7 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
-      <c r="AR247" s="33" t="s">
+      <c r="AR247" s="529" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31391,7 +31415,7 @@
       <c r="B248" s="454" t="s">
         <v>961</v>
       </c>
-      <c r="C248" s="473"/>
+      <c r="C248" s="527"/>
       <c r="D248" s="308" t="s">
         <v>745</v>
       </c>
@@ -31500,14 +31524,14 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
-      <c r="AR248" s="52" t="s">
+      <c r="AR248" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="249" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A249" s="457"/>
       <c r="B249" s="454"/>
-      <c r="C249" s="472"/>
+      <c r="C249" s="526"/>
       <c r="D249" s="308"/>
       <c r="E249" s="185"/>
       <c r="F249" s="259"/>
@@ -31590,14 +31614,14 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
-      <c r="AR249" s="52" t="s">
+      <c r="AR249" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="250" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A250" s="457"/>
       <c r="B250" s="454"/>
-      <c r="C250" s="472"/>
+      <c r="C250" s="526"/>
       <c r="D250" s="308"/>
       <c r="E250" s="185"/>
       <c r="F250" s="259"/>
@@ -31680,14 +31704,14 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
-      <c r="AR250" s="37" t="s">
+      <c r="AR250" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="251" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A251" s="457"/>
       <c r="B251" s="454"/>
-      <c r="C251" s="472"/>
+      <c r="C251" s="526"/>
       <c r="D251" s="308"/>
       <c r="E251" s="189"/>
       <c r="F251" s="261"/>
@@ -31770,7 +31794,7 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
-      <c r="AR251" s="66" t="s">
+      <c r="AR251" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31781,7 +31805,7 @@
       <c r="B252" s="454" t="s">
         <v>962</v>
       </c>
-      <c r="C252" s="472"/>
+      <c r="C252" s="526"/>
       <c r="D252" s="308" t="s">
         <v>745</v>
       </c>
@@ -31896,14 +31920,14 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
-      <c r="AR252" s="33" t="s">
+      <c r="AR252" s="529" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="253" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A253" s="457"/>
       <c r="B253" s="454"/>
-      <c r="C253" s="472"/>
+      <c r="C253" s="526"/>
       <c r="D253" s="308"/>
       <c r="E253" s="185"/>
       <c r="F253" s="259"/>
@@ -31984,14 +32008,14 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
-      <c r="AR253" s="37" t="s">
+      <c r="AR253" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="254" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A254" s="457"/>
       <c r="B254" s="454"/>
-      <c r="C254" s="472"/>
+      <c r="C254" s="526"/>
       <c r="D254" s="308"/>
       <c r="E254" s="185"/>
       <c r="F254" s="259"/>
@@ -32072,14 +32096,14 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
-      <c r="AR254" s="52" t="s">
+      <c r="AR254" s="532" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="255" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A255" s="457"/>
       <c r="B255" s="454"/>
-      <c r="C255" s="472"/>
+      <c r="C255" s="526"/>
       <c r="D255" s="308"/>
       <c r="E255" s="185"/>
       <c r="F255" s="259"/>
@@ -32160,14 +32184,14 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
-      <c r="AR255" s="37" t="s">
+      <c r="AR255" s="530" t="s">
         <v>981</v>
       </c>
     </row>
     <row r="256" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="457"/>
       <c r="B256" s="454"/>
-      <c r="C256" s="474"/>
+      <c r="C256" s="528"/>
       <c r="D256" s="321"/>
       <c r="E256" s="186"/>
       <c r="F256" s="260"/>
@@ -32248,7 +32272,7 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
-      <c r="AR256" s="51" t="s">
+      <c r="AR256" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32259,7 +32283,7 @@
       <c r="B257" s="454" t="s">
         <v>963</v>
       </c>
-      <c r="C257" s="459">
+      <c r="C257" s="513">
         <v>107</v>
       </c>
       <c r="D257" s="307" t="s">
@@ -32376,14 +32400,14 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
-      <c r="AR257" s="33" t="s">
+      <c r="AR257" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="258" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A258" s="457"/>
       <c r="B258" s="454"/>
-      <c r="C258" s="460"/>
+      <c r="C258" s="514"/>
       <c r="D258" s="307"/>
       <c r="E258" s="174"/>
       <c r="F258" s="256"/>
@@ -32466,14 +32490,14 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
-      <c r="AR258" s="52" t="s">
+      <c r="AR258" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="259" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A259" s="457"/>
       <c r="B259" s="454"/>
-      <c r="C259" s="460"/>
+      <c r="C259" s="514"/>
       <c r="D259" s="307"/>
       <c r="E259" s="174"/>
       <c r="F259" s="256"/>
@@ -32556,14 +32580,14 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
-      <c r="AR259" s="37" t="s">
+      <c r="AR259" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="260" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A260" s="457"/>
       <c r="B260" s="454"/>
-      <c r="C260" s="460"/>
+      <c r="C260" s="514"/>
       <c r="D260" s="307"/>
       <c r="E260" s="178"/>
       <c r="F260" s="258"/>
@@ -32644,7 +32668,7 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
-      <c r="AR260" s="66" t="s">
+      <c r="AR260" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32655,7 +32679,7 @@
       <c r="B261" s="454" t="s">
         <v>964</v>
       </c>
-      <c r="C261" s="460"/>
+      <c r="C261" s="514"/>
       <c r="D261" s="307" t="s">
         <v>745</v>
       </c>
@@ -32770,14 +32794,14 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
-      <c r="AR261" s="33" t="s">
+      <c r="AR261" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="262" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A262" s="457"/>
       <c r="B262" s="454"/>
-      <c r="C262" s="460"/>
+      <c r="C262" s="514"/>
       <c r="D262" s="307"/>
       <c r="E262" s="174"/>
       <c r="F262" s="256"/>
@@ -32856,14 +32880,14 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
-      <c r="AR262" s="37" t="s">
+      <c r="AR262" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="263" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="457"/>
       <c r="B263" s="454"/>
-      <c r="C263" s="461"/>
+      <c r="C263" s="515"/>
       <c r="D263" s="320"/>
       <c r="E263" s="175"/>
       <c r="F263" s="257"/>
@@ -32942,7 +32966,7 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
-      <c r="AR263" s="51" t="s">
+      <c r="AR263" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32953,7 +32977,7 @@
       <c r="B264" s="454" t="s">
         <v>965</v>
       </c>
-      <c r="C264" s="459">
+      <c r="C264" s="513">
         <v>108</v>
       </c>
       <c r="D264" s="307" t="s">
@@ -33072,14 +33096,14 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
-      <c r="AR264" s="33" t="s">
+      <c r="AR264" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="265" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A265" s="457"/>
       <c r="B265" s="454"/>
-      <c r="C265" s="460"/>
+      <c r="C265" s="514"/>
       <c r="D265" s="307"/>
       <c r="E265" s="174"/>
       <c r="F265" s="256"/>
@@ -33162,14 +33186,14 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
-      <c r="AR265" s="52" t="s">
+      <c r="AR265" s="532" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="266" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A266" s="457"/>
       <c r="B266" s="454"/>
-      <c r="C266" s="460"/>
+      <c r="C266" s="514"/>
       <c r="D266" s="307"/>
       <c r="E266" s="174"/>
       <c r="F266" s="256"/>
@@ -33252,14 +33276,14 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
-      <c r="AR266" s="37" t="s">
+      <c r="AR266" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="267" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="457"/>
       <c r="B267" s="454"/>
-      <c r="C267" s="461"/>
+      <c r="C267" s="515"/>
       <c r="D267" s="320"/>
       <c r="E267" s="175"/>
       <c r="F267" s="257"/>
@@ -33342,7 +33366,7 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
-      <c r="AR267" s="51" t="s">
+      <c r="AR267" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33353,7 +33377,7 @@
       <c r="B268" s="454" t="s">
         <v>966</v>
       </c>
-      <c r="C268" s="459">
+      <c r="C268" s="513">
         <v>109</v>
       </c>
       <c r="D268" s="307" t="s">
@@ -33474,14 +33498,14 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
-      <c r="AR268" s="33" t="s">
+      <c r="AR268" s="529" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="269" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A269" s="457"/>
       <c r="B269" s="454"/>
-      <c r="C269" s="460"/>
+      <c r="C269" s="514"/>
       <c r="D269" s="307"/>
       <c r="E269" s="174"/>
       <c r="F269" s="256"/>
@@ -33566,14 +33590,14 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
-      <c r="AR269" s="37" t="s">
+      <c r="AR269" s="530" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="270" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="457"/>
       <c r="B270" s="454"/>
-      <c r="C270" s="461"/>
+      <c r="C270" s="515"/>
       <c r="D270" s="320"/>
       <c r="E270" s="175"/>
       <c r="F270" s="257"/>
@@ -33658,7 +33682,7 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
-      <c r="AR270" s="51" t="s">
+      <c r="AR270" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33669,7 +33693,7 @@
       <c r="B271" s="454" t="s">
         <v>967</v>
       </c>
-      <c r="C271" s="462">
+      <c r="C271" s="516">
         <v>111</v>
       </c>
       <c r="D271" s="309" t="s">
@@ -33790,14 +33814,14 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
-      <c r="AR271" s="33" t="s">
+      <c r="AR271" s="529" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="272" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A272" s="457"/>
       <c r="B272" s="454"/>
-      <c r="C272" s="463"/>
+      <c r="C272" s="517"/>
       <c r="D272" s="309"/>
       <c r="E272" s="197"/>
       <c r="F272" s="262"/>
@@ -33880,14 +33904,14 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
-      <c r="AR272" s="37" t="s">
+      <c r="AR272" s="530" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="273" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A273" s="457"/>
       <c r="B273" s="454"/>
-      <c r="C273" s="463"/>
+      <c r="C273" s="517"/>
       <c r="D273" s="309"/>
       <c r="E273" s="198"/>
       <c r="F273" s="263"/>
@@ -33970,7 +33994,7 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
-      <c r="AR273" s="66" t="s">
+      <c r="AR273" s="533" t="s">
         <v>982</v>
       </c>
     </row>
@@ -33981,7 +34005,7 @@
       <c r="B274" s="454" t="s">
         <v>968</v>
       </c>
-      <c r="C274" s="463"/>
+      <c r="C274" s="517"/>
       <c r="D274" s="309" t="s">
         <v>746</v>
       </c>
@@ -34092,14 +34116,14 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
-      <c r="AR274" s="37" t="s">
+      <c r="AR274" s="530" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="275" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A275" s="457"/>
       <c r="B275" s="454"/>
-      <c r="C275" s="463"/>
+      <c r="C275" s="517"/>
       <c r="D275" s="309"/>
       <c r="E275" s="197"/>
       <c r="F275" s="262"/>
@@ -34188,14 +34212,14 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
-      <c r="AR275" s="33" t="s">
+      <c r="AR275" s="529" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="276" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A276" s="457"/>
       <c r="B276" s="454"/>
-      <c r="C276" s="463"/>
+      <c r="C276" s="517"/>
       <c r="D276" s="309"/>
       <c r="E276" s="197"/>
       <c r="F276" s="262"/>
@@ -34278,14 +34302,14 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
-      <c r="AR276" s="37" t="s">
+      <c r="AR276" s="530" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="277" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="457"/>
       <c r="B277" s="454"/>
-      <c r="C277" s="464"/>
+      <c r="C277" s="518"/>
       <c r="D277" s="322"/>
       <c r="E277" s="201"/>
       <c r="F277" s="264"/>
@@ -34368,7 +34392,7 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
-      <c r="AR277" s="51" t="s">
+      <c r="AR277" s="531" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34379,7 +34403,7 @@
       <c r="B278" s="454" t="s">
         <v>969</v>
       </c>
-      <c r="C278" s="465">
+      <c r="C278" s="519">
         <v>112</v>
       </c>
       <c r="D278" s="309" t="s">
@@ -34496,14 +34520,14 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
-      <c r="AR278" s="33" t="s">
+      <c r="AR278" s="529" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="279" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A279" s="457"/>
       <c r="B279" s="454"/>
-      <c r="C279" s="466"/>
+      <c r="C279" s="520"/>
       <c r="D279" s="309"/>
       <c r="E279" s="197"/>
       <c r="F279" s="262"/>
@@ -34584,14 +34608,14 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
-      <c r="AR279" s="52" t="s">
+      <c r="AR279" s="532" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="280" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A280" s="457"/>
       <c r="B280" s="454"/>
-      <c r="C280" s="466"/>
+      <c r="C280" s="520"/>
       <c r="D280" s="309"/>
       <c r="E280" s="197"/>
       <c r="F280" s="262"/>
@@ -34672,14 +34696,14 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
-      <c r="AR280" s="204" t="s">
+      <c r="AR280" s="532" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="281" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="458"/>
       <c r="B281" s="455"/>
-      <c r="C281" s="467"/>
+      <c r="C281" s="521"/>
       <c r="D281" s="322"/>
       <c r="E281" s="201"/>
       <c r="F281" s="264"/>
@@ -34760,18 +34784,34 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
-      <c r="AR281" s="205" t="s">
+      <c r="AR281" s="536" t="s">
         <v>983</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C12"/>
-    <mergeCell ref="C13:C22"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C264:C267"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="C271:C277"/>
+    <mergeCell ref="C278:C281"/>
+    <mergeCell ref="C216:C219"/>
+    <mergeCell ref="C220:C226"/>
+    <mergeCell ref="C227:C234"/>
+    <mergeCell ref="C235:C238"/>
+    <mergeCell ref="C239:C256"/>
+    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C209:C215"/>
+    <mergeCell ref="C106:C114"/>
+    <mergeCell ref="C115:C122"/>
+    <mergeCell ref="C123:C131"/>
+    <mergeCell ref="C132:C140"/>
+    <mergeCell ref="C141:C149"/>
+    <mergeCell ref="C150:C158"/>
+    <mergeCell ref="C159:C170"/>
+    <mergeCell ref="C171:C183"/>
+    <mergeCell ref="C184:C191"/>
+    <mergeCell ref="C192:C199"/>
+    <mergeCell ref="C200:C208"/>
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="C35:C43"/>
     <mergeCell ref="C44:C46"/>
@@ -34784,28 +34824,12 @@
     <mergeCell ref="C83:C85"/>
     <mergeCell ref="C86:C97"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C209:C215"/>
-    <mergeCell ref="C106:C114"/>
-    <mergeCell ref="C115:C122"/>
-    <mergeCell ref="C123:C131"/>
-    <mergeCell ref="C132:C140"/>
-    <mergeCell ref="C141:C149"/>
-    <mergeCell ref="C150:C158"/>
-    <mergeCell ref="C159:C170"/>
-    <mergeCell ref="C171:C183"/>
-    <mergeCell ref="C184:C191"/>
-    <mergeCell ref="C192:C199"/>
-    <mergeCell ref="C200:C208"/>
-    <mergeCell ref="C264:C267"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="C271:C277"/>
-    <mergeCell ref="C278:C281"/>
-    <mergeCell ref="C216:C219"/>
-    <mergeCell ref="C220:C226"/>
-    <mergeCell ref="C227:C234"/>
-    <mergeCell ref="C235:C238"/>
-    <mergeCell ref="C239:C256"/>
-    <mergeCell ref="C257:C263"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C12"/>
+    <mergeCell ref="C13:C22"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="C26:C30"/>
   </mergeCells>
   <phoneticPr fontId="39" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
+++ b/70_Typterres_Alsace_v04_2018_publipostageREVU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resoca-my.sharepoint.com/personal/martin_troup_grandest_chambagri_fr/Documents/TypTerre/Publisher/Alsace/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBD2F744-E413-4338-98E7-C3781CB965C0}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="11_6358DAA78F86C58B0F3FBDB3787C52EC37105F0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF77EB7-4CBC-455A-86D3-7E8633262681}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4478,7 +4478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="537">
+  <cellXfs count="539">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5854,28 +5854,34 @@
     <xf numFmtId="0" fontId="3" fillId="32" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6230,7 +6236,7 @@
     <col min="32" max="32" width="11.5546875" style="206"/>
     <col min="34" max="35" width="11.5546875" style="206"/>
     <col min="41" max="43" width="11.5546875" style="206"/>
-    <col min="44" max="44" width="19.6640625" style="207" customWidth="1"/>
+    <col min="44" max="44" width="19.6640625" style="538" customWidth="1"/>
     <col min="262" max="262" width="19.21875" customWidth="1"/>
     <col min="263" max="263" width="51.109375" customWidth="1"/>
     <col min="264" max="264" width="25.5546875" customWidth="1"/>
@@ -7182,7 +7188,7 @@
       <c r="AQ1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AR1" s="15" t="s">
+      <c r="AR1" s="529" t="s">
         <v>984</v>
       </c>
     </row>
@@ -7314,7 +7320,7 @@
       <c r="AQ2" s="33">
         <v>57</v>
       </c>
-      <c r="AR2" s="529" t="s">
+      <c r="AR2" s="530" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7406,7 +7412,7 @@
       <c r="AO3" s="36"/>
       <c r="AP3" s="37"/>
       <c r="AQ3" s="37"/>
-      <c r="AR3" s="530" t="s">
+      <c r="AR3" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7498,7 +7504,7 @@
       <c r="AO4" s="50"/>
       <c r="AP4" s="51"/>
       <c r="AQ4" s="51"/>
-      <c r="AR4" s="531" t="s">
+      <c r="AR4" s="532" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7628,7 +7634,7 @@
       <c r="AQ5" s="33">
         <v>147</v>
       </c>
-      <c r="AR5" s="529" t="s">
+      <c r="AR5" s="530" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7718,7 +7724,7 @@
       <c r="AO6" s="52"/>
       <c r="AP6" s="52"/>
       <c r="AQ6" s="52"/>
-      <c r="AR6" s="532" t="s">
+      <c r="AR6" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7808,7 +7814,7 @@
       <c r="AO7" s="36"/>
       <c r="AP7" s="37"/>
       <c r="AQ7" s="37"/>
-      <c r="AR7" s="530" t="s">
+      <c r="AR7" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -7896,7 +7902,7 @@
       <c r="AO8" s="65"/>
       <c r="AP8" s="66"/>
       <c r="AQ8" s="66"/>
-      <c r="AR8" s="533" t="s">
+      <c r="AR8" s="534" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8022,7 +8028,7 @@
       <c r="AQ9" s="33">
         <v>179</v>
       </c>
-      <c r="AR9" s="529" t="s">
+      <c r="AR9" s="530" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8110,7 +8116,7 @@
       <c r="AO10" s="52"/>
       <c r="AP10" s="52"/>
       <c r="AQ10" s="52"/>
-      <c r="AR10" s="532" t="s">
+      <c r="AR10" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8198,7 +8204,7 @@
       <c r="AO11" s="36"/>
       <c r="AP11" s="37"/>
       <c r="AQ11" s="37"/>
-      <c r="AR11" s="530" t="s">
+      <c r="AR11" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8284,7 +8290,7 @@
       <c r="AO12" s="50"/>
       <c r="AP12" s="51"/>
       <c r="AQ12" s="51"/>
-      <c r="AR12" s="531" t="s">
+      <c r="AR12" s="532" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8412,7 +8418,7 @@
       <c r="AQ13" s="33">
         <v>175</v>
       </c>
-      <c r="AR13" s="529" t="s">
+      <c r="AR13" s="530" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8500,7 +8506,7 @@
       <c r="AO14" s="36"/>
       <c r="AP14" s="37"/>
       <c r="AQ14" s="37"/>
-      <c r="AR14" s="530" t="s">
+      <c r="AR14" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8588,7 +8594,7 @@
       <c r="AO15" s="52"/>
       <c r="AP15" s="52"/>
       <c r="AQ15" s="52"/>
-      <c r="AR15" s="532" t="s">
+      <c r="AR15" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8676,7 +8682,7 @@
       <c r="AO16" s="36"/>
       <c r="AP16" s="37"/>
       <c r="AQ16" s="37"/>
-      <c r="AR16" s="530" t="s">
+      <c r="AR16" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8762,7 +8768,7 @@
       <c r="AO17" s="65"/>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="66"/>
-      <c r="AR17" s="533" t="s">
+      <c r="AR17" s="534" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8886,7 +8892,7 @@
       <c r="AQ18" s="33">
         <v>84</v>
       </c>
-      <c r="AR18" s="529" t="s">
+      <c r="AR18" s="530" t="s">
         <v>970</v>
       </c>
     </row>
@@ -8974,7 +8980,7 @@
       <c r="AO19" s="36"/>
       <c r="AP19" s="37"/>
       <c r="AQ19" s="37"/>
-      <c r="AR19" s="530" t="s">
+      <c r="AR19" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9062,7 +9068,7 @@
       <c r="AO20" s="52"/>
       <c r="AP20" s="52"/>
       <c r="AQ20" s="52"/>
-      <c r="AR20" s="532" t="s">
+      <c r="AR20" s="533" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9150,7 +9156,7 @@
       <c r="AO21" s="36"/>
       <c r="AP21" s="37"/>
       <c r="AQ21" s="37"/>
-      <c r="AR21" s="530" t="s">
+      <c r="AR21" s="531" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9238,7 +9244,7 @@
       <c r="AO22" s="50"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" s="531" t="s">
+      <c r="AR22" s="532" t="s">
         <v>970</v>
       </c>
     </row>
@@ -9370,7 +9376,7 @@
       <c r="AQ23" s="33">
         <v>70</v>
       </c>
-      <c r="AR23" s="529" t="s">
+      <c r="AR23" s="530" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9462,7 +9468,7 @@
       <c r="AO24" s="36"/>
       <c r="AP24" s="37"/>
       <c r="AQ24" s="37"/>
-      <c r="AR24" s="530" t="s">
+      <c r="AR24" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9554,7 +9560,7 @@
       <c r="AO25" s="50"/>
       <c r="AP25" s="51"/>
       <c r="AQ25" s="51"/>
-      <c r="AR25" s="531" t="s">
+      <c r="AR25" s="532" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9682,7 +9688,7 @@
       <c r="AQ26" s="33">
         <v>148</v>
       </c>
-      <c r="AR26" s="529" t="s">
+      <c r="AR26" s="530" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9770,7 +9776,7 @@
       <c r="AO27" s="36"/>
       <c r="AP27" s="37"/>
       <c r="AQ27" s="37"/>
-      <c r="AR27" s="530" t="s">
+      <c r="AR27" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9858,7 +9864,7 @@
       <c r="AO28" s="52"/>
       <c r="AP28" s="52"/>
       <c r="AQ28" s="52"/>
-      <c r="AR28" s="532" t="s">
+      <c r="AR28" s="533" t="s">
         <v>971</v>
       </c>
     </row>
@@ -9948,7 +9954,7 @@
       <c r="AO29" s="36"/>
       <c r="AP29" s="37"/>
       <c r="AQ29" s="37"/>
-      <c r="AR29" s="530" t="s">
+      <c r="AR29" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10034,7 +10040,7 @@
       <c r="AO30" s="50"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" s="531" t="s">
+      <c r="AR30" s="532" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10166,7 +10172,7 @@
       <c r="AQ31" s="33">
         <v>116</v>
       </c>
-      <c r="AR31" s="529" t="s">
+      <c r="AR31" s="530" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10258,7 +10264,7 @@
       <c r="AO32" s="52"/>
       <c r="AP32" s="52"/>
       <c r="AQ32" s="52"/>
-      <c r="AR32" s="532" t="s">
+      <c r="AR32" s="533" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10350,7 +10356,7 @@
       <c r="AO33" s="36"/>
       <c r="AP33" s="37"/>
       <c r="AQ33" s="37"/>
-      <c r="AR33" s="530" t="s">
+      <c r="AR33" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10442,7 +10448,7 @@
       <c r="AO34" s="50"/>
       <c r="AP34" s="51"/>
       <c r="AQ34" s="51"/>
-      <c r="AR34" s="531" t="s">
+      <c r="AR34" s="532" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10568,7 +10574,7 @@
       <c r="AQ35" s="33">
         <v>72</v>
       </c>
-      <c r="AR35" s="529" t="s">
+      <c r="AR35" s="530" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10656,7 +10662,7 @@
       <c r="AO36" s="52"/>
       <c r="AP36" s="52"/>
       <c r="AQ36" s="52"/>
-      <c r="AR36" s="532" t="s">
+      <c r="AR36" s="533" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10744,7 +10750,7 @@
       <c r="AO37" s="36"/>
       <c r="AP37" s="37"/>
       <c r="AQ37" s="37"/>
-      <c r="AR37" s="530" t="s">
+      <c r="AR37" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10832,7 +10838,7 @@
       <c r="AO38" s="65"/>
       <c r="AP38" s="66"/>
       <c r="AQ38" s="66"/>
-      <c r="AR38" s="533" t="s">
+      <c r="AR38" s="534" t="s">
         <v>971</v>
       </c>
     </row>
@@ -10958,7 +10964,7 @@
       <c r="AQ39" s="33">
         <v>105</v>
       </c>
-      <c r="AR39" s="529" t="s">
+      <c r="AR39" s="530" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11046,7 +11052,7 @@
       <c r="AO40" s="36"/>
       <c r="AP40" s="37"/>
       <c r="AQ40" s="37"/>
-      <c r="AR40" s="530" t="s">
+      <c r="AR40" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11134,7 +11140,7 @@
       <c r="AO41" s="52"/>
       <c r="AP41" s="52"/>
       <c r="AQ41" s="52"/>
-      <c r="AR41" s="532" t="s">
+      <c r="AR41" s="533" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11222,7 +11228,7 @@
       <c r="AO42" s="36"/>
       <c r="AP42" s="37"/>
       <c r="AQ42" s="37"/>
-      <c r="AR42" s="530" t="s">
+      <c r="AR42" s="531" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11308,7 +11314,7 @@
       <c r="AO43" s="50"/>
       <c r="AP43" s="51"/>
       <c r="AQ43" s="51"/>
-      <c r="AR43" s="531" t="s">
+      <c r="AR43" s="532" t="s">
         <v>971</v>
       </c>
     </row>
@@ -11438,7 +11444,7 @@
       <c r="AQ44" s="33">
         <v>77</v>
       </c>
-      <c r="AR44" s="529" t="s">
+      <c r="AR44" s="530" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11530,7 +11536,7 @@
       <c r="AO45" s="36"/>
       <c r="AP45" s="37"/>
       <c r="AQ45" s="37"/>
-      <c r="AR45" s="530" t="s">
+      <c r="AR45" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11622,7 +11628,7 @@
       <c r="AO46" s="50"/>
       <c r="AP46" s="51"/>
       <c r="AQ46" s="51"/>
-      <c r="AR46" s="531" t="s">
+      <c r="AR46" s="532" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11752,7 +11758,7 @@
       <c r="AQ47" s="33">
         <v>219</v>
       </c>
-      <c r="AR47" s="529" t="s">
+      <c r="AR47" s="530" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11842,7 +11848,7 @@
       <c r="AO48" s="52"/>
       <c r="AP48" s="52"/>
       <c r="AQ48" s="52"/>
-      <c r="AR48" s="532" t="s">
+      <c r="AR48" s="533" t="s">
         <v>972</v>
       </c>
     </row>
@@ -11932,7 +11938,7 @@
       <c r="AO49" s="36"/>
       <c r="AP49" s="37"/>
       <c r="AQ49" s="37"/>
-      <c r="AR49" s="530" t="s">
+      <c r="AR49" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12022,7 +12028,7 @@
       <c r="AO50" s="50"/>
       <c r="AP50" s="51"/>
       <c r="AQ50" s="51"/>
-      <c r="AR50" s="531" t="s">
+      <c r="AR50" s="532" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12154,7 +12160,7 @@
       <c r="AQ51" s="33">
         <v>163</v>
       </c>
-      <c r="AR51" s="529" t="s">
+      <c r="AR51" s="530" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12246,7 +12252,7 @@
       <c r="AO52" s="52"/>
       <c r="AP52" s="52"/>
       <c r="AQ52" s="52"/>
-      <c r="AR52" s="532" t="s">
+      <c r="AR52" s="533" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12334,7 +12340,7 @@
       <c r="AO53" s="36"/>
       <c r="AP53" s="37"/>
       <c r="AQ53" s="37"/>
-      <c r="AR53" s="530" t="s">
+      <c r="AR53" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12420,7 +12426,7 @@
       <c r="AO54" s="50"/>
       <c r="AP54" s="51"/>
       <c r="AQ54" s="51"/>
-      <c r="AR54" s="531" t="s">
+      <c r="AR54" s="532" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12546,7 +12552,7 @@
       <c r="AQ55" s="33">
         <v>150</v>
       </c>
-      <c r="AR55" s="529" t="s">
+      <c r="AR55" s="530" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12634,7 +12640,7 @@
       <c r="AO56" s="36"/>
       <c r="AP56" s="37"/>
       <c r="AQ56" s="37"/>
-      <c r="AR56" s="530" t="s">
+      <c r="AR56" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12722,7 +12728,7 @@
       <c r="AO57" s="52"/>
       <c r="AP57" s="52"/>
       <c r="AQ57" s="52"/>
-      <c r="AR57" s="532" t="s">
+      <c r="AR57" s="533" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12810,7 +12816,7 @@
       <c r="AO58" s="36"/>
       <c r="AP58" s="37"/>
       <c r="AQ58" s="37"/>
-      <c r="AR58" s="530" t="s">
+      <c r="AR58" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -12898,7 +12904,7 @@
       <c r="AO59" s="65"/>
       <c r="AP59" s="66"/>
       <c r="AQ59" s="66"/>
-      <c r="AR59" s="533" t="s">
+      <c r="AR59" s="534" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13024,7 +13030,7 @@
       <c r="AQ60" s="33">
         <v>137</v>
       </c>
-      <c r="AR60" s="529" t="s">
+      <c r="AR60" s="530" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13112,7 +13118,7 @@
       <c r="AO61" s="52"/>
       <c r="AP61" s="52"/>
       <c r="AQ61" s="52"/>
-      <c r="AR61" s="532" t="s">
+      <c r="AR61" s="533" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13200,7 +13206,7 @@
       <c r="AO62" s="36"/>
       <c r="AP62" s="37"/>
       <c r="AQ62" s="37"/>
-      <c r="AR62" s="530" t="s">
+      <c r="AR62" s="531" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13288,7 +13294,7 @@
       <c r="AO63" s="50"/>
       <c r="AP63" s="51"/>
       <c r="AQ63" s="51"/>
-      <c r="AR63" s="531" t="s">
+      <c r="AR63" s="532" t="s">
         <v>972</v>
       </c>
     </row>
@@ -13418,7 +13424,7 @@
       <c r="AQ64" s="33">
         <v>63</v>
       </c>
-      <c r="AR64" s="529" t="s">
+      <c r="AR64" s="530" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13510,7 +13516,7 @@
       <c r="AO65" s="36"/>
       <c r="AP65" s="37"/>
       <c r="AQ65" s="37"/>
-      <c r="AR65" s="530" t="s">
+      <c r="AR65" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13602,7 +13608,7 @@
       <c r="AO66" s="50"/>
       <c r="AP66" s="51"/>
       <c r="AQ66" s="51"/>
-      <c r="AR66" s="531" t="s">
+      <c r="AR66" s="532" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13732,7 +13738,7 @@
       <c r="AQ67" s="33">
         <v>55</v>
       </c>
-      <c r="AR67" s="529" t="s">
+      <c r="AR67" s="530" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13822,7 +13828,7 @@
       <c r="AO68" s="36"/>
       <c r="AP68" s="37"/>
       <c r="AQ68" s="37"/>
-      <c r="AR68" s="530" t="s">
+      <c r="AR68" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -13912,7 +13918,7 @@
       <c r="AO69" s="65"/>
       <c r="AP69" s="66"/>
       <c r="AQ69" s="66"/>
-      <c r="AR69" s="533" t="s">
+      <c r="AR69" s="534" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14036,7 +14042,7 @@
       <c r="AQ70" s="33">
         <v>137</v>
       </c>
-      <c r="AR70" s="529" t="s">
+      <c r="AR70" s="530" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14124,7 +14130,7 @@
       <c r="AO71" s="52"/>
       <c r="AP71" s="52"/>
       <c r="AQ71" s="52"/>
-      <c r="AR71" s="532" t="s">
+      <c r="AR71" s="533" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14212,7 +14218,7 @@
       <c r="AO72" s="36"/>
       <c r="AP72" s="103"/>
       <c r="AQ72" s="103"/>
-      <c r="AR72" s="530" t="s">
+      <c r="AR72" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14300,7 +14306,7 @@
       <c r="AO73" s="36"/>
       <c r="AP73" s="37"/>
       <c r="AQ73" s="37"/>
-      <c r="AR73" s="530" t="s">
+      <c r="AR73" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14388,7 +14394,7 @@
       <c r="AO74" s="50"/>
       <c r="AP74" s="51"/>
       <c r="AQ74" s="51"/>
-      <c r="AR74" s="531" t="s">
+      <c r="AR74" s="532" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14516,7 +14522,7 @@
       <c r="AQ75" s="33">
         <v>114</v>
       </c>
-      <c r="AR75" s="529" t="s">
+      <c r="AR75" s="530" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14604,7 +14610,7 @@
       <c r="AO76" s="36"/>
       <c r="AP76" s="37"/>
       <c r="AQ76" s="37"/>
-      <c r="AR76" s="530" t="s">
+      <c r="AR76" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14692,7 +14698,7 @@
       <c r="AO77" s="52"/>
       <c r="AP77" s="52"/>
       <c r="AQ77" s="52"/>
-      <c r="AR77" s="532" t="s">
+      <c r="AR77" s="533" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14780,7 +14786,7 @@
       <c r="AO78" s="36"/>
       <c r="AP78" s="37"/>
       <c r="AQ78" s="37"/>
-      <c r="AR78" s="530" t="s">
+      <c r="AR78" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14868,7 +14874,7 @@
       <c r="AO79" s="65"/>
       <c r="AP79" s="66"/>
       <c r="AQ79" s="66"/>
-      <c r="AR79" s="533" t="s">
+      <c r="AR79" s="534" t="s">
         <v>973</v>
       </c>
     </row>
@@ -14990,7 +14996,7 @@
       <c r="AQ80" s="33">
         <v>41</v>
       </c>
-      <c r="AR80" s="529" t="s">
+      <c r="AR80" s="530" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15078,7 +15084,7 @@
       <c r="AO81" s="36"/>
       <c r="AP81" s="37"/>
       <c r="AQ81" s="37"/>
-      <c r="AR81" s="530" t="s">
+      <c r="AR81" s="531" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15164,7 +15170,7 @@
       <c r="AO82" s="50"/>
       <c r="AP82" s="51"/>
       <c r="AQ82" s="51"/>
-      <c r="AR82" s="531" t="s">
+      <c r="AR82" s="532" t="s">
         <v>973</v>
       </c>
     </row>
@@ -15296,7 +15302,7 @@
       <c r="AQ83" s="33">
         <v>64</v>
       </c>
-      <c r="AR83" s="529" t="s">
+      <c r="AR83" s="530" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15388,7 +15394,7 @@
       <c r="AO84" s="36"/>
       <c r="AP84" s="37"/>
       <c r="AQ84" s="37"/>
-      <c r="AR84" s="530" t="s">
+      <c r="AR84" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15478,7 +15484,7 @@
       <c r="AO85" s="50"/>
       <c r="AP85" s="51"/>
       <c r="AQ85" s="51"/>
-      <c r="AR85" s="531" t="s">
+      <c r="AR85" s="532" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15608,7 +15614,7 @@
       <c r="AQ86" s="33">
         <v>157</v>
       </c>
-      <c r="AR86" s="529" t="s">
+      <c r="AR86" s="530" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15700,7 +15706,7 @@
       <c r="AO87" s="52"/>
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52"/>
-      <c r="AR87" s="532" t="s">
+      <c r="AR87" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15792,7 +15798,7 @@
       <c r="AO88" s="36"/>
       <c r="AP88" s="37"/>
       <c r="AQ88" s="37"/>
-      <c r="AR88" s="530" t="s">
+      <c r="AR88" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -15884,7 +15890,7 @@
       <c r="AO89" s="65"/>
       <c r="AP89" s="66"/>
       <c r="AQ89" s="66"/>
-      <c r="AR89" s="533" t="s">
+      <c r="AR89" s="534" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16012,7 +16018,7 @@
       <c r="AQ90" s="33">
         <v>230</v>
       </c>
-      <c r="AR90" s="529" t="s">
+      <c r="AR90" s="530" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16102,7 +16108,7 @@
       <c r="AO91" s="52"/>
       <c r="AP91" s="52"/>
       <c r="AQ91" s="52"/>
-      <c r="AR91" s="532" t="s">
+      <c r="AR91" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16192,7 +16198,7 @@
       <c r="AO92" s="36"/>
       <c r="AP92" s="37"/>
       <c r="AQ92" s="37"/>
-      <c r="AR92" s="530" t="s">
+      <c r="AR92" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16282,7 +16288,7 @@
       <c r="AO93" s="65"/>
       <c r="AP93" s="66"/>
       <c r="AQ93" s="66"/>
-      <c r="AR93" s="533" t="s">
+      <c r="AR93" s="534" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16410,7 +16416,7 @@
       <c r="AQ94" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR94" s="534" t="s">
+      <c r="AR94" s="535" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16500,7 +16506,7 @@
       <c r="AO95" s="52"/>
       <c r="AP95" s="52"/>
       <c r="AQ95" s="52"/>
-      <c r="AR95" s="532" t="s">
+      <c r="AR95" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16590,7 +16596,7 @@
       <c r="AO96" s="36"/>
       <c r="AP96" s="37"/>
       <c r="AQ96" s="37"/>
-      <c r="AR96" s="530" t="s">
+      <c r="AR96" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16680,7 +16686,7 @@
       <c r="AO97" s="50"/>
       <c r="AP97" s="51"/>
       <c r="AQ97" s="51"/>
-      <c r="AR97" s="531" t="s">
+      <c r="AR97" s="532" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16808,7 +16814,7 @@
       <c r="AQ98" s="33">
         <v>151</v>
       </c>
-      <c r="AR98" s="529" t="s">
+      <c r="AR98" s="530" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16898,7 +16904,7 @@
       <c r="AO99" s="52"/>
       <c r="AP99" s="52"/>
       <c r="AQ99" s="52"/>
-      <c r="AR99" s="532" t="s">
+      <c r="AR99" s="533" t="s">
         <v>974</v>
       </c>
     </row>
@@ -16986,7 +16992,7 @@
       <c r="AO100" s="36"/>
       <c r="AP100" s="37"/>
       <c r="AQ100" s="37"/>
-      <c r="AR100" s="530" t="s">
+      <c r="AR100" s="531" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17076,7 +17082,7 @@
       <c r="AO101" s="50"/>
       <c r="AP101" s="51"/>
       <c r="AQ101" s="51"/>
-      <c r="AR101" s="531" t="s">
+      <c r="AR101" s="532" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17200,7 +17206,7 @@
       <c r="AQ102" s="33">
         <v>154</v>
       </c>
-      <c r="AR102" s="529" t="s">
+      <c r="AR102" s="530" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17288,7 +17294,7 @@
       <c r="AO103" s="52"/>
       <c r="AP103" s="52"/>
       <c r="AQ103" s="52"/>
-      <c r="AR103" s="532" t="s">
+      <c r="AR103" s="533" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17376,7 +17382,7 @@
       <c r="AO104" s="36"/>
       <c r="AP104" s="37"/>
       <c r="AQ104" s="37"/>
-      <c r="AR104" s="530" t="s">
+      <c r="AR104" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17464,7 +17470,7 @@
       <c r="AO105" s="50"/>
       <c r="AP105" s="51"/>
       <c r="AQ105" s="51"/>
-      <c r="AR105" s="531" t="s">
+      <c r="AR105" s="532" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17592,7 +17598,7 @@
       <c r="AQ106" s="33">
         <v>128</v>
       </c>
-      <c r="AR106" s="529" t="s">
+      <c r="AR106" s="530" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17680,7 +17686,7 @@
       <c r="AO107" s="52"/>
       <c r="AP107" s="52"/>
       <c r="AQ107" s="52"/>
-      <c r="AR107" s="532" t="s">
+      <c r="AR107" s="533" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17768,7 +17774,7 @@
       <c r="AO108" s="36"/>
       <c r="AP108" s="37"/>
       <c r="AQ108" s="37"/>
-      <c r="AR108" s="530" t="s">
+      <c r="AR108" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17856,7 +17862,7 @@
       <c r="AO109" s="65"/>
       <c r="AP109" s="66"/>
       <c r="AQ109" s="66"/>
-      <c r="AR109" s="533" t="s">
+      <c r="AR109" s="534" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17982,7 +17988,7 @@
       <c r="AQ110" s="33">
         <v>214</v>
       </c>
-      <c r="AR110" s="529" t="s">
+      <c r="AR110" s="530" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18070,7 +18076,7 @@
       <c r="AO111" s="36"/>
       <c r="AP111" s="37"/>
       <c r="AQ111" s="37"/>
-      <c r="AR111" s="530" t="s">
+      <c r="AR111" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18158,7 +18164,7 @@
       <c r="AO112" s="52"/>
       <c r="AP112" s="52"/>
       <c r="AQ112" s="52"/>
-      <c r="AR112" s="532" t="s">
+      <c r="AR112" s="533" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18246,7 +18252,7 @@
       <c r="AO113" s="36"/>
       <c r="AP113" s="37"/>
       <c r="AQ113" s="37"/>
-      <c r="AR113" s="530" t="s">
+      <c r="AR113" s="531" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18332,7 +18338,7 @@
       <c r="AO114" s="50"/>
       <c r="AP114" s="51"/>
       <c r="AQ114" s="51"/>
-      <c r="AR114" s="531" t="s">
+      <c r="AR114" s="532" t="s">
         <v>975</v>
       </c>
     </row>
@@ -18460,7 +18466,7 @@
       <c r="AQ115" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR115" s="534" t="s">
+      <c r="AR115" s="535" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18548,7 +18554,7 @@
       <c r="AO116" s="52"/>
       <c r="AP116" s="52"/>
       <c r="AQ116" s="52"/>
-      <c r="AR116" s="532" t="s">
+      <c r="AR116" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18636,7 +18642,7 @@
       <c r="AO117" s="36"/>
       <c r="AP117" s="37"/>
       <c r="AQ117" s="37"/>
-      <c r="AR117" s="530" t="s">
+      <c r="AR117" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18724,7 +18730,7 @@
       <c r="AO118" s="65"/>
       <c r="AP118" s="66"/>
       <c r="AQ118" s="66"/>
-      <c r="AR118" s="533" t="s">
+      <c r="AR118" s="534" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18848,7 +18854,7 @@
       <c r="AQ119" s="33">
         <v>244</v>
       </c>
-      <c r="AR119" s="529" t="s">
+      <c r="AR119" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -18936,7 +18942,7 @@
       <c r="AO120" s="52"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="52"/>
-      <c r="AR120" s="532" t="s">
+      <c r="AR120" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19024,7 +19030,7 @@
       <c r="AO121" s="36"/>
       <c r="AP121" s="37"/>
       <c r="AQ121" s="37"/>
-      <c r="AR121" s="530" t="s">
+      <c r="AR121" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19112,7 +19118,7 @@
       <c r="AO122" s="50"/>
       <c r="AP122" s="51"/>
       <c r="AQ122" s="51"/>
-      <c r="AR122" s="531" t="s">
+      <c r="AR122" s="532" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19238,7 +19244,7 @@
       <c r="AQ123" s="33">
         <v>244</v>
       </c>
-      <c r="AR123" s="529" t="s">
+      <c r="AR123" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19326,7 +19332,7 @@
       <c r="AO124" s="36"/>
       <c r="AP124" s="37"/>
       <c r="AQ124" s="37"/>
-      <c r="AR124" s="530" t="s">
+      <c r="AR124" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19414,7 +19420,7 @@
       <c r="AO125" s="52"/>
       <c r="AP125" s="52"/>
       <c r="AQ125" s="52"/>
-      <c r="AR125" s="532" t="s">
+      <c r="AR125" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19502,7 +19508,7 @@
       <c r="AO126" s="36"/>
       <c r="AP126" s="37"/>
       <c r="AQ126" s="37"/>
-      <c r="AR126" s="530" t="s">
+      <c r="AR126" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19590,7 +19596,7 @@
       <c r="AO127" s="65"/>
       <c r="AP127" s="66"/>
       <c r="AQ127" s="66"/>
-      <c r="AR127" s="533" t="s">
+      <c r="AR127" s="534" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19718,7 +19724,7 @@
       <c r="AQ128" s="33">
         <v>122</v>
       </c>
-      <c r="AR128" s="529" t="s">
+      <c r="AR128" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19810,7 +19816,7 @@
       <c r="AO129" s="52"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="52"/>
-      <c r="AR129" s="532" t="s">
+      <c r="AR129" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19902,7 +19908,7 @@
       <c r="AO130" s="36"/>
       <c r="AP130" s="37"/>
       <c r="AQ130" s="37"/>
-      <c r="AR130" s="530" t="s">
+      <c r="AR130" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -19986,7 +19992,7 @@
       <c r="AO131" s="50"/>
       <c r="AP131" s="51"/>
       <c r="AQ131" s="51"/>
-      <c r="AR131" s="531" t="s">
+      <c r="AR131" s="532" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20114,7 +20120,7 @@
       <c r="AQ132" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR132" s="534" t="s">
+      <c r="AR132" s="535" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20202,7 +20208,7 @@
       <c r="AO133" s="52"/>
       <c r="AP133" s="52"/>
       <c r="AQ133" s="52"/>
-      <c r="AR133" s="532" t="s">
+      <c r="AR133" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20290,7 +20296,7 @@
       <c r="AO134" s="36"/>
       <c r="AP134" s="37"/>
       <c r="AQ134" s="37"/>
-      <c r="AR134" s="530" t="s">
+      <c r="AR134" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20378,7 +20384,7 @@
       <c r="AO135" s="65"/>
       <c r="AP135" s="66"/>
       <c r="AQ135" s="66"/>
-      <c r="AR135" s="533" t="s">
+      <c r="AR135" s="534" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20504,7 +20510,7 @@
       <c r="AQ136" s="33">
         <v>272</v>
       </c>
-      <c r="AR136" s="529" t="s">
+      <c r="AR136" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20592,7 +20598,7 @@
       <c r="AO137" s="36"/>
       <c r="AP137" s="37"/>
       <c r="AQ137" s="37"/>
-      <c r="AR137" s="530" t="s">
+      <c r="AR137" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20680,7 +20686,7 @@
       <c r="AO138" s="52"/>
       <c r="AP138" s="52"/>
       <c r="AQ138" s="52"/>
-      <c r="AR138" s="532" t="s">
+      <c r="AR138" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20768,7 +20774,7 @@
       <c r="AO139" s="36"/>
       <c r="AP139" s="37"/>
       <c r="AQ139" s="37"/>
-      <c r="AR139" s="530" t="s">
+      <c r="AR139" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20854,7 +20860,7 @@
       <c r="AO140" s="50"/>
       <c r="AP140" s="51"/>
       <c r="AQ140" s="51"/>
-      <c r="AR140" s="531" t="s">
+      <c r="AR140" s="532" t="s">
         <v>976</v>
       </c>
     </row>
@@ -20980,7 +20986,7 @@
       <c r="AQ141" s="33">
         <v>193</v>
       </c>
-      <c r="AR141" s="529" t="s">
+      <c r="AR141" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21068,7 +21074,7 @@
       <c r="AO142" s="36"/>
       <c r="AP142" s="37"/>
       <c r="AQ142" s="37"/>
-      <c r="AR142" s="530" t="s">
+      <c r="AR142" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21156,7 +21162,7 @@
       <c r="AO143" s="52"/>
       <c r="AP143" s="52"/>
       <c r="AQ143" s="52"/>
-      <c r="AR143" s="532" t="s">
+      <c r="AR143" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21244,7 +21250,7 @@
       <c r="AO144" s="36"/>
       <c r="AP144" s="37"/>
       <c r="AQ144" s="37"/>
-      <c r="AR144" s="530" t="s">
+      <c r="AR144" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21332,7 +21338,7 @@
       <c r="AO145" s="65"/>
       <c r="AP145" s="66"/>
       <c r="AQ145" s="66"/>
-      <c r="AR145" s="533" t="s">
+      <c r="AR145" s="534" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21458,7 +21464,7 @@
       <c r="AQ146" s="33">
         <v>215</v>
       </c>
-      <c r="AR146" s="529" t="s">
+      <c r="AR146" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21546,7 +21552,7 @@
       <c r="AO147" s="52"/>
       <c r="AP147" s="52"/>
       <c r="AQ147" s="52"/>
-      <c r="AR147" s="532" t="s">
+      <c r="AR147" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21634,7 +21640,7 @@
       <c r="AO148" s="36"/>
       <c r="AP148" s="37"/>
       <c r="AQ148" s="37"/>
-      <c r="AR148" s="530" t="s">
+      <c r="AR148" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21722,7 +21728,7 @@
       <c r="AO149" s="50"/>
       <c r="AP149" s="51"/>
       <c r="AQ149" s="51"/>
-      <c r="AR149" s="531" t="s">
+      <c r="AR149" s="532" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21848,7 +21854,7 @@
       <c r="AQ150" s="33">
         <v>273</v>
       </c>
-      <c r="AR150" s="529" t="s">
+      <c r="AR150" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -21936,7 +21942,7 @@
       <c r="AO151" s="52"/>
       <c r="AP151" s="52"/>
       <c r="AQ151" s="52"/>
-      <c r="AR151" s="532" t="s">
+      <c r="AR151" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22024,7 +22030,7 @@
       <c r="AO152" s="36"/>
       <c r="AP152" s="37"/>
       <c r="AQ152" s="37"/>
-      <c r="AR152" s="530" t="s">
+      <c r="AR152" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22112,7 +22118,7 @@
       <c r="AO153" s="65"/>
       <c r="AP153" s="66"/>
       <c r="AQ153" s="66"/>
-      <c r="AR153" s="533" t="s">
+      <c r="AR153" s="534" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22236,7 +22242,7 @@
       <c r="AQ154" s="33">
         <v>162</v>
       </c>
-      <c r="AR154" s="529" t="s">
+      <c r="AR154" s="530" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22324,7 +22330,7 @@
       <c r="AO155" s="36"/>
       <c r="AP155" s="37"/>
       <c r="AQ155" s="37"/>
-      <c r="AR155" s="530" t="s">
+      <c r="AR155" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22412,7 +22418,7 @@
       <c r="AO156" s="52"/>
       <c r="AP156" s="52"/>
       <c r="AQ156" s="52"/>
-      <c r="AR156" s="532" t="s">
+      <c r="AR156" s="533" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22500,7 +22506,7 @@
       <c r="AO157" s="36"/>
       <c r="AP157" s="37"/>
       <c r="AQ157" s="37"/>
-      <c r="AR157" s="530" t="s">
+      <c r="AR157" s="531" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22586,7 +22592,7 @@
       <c r="AO158" s="50"/>
       <c r="AP158" s="51"/>
       <c r="AQ158" s="51"/>
-      <c r="AR158" s="531" t="s">
+      <c r="AR158" s="532" t="s">
         <v>976</v>
       </c>
     </row>
@@ -22714,7 +22720,7 @@
       <c r="AQ159" s="33">
         <v>199</v>
       </c>
-      <c r="AR159" s="529" t="s">
+      <c r="AR159" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22802,7 +22808,7 @@
       <c r="AO160" s="52"/>
       <c r="AP160" s="52"/>
       <c r="AQ160" s="52"/>
-      <c r="AR160" s="532" t="s">
+      <c r="AR160" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22890,7 +22896,7 @@
       <c r="AO161" s="36"/>
       <c r="AP161" s="37"/>
       <c r="AQ161" s="37"/>
-      <c r="AR161" s="530" t="s">
+      <c r="AR161" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -22978,7 +22984,7 @@
       <c r="AO162" s="65"/>
       <c r="AP162" s="66"/>
       <c r="AQ162" s="66"/>
-      <c r="AR162" s="533" t="s">
+      <c r="AR162" s="534" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23104,7 +23110,7 @@
       <c r="AQ163" s="33">
         <v>201</v>
       </c>
-      <c r="AR163" s="529" t="s">
+      <c r="AR163" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23192,7 +23198,7 @@
       <c r="AO164" s="52"/>
       <c r="AP164" s="52"/>
       <c r="AQ164" s="52"/>
-      <c r="AR164" s="532" t="s">
+      <c r="AR164" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23280,7 +23286,7 @@
       <c r="AO165" s="36"/>
       <c r="AP165" s="37"/>
       <c r="AQ165" s="37"/>
-      <c r="AR165" s="530" t="s">
+      <c r="AR165" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23368,7 +23374,7 @@
       <c r="AO166" s="65"/>
       <c r="AP166" s="66"/>
       <c r="AQ166" s="66"/>
-      <c r="AR166" s="533" t="s">
+      <c r="AR166" s="534" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23494,7 +23500,7 @@
       <c r="AQ167" s="33">
         <v>198</v>
       </c>
-      <c r="AR167" s="529" t="s">
+      <c r="AR167" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23582,7 +23588,7 @@
       <c r="AO168" s="52"/>
       <c r="AP168" s="52"/>
       <c r="AQ168" s="52"/>
-      <c r="AR168" s="532" t="s">
+      <c r="AR168" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23670,7 +23676,7 @@
       <c r="AO169" s="36"/>
       <c r="AP169" s="103"/>
       <c r="AQ169" s="103"/>
-      <c r="AR169" s="530" t="s">
+      <c r="AR169" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23758,7 +23764,7 @@
       <c r="AO170" s="50"/>
       <c r="AP170" s="51"/>
       <c r="AQ170" s="51"/>
-      <c r="AR170" s="531" t="s">
+      <c r="AR170" s="532" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23886,7 +23892,7 @@
       <c r="AQ171" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR171" s="534" t="s">
+      <c r="AR171" s="535" t="s">
         <v>977</v>
       </c>
     </row>
@@ -23974,7 +23980,7 @@
       <c r="AO172" s="36"/>
       <c r="AP172" s="37"/>
       <c r="AQ172" s="37"/>
-      <c r="AR172" s="530" t="s">
+      <c r="AR172" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24062,7 +24068,7 @@
       <c r="AO173" s="52"/>
       <c r="AP173" s="52"/>
       <c r="AQ173" s="52"/>
-      <c r="AR173" s="532" t="s">
+      <c r="AR173" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24152,7 +24158,7 @@
       <c r="AO174" s="65"/>
       <c r="AP174" s="66"/>
       <c r="AQ174" s="66"/>
-      <c r="AR174" s="533" t="s">
+      <c r="AR174" s="534" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24278,7 +24284,7 @@
       <c r="AQ175" s="33">
         <v>256</v>
       </c>
-      <c r="AR175" s="529" t="s">
+      <c r="AR175" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24372,7 +24378,7 @@
       <c r="AO176" s="36"/>
       <c r="AP176" s="37"/>
       <c r="AQ176" s="37"/>
-      <c r="AR176" s="530" t="s">
+      <c r="AR176" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24464,7 +24470,7 @@
       <c r="AO177" s="52"/>
       <c r="AP177" s="52"/>
       <c r="AQ177" s="52"/>
-      <c r="AR177" s="532" t="s">
+      <c r="AR177" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24554,7 +24560,7 @@
       <c r="AO178" s="65"/>
       <c r="AP178" s="66"/>
       <c r="AQ178" s="66"/>
-      <c r="AR178" s="533" t="s">
+      <c r="AR178" s="534" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24680,7 +24686,7 @@
       <c r="AQ179" s="118" t="s">
         <v>280</v>
       </c>
-      <c r="AR179" s="534" t="s">
+      <c r="AR179" s="535" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24768,7 +24774,7 @@
       <c r="AO180" s="36"/>
       <c r="AP180" s="37"/>
       <c r="AQ180" s="37"/>
-      <c r="AR180" s="530" t="s">
+      <c r="AR180" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24856,7 +24862,7 @@
       <c r="AO181" s="52"/>
       <c r="AP181" s="52"/>
       <c r="AQ181" s="52"/>
-      <c r="AR181" s="532" t="s">
+      <c r="AR181" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -24944,7 +24950,7 @@
       <c r="AO182" s="36"/>
       <c r="AP182" s="37"/>
       <c r="AQ182" s="37"/>
-      <c r="AR182" s="530" t="s">
+      <c r="AR182" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25032,7 +25038,7 @@
       <c r="AO183" s="50"/>
       <c r="AP183" s="51"/>
       <c r="AQ183" s="51"/>
-      <c r="AR183" s="531" t="s">
+      <c r="AR183" s="532" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25160,7 +25166,7 @@
       <c r="AQ184" s="33">
         <v>224</v>
       </c>
-      <c r="AR184" s="529" t="s">
+      <c r="AR184" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25250,7 +25256,7 @@
       <c r="AO185" s="36"/>
       <c r="AP185" s="37"/>
       <c r="AQ185" s="37"/>
-      <c r="AR185" s="530" t="s">
+      <c r="AR185" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25338,7 +25344,7 @@
       <c r="AO186" s="36"/>
       <c r="AP186" s="37"/>
       <c r="AQ186" s="37"/>
-      <c r="AR186" s="530" t="s">
+      <c r="AR186" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25428,7 +25434,7 @@
       <c r="AO187" s="119"/>
       <c r="AP187" s="119"/>
       <c r="AQ187" s="119"/>
-      <c r="AR187" s="535" t="s">
+      <c r="AR187" s="536" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25552,7 +25558,7 @@
       <c r="AQ188" s="33">
         <v>237</v>
       </c>
-      <c r="AR188" s="529" t="s">
+      <c r="AR188" s="530" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25640,7 +25646,7 @@
       <c r="AO189" s="52"/>
       <c r="AP189" s="52"/>
       <c r="AQ189" s="52"/>
-      <c r="AR189" s="532" t="s">
+      <c r="AR189" s="533" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25728,7 +25734,7 @@
       <c r="AO190" s="36"/>
       <c r="AP190" s="37"/>
       <c r="AQ190" s="37"/>
-      <c r="AR190" s="530" t="s">
+      <c r="AR190" s="531" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25814,7 +25820,7 @@
       <c r="AO191" s="50"/>
       <c r="AP191" s="51"/>
       <c r="AQ191" s="51"/>
-      <c r="AR191" s="531" t="s">
+      <c r="AR191" s="532" t="s">
         <v>977</v>
       </c>
     </row>
@@ -25940,7 +25946,7 @@
       <c r="AQ192" s="33">
         <v>117</v>
       </c>
-      <c r="AR192" s="529" t="s">
+      <c r="AR192" s="530" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26028,7 +26034,7 @@
       <c r="AO193" s="52"/>
       <c r="AP193" s="52"/>
       <c r="AQ193" s="52"/>
-      <c r="AR193" s="532" t="s">
+      <c r="AR193" s="533" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26116,7 +26122,7 @@
       <c r="AO194" s="36"/>
       <c r="AP194" s="37"/>
       <c r="AQ194" s="37"/>
-      <c r="AR194" s="530" t="s">
+      <c r="AR194" s="531" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26204,7 +26210,7 @@
       <c r="AO195" s="65"/>
       <c r="AP195" s="66"/>
       <c r="AQ195" s="66"/>
-      <c r="AR195" s="533" t="s">
+      <c r="AR195" s="534" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26328,7 +26334,7 @@
       <c r="AQ196" s="33">
         <v>131</v>
       </c>
-      <c r="AR196" s="529" t="s">
+      <c r="AR196" s="530" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26416,7 +26422,7 @@
       <c r="AO197" s="52"/>
       <c r="AP197" s="52"/>
       <c r="AQ197" s="52"/>
-      <c r="AR197" s="532" t="s">
+      <c r="AR197" s="533" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26504,7 +26510,7 @@
       <c r="AO198" s="36"/>
       <c r="AP198" s="37"/>
       <c r="AQ198" s="37"/>
-      <c r="AR198" s="530" t="s">
+      <c r="AR198" s="531" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26592,7 +26598,7 @@
       <c r="AO199" s="50"/>
       <c r="AP199" s="51"/>
       <c r="AQ199" s="51"/>
-      <c r="AR199" s="531" t="s">
+      <c r="AR199" s="532" t="s">
         <v>978</v>
       </c>
     </row>
@@ -26722,7 +26728,7 @@
       <c r="AQ200" s="33">
         <v>66</v>
       </c>
-      <c r="AR200" s="529" t="s">
+      <c r="AR200" s="530" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26814,7 +26820,7 @@
       <c r="AO201" s="36"/>
       <c r="AP201" s="37"/>
       <c r="AQ201" s="37"/>
-      <c r="AR201" s="530" t="s">
+      <c r="AR201" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -26904,7 +26910,7 @@
       <c r="AO202" s="119"/>
       <c r="AP202" s="119"/>
       <c r="AQ202" s="119"/>
-      <c r="AR202" s="535" t="s">
+      <c r="AR202" s="536" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27034,7 +27040,7 @@
       <c r="AQ203" s="33">
         <v>47</v>
       </c>
-      <c r="AR203" s="529" t="s">
+      <c r="AR203" s="530" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27126,7 +27132,7 @@
       <c r="AO204" s="36"/>
       <c r="AP204" s="37"/>
       <c r="AQ204" s="37"/>
-      <c r="AR204" s="530" t="s">
+      <c r="AR204" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27216,7 +27222,7 @@
       <c r="AO205" s="65"/>
       <c r="AP205" s="66"/>
       <c r="AQ205" s="66"/>
-      <c r="AR205" s="533" t="s">
+      <c r="AR205" s="534" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27346,7 +27352,7 @@
       <c r="AQ206" s="33">
         <v>42</v>
       </c>
-      <c r="AR206" s="529" t="s">
+      <c r="AR206" s="530" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27434,7 +27440,7 @@
       <c r="AO207" s="36"/>
       <c r="AP207" s="37"/>
       <c r="AQ207" s="37"/>
-      <c r="AR207" s="530" t="s">
+      <c r="AR207" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27526,7 +27532,7 @@
       <c r="AO208" s="50"/>
       <c r="AP208" s="51"/>
       <c r="AQ208" s="51"/>
-      <c r="AR208" s="531" t="s">
+      <c r="AR208" s="532" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27658,7 +27664,7 @@
       <c r="AQ209" s="33">
         <v>151</v>
       </c>
-      <c r="AR209" s="529" t="s">
+      <c r="AR209" s="530" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27750,7 +27756,7 @@
       <c r="AO210" s="52"/>
       <c r="AP210" s="52"/>
       <c r="AQ210" s="52"/>
-      <c r="AR210" s="532" t="s">
+      <c r="AR210" s="533" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27842,7 +27848,7 @@
       <c r="AO211" s="36"/>
       <c r="AP211" s="37"/>
       <c r="AQ211" s="37"/>
-      <c r="AR211" s="530" t="s">
+      <c r="AR211" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -27932,7 +27938,7 @@
       <c r="AO212" s="65"/>
       <c r="AP212" s="66"/>
       <c r="AQ212" s="66"/>
-      <c r="AR212" s="533" t="s">
+      <c r="AR212" s="534" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28062,7 +28068,7 @@
       <c r="AQ213" s="33">
         <v>130</v>
       </c>
-      <c r="AR213" s="529" t="s">
+      <c r="AR213" s="530" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28154,7 +28160,7 @@
       <c r="AO214" s="36"/>
       <c r="AP214" s="37"/>
       <c r="AQ214" s="37"/>
-      <c r="AR214" s="530" t="s">
+      <c r="AR214" s="531" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28246,7 +28252,7 @@
       <c r="AO215" s="50"/>
       <c r="AP215" s="51"/>
       <c r="AQ215" s="51"/>
-      <c r="AR215" s="531" t="s">
+      <c r="AR215" s="532" t="s">
         <v>979</v>
       </c>
     </row>
@@ -28378,7 +28384,7 @@
       <c r="AQ216" s="33">
         <v>81</v>
       </c>
-      <c r="AR216" s="529" t="s">
+      <c r="AR216" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28470,7 +28476,7 @@
       <c r="AO217" s="52"/>
       <c r="AP217" s="52"/>
       <c r="AQ217" s="52"/>
-      <c r="AR217" s="532" t="s">
+      <c r="AR217" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28562,7 +28568,7 @@
       <c r="AO218" s="36"/>
       <c r="AP218" s="37"/>
       <c r="AQ218" s="37"/>
-      <c r="AR218" s="530" t="s">
+      <c r="AR218" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28654,7 +28660,7 @@
       <c r="AO219" s="50"/>
       <c r="AP219" s="51"/>
       <c r="AQ219" s="51"/>
-      <c r="AR219" s="531" t="s">
+      <c r="AR219" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28782,7 +28788,7 @@
       <c r="AQ220" s="33">
         <v>119</v>
       </c>
-      <c r="AR220" s="529" t="s">
+      <c r="AR220" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28872,7 +28878,7 @@
       <c r="AO221" s="36"/>
       <c r="AP221" s="37"/>
       <c r="AQ221" s="37"/>
-      <c r="AR221" s="530" t="s">
+      <c r="AR221" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -28962,7 +28968,7 @@
       <c r="AO222" s="65"/>
       <c r="AP222" s="66"/>
       <c r="AQ222" s="66"/>
-      <c r="AR222" s="533" t="s">
+      <c r="AR222" s="534" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29092,7 +29098,7 @@
       <c r="AQ223" s="33">
         <v>151</v>
       </c>
-      <c r="AR223" s="529" t="s">
+      <c r="AR223" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29184,7 +29190,7 @@
       <c r="AO224" s="52"/>
       <c r="AP224" s="52"/>
       <c r="AQ224" s="52"/>
-      <c r="AR224" s="532" t="s">
+      <c r="AR224" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29276,7 +29282,7 @@
       <c r="AO225" s="36"/>
       <c r="AP225" s="37"/>
       <c r="AQ225" s="37"/>
-      <c r="AR225" s="530" t="s">
+      <c r="AR225" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29362,7 +29368,7 @@
       <c r="AO226" s="50"/>
       <c r="AP226" s="51"/>
       <c r="AQ226" s="51"/>
-      <c r="AR226" s="531" t="s">
+      <c r="AR226" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29490,7 +29496,7 @@
       <c r="AQ227" s="33">
         <v>139</v>
       </c>
-      <c r="AR227" s="529" t="s">
+      <c r="AR227" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29578,7 +29584,7 @@
       <c r="AO228" s="52"/>
       <c r="AP228" s="52"/>
       <c r="AQ228" s="52"/>
-      <c r="AR228" s="532" t="s">
+      <c r="AR228" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29666,7 +29672,7 @@
       <c r="AO229" s="36"/>
       <c r="AP229" s="37"/>
       <c r="AQ229" s="37"/>
-      <c r="AR229" s="530" t="s">
+      <c r="AR229" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29754,7 +29760,7 @@
       <c r="AO230" s="65"/>
       <c r="AP230" s="66"/>
       <c r="AQ230" s="66"/>
-      <c r="AR230" s="533" t="s">
+      <c r="AR230" s="534" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29880,7 +29886,7 @@
       <c r="AQ231" s="33">
         <v>134</v>
       </c>
-      <c r="AR231" s="529" t="s">
+      <c r="AR231" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -29968,7 +29974,7 @@
       <c r="AO232" s="52"/>
       <c r="AP232" s="52"/>
       <c r="AQ232" s="52"/>
-      <c r="AR232" s="532" t="s">
+      <c r="AR232" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30056,7 +30062,7 @@
       <c r="AO233" s="36"/>
       <c r="AP233" s="37"/>
       <c r="AQ233" s="37"/>
-      <c r="AR233" s="530" t="s">
+      <c r="AR233" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30140,7 +30146,7 @@
       <c r="AO234" s="50"/>
       <c r="AP234" s="51"/>
       <c r="AQ234" s="51"/>
-      <c r="AR234" s="531" t="s">
+      <c r="AR234" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -30268,7 +30274,7 @@
       <c r="AQ235" s="33">
         <v>146</v>
       </c>
-      <c r="AR235" s="529" t="s">
+      <c r="AR235" s="530" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30356,7 +30362,7 @@
       <c r="AO236" s="52"/>
       <c r="AP236" s="52"/>
       <c r="AQ236" s="52"/>
-      <c r="AR236" s="532" t="s">
+      <c r="AR236" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30444,7 +30450,7 @@
       <c r="AO237" s="36"/>
       <c r="AP237" s="37"/>
       <c r="AQ237" s="37"/>
-      <c r="AR237" s="530" t="s">
+      <c r="AR237" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30530,7 +30536,7 @@
       <c r="AO238" s="50"/>
       <c r="AP238" s="51"/>
       <c r="AQ238" s="51"/>
-      <c r="AR238" s="531" t="s">
+      <c r="AR238" s="532" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30658,7 +30664,7 @@
       <c r="AQ239" s="33">
         <v>193</v>
       </c>
-      <c r="AR239" s="529" t="s">
+      <c r="AR239" s="530" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30746,7 +30752,7 @@
       <c r="AO240" s="52"/>
       <c r="AP240" s="52"/>
       <c r="AQ240" s="52"/>
-      <c r="AR240" s="532" t="s">
+      <c r="AR240" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30834,7 +30840,7 @@
       <c r="AO241" s="36"/>
       <c r="AP241" s="37"/>
       <c r="AQ241" s="37"/>
-      <c r="AR241" s="530" t="s">
+      <c r="AR241" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -30920,7 +30926,7 @@
       <c r="AO242" s="65"/>
       <c r="AP242" s="66"/>
       <c r="AQ242" s="66"/>
-      <c r="AR242" s="533" t="s">
+      <c r="AR242" s="534" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31046,7 +31052,7 @@
       <c r="AQ243" s="33">
         <v>74</v>
       </c>
-      <c r="AR243" s="529" t="s">
+      <c r="AR243" s="530" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31134,7 +31140,7 @@
       <c r="AO244" s="36"/>
       <c r="AP244" s="37"/>
       <c r="AQ244" s="37"/>
-      <c r="AR244" s="530" t="s">
+      <c r="AR244" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31222,7 +31228,7 @@
       <c r="AO245" s="52"/>
       <c r="AP245" s="52"/>
       <c r="AQ245" s="52"/>
-      <c r="AR245" s="532" t="s">
+      <c r="AR245" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31310,7 +31316,7 @@
       <c r="AO246" s="65"/>
       <c r="AP246" s="66"/>
       <c r="AQ246" s="66"/>
-      <c r="AR246" s="533" t="s">
+      <c r="AR246" s="534" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31404,7 +31410,7 @@
       <c r="AQ247" s="33">
         <v>191</v>
       </c>
-      <c r="AR247" s="529" t="s">
+      <c r="AR247" s="530" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31524,7 +31530,7 @@
       <c r="AO248" s="52"/>
       <c r="AP248" s="52"/>
       <c r="AQ248" s="52"/>
-      <c r="AR248" s="532" t="s">
+      <c r="AR248" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31614,7 +31620,7 @@
       <c r="AO249" s="52"/>
       <c r="AP249" s="52"/>
       <c r="AQ249" s="52"/>
-      <c r="AR249" s="532" t="s">
+      <c r="AR249" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31704,7 +31710,7 @@
       <c r="AO250" s="36"/>
       <c r="AP250" s="37"/>
       <c r="AQ250" s="37"/>
-      <c r="AR250" s="530" t="s">
+      <c r="AR250" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31794,7 +31800,7 @@
       <c r="AO251" s="65"/>
       <c r="AP251" s="66"/>
       <c r="AQ251" s="66"/>
-      <c r="AR251" s="533" t="s">
+      <c r="AR251" s="534" t="s">
         <v>981</v>
       </c>
     </row>
@@ -31920,7 +31926,7 @@
       <c r="AQ252" s="33">
         <v>160</v>
       </c>
-      <c r="AR252" s="529" t="s">
+      <c r="AR252" s="530" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32008,7 +32014,7 @@
       <c r="AO253" s="36"/>
       <c r="AP253" s="37"/>
       <c r="AQ253" s="37"/>
-      <c r="AR253" s="530" t="s">
+      <c r="AR253" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32096,7 +32102,7 @@
       <c r="AO254" s="52"/>
       <c r="AP254" s="52"/>
       <c r="AQ254" s="52"/>
-      <c r="AR254" s="532" t="s">
+      <c r="AR254" s="533" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32184,7 +32190,7 @@
       <c r="AO255" s="36"/>
       <c r="AP255" s="37"/>
       <c r="AQ255" s="37"/>
-      <c r="AR255" s="530" t="s">
+      <c r="AR255" s="531" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32272,7 +32278,7 @@
       <c r="AO256" s="50"/>
       <c r="AP256" s="51"/>
       <c r="AQ256" s="51"/>
-      <c r="AR256" s="531" t="s">
+      <c r="AR256" s="532" t="s">
         <v>981</v>
       </c>
     </row>
@@ -32400,7 +32406,7 @@
       <c r="AQ257" s="33">
         <v>210</v>
       </c>
-      <c r="AR257" s="529" t="s">
+      <c r="AR257" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32490,7 +32496,7 @@
       <c r="AO258" s="52"/>
       <c r="AP258" s="52"/>
       <c r="AQ258" s="52"/>
-      <c r="AR258" s="532" t="s">
+      <c r="AR258" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32580,7 +32586,7 @@
       <c r="AO259" s="36"/>
       <c r="AP259" s="37"/>
       <c r="AQ259" s="37"/>
-      <c r="AR259" s="530" t="s">
+      <c r="AR259" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32668,7 +32674,7 @@
       <c r="AO260" s="65"/>
       <c r="AP260" s="66"/>
       <c r="AQ260" s="66"/>
-      <c r="AR260" s="533" t="s">
+      <c r="AR260" s="534" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32794,7 +32800,7 @@
       <c r="AQ261" s="33">
         <v>101</v>
       </c>
-      <c r="AR261" s="529" t="s">
+      <c r="AR261" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32880,7 +32886,7 @@
       <c r="AO262" s="36"/>
       <c r="AP262" s="37"/>
       <c r="AQ262" s="37"/>
-      <c r="AR262" s="530" t="s">
+      <c r="AR262" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -32966,7 +32972,7 @@
       <c r="AO263" s="50"/>
       <c r="AP263" s="51"/>
       <c r="AQ263" s="51"/>
-      <c r="AR263" s="531" t="s">
+      <c r="AR263" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33096,7 +33102,7 @@
       <c r="AQ264" s="33">
         <v>231</v>
       </c>
-      <c r="AR264" s="529" t="s">
+      <c r="AR264" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33186,7 +33192,7 @@
       <c r="AO265" s="52"/>
       <c r="AP265" s="52"/>
       <c r="AQ265" s="52"/>
-      <c r="AR265" s="532" t="s">
+      <c r="AR265" s="533" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33276,7 +33282,7 @@
       <c r="AO266" s="36"/>
       <c r="AP266" s="37"/>
       <c r="AQ266" s="37"/>
-      <c r="AR266" s="530" t="s">
+      <c r="AR266" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33366,7 +33372,7 @@
       <c r="AO267" s="50"/>
       <c r="AP267" s="51"/>
       <c r="AQ267" s="51"/>
-      <c r="AR267" s="531" t="s">
+      <c r="AR267" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33498,7 +33504,7 @@
       <c r="AQ268" s="33">
         <v>76</v>
       </c>
-      <c r="AR268" s="529" t="s">
+      <c r="AR268" s="530" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33590,7 +33596,7 @@
       <c r="AO269" s="36"/>
       <c r="AP269" s="37"/>
       <c r="AQ269" s="37"/>
-      <c r="AR269" s="530" t="s">
+      <c r="AR269" s="531" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33682,7 +33688,7 @@
       <c r="AO270" s="50"/>
       <c r="AP270" s="51"/>
       <c r="AQ270" s="51"/>
-      <c r="AR270" s="531" t="s">
+      <c r="AR270" s="532" t="s">
         <v>980</v>
       </c>
     </row>
@@ -33814,7 +33820,7 @@
       <c r="AQ271" s="33">
         <v>46</v>
       </c>
-      <c r="AR271" s="529" t="s">
+      <c r="AR271" s="530" t="s">
         <v>982</v>
       </c>
     </row>
@@ -33904,7 +33910,7 @@
       <c r="AO272" s="36"/>
       <c r="AP272" s="37"/>
       <c r="AQ272" s="37"/>
-      <c r="AR272" s="530" t="s">
+      <c r="AR272" s="531" t="s">
         <v>982</v>
       </c>
     </row>
@@ -33994,7 +34000,7 @@
       <c r="AO273" s="65"/>
       <c r="AP273" s="66"/>
       <c r="AQ273" s="66"/>
-      <c r="AR273" s="533" t="s">
+      <c r="AR273" s="534" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34116,7 +34122,7 @@
       <c r="AO274" s="36"/>
       <c r="AP274" s="37"/>
       <c r="AQ274" s="37"/>
-      <c r="AR274" s="530" t="s">
+      <c r="AR274" s="531" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34212,7 +34218,7 @@
       <c r="AQ275" s="33">
         <v>126</v>
       </c>
-      <c r="AR275" s="529" t="s">
+      <c r="AR275" s="530" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34302,7 +34308,7 @@
       <c r="AO276" s="36"/>
       <c r="AP276" s="37"/>
       <c r="AQ276" s="37"/>
-      <c r="AR276" s="530" t="s">
+      <c r="AR276" s="531" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34392,7 +34398,7 @@
       <c r="AO277" s="50"/>
       <c r="AP277" s="51"/>
       <c r="AQ277" s="51"/>
-      <c r="AR277" s="531" t="s">
+      <c r="AR277" s="532" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34520,7 +34526,7 @@
       <c r="AQ278" s="33">
         <v>72</v>
       </c>
-      <c r="AR278" s="529" t="s">
+      <c r="AR278" s="530" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34608,7 +34614,7 @@
       <c r="AO279" s="52"/>
       <c r="AP279" s="52"/>
       <c r="AQ279" s="52"/>
-      <c r="AR279" s="532" t="s">
+      <c r="AR279" s="533" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34696,7 +34702,7 @@
       <c r="AO280" s="204"/>
       <c r="AP280" s="204"/>
       <c r="AQ280" s="204"/>
-      <c r="AR280" s="532" t="s">
+      <c r="AR280" s="533" t="s">
         <v>982</v>
       </c>
     </row>
@@ -34784,7 +34790,7 @@
       <c r="AO281" s="205"/>
       <c r="AP281" s="205"/>
       <c r="AQ281" s="205"/>
-      <c r="AR281" s="536" t="s">
+      <c r="AR281" s="537" t="s">
         <v>983</v>
       </c>
     </row>
